--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,81 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>2026-09-23 00:02:48</t>
   </si>
 </sst>
 </file>
@@ -585,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +903,2184 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2">
+        <v>1.87</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4.3</v>
+      </c>
+      <c r="I2">
+        <v>4.8</v>
+      </c>
+      <c r="J2">
+        <v>3.6</v>
+      </c>
+      <c r="K2">
+        <v>4.1</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.9</v>
+      </c>
+      <c r="O2">
+        <v>1.3</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>1.84</v>
+      </c>
+      <c r="R2">
+        <v>1.39</v>
+      </c>
+      <c r="S2">
+        <v>3.2</v>
+      </c>
+      <c r="T2">
+        <v>1.75</v>
+      </c>
+      <c r="U2">
+        <v>2.1</v>
+      </c>
+      <c r="V2">
+        <v>1.26</v>
+      </c>
+      <c r="W2">
+        <v>1.99</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
+        <v>17.5</v>
+      </c>
+      <c r="Z2">
+        <v>36</v>
+      </c>
+      <c r="AA2">
+        <v>110</v>
+      </c>
+      <c r="AB2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>12.5</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>25</v>
+      </c>
+      <c r="AK2">
+        <v>23</v>
+      </c>
+      <c r="AL2">
+        <v>36</v>
+      </c>
+      <c r="AM2">
+        <v>110</v>
+      </c>
+      <c r="AN2">
+        <v>13.5</v>
+      </c>
+      <c r="AO2">
+        <v>65</v>
+      </c>
+      <c r="AP2">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2">
+        <v>14.5</v>
+      </c>
+      <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>7.8</v>
+      </c>
+      <c r="AT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>7.6</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
+        <v>8</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>8</v>
+      </c>
+      <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
+        <v>17</v>
+      </c>
+      <c r="BD2">
+        <v>7.2</v>
+      </c>
+      <c r="BE2">
+        <v>7.8</v>
+      </c>
+      <c r="BF2">
+        <v>10.5</v>
+      </c>
+      <c r="BG2">
+        <v>8</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3">
+        <v>1.77</v>
+      </c>
+      <c r="G3">
+        <v>1.8</v>
+      </c>
+      <c r="H3">
+        <v>5.2</v>
+      </c>
+      <c r="I3">
+        <v>5.6</v>
+      </c>
+      <c r="J3">
+        <v>3.9</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.94</v>
+      </c>
+      <c r="Q3">
+        <v>1.96</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>1.91</v>
+      </c>
+      <c r="U3">
+        <v>1.98</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>15</v>
+      </c>
+      <c r="Y3">
+        <v>17.5</v>
+      </c>
+      <c r="Z3">
+        <v>44</v>
+      </c>
+      <c r="AA3">
+        <v>160</v>
+      </c>
+      <c r="AB3">
+        <v>8.6</v>
+      </c>
+      <c r="AC3">
+        <v>9</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>85</v>
+      </c>
+      <c r="AF3">
+        <v>11</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
+        <v>22</v>
+      </c>
+      <c r="AI3">
+        <v>85</v>
+      </c>
+      <c r="AJ3">
+        <v>18.5</v>
+      </c>
+      <c r="AK3">
+        <v>20</v>
+      </c>
+      <c r="AL3">
+        <v>40</v>
+      </c>
+      <c r="AM3">
+        <v>140</v>
+      </c>
+      <c r="AN3">
+        <v>12</v>
+      </c>
+      <c r="AO3">
+        <v>110</v>
+      </c>
+      <c r="AP3">
+        <v>12.5</v>
+      </c>
+      <c r="AQ3">
+        <v>14.5</v>
+      </c>
+      <c r="AR3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS3">
+        <v>10</v>
+      </c>
+      <c r="AT3">
+        <v>7.4</v>
+      </c>
+      <c r="AU3">
+        <v>7.8</v>
+      </c>
+      <c r="AV3">
+        <v>17</v>
+      </c>
+      <c r="AW3">
+        <v>9.6</v>
+      </c>
+      <c r="AX3">
+        <v>9.4</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
+        <v>9.6</v>
+      </c>
+      <c r="BB3">
+        <v>16</v>
+      </c>
+      <c r="BC3">
+        <v>17</v>
+      </c>
+      <c r="BD3">
+        <v>8.6</v>
+      </c>
+      <c r="BE3">
+        <v>10</v>
+      </c>
+      <c r="BF3">
+        <v>10</v>
+      </c>
+      <c r="BG3">
+        <v>10</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4">
+        <v>1.9</v>
+      </c>
+      <c r="G4">
+        <v>1.91</v>
+      </c>
+      <c r="H4">
+        <v>4.6</v>
+      </c>
+      <c r="I4">
+        <v>4.7</v>
+      </c>
+      <c r="J4">
+        <v>3.8</v>
+      </c>
+      <c r="K4">
+        <v>3.9</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.5</v>
+      </c>
+      <c r="O4">
+        <v>1.36</v>
+      </c>
+      <c r="P4">
+        <v>1.87</v>
+      </c>
+      <c r="Q4">
+        <v>2.04</v>
+      </c>
+      <c r="R4">
+        <v>1.34</v>
+      </c>
+      <c r="S4">
+        <v>3.7</v>
+      </c>
+      <c r="T4">
+        <v>1.9</v>
+      </c>
+      <c r="U4">
+        <v>1.96</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>13.5</v>
+      </c>
+      <c r="Y4">
+        <v>15.5</v>
+      </c>
+      <c r="Z4">
+        <v>46</v>
+      </c>
+      <c r="AA4">
+        <v>150</v>
+      </c>
+      <c r="AB4">
+        <v>8.4</v>
+      </c>
+      <c r="AC4">
+        <v>8.6</v>
+      </c>
+      <c r="AD4">
+        <v>23</v>
+      </c>
+      <c r="AE4">
+        <v>80</v>
+      </c>
+      <c r="AF4">
+        <v>11.5</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>90</v>
+      </c>
+      <c r="AJ4">
+        <v>25</v>
+      </c>
+      <c r="AK4">
+        <v>23</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>14</v>
+      </c>
+      <c r="AO4">
+        <v>110</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>13.5</v>
+      </c>
+      <c r="AR4">
+        <v>30</v>
+      </c>
+      <c r="AS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>7.4</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>16.5</v>
+      </c>
+      <c r="AW4">
+        <v>7.6</v>
+      </c>
+      <c r="AX4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>17.5</v>
+      </c>
+      <c r="BA4">
+        <v>7.8</v>
+      </c>
+      <c r="BB4">
+        <v>18</v>
+      </c>
+      <c r="BC4">
+        <v>18</v>
+      </c>
+      <c r="BD4">
+        <v>32</v>
+      </c>
+      <c r="BE4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF4">
+        <v>12.5</v>
+      </c>
+      <c r="BG4">
+        <v>8</v>
+      </c>
+      <c r="BH4">
+        <v>3.3</v>
+      </c>
+      <c r="BI4">
+        <v>2.98</v>
+      </c>
+      <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>9</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>4.5</v>
+      </c>
+      <c r="BO4">
+        <v>4</v>
+      </c>
+      <c r="BP4">
+        <v>13.5</v>
+      </c>
+      <c r="BQ4">
+        <v>11.5</v>
+      </c>
+      <c r="BR4">
+        <v>30</v>
+      </c>
+      <c r="BS4">
+        <v>21</v>
+      </c>
+      <c r="BT4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU4">
+        <v>7</v>
+      </c>
+      <c r="BV4">
+        <v>44</v>
+      </c>
+      <c r="BW4">
+        <v>30</v>
+      </c>
+      <c r="BX4">
+        <v>55</v>
+      </c>
+      <c r="BY4">
+        <v>38</v>
+      </c>
+      <c r="BZ4">
+        <v>27</v>
+      </c>
+      <c r="CA4">
+        <v>19</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>1.55</v>
+      </c>
+      <c r="G5">
+        <v>1.57</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4.6</v>
+      </c>
+      <c r="K5">
+        <v>4.9</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>1.22</v>
+      </c>
+      <c r="P5">
+        <v>2.36</v>
+      </c>
+      <c r="Q5">
+        <v>1.57</v>
+      </c>
+      <c r="R5">
+        <v>1.55</v>
+      </c>
+      <c r="S5">
+        <v>2.62</v>
+      </c>
+      <c r="T5">
+        <v>1.8</v>
+      </c>
+      <c r="U5">
+        <v>2.12</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>23</v>
+      </c>
+      <c r="Y5">
+        <v>29</v>
+      </c>
+      <c r="Z5">
+        <v>70</v>
+      </c>
+      <c r="AA5">
+        <v>210</v>
+      </c>
+      <c r="AB5">
+        <v>10.5</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>26</v>
+      </c>
+      <c r="AE5">
+        <v>100</v>
+      </c>
+      <c r="AF5">
+        <v>10.5</v>
+      </c>
+      <c r="AG5">
+        <v>10.5</v>
+      </c>
+      <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>90</v>
+      </c>
+      <c r="AJ5">
+        <v>15</v>
+      </c>
+      <c r="AK5">
+        <v>15.5</v>
+      </c>
+      <c r="AL5">
+        <v>32</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>6.6</v>
+      </c>
+      <c r="AO5">
+        <v>110</v>
+      </c>
+      <c r="AP5">
+        <v>19.5</v>
+      </c>
+      <c r="AQ5">
+        <v>19.5</v>
+      </c>
+      <c r="AR5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5">
+        <v>10</v>
+      </c>
+      <c r="AT5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV5">
+        <v>19</v>
+      </c>
+      <c r="AW5">
+        <v>9.6</v>
+      </c>
+      <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ5">
+        <v>18.5</v>
+      </c>
+      <c r="BA5">
+        <v>9.4</v>
+      </c>
+      <c r="BB5">
+        <v>13</v>
+      </c>
+      <c r="BC5">
+        <v>13.5</v>
+      </c>
+      <c r="BD5">
+        <v>7.8</v>
+      </c>
+      <c r="BE5">
+        <v>9.6</v>
+      </c>
+      <c r="BF5">
+        <v>6</v>
+      </c>
+      <c r="BG5">
+        <v>9.6</v>
+      </c>
+      <c r="BH5">
+        <v>4.1</v>
+      </c>
+      <c r="BI5">
+        <v>3.75</v>
+      </c>
+      <c r="BJ5">
+        <v>11.5</v>
+      </c>
+      <c r="BK5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL5">
+        <v>130</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>4.3</v>
+      </c>
+      <c r="BO5">
+        <v>3.9</v>
+      </c>
+      <c r="BP5">
+        <v>11</v>
+      </c>
+      <c r="BQ5">
+        <v>8.4</v>
+      </c>
+      <c r="BR5">
+        <v>26</v>
+      </c>
+      <c r="BS5">
+        <v>16.5</v>
+      </c>
+      <c r="BT5">
+        <v>12</v>
+      </c>
+      <c r="BU5">
+        <v>9</v>
+      </c>
+      <c r="BV5">
+        <v>60</v>
+      </c>
+      <c r="BW5">
+        <v>38</v>
+      </c>
+      <c r="BX5">
+        <v>60</v>
+      </c>
+      <c r="BY5">
+        <v>38</v>
+      </c>
+      <c r="BZ5">
+        <v>16.5</v>
+      </c>
+      <c r="CA5">
+        <v>11</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>1.72</v>
+      </c>
+      <c r="G6">
+        <v>1.76</v>
+      </c>
+      <c r="H6">
+        <v>5.4</v>
+      </c>
+      <c r="I6">
+        <v>5.9</v>
+      </c>
+      <c r="J6">
+        <v>3.9</v>
+      </c>
+      <c r="K6">
+        <v>4.1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.65</v>
+      </c>
+      <c r="O6">
+        <v>1.34</v>
+      </c>
+      <c r="P6">
+        <v>1.88</v>
+      </c>
+      <c r="Q6">
+        <v>2.06</v>
+      </c>
+      <c r="R6">
+        <v>1.34</v>
+      </c>
+      <c r="S6">
+        <v>3.75</v>
+      </c>
+      <c r="T6">
+        <v>1.95</v>
+      </c>
+      <c r="U6">
+        <v>1.94</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>15.5</v>
+      </c>
+      <c r="Y6">
+        <v>18</v>
+      </c>
+      <c r="Z6">
+        <v>50</v>
+      </c>
+      <c r="AA6">
+        <v>180</v>
+      </c>
+      <c r="AB6">
+        <v>8</v>
+      </c>
+      <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>23</v>
+      </c>
+      <c r="AE6">
+        <v>100</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+      <c r="AH6">
+        <v>24</v>
+      </c>
+      <c r="AI6">
+        <v>95</v>
+      </c>
+      <c r="AJ6">
+        <v>20</v>
+      </c>
+      <c r="AK6">
+        <v>21</v>
+      </c>
+      <c r="AL6">
+        <v>50</v>
+      </c>
+      <c r="AM6">
+        <v>150</v>
+      </c>
+      <c r="AN6">
+        <v>12</v>
+      </c>
+      <c r="AO6">
+        <v>130</v>
+      </c>
+      <c r="AP6">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS6">
+        <v>10.5</v>
+      </c>
+      <c r="AT6">
+        <v>7</v>
+      </c>
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>19</v>
+      </c>
+      <c r="AW6">
+        <v>10</v>
+      </c>
+      <c r="AX6">
+        <v>8.6</v>
+      </c>
+      <c r="AY6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>18.5</v>
+      </c>
+      <c r="BA6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB6">
+        <v>16.5</v>
+      </c>
+      <c r="BC6">
+        <v>16.5</v>
+      </c>
+      <c r="BD6">
+        <v>8.6</v>
+      </c>
+      <c r="BE6">
+        <v>10</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
+      <c r="BG6">
+        <v>10</v>
+      </c>
+      <c r="BH6">
+        <v>3.35</v>
+      </c>
+      <c r="BI6">
+        <v>3.15</v>
+      </c>
+      <c r="BJ6">
+        <v>11</v>
+      </c>
+      <c r="BK6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>4.3</v>
+      </c>
+      <c r="BO6">
+        <v>3.85</v>
+      </c>
+      <c r="BP6">
+        <v>12</v>
+      </c>
+      <c r="BQ6">
+        <v>10</v>
+      </c>
+      <c r="BR6">
+        <v>29</v>
+      </c>
+      <c r="BS6">
+        <v>21</v>
+      </c>
+      <c r="BT6">
+        <v>9</v>
+      </c>
+      <c r="BU6">
+        <v>7.8</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>36</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>42</v>
+      </c>
+      <c r="BZ6">
+        <v>24</v>
+      </c>
+      <c r="CA6">
+        <v>17.5</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>2.32</v>
+      </c>
+      <c r="G7">
+        <v>2.48</v>
+      </c>
+      <c r="H7">
+        <v>3.25</v>
+      </c>
+      <c r="I7">
+        <v>3.55</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
+        <v>3.5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
+        <v>3.35</v>
+      </c>
+      <c r="O7">
+        <v>1.36</v>
+      </c>
+      <c r="P7">
+        <v>1.83</v>
+      </c>
+      <c r="Q7">
+        <v>2.06</v>
+      </c>
+      <c r="R7">
+        <v>1.32</v>
+      </c>
+      <c r="S7">
+        <v>3.75</v>
+      </c>
+      <c r="T7">
+        <v>1.82</v>
+      </c>
+      <c r="U7">
+        <v>2.06</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>13</v>
+      </c>
+      <c r="Y7">
+        <v>12.5</v>
+      </c>
+      <c r="Z7">
+        <v>29</v>
+      </c>
+      <c r="AA7">
+        <v>80</v>
+      </c>
+      <c r="AB7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>15</v>
+      </c>
+      <c r="AE7">
+        <v>55</v>
+      </c>
+      <c r="AF7">
+        <v>18.5</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>22</v>
+      </c>
+      <c r="AI7">
+        <v>65</v>
+      </c>
+      <c r="AJ7">
+        <v>36</v>
+      </c>
+      <c r="AK7">
+        <v>29</v>
+      </c>
+      <c r="AL7">
+        <v>55</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>22</v>
+      </c>
+      <c r="AO7">
+        <v>55</v>
+      </c>
+      <c r="AP7">
+        <v>11</v>
+      </c>
+      <c r="AQ7">
+        <v>10.5</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>7.6</v>
+      </c>
+      <c r="AT7">
+        <v>8.6</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>12.5</v>
+      </c>
+      <c r="AW7">
+        <v>7.4</v>
+      </c>
+      <c r="AX7">
+        <v>13</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>7.4</v>
+      </c>
+      <c r="BB7">
+        <v>6.8</v>
+      </c>
+      <c r="BC7">
+        <v>6.6</v>
+      </c>
+      <c r="BD7">
+        <v>7.4</v>
+      </c>
+      <c r="BE7">
+        <v>7.4</v>
+      </c>
+      <c r="BF7">
+        <v>18.5</v>
+      </c>
+      <c r="BG7">
+        <v>7.2</v>
+      </c>
+      <c r="BH7">
+        <v>3.25</v>
+      </c>
+      <c r="BI7">
+        <v>2.9</v>
+      </c>
+      <c r="BJ7">
+        <v>12</v>
+      </c>
+      <c r="BK7">
+        <v>8.4</v>
+      </c>
+      <c r="BL7">
+        <v>160</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>6.2</v>
+      </c>
+      <c r="BO7">
+        <v>4.6</v>
+      </c>
+      <c r="BP7">
+        <v>23</v>
+      </c>
+      <c r="BQ7">
+        <v>16</v>
+      </c>
+      <c r="BR7">
+        <v>42</v>
+      </c>
+      <c r="BS7">
+        <v>24</v>
+      </c>
+      <c r="BT7">
+        <v>7.8</v>
+      </c>
+      <c r="BU7">
+        <v>5.7</v>
+      </c>
+      <c r="BV7">
+        <v>34</v>
+      </c>
+      <c r="BW7">
+        <v>20</v>
+      </c>
+      <c r="BX7">
+        <v>50</v>
+      </c>
+      <c r="BY7">
+        <v>29</v>
+      </c>
+      <c r="BZ7">
+        <v>38</v>
+      </c>
+      <c r="CA7">
+        <v>22</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8">
+        <v>2.26</v>
+      </c>
+      <c r="G8">
+        <v>2.3</v>
+      </c>
+      <c r="H8">
+        <v>3.4</v>
+      </c>
+      <c r="I8">
+        <v>3.5</v>
+      </c>
+      <c r="J8">
+        <v>3.65</v>
+      </c>
+      <c r="K8">
+        <v>3.75</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>4.3</v>
+      </c>
+      <c r="O8">
+        <v>1.28</v>
+      </c>
+      <c r="P8">
+        <v>2.08</v>
+      </c>
+      <c r="Q8">
+        <v>1.85</v>
+      </c>
+      <c r="R8">
+        <v>1.42</v>
+      </c>
+      <c r="S8">
+        <v>3.15</v>
+      </c>
+      <c r="T8">
+        <v>1.71</v>
+      </c>
+      <c r="U8">
+        <v>2.3</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>17.5</v>
+      </c>
+      <c r="Y8">
+        <v>14.5</v>
+      </c>
+      <c r="Z8">
+        <v>26</v>
+      </c>
+      <c r="AA8">
+        <v>75</v>
+      </c>
+      <c r="AB8">
+        <v>11.5</v>
+      </c>
+      <c r="AC8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD8">
+        <v>14.5</v>
+      </c>
+      <c r="AE8">
+        <v>44</v>
+      </c>
+      <c r="AF8">
+        <v>15.5</v>
+      </c>
+      <c r="AG8">
+        <v>11.5</v>
+      </c>
+      <c r="AH8">
+        <v>19.5</v>
+      </c>
+      <c r="AI8">
+        <v>55</v>
+      </c>
+      <c r="AJ8">
+        <v>36</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>42</v>
+      </c>
+      <c r="AM8">
+        <v>95</v>
+      </c>
+      <c r="AN8">
+        <v>16</v>
+      </c>
+      <c r="AO8">
+        <v>38</v>
+      </c>
+      <c r="AP8">
+        <v>15</v>
+      </c>
+      <c r="AQ8">
+        <v>12.5</v>
+      </c>
+      <c r="AR8">
+        <v>18.5</v>
+      </c>
+      <c r="AS8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8">
+        <v>10</v>
+      </c>
+      <c r="AU8">
+        <v>7.4</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>8</v>
+      </c>
+      <c r="AX8">
+        <v>13.5</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>15</v>
+      </c>
+      <c r="BA8">
+        <v>30</v>
+      </c>
+      <c r="BB8">
+        <v>23</v>
+      </c>
+      <c r="BC8">
+        <v>20</v>
+      </c>
+      <c r="BD8">
+        <v>8</v>
+      </c>
+      <c r="BE8">
+        <v>9</v>
+      </c>
+      <c r="BF8">
+        <v>13.5</v>
+      </c>
+      <c r="BG8">
+        <v>8.4</v>
+      </c>
+      <c r="BH8">
+        <v>3.65</v>
+      </c>
+      <c r="BI8">
+        <v>3.35</v>
+      </c>
+      <c r="BJ8">
+        <v>11</v>
+      </c>
+      <c r="BK8">
+        <v>8</v>
+      </c>
+      <c r="BL8">
+        <v>130</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>6.2</v>
+      </c>
+      <c r="BO8">
+        <v>4.7</v>
+      </c>
+      <c r="BP8">
+        <v>19</v>
+      </c>
+      <c r="BQ8">
+        <v>13.5</v>
+      </c>
+      <c r="BR8">
+        <v>34</v>
+      </c>
+      <c r="BS8">
+        <v>19.5</v>
+      </c>
+      <c r="BT8">
+        <v>8</v>
+      </c>
+      <c r="BU8">
+        <v>6</v>
+      </c>
+      <c r="BV8">
+        <v>32</v>
+      </c>
+      <c r="BW8">
+        <v>19</v>
+      </c>
+      <c r="BX8">
+        <v>44</v>
+      </c>
+      <c r="BY8">
+        <v>25</v>
+      </c>
+      <c r="BZ8">
+        <v>28</v>
+      </c>
+      <c r="CA8">
+        <v>16</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9">
+        <v>1.77</v>
+      </c>
+      <c r="G9">
+        <v>1.79</v>
+      </c>
+      <c r="H9">
+        <v>5.3</v>
+      </c>
+      <c r="I9">
+        <v>5.7</v>
+      </c>
+      <c r="J9">
+        <v>3.85</v>
+      </c>
+      <c r="K9">
+        <v>3.95</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.88</v>
+      </c>
+      <c r="Q9">
+        <v>2.02</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1.93</v>
+      </c>
+      <c r="U9">
+        <v>1.96</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>14</v>
+      </c>
+      <c r="Y9">
+        <v>17.5</v>
+      </c>
+      <c r="Z9">
+        <v>55</v>
+      </c>
+      <c r="AA9">
+        <v>180</v>
+      </c>
+      <c r="AB9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9">
+        <v>8.6</v>
+      </c>
+      <c r="AD9">
+        <v>22</v>
+      </c>
+      <c r="AE9">
+        <v>100</v>
+      </c>
+      <c r="AF9">
+        <v>10.5</v>
+      </c>
+      <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>100</v>
+      </c>
+      <c r="AJ9">
+        <v>19</v>
+      </c>
+      <c r="AK9">
+        <v>20</v>
+      </c>
+      <c r="AL9">
+        <v>48</v>
+      </c>
+      <c r="AM9">
+        <v>160</v>
+      </c>
+      <c r="AN9">
+        <v>12.5</v>
+      </c>
+      <c r="AO9">
+        <v>130</v>
+      </c>
+      <c r="AP9">
+        <v>12</v>
+      </c>
+      <c r="AQ9">
+        <v>15</v>
+      </c>
+      <c r="AR9">
+        <v>9.6</v>
+      </c>
+      <c r="AS9">
+        <v>11</v>
+      </c>
+      <c r="AT9">
+        <v>7.2</v>
+      </c>
+      <c r="AU9">
+        <v>7.6</v>
+      </c>
+      <c r="AV9">
+        <v>19</v>
+      </c>
+      <c r="AW9">
+        <v>10.5</v>
+      </c>
+      <c r="AX9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9">
+        <v>18</v>
+      </c>
+      <c r="BA9">
+        <v>10.5</v>
+      </c>
+      <c r="BB9">
+        <v>16.5</v>
+      </c>
+      <c r="BC9">
+        <v>17</v>
+      </c>
+      <c r="BD9">
+        <v>9.4</v>
+      </c>
+      <c r="BE9">
+        <v>11</v>
+      </c>
+      <c r="BF9">
+        <v>10.5</v>
+      </c>
+      <c r="BG9">
+        <v>10.5</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10">
+        <v>7.2</v>
+      </c>
+      <c r="G10">
+        <v>7.6</v>
+      </c>
+      <c r="H10">
+        <v>1.5</v>
+      </c>
+      <c r="I10">
+        <v>1.51</v>
+      </c>
+      <c r="J10">
+        <v>4.9</v>
+      </c>
+      <c r="K10">
+        <v>5.1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.03</v>
+      </c>
+      <c r="N10">
+        <v>5.9</v>
+      </c>
+      <c r="O10">
+        <v>1.18</v>
+      </c>
+      <c r="P10">
+        <v>2.7</v>
+      </c>
+      <c r="Q10">
+        <v>1.54</v>
+      </c>
+      <c r="R10">
+        <v>1.69</v>
+      </c>
+      <c r="S10">
+        <v>2.32</v>
+      </c>
+      <c r="T10">
+        <v>1.69</v>
+      </c>
+      <c r="U10">
+        <v>2.36</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>29</v>
+      </c>
+      <c r="Y10">
+        <v>12.5</v>
+      </c>
+      <c r="Z10">
+        <v>11.5</v>
+      </c>
+      <c r="AA10">
+        <v>15</v>
+      </c>
+      <c r="AB10">
+        <v>34</v>
+      </c>
+      <c r="AC10">
+        <v>11.5</v>
+      </c>
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
+        <v>14.5</v>
+      </c>
+      <c r="AF10">
+        <v>75</v>
+      </c>
+      <c r="AG10">
+        <v>29</v>
+      </c>
+      <c r="AH10">
+        <v>20</v>
+      </c>
+      <c r="AI10">
+        <v>28</v>
+      </c>
+      <c r="AJ10">
+        <v>220</v>
+      </c>
+      <c r="AK10">
+        <v>95</v>
+      </c>
+      <c r="AL10">
+        <v>75</v>
+      </c>
+      <c r="AM10">
+        <v>80</v>
+      </c>
+      <c r="AN10">
+        <v>80</v>
+      </c>
+      <c r="AO10">
+        <v>5.4</v>
+      </c>
+      <c r="AP10">
+        <v>22</v>
+      </c>
+      <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <v>13.5</v>
+      </c>
+      <c r="AT10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10">
+        <v>10</v>
+      </c>
+      <c r="AV10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW10">
+        <v>13</v>
+      </c>
+      <c r="AX10">
+        <v>11.5</v>
+      </c>
+      <c r="AY10">
+        <v>20</v>
+      </c>
+      <c r="AZ10">
+        <v>16.5</v>
+      </c>
+      <c r="BA10">
+        <v>21</v>
+      </c>
+      <c r="BB10">
+        <v>13</v>
+      </c>
+      <c r="BC10">
+        <v>12</v>
+      </c>
+      <c r="BD10">
+        <v>11.5</v>
+      </c>
+      <c r="BE10">
+        <v>11.5</v>
+      </c>
+      <c r="BF10">
+        <v>11.5</v>
+      </c>
+      <c r="BG10">
+        <v>5</v>
+      </c>
+      <c r="BH10">
+        <v>4.6</v>
+      </c>
+      <c r="BI10">
+        <v>4.2</v>
+      </c>
+      <c r="BJ10">
+        <v>9.6</v>
+      </c>
+      <c r="BK10">
+        <v>8.4</v>
+      </c>
+      <c r="BL10">
+        <v>95</v>
+      </c>
+      <c r="BM10">
+        <v>65</v>
+      </c>
+      <c r="BN10">
+        <v>10.5</v>
+      </c>
+      <c r="BO10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BP10">
+        <v>50</v>
+      </c>
+      <c r="BQ10">
+        <v>34</v>
+      </c>
+      <c r="BR10">
+        <v>46</v>
+      </c>
+      <c r="BS10">
+        <v>32</v>
+      </c>
+      <c r="BT10">
+        <v>4.4</v>
+      </c>
+      <c r="BU10">
+        <v>4</v>
+      </c>
+      <c r="BV10">
+        <v>9</v>
+      </c>
+      <c r="BW10">
+        <v>8</v>
+      </c>
+      <c r="BX10">
+        <v>21</v>
+      </c>
+      <c r="BY10">
+        <v>14.5</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -328,7 +328,7 @@
     <t>France</t>
   </si>
   <si>
-    <t>2026-09-23 00:02:48</t>
+    <t>2026-09-23 02:13:27</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>1.87</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
         <v>4.3</v>
@@ -934,10 +934,10 @@
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -949,13 +949,13 @@
         <v>3.9</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
         <v>1.39</v>
@@ -964,7 +964,7 @@
         <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
         <v>2.1</v>
@@ -973,7 +973,7 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X2">
         <v>18</v>
@@ -1000,7 +1000,7 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1024,7 +1024,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>65</v>
@@ -1036,10 +1036,10 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
+        <v>6.8</v>
+      </c>
+      <c r="AS2">
         <v>7.2</v>
-      </c>
-      <c r="AS2">
-        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1051,7 +1051,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1060,10 +1060,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB2">
         <v>18</v>
@@ -1072,16 +1072,16 @@
         <v>17</v>
       </c>
       <c r="BD2">
+        <v>6.8</v>
+      </c>
+      <c r="BE2">
         <v>7.2</v>
-      </c>
-      <c r="BE2">
-        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U3">
         <v>1.98</v>
@@ -1415,7 +1415,7 @@
         <v>4.6</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4">
         <v>3.8</v>
@@ -1439,7 +1439,7 @@
         <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.34</v>
@@ -1448,10 +1448,10 @@
         <v>3.7</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>150</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
         <v>8.6</v>
@@ -1484,7 +1484,7 @@
         <v>80</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1523,19 +1523,19 @@
         <v>30</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
+        <v>7.2</v>
+      </c>
+      <c r="AU4">
         <v>7.4</v>
-      </c>
-      <c r="AU4">
-        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4">
         <v>9.800000000000001</v>
@@ -1547,7 +1547,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1559,19 +1559,19 @@
         <v>32</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH4">
         <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -1592,13 +1592,13 @@
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
         <v>11.5</v>
       </c>
       <c r="BR4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS4">
         <v>21</v>
@@ -1625,7 +1625,7 @@
         <v>27</v>
       </c>
       <c r="CA4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CB4" t="s">
         <v>104</v>
@@ -1651,7 +1651,7 @@
         <v>1.55</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -1660,7 +1660,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
         <v>4.9</v>
@@ -1678,16 +1678,16 @@
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R5">
         <v>1.55</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
         <v>1.8</v>
@@ -1702,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z5">
         <v>70</v>
@@ -1732,7 +1732,7 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5">
         <v>90</v>
@@ -1741,7 +1741,7 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -1762,10 +1762,10 @@
         <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT5">
         <v>9.199999999999999</v>
@@ -1777,7 +1777,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1789,25 +1789,25 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
         <v>13</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1816,10 +1816,10 @@
         <v>3.75</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL5">
         <v>130</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5">
         <v>16.5</v>
@@ -1867,7 +1867,7 @@
         <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="s">
         <v>104</v>
@@ -1968,7 +1968,7 @@
         <v>100</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -2004,7 +2004,7 @@
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS6">
         <v>10.5</v>
@@ -2031,7 +2031,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB6">
         <v>16.5</v>
@@ -2040,16 +2040,16 @@
         <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
         <v>3.35</v>
@@ -2132,16 +2132,16 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
         <v>3.45</v>
@@ -2159,13 +2159,13 @@
         <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
         <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
         <v>1.32</v>
@@ -2192,13 +2192,13 @@
         <v>12.5</v>
       </c>
       <c r="Z7">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA7">
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2210,7 +2210,7 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2225,7 +2225,7 @@
         <v>36</v>
       </c>
       <c r="AK7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2234,7 +2234,7 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO7">
         <v>55</v>
@@ -2249,10 +2249,10 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
@@ -2261,7 +2261,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2273,25 +2273,25 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB7">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BG7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2321,7 +2321,7 @@
         <v>23</v>
       </c>
       <c r="BQ7">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BR7">
         <v>42</v>
@@ -2434,7 +2434,7 @@
         <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA8">
         <v>75</v>
@@ -2443,7 +2443,7 @@
         <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
         <v>14.5</v>
@@ -2491,7 +2491,7 @@
         <v>18.5</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX8">
         <v>13.5</v>
@@ -2524,10 +2524,10 @@
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8">
         <v>13.5</v>
@@ -2563,7 +2563,7 @@
         <v>19</v>
       </c>
       <c r="BQ8">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
         <v>34</v>
@@ -2581,7 +2581,7 @@
         <v>32</v>
       </c>
       <c r="BW8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BX8">
         <v>44</v>
@@ -2622,10 +2622,10 @@
         <v>1.79</v>
       </c>
       <c r="H9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
         <v>3.85</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2658,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U9">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>14</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="Z9">
         <v>55</v>
@@ -2685,7 +2685,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>22</v>
@@ -2706,19 +2706,19 @@
         <v>100</v>
       </c>
       <c r="AJ9">
+        <v>18.5</v>
+      </c>
+      <c r="AK9">
         <v>19</v>
-      </c>
-      <c r="AK9">
-        <v>20</v>
       </c>
       <c r="AL9">
         <v>48</v>
       </c>
       <c r="AM9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO9">
         <v>130</v>
@@ -2730,10 +2730,10 @@
         <v>15</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9">
         <v>7.2</v>
@@ -2745,37 +2745,37 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
+        <v>6.8</v>
+      </c>
+      <c r="BC9">
         <v>16.5</v>
       </c>
-      <c r="BC9">
-        <v>17</v>
-      </c>
       <c r="BD9">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF9">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH9">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         <v>7.6</v>
       </c>
       <c r="H10">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I10">
         <v>1.51</v>
@@ -2891,7 +2891,7 @@
         <v>2.7</v>
       </c>
       <c r="Q10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R10">
         <v>1.69</v>
@@ -2939,7 +2939,7 @@
         <v>75</v>
       </c>
       <c r="AG10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH10">
         <v>20</v>
@@ -2948,13 +2948,13 @@
         <v>28</v>
       </c>
       <c r="AJ10">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK10">
         <v>95</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM10">
         <v>80</v>
@@ -2963,7 +2963,7 @@
         <v>80</v>
       </c>
       <c r="AO10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AP10">
         <v>22</v>
@@ -2978,7 +2978,7 @@
         <v>13.5</v>
       </c>
       <c r="AT10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -2990,25 +2990,25 @@
         <v>13</v>
       </c>
       <c r="AX10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY10">
         <v>20</v>
       </c>
       <c r="AZ10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10">
         <v>21</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE10">
         <v>11.5</v>
@@ -3044,7 +3044,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BP10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ10">
         <v>34</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -328,7 +328,7 @@
     <t>France</t>
   </si>
   <si>
-    <t>2026-09-23 02:13:27</t>
+    <t>2026-09-23 03:30:34</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>1.87</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
         <v>4.3</v>
@@ -949,22 +949,22 @@
         <v>3.9</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R2">
         <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
         <v>2.1</v>
@@ -973,7 +973,7 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
         <v>18</v>
@@ -1024,7 +1024,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
         <v>65</v>
@@ -1036,10 +1036,10 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1051,7 +1051,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1063,7 +1063,7 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
         <v>18</v>
@@ -1072,16 +1072,16 @@
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q3">
         <v>1.96</v>
@@ -1412,16 +1412,16 @@
         <v>1.91</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
         <v>4.8</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>90</v>
@@ -1762,7 +1762,7 @@
         <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS5">
         <v>11.5</v>
@@ -1777,7 +1777,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1789,7 +1789,7 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1798,7 +1798,7 @@
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE5">
         <v>11</v>
@@ -1807,7 +1807,7 @@
         <v>5.9</v>
       </c>
       <c r="BG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1920,7 +1920,7 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q6">
         <v>2.06</v>
@@ -2159,7 +2159,7 @@
         <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
         <v>1.83</v>
@@ -2171,7 +2171,7 @@
         <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
         <v>1.82</v>
@@ -2195,10 +2195,10 @@
         <v>24</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2210,22 +2210,22 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>65</v>
       </c>
       <c r="AJ7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2240,7 +2240,7 @@
         <v>55</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
         <v>10.5</v>
@@ -2249,10 +2249,10 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
@@ -2261,7 +2261,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2273,31 +2273,31 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
         <v>8.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BD7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE7">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2318,16 +2318,16 @@
         <v>4.6</v>
       </c>
       <c r="BP7">
+        <v>22</v>
+      </c>
+      <c r="BQ7">
+        <v>13</v>
+      </c>
+      <c r="BR7">
+        <v>40</v>
+      </c>
+      <c r="BS7">
         <v>23</v>
-      </c>
-      <c r="BQ7">
-        <v>13.5</v>
-      </c>
-      <c r="BR7">
-        <v>42</v>
-      </c>
-      <c r="BS7">
-        <v>24</v>
       </c>
       <c r="BT7">
         <v>7.8</v>
@@ -2351,7 +2351,7 @@
         <v>38</v>
       </c>
       <c r="CA7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CB7" t="s">
         <v>104</v>
@@ -2401,7 +2401,7 @@
         <v>4.3</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
         <v>2.08</v>
@@ -2524,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BE8">
         <v>8.800000000000001</v>
@@ -2616,10 +2616,10 @@
         <v>102</v>
       </c>
       <c r="F9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
         <v>5.4</v>
@@ -2628,7 +2628,7 @@
         <v>5.6</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>3.95</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2670,16 +2670,16 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z9">
         <v>55</v>
       </c>
       <c r="AA9">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB9">
         <v>8.199999999999999</v>
@@ -2718,7 +2718,7 @@
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO9">
         <v>130</v>
@@ -2727,13 +2727,13 @@
         <v>12</v>
       </c>
       <c r="AQ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT9">
         <v>7.2</v>
@@ -2745,7 +2745,7 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
@@ -2757,22 +2757,22 @@
         <v>18.5</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB9">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE9">
+        <v>10.5</v>
+      </c>
+      <c r="BF9">
         <v>10</v>
-      </c>
-      <c r="BF9">
-        <v>8</v>
       </c>
       <c r="BG9">
         <v>10</v>
@@ -2867,7 +2867,7 @@
         <v>1.49</v>
       </c>
       <c r="I10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J10">
         <v>4.9</v>
@@ -2924,10 +2924,10 @@
         <v>15</v>
       </c>
       <c r="AB10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD10">
         <v>10</v>
@@ -2990,7 +2990,7 @@
         <v>13</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY10">
         <v>20</v>
@@ -3002,19 +3002,19 @@
         <v>21</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD10">
+        <v>10.5</v>
+      </c>
+      <c r="BE10">
+        <v>10.5</v>
+      </c>
+      <c r="BF10">
         <v>11</v>
-      </c>
-      <c r="BE10">
-        <v>11.5</v>
-      </c>
-      <c r="BF10">
-        <v>11.5</v>
       </c>
       <c r="BG10">
         <v>5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -328,7 +328,7 @@
     <t>France</t>
   </si>
   <si>
-    <t>2026-09-23 03:30:34</t>
+    <t>2026-09-23 05:41:42</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>1.87</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
         <v>4.3</v>
@@ -934,10 +934,10 @@
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -955,16 +955,16 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
         <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
         <v>2.1</v>
@@ -976,7 +976,7 @@
         <v>2.02</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y2">
         <v>17.5</v>
@@ -1024,7 +1024,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO2">
         <v>65</v>
@@ -1060,7 +1060,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BA2">
         <v>7.6</v>
@@ -1164,22 +1164,22 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G3">
         <v>1.8</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J3">
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U3">
         <v>1.98</v>
@@ -1290,7 +1290,7 @@
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW3">
         <v>9.6</v>
@@ -1547,7 +1547,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1568,7 +1568,7 @@
         <v>8.4</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
         <v>2.96</v>
@@ -1592,13 +1592,13 @@
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
         <v>11.5</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4">
         <v>21</v>
@@ -1625,7 +1625,7 @@
         <v>27</v>
       </c>
       <c r="CA4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CB4" t="s">
         <v>104</v>
@@ -1648,13 +1648,13 @@
         <v>98</v>
       </c>
       <c r="F5">
+        <v>1.54</v>
+      </c>
+      <c r="G5">
         <v>1.55</v>
       </c>
-      <c r="G5">
-        <v>1.56</v>
-      </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1678,10 +1678,10 @@
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
         <v>1.55</v>
@@ -1759,7 +1759,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR5">
         <v>10.5</v>
@@ -1816,7 +1816,7 @@
         <v>3.75</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>9</v>
@@ -1840,7 +1840,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS5">
         <v>16.5</v>
@@ -1867,7 +1867,7 @@
         <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>104</v>
@@ -1893,7 +1893,7 @@
         <v>1.72</v>
       </c>
       <c r="G6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H6">
         <v>5.4</v>
@@ -1902,7 +1902,7 @@
         <v>5.9</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -1920,7 +1920,7 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q6">
         <v>2.06</v>
@@ -1974,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI6">
         <v>95</v>
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>3.35</v>
@@ -2132,16 +2132,16 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G7">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
         <v>3.45</v>
@@ -2162,7 +2162,7 @@
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y7">
         <v>12.5</v>
@@ -2204,7 +2204,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE7">
         <v>55</v>
@@ -2225,7 +2225,7 @@
         <v>40</v>
       </c>
       <c r="AK7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2249,7 +2249,7 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT7">
         <v>8.6</v>
@@ -2261,7 +2261,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AX7">
         <v>13</v>
@@ -2273,25 +2273,25 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC7">
         <v>19.5</v>
       </c>
       <c r="BD7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
         <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2321,7 +2321,7 @@
         <v>22</v>
       </c>
       <c r="BQ7">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BR7">
         <v>40</v>
@@ -2330,7 +2330,7 @@
         <v>23</v>
       </c>
       <c r="BT7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU7">
         <v>5.7</v>
@@ -2401,13 +2401,13 @@
         <v>4.3</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
         <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R8">
         <v>1.42</v>
@@ -2419,7 +2419,7 @@
         <v>1.71</v>
       </c>
       <c r="U8">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
         <v>14.5</v>
@@ -2488,10 +2488,10 @@
         <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX8">
         <v>13.5</v>
@@ -2527,13 +2527,13 @@
         <v>25</v>
       </c>
       <c r="BE8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF8">
         <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH8">
         <v>3.65</v>
@@ -2563,7 +2563,7 @@
         <v>19</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR8">
         <v>34</v>
@@ -2581,7 +2581,7 @@
         <v>32</v>
       </c>
       <c r="BW8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BX8">
         <v>44</v>
@@ -2616,22 +2616,22 @@
         <v>102</v>
       </c>
       <c r="F9">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I9">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
         <v>3.8</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>1.92</v>
       </c>
       <c r="U9">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA9">
         <v>170</v>
       </c>
       <c r="AB9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2700,16 +2700,16 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI9">
         <v>100</v>
       </c>
       <c r="AJ9">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AK9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL9">
         <v>48</v>
@@ -2718,34 +2718,34 @@
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP9">
         <v>12</v>
       </c>
       <c r="AQ9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR9">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AS9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU9">
         <v>7.6</v>
       </c>
       <c r="AV9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
@@ -2754,28 +2754,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BB9">
         <v>16</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9">
         <v>10</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH9">
         <v>0</v>
@@ -2858,19 +2858,19 @@
         <v>103</v>
       </c>
       <c r="F10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G10">
         <v>7.6</v>
       </c>
       <c r="H10">
+        <v>1.48</v>
+      </c>
+      <c r="I10">
         <v>1.49</v>
       </c>
-      <c r="I10">
-        <v>1.5</v>
-      </c>
       <c r="J10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5.1</v>
@@ -2885,10 +2885,10 @@
         <v>5.9</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q10">
         <v>1.53</v>
@@ -2903,7 +2903,7 @@
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>20</v>
       </c>
       <c r="AI10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ10">
         <v>210</v>
@@ -2963,10 +2963,10 @@
         <v>80</v>
       </c>
       <c r="AO10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AP10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -2984,37 +2984,37 @@
         <v>10</v>
       </c>
       <c r="AV10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ10">
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB10">
+        <v>12.5</v>
+      </c>
+      <c r="BC10">
         <v>11.5</v>
       </c>
-      <c r="BC10">
-        <v>10.5</v>
-      </c>
       <c r="BD10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG10">
         <v>5</v>
@@ -3032,7 +3032,7 @@
         <v>8.4</v>
       </c>
       <c r="BL10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
         <v>65</v>
@@ -3068,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="BX10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY10">
         <v>14.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -328,7 +328,7 @@
     <t>France</t>
   </si>
   <si>
-    <t>2026-09-23 05:41:42</t>
+    <t>2026-09-23 07:53:17</t>
   </si>
 </sst>
 </file>
@@ -922,52 +922,52 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
         <v>1.26</v>
@@ -979,7 +979,7 @@
         <v>19</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z2">
         <v>36</v>
@@ -988,58 +988,58 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
         <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
+        <v>19</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>24</v>
+      </c>
+      <c r="AK2">
         <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>70</v>
-      </c>
-      <c r="AJ2">
-        <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
       </c>
       <c r="AL2">
         <v>36</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1051,7 +1051,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1060,28 +1060,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB2">
         <v>18</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1164,13 +1164,13 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
         <v>5.5</v>
@@ -1179,7 +1179,7 @@
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1206,10 +1206,10 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U3">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -1406,10 +1406,10 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H4">
         <v>4.7</v>
@@ -1418,10 +1418,10 @@
         <v>4.8</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1430,19 +1430,19 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
         <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
         <v>3.7</v>
@@ -1451,7 +1451,7 @@
         <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1508,7 +1508,7 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO4">
         <v>110</v>
@@ -1541,13 +1541,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1598,16 +1598,16 @@
         <v>11.5</v>
       </c>
       <c r="BR4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS4">
         <v>21</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV4">
         <v>44</v>
@@ -1705,7 +1705,7 @@
         <v>22</v>
       </c>
       <c r="Y5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z5">
         <v>70</v>
@@ -1744,7 +1744,7 @@
         <v>15</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>120</v>
@@ -1762,10 +1762,10 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>9.199999999999999</v>
@@ -1777,7 +1777,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1789,7 +1789,7 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1798,16 +1798,16 @@
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1816,7 +1816,7 @@
         <v>3.75</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
         <v>9</v>
@@ -1840,7 +1840,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5">
         <v>16.5</v>
@@ -1867,7 +1867,7 @@
         <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="s">
         <v>104</v>
@@ -1890,16 +1890,16 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H6">
         <v>5.4</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J6">
         <v>3.95</v>
@@ -1929,13 +1929,13 @@
         <v>1.34</v>
       </c>
       <c r="S6">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T6">
         <v>1.95</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO6">
         <v>130</v>
@@ -2004,10 +2004,10 @@
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2019,7 +2019,7 @@
         <v>19</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
         <v>8.6</v>
@@ -2040,7 +2040,7 @@
         <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE6">
         <v>10.5</v>
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
         <v>3.35</v>
@@ -2135,7 +2135,7 @@
         <v>2.38</v>
       </c>
       <c r="G7">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H7">
         <v>3.35</v>
@@ -2156,28 +2156,28 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
+        <v>1.76</v>
+      </c>
+      <c r="Q7">
+        <v>2.14</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
+        <v>3.8</v>
+      </c>
+      <c r="T7">
         <v>1.84</v>
       </c>
-      <c r="Q7">
-        <v>2.04</v>
-      </c>
-      <c r="R7">
-        <v>1.32</v>
-      </c>
-      <c r="S7">
-        <v>3.7</v>
-      </c>
-      <c r="T7">
-        <v>1.82</v>
-      </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2186,46 +2186,46 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA7">
         <v>75</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7">
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI7">
         <v>65</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2234,64 +2234,64 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO7">
         <v>55</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR7">
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>13</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC7">
         <v>19.5</v>
       </c>
       <c r="BD7">
+        <v>8.4</v>
+      </c>
+      <c r="BE7">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE7">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2374,7 +2374,7 @@
         <v>101</v>
       </c>
       <c r="F8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G8">
         <v>2.3</v>
@@ -2383,7 +2383,7 @@
         <v>3.4</v>
       </c>
       <c r="I8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J8">
         <v>3.65</v>
@@ -2404,10 +2404,10 @@
         <v>1.28</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
         <v>1.42</v>
@@ -2419,7 +2419,7 @@
         <v>1.71</v>
       </c>
       <c r="U8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="BE8">
         <v>9</v>
@@ -2581,7 +2581,7 @@
         <v>32</v>
       </c>
       <c r="BW8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BX8">
         <v>44</v>
@@ -2616,13 +2616,13 @@
         <v>102</v>
       </c>
       <c r="F9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G9">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
         <v>5.5</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2670,16 +2670,16 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z9">
         <v>50</v>
       </c>
       <c r="AA9">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB9">
         <v>8.4</v>
@@ -2688,10 +2688,10 @@
         <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2700,25 +2700,25 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI9">
         <v>100</v>
       </c>
       <c r="AJ9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM9">
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AO9">
         <v>120</v>
@@ -2733,31 +2733,31 @@
         <v>36</v>
       </c>
       <c r="AS9">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT9">
         <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV9">
         <v>18.5</v>
       </c>
       <c r="AW9">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
         <v>19</v>
       </c>
       <c r="BA9">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9">
         <v>16</v>
@@ -2769,13 +2769,13 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF9">
         <v>10</v>
       </c>
       <c r="BG9">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH9">
         <v>0</v>
@@ -2858,10 +2858,10 @@
         <v>103</v>
       </c>
       <c r="F10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H10">
         <v>1.48</v>
@@ -2888,7 +2888,7 @@
         <v>1.17</v>
       </c>
       <c r="P10">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q10">
         <v>1.53</v>
@@ -2897,13 +2897,13 @@
         <v>1.69</v>
       </c>
       <c r="S10">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T10">
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V10">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
   <si>
     <t>League</t>
   </si>
@@ -256,27 +256,54 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
     <t>UEFA Nations League</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>2026-09-25</t>
   </si>
   <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:20:00</t>
+  </si>
+  <si>
     <t>00:30:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
     <t>18:45:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
     <t>Armenia</t>
   </si>
   <si>
@@ -301,9 +328,21 @@
     <t>Türkiye</t>
   </si>
   <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Trinidad &amp; Tobago</t>
+  </si>
+  <si>
     <t>Millonarios</t>
   </si>
   <si>
+    <t>Curacao</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
@@ -328,7 +367,10 @@
     <t>France</t>
   </si>
   <si>
-    <t>2026-09-23 07:53:17</t>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>2026-09-23 10:07:11</t>
   </si>
 </sst>
 </file>
@@ -660,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -910,178 +952,178 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F2">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
+        <v>6.6</v>
+      </c>
+      <c r="J2">
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <v>3.85</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.1</v>
+      </c>
+      <c r="N2">
+        <v>2.74</v>
+      </c>
+      <c r="O2">
+        <v>1.4</v>
+      </c>
+      <c r="P2">
+        <v>1.67</v>
+      </c>
+      <c r="Q2">
+        <v>1.97</v>
+      </c>
+      <c r="R2">
+        <v>1.27</v>
+      </c>
+      <c r="S2">
+        <v>2.24</v>
+      </c>
+      <c r="T2">
+        <v>1.68</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.18</v>
+      </c>
+      <c r="W2">
+        <v>2.08</v>
+      </c>
+      <c r="X2">
+        <v>14.5</v>
+      </c>
+      <c r="Y2">
+        <v>16.5</v>
+      </c>
+      <c r="Z2">
+        <v>55</v>
+      </c>
+      <c r="AA2">
+        <v>190</v>
+      </c>
+      <c r="AB2">
+        <v>7.6</v>
+      </c>
+      <c r="AC2">
+        <v>10</v>
+      </c>
+      <c r="AD2">
+        <v>27</v>
+      </c>
+      <c r="AE2">
+        <v>110</v>
+      </c>
+      <c r="AF2">
+        <v>11</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>120</v>
+      </c>
+      <c r="AJ2">
+        <v>25</v>
+      </c>
+      <c r="AK2">
+        <v>23</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>190</v>
+      </c>
+      <c r="AN2">
+        <v>19</v>
+      </c>
+      <c r="AO2">
+        <v>160</v>
+      </c>
+      <c r="AP2">
+        <v>3.85</v>
+      </c>
+      <c r="AQ2">
+        <v>4</v>
+      </c>
+      <c r="AR2">
         <v>4.8</v>
       </c>
-      <c r="J2">
+      <c r="AS2">
+        <v>5.1</v>
+      </c>
+      <c r="AT2">
+        <v>3.1</v>
+      </c>
+      <c r="AU2">
+        <v>3.45</v>
+      </c>
+      <c r="AV2">
+        <v>4.4</v>
+      </c>
+      <c r="AW2">
+        <v>5</v>
+      </c>
+      <c r="AX2">
+        <v>3.55</v>
+      </c>
+      <c r="AY2">
         <v>3.7</v>
       </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>1.02</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-      <c r="O2">
-        <v>1.28</v>
-      </c>
-      <c r="P2">
-        <v>2.04</v>
-      </c>
-      <c r="Q2">
-        <v>1.84</v>
-      </c>
-      <c r="R2">
-        <v>1.42</v>
-      </c>
-      <c r="S2">
-        <v>3.2</v>
-      </c>
-      <c r="T2">
-        <v>1.76</v>
-      </c>
-      <c r="U2">
-        <v>2.16</v>
-      </c>
-      <c r="V2">
-        <v>1.26</v>
-      </c>
-      <c r="W2">
-        <v>2.02</v>
-      </c>
-      <c r="X2">
-        <v>19</v>
-      </c>
-      <c r="Y2">
-        <v>18</v>
-      </c>
-      <c r="Z2">
-        <v>36</v>
-      </c>
-      <c r="AA2">
-        <v>110</v>
-      </c>
-      <c r="AB2">
-        <v>11</v>
-      </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>18.5</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>19</v>
-      </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>24</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
-        <v>36</v>
-      </c>
-      <c r="AM2">
-        <v>100</v>
-      </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>60</v>
-      </c>
-      <c r="AP2">
-        <v>14</v>
-      </c>
-      <c r="AQ2">
-        <v>15</v>
-      </c>
-      <c r="AR2">
-        <v>6.8</v>
-      </c>
-      <c r="AS2">
-        <v>7.4</v>
-      </c>
-      <c r="AT2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>15.5</v>
-      </c>
-      <c r="AW2">
-        <v>7.4</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1144,249 +1186,249 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>110</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X3">
+        <v>16</v>
+      </c>
+      <c r="Y3">
+        <v>26</v>
+      </c>
+      <c r="Z3">
+        <v>75</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>10</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>36</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>13.5</v>
+      </c>
+      <c r="AG3">
         <v>15</v>
       </c>
-      <c r="Y3">
-        <v>17.5</v>
-      </c>
-      <c r="Z3">
-        <v>44</v>
-      </c>
-      <c r="AA3">
-        <v>160</v>
-      </c>
-      <c r="AB3">
-        <v>8.6</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>85</v>
-      </c>
-      <c r="AF3">
-        <v>11</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
       <c r="AH3">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>12.5</v>
+        <v>2.06</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>2.18</v>
       </c>
       <c r="AR3">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="AS3">
-        <v>10</v>
+        <v>2.38</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>1.92</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>2.22</v>
       </c>
       <c r="AW3">
-        <v>9.6</v>
+        <v>2.38</v>
       </c>
       <c r="AX3">
-        <v>9.4</v>
+        <v>2.02</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>2.22</v>
       </c>
       <c r="BA3">
-        <v>9.6</v>
+        <v>2.38</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>2.16</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>2.2</v>
       </c>
       <c r="BD3">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>2.38</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>2.38</v>
       </c>
       <c r="BG3">
-        <v>10</v>
+        <v>2.38</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1394,106 +1436,106 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="H4">
+        <v>4.3</v>
+      </c>
+      <c r="I4">
         <v>4.7</v>
       </c>
-      <c r="I4">
-        <v>4.8</v>
-      </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>25</v>
@@ -1502,82 +1544,82 @@
         <v>23</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
         <v>18</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE4">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1586,323 +1628,323 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="G5">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>4.3</v>
+      </c>
+      <c r="L5">
+        <v>1.43</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>2.8</v>
+      </c>
+      <c r="O5">
+        <v>1.37</v>
+      </c>
+      <c r="P5">
+        <v>1.73</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>1.27</v>
+      </c>
+      <c r="S5">
+        <v>3.5</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>1.77</v>
+      </c>
+      <c r="V5">
+        <v>1.16</v>
+      </c>
+      <c r="W5">
+        <v>2.34</v>
+      </c>
+      <c r="X5">
+        <v>15</v>
+      </c>
+      <c r="Y5">
+        <v>21</v>
+      </c>
+      <c r="Z5">
+        <v>55</v>
+      </c>
+      <c r="AA5">
+        <v>230</v>
+      </c>
+      <c r="AB5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>29</v>
+      </c>
+      <c r="AE5">
+        <v>130</v>
+      </c>
+      <c r="AF5">
+        <v>11</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>26</v>
+      </c>
+      <c r="AI5">
+        <v>130</v>
+      </c>
+      <c r="AJ5">
+        <v>20</v>
+      </c>
+      <c r="AK5">
+        <v>24</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>200</v>
+      </c>
+      <c r="AN5">
+        <v>15</v>
+      </c>
+      <c r="AO5">
+        <v>190</v>
+      </c>
+      <c r="AP5">
+        <v>3.9</v>
+      </c>
+      <c r="AQ5">
+        <v>4.2</v>
+      </c>
+      <c r="AR5">
         <v>4.8</v>
       </c>
-      <c r="K5">
-        <v>4.9</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>1.04</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>1.22</v>
-      </c>
-      <c r="P5">
-        <v>2.36</v>
-      </c>
-      <c r="Q5">
-        <v>1.65</v>
-      </c>
-      <c r="R5">
-        <v>1.55</v>
-      </c>
-      <c r="S5">
-        <v>2.6</v>
-      </c>
-      <c r="T5">
-        <v>1.8</v>
-      </c>
-      <c r="U5">
-        <v>2.12</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>22</v>
-      </c>
-      <c r="Y5">
-        <v>32</v>
-      </c>
-      <c r="Z5">
-        <v>70</v>
-      </c>
-      <c r="AA5">
-        <v>210</v>
-      </c>
-      <c r="AB5">
-        <v>10.5</v>
-      </c>
-      <c r="AC5">
-        <v>11</v>
-      </c>
-      <c r="AD5">
-        <v>26</v>
-      </c>
-      <c r="AE5">
-        <v>100</v>
-      </c>
-      <c r="AF5">
-        <v>10.5</v>
-      </c>
-      <c r="AG5">
-        <v>10.5</v>
-      </c>
-      <c r="AH5">
-        <v>21</v>
-      </c>
-      <c r="AI5">
-        <v>90</v>
-      </c>
-      <c r="AJ5">
-        <v>15</v>
-      </c>
-      <c r="AK5">
-        <v>15</v>
-      </c>
-      <c r="AL5">
-        <v>36</v>
-      </c>
-      <c r="AM5">
-        <v>120</v>
-      </c>
-      <c r="AN5">
-        <v>6.6</v>
-      </c>
-      <c r="AO5">
-        <v>110</v>
-      </c>
-      <c r="AP5">
-        <v>19.5</v>
-      </c>
-      <c r="AQ5">
-        <v>20</v>
-      </c>
-      <c r="AR5">
-        <v>10</v>
-      </c>
       <c r="AS5">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AU5">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AW5">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF5">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="BG5">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F6">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G6">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -1911,31 +1953,31 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P6">
+        <v>1.94</v>
+      </c>
+      <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>1.9</v>
       </c>
-      <c r="Q6">
-        <v>2.06</v>
-      </c>
-      <c r="R6">
-        <v>1.34</v>
-      </c>
-      <c r="S6">
-        <v>3.6</v>
-      </c>
-      <c r="T6">
-        <v>1.95</v>
-      </c>
       <c r="U6">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1944,210 +1986,210 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA6">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
         <v>9</v>
       </c>
       <c r="AD6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE6">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
+        <v>18.5</v>
+      </c>
+      <c r="AK6">
         <v>20</v>
       </c>
-      <c r="AK6">
-        <v>21</v>
-      </c>
       <c r="AL6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO6">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP6">
         <v>12.5</v>
       </c>
       <c r="AQ6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
         <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW6">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY6">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC6">
         <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF6">
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH6">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK6">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO6">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BQ6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR6">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU6">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BZ6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="G7">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2156,28 +2198,28 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.8</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2186,240 +2228,240 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
+        <v>46</v>
+      </c>
+      <c r="AA7">
+        <v>150</v>
+      </c>
+      <c r="AB7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>8.6</v>
+      </c>
+      <c r="AD7">
         <v>23</v>
       </c>
-      <c r="AA7">
-        <v>75</v>
-      </c>
-      <c r="AB7">
+      <c r="AE7">
+        <v>80</v>
+      </c>
+      <c r="AF7">
+        <v>11</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>24</v>
+      </c>
+      <c r="AI7">
+        <v>90</v>
+      </c>
+      <c r="AJ7">
+        <v>22</v>
+      </c>
+      <c r="AK7">
+        <v>23</v>
+      </c>
+      <c r="AL7">
+        <v>50</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>14.5</v>
+      </c>
+      <c r="AO7">
+        <v>110</v>
+      </c>
+      <c r="AP7">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7">
+        <v>13.5</v>
+      </c>
+      <c r="AR7">
+        <v>30</v>
+      </c>
+      <c r="AS7">
+        <v>9</v>
+      </c>
+      <c r="AT7">
+        <v>7.2</v>
+      </c>
+      <c r="AU7">
+        <v>7.4</v>
+      </c>
+      <c r="AV7">
+        <v>16.5</v>
+      </c>
+      <c r="AW7">
+        <v>8.6</v>
+      </c>
+      <c r="AX7">
+        <v>9.6</v>
+      </c>
+      <c r="AY7">
         <v>9.4</v>
       </c>
-      <c r="AC7">
-        <v>7.6</v>
-      </c>
-      <c r="AD7">
-        <v>15.5</v>
-      </c>
-      <c r="AE7">
-        <v>55</v>
-      </c>
-      <c r="AF7">
-        <v>15</v>
-      </c>
-      <c r="AG7">
-        <v>12</v>
-      </c>
-      <c r="AH7">
-        <v>23</v>
-      </c>
-      <c r="AI7">
-        <v>65</v>
-      </c>
-      <c r="AJ7">
-        <v>42</v>
-      </c>
-      <c r="AK7">
-        <v>36</v>
-      </c>
-      <c r="AL7">
-        <v>55</v>
-      </c>
-      <c r="AM7">
-        <v>130</v>
-      </c>
-      <c r="AN7">
-        <v>22</v>
-      </c>
-      <c r="AO7">
-        <v>55</v>
-      </c>
-      <c r="AP7">
-        <v>11</v>
-      </c>
-      <c r="AQ7">
-        <v>10</v>
-      </c>
-      <c r="AR7">
-        <v>20</v>
-      </c>
-      <c r="AS7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU7">
-        <v>6.6</v>
-      </c>
-      <c r="AV7">
-        <v>13</v>
-      </c>
-      <c r="AW7">
-        <v>36</v>
-      </c>
-      <c r="AX7">
-        <v>13</v>
-      </c>
-      <c r="AY7">
-        <v>10.5</v>
-      </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA7">
         <v>8.6</v>
       </c>
       <c r="BB7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BC7">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD7">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
+        <v>9</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>4.5</v>
+      </c>
+      <c r="BO7">
+        <v>4</v>
+      </c>
+      <c r="BP7">
+        <v>13.5</v>
+      </c>
+      <c r="BQ7">
+        <v>11.5</v>
+      </c>
+      <c r="BR7">
+        <v>30</v>
+      </c>
+      <c r="BS7">
+        <v>21</v>
+      </c>
+      <c r="BT7">
         <v>8.4</v>
       </c>
-      <c r="BL7">
-        <v>160</v>
-      </c>
-      <c r="BM7">
-        <v>1.01</v>
-      </c>
-      <c r="BN7">
-        <v>6.2</v>
-      </c>
-      <c r="BO7">
-        <v>4.6</v>
-      </c>
-      <c r="BP7">
-        <v>22</v>
-      </c>
-      <c r="BQ7">
-        <v>15.5</v>
-      </c>
-      <c r="BR7">
-        <v>40</v>
-      </c>
-      <c r="BS7">
-        <v>23</v>
-      </c>
-      <c r="BT7">
-        <v>7.6</v>
-      </c>
       <c r="BU7">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BX7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="CA7">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CB7" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>1.55</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="H8">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="I8">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S8">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="T8">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="U8">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2428,124 +2470,124 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="Z8">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD8">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AE8">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AF8">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
+        <v>21</v>
+      </c>
+      <c r="AI8">
+        <v>90</v>
+      </c>
+      <c r="AJ8">
+        <v>15</v>
+      </c>
+      <c r="AK8">
+        <v>15</v>
+      </c>
+      <c r="AL8">
+        <v>36</v>
+      </c>
+      <c r="AM8">
+        <v>120</v>
+      </c>
+      <c r="AN8">
+        <v>6.6</v>
+      </c>
+      <c r="AO8">
+        <v>110</v>
+      </c>
+      <c r="AP8">
         <v>19.5</v>
       </c>
-      <c r="AI8">
-        <v>55</v>
-      </c>
-      <c r="AJ8">
-        <v>36</v>
-      </c>
-      <c r="AK8">
-        <v>24</v>
-      </c>
-      <c r="AL8">
-        <v>42</v>
-      </c>
-      <c r="AM8">
-        <v>95</v>
-      </c>
-      <c r="AN8">
-        <v>16</v>
-      </c>
-      <c r="AO8">
-        <v>38</v>
-      </c>
-      <c r="AP8">
-        <v>15</v>
-      </c>
       <c r="AQ8">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR8">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT8">
         <v>10</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AW8">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AX8">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>18.5</v>
+      </c>
+      <c r="BA8">
         <v>10</v>
       </c>
-      <c r="AZ8">
-        <v>15</v>
-      </c>
-      <c r="BA8">
-        <v>30</v>
-      </c>
       <c r="BB8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BC8">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD8">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE8">
+        <v>10.5</v>
+      </c>
+      <c r="BF8">
+        <v>5.8</v>
+      </c>
+      <c r="BG8">
+        <v>10.5</v>
+      </c>
+      <c r="BH8">
+        <v>4.1</v>
+      </c>
+      <c r="BI8">
+        <v>3.75</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
         <v>9</v>
-      </c>
-      <c r="BF8">
-        <v>13.5</v>
-      </c>
-      <c r="BG8">
-        <v>8.6</v>
-      </c>
-      <c r="BH8">
-        <v>3.65</v>
-      </c>
-      <c r="BI8">
-        <v>3.35</v>
-      </c>
-      <c r="BJ8">
-        <v>11</v>
-      </c>
-      <c r="BK8">
-        <v>8</v>
       </c>
       <c r="BL8">
         <v>130</v>
@@ -2554,114 +2596,114 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BQ8">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS8">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BV8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BW8">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="BX8">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BY8">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BZ8">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="CA8">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
         <v>1.91</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U9">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2670,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z9">
         <v>50</v>
@@ -2682,228 +2724,228 @@
         <v>180</v>
       </c>
       <c r="AB9">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE9">
         <v>100</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ9">
+        <v>20</v>
+      </c>
+      <c r="AK9">
         <v>21</v>
       </c>
-      <c r="AK9">
-        <v>23</v>
-      </c>
       <c r="AL9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM9">
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO9">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9">
         <v>15</v>
       </c>
       <c r="AR9">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AT9">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
       </c>
       <c r="AV9">
+        <v>19</v>
+      </c>
+      <c r="AW9">
+        <v>10.5</v>
+      </c>
+      <c r="AX9">
+        <v>8.6</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
         <v>18.5</v>
       </c>
-      <c r="AW9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9">
-        <v>19</v>
-      </c>
       <c r="BA9">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="BE9">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
         <v>10</v>
       </c>
       <c r="BG9">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F10">
-        <v>7.6</v>
+        <v>2.38</v>
       </c>
       <c r="G10">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>1.49</v>
+        <v>3.5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N10">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="P10">
-        <v>2.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q10">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2912,175 +2954,1143 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>9.4</v>
+      </c>
+      <c r="AC10">
+        <v>7.4</v>
+      </c>
+      <c r="AD10">
+        <v>15.5</v>
+      </c>
+      <c r="AE10">
+        <v>55</v>
+      </c>
+      <c r="AF10">
         <v>15</v>
       </c>
-      <c r="AB10">
-        <v>38</v>
-      </c>
-      <c r="AC10">
+      <c r="AG10">
         <v>12</v>
       </c>
-      <c r="AD10">
+      <c r="AH10">
+        <v>23</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>42</v>
+      </c>
+      <c r="AK10">
+        <v>36</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
+        <v>130</v>
+      </c>
+      <c r="AN10">
+        <v>22</v>
+      </c>
+      <c r="AO10">
+        <v>60</v>
+      </c>
+      <c r="AP10">
+        <v>10.5</v>
+      </c>
+      <c r="AQ10">
         <v>10</v>
       </c>
-      <c r="AE10">
-        <v>14.5</v>
-      </c>
-      <c r="AF10">
-        <v>75</v>
-      </c>
-      <c r="AG10">
-        <v>27</v>
-      </c>
-      <c r="AH10">
-        <v>20</v>
-      </c>
-      <c r="AI10">
-        <v>27</v>
-      </c>
-      <c r="AJ10">
-        <v>210</v>
-      </c>
-      <c r="AK10">
-        <v>95</v>
-      </c>
-      <c r="AL10">
-        <v>70</v>
-      </c>
-      <c r="AM10">
-        <v>80</v>
-      </c>
-      <c r="AN10">
-        <v>80</v>
-      </c>
-      <c r="AO10">
-        <v>5.4</v>
-      </c>
-      <c r="AP10">
-        <v>23</v>
-      </c>
-      <c r="AQ10">
+      <c r="AR10">
+        <v>19</v>
+      </c>
+      <c r="AS10">
+        <v>9.4</v>
+      </c>
+      <c r="AT10">
+        <v>8</v>
+      </c>
+      <c r="AU10">
+        <v>6.6</v>
+      </c>
+      <c r="AV10">
+        <v>13</v>
+      </c>
+      <c r="AW10">
+        <v>9</v>
+      </c>
+      <c r="AX10">
+        <v>13</v>
+      </c>
+      <c r="AY10">
         <v>10.5</v>
       </c>
-      <c r="AR10">
-        <v>10</v>
-      </c>
-      <c r="AS10">
-        <v>13.5</v>
-      </c>
-      <c r="AT10">
-        <v>9.6</v>
-      </c>
-      <c r="AU10">
-        <v>10</v>
-      </c>
-      <c r="AV10">
+      <c r="AZ10">
+        <v>16.5</v>
+      </c>
+      <c r="BA10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB10">
+        <v>8.4</v>
+      </c>
+      <c r="BC10">
+        <v>19.5</v>
+      </c>
+      <c r="BD10">
         <v>9</v>
       </c>
-      <c r="AW10">
-        <v>12.5</v>
-      </c>
-      <c r="AX10">
-        <v>11</v>
-      </c>
-      <c r="AY10">
-        <v>23</v>
-      </c>
-      <c r="AZ10">
-        <v>17</v>
-      </c>
-      <c r="BA10">
-        <v>22</v>
-      </c>
-      <c r="BB10">
-        <v>12.5</v>
-      </c>
-      <c r="BC10">
-        <v>11.5</v>
-      </c>
-      <c r="BD10">
-        <v>11</v>
-      </c>
       <c r="BE10">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BG10">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI10">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BK10">
         <v>8.4</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>6.2</v>
+      </c>
+      <c r="BO10">
+        <v>4.5</v>
+      </c>
+      <c r="BP10">
+        <v>22</v>
+      </c>
+      <c r="BQ10">
+        <v>13</v>
+      </c>
+      <c r="BR10">
+        <v>40</v>
+      </c>
+      <c r="BS10">
+        <v>24</v>
+      </c>
+      <c r="BT10">
+        <v>7.8</v>
+      </c>
+      <c r="BU10">
+        <v>5.7</v>
+      </c>
+      <c r="BV10">
+        <v>36</v>
+      </c>
+      <c r="BW10">
+        <v>20</v>
+      </c>
+      <c r="BX10">
+        <v>50</v>
+      </c>
+      <c r="BY10">
+        <v>30</v>
+      </c>
+      <c r="BZ10">
+        <v>38</v>
+      </c>
+      <c r="CA10">
+        <v>22</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11">
+        <v>2.26</v>
+      </c>
+      <c r="G11">
+        <v>2.28</v>
+      </c>
+      <c r="H11">
+        <v>3.4</v>
+      </c>
+      <c r="I11">
+        <v>3.45</v>
+      </c>
+      <c r="J11">
+        <v>3.65</v>
+      </c>
+      <c r="K11">
+        <v>3.75</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
+        <v>4.3</v>
+      </c>
+      <c r="O11">
+        <v>1.29</v>
+      </c>
+      <c r="P11">
+        <v>2.1</v>
+      </c>
+      <c r="Q11">
+        <v>1.86</v>
+      </c>
+      <c r="R11">
+        <v>1.42</v>
+      </c>
+      <c r="S11">
+        <v>3.15</v>
+      </c>
+      <c r="T11">
+        <v>1.72</v>
+      </c>
+      <c r="U11">
+        <v>2.3</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>17.5</v>
+      </c>
+      <c r="Y11">
+        <v>14.5</v>
+      </c>
+      <c r="Z11">
+        <v>25</v>
+      </c>
+      <c r="AA11">
+        <v>75</v>
+      </c>
+      <c r="AB11">
+        <v>11.5</v>
+      </c>
+      <c r="AC11">
+        <v>8.4</v>
+      </c>
+      <c r="AD11">
+        <v>14.5</v>
+      </c>
+      <c r="AE11">
+        <v>44</v>
+      </c>
+      <c r="AF11">
+        <v>15.5</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>19.5</v>
+      </c>
+      <c r="AI11">
+        <v>55</v>
+      </c>
+      <c r="AJ11">
+        <v>36</v>
+      </c>
+      <c r="AK11">
+        <v>24</v>
+      </c>
+      <c r="AL11">
+        <v>42</v>
+      </c>
+      <c r="AM11">
+        <v>95</v>
+      </c>
+      <c r="AN11">
+        <v>16</v>
+      </c>
+      <c r="AO11">
+        <v>38</v>
+      </c>
+      <c r="AP11">
+        <v>14.5</v>
+      </c>
+      <c r="AQ11">
+        <v>12.5</v>
+      </c>
+      <c r="AR11">
+        <v>22</v>
+      </c>
+      <c r="AS11">
+        <v>8.6</v>
+      </c>
+      <c r="AT11">
+        <v>10</v>
+      </c>
+      <c r="AU11">
+        <v>7.4</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>8.6</v>
+      </c>
+      <c r="AX11">
+        <v>13.5</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>15</v>
+      </c>
+      <c r="BA11">
+        <v>30</v>
+      </c>
+      <c r="BB11">
+        <v>24</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>25</v>
+      </c>
+      <c r="BE11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11">
+        <v>13.5</v>
+      </c>
+      <c r="BG11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH11">
+        <v>3.65</v>
+      </c>
+      <c r="BI11">
+        <v>3.35</v>
+      </c>
+      <c r="BJ11">
+        <v>11</v>
+      </c>
+      <c r="BK11">
+        <v>8</v>
+      </c>
+      <c r="BL11">
+        <v>130</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>6.2</v>
+      </c>
+      <c r="BO11">
+        <v>4.7</v>
+      </c>
+      <c r="BP11">
+        <v>19</v>
+      </c>
+      <c r="BQ11">
+        <v>13.5</v>
+      </c>
+      <c r="BR11">
+        <v>34</v>
+      </c>
+      <c r="BS11">
+        <v>19.5</v>
+      </c>
+      <c r="BT11">
+        <v>8</v>
+      </c>
+      <c r="BU11">
+        <v>6</v>
+      </c>
+      <c r="BV11">
+        <v>32</v>
+      </c>
+      <c r="BW11">
+        <v>18.5</v>
+      </c>
+      <c r="BX11">
+        <v>44</v>
+      </c>
+      <c r="BY11">
+        <v>25</v>
+      </c>
+      <c r="BZ11">
+        <v>28</v>
+      </c>
+      <c r="CA11">
+        <v>16</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12">
+        <v>1.79</v>
+      </c>
+      <c r="G12">
+        <v>1.81</v>
+      </c>
+      <c r="H12">
+        <v>5.3</v>
+      </c>
+      <c r="I12">
+        <v>5.5</v>
+      </c>
+      <c r="J12">
+        <v>3.85</v>
+      </c>
+      <c r="K12">
+        <v>3.9</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.89</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1.93</v>
+      </c>
+      <c r="U12">
+        <v>1.96</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>14.5</v>
+      </c>
+      <c r="Y12">
+        <v>20</v>
+      </c>
+      <c r="Z12">
+        <v>42</v>
+      </c>
+      <c r="AA12">
+        <v>170</v>
+      </c>
+      <c r="AB12">
+        <v>8.4</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>21</v>
+      </c>
+      <c r="AE12">
+        <v>100</v>
+      </c>
+      <c r="AF12">
+        <v>10.5</v>
+      </c>
+      <c r="AG12">
+        <v>10.5</v>
+      </c>
+      <c r="AH12">
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <v>100</v>
+      </c>
+      <c r="AJ12">
+        <v>21</v>
+      </c>
+      <c r="AK12">
+        <v>20</v>
+      </c>
+      <c r="AL12">
+        <v>50</v>
+      </c>
+      <c r="AM12">
+        <v>150</v>
+      </c>
+      <c r="AN12">
+        <v>14.5</v>
+      </c>
+      <c r="AO12">
+        <v>120</v>
+      </c>
+      <c r="AP12">
+        <v>12</v>
+      </c>
+      <c r="AQ12">
+        <v>15.5</v>
+      </c>
+      <c r="AR12">
+        <v>34</v>
+      </c>
+      <c r="AS12">
+        <v>9.6</v>
+      </c>
+      <c r="AT12">
+        <v>7.6</v>
+      </c>
+      <c r="AU12">
+        <v>7.8</v>
+      </c>
+      <c r="AV12">
+        <v>18.5</v>
+      </c>
+      <c r="AW12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB12">
+        <v>16</v>
+      </c>
+      <c r="BC12">
+        <v>17</v>
+      </c>
+      <c r="BD12">
+        <v>8.4</v>
+      </c>
+      <c r="BE12">
+        <v>9.6</v>
+      </c>
+      <c r="BF12">
+        <v>10</v>
+      </c>
+      <c r="BG12">
+        <v>9.4</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13">
+        <v>7.4</v>
+      </c>
+      <c r="G13">
+        <v>7.6</v>
+      </c>
+      <c r="H13">
+        <v>1.48</v>
+      </c>
+      <c r="I13">
+        <v>1.5</v>
+      </c>
+      <c r="J13">
+        <v>5.1</v>
+      </c>
+      <c r="K13">
+        <v>5.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
+        <v>5.9</v>
+      </c>
+      <c r="O13">
+        <v>1.17</v>
+      </c>
+      <c r="P13">
+        <v>2.76</v>
+      </c>
+      <c r="Q13">
+        <v>1.53</v>
+      </c>
+      <c r="R13">
+        <v>1.7</v>
+      </c>
+      <c r="S13">
+        <v>2.3</v>
+      </c>
+      <c r="T13">
+        <v>1.69</v>
+      </c>
+      <c r="U13">
+        <v>2.36</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>29</v>
+      </c>
+      <c r="Y13">
+        <v>12.5</v>
+      </c>
+      <c r="Z13">
+        <v>11.5</v>
+      </c>
+      <c r="AA13">
+        <v>15</v>
+      </c>
+      <c r="AB13">
+        <v>38</v>
+      </c>
+      <c r="AC13">
+        <v>12</v>
+      </c>
+      <c r="AD13">
+        <v>10</v>
+      </c>
+      <c r="AE13">
+        <v>14.5</v>
+      </c>
+      <c r="AF13">
+        <v>75</v>
+      </c>
+      <c r="AG13">
+        <v>29</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>27</v>
+      </c>
+      <c r="AJ13">
+        <v>210</v>
+      </c>
+      <c r="AK13">
+        <v>95</v>
+      </c>
+      <c r="AL13">
+        <v>70</v>
+      </c>
+      <c r="AM13">
+        <v>80</v>
+      </c>
+      <c r="AN13">
+        <v>80</v>
+      </c>
+      <c r="AO13">
+        <v>5.3</v>
+      </c>
+      <c r="AP13">
+        <v>23</v>
+      </c>
+      <c r="AQ13">
+        <v>10.5</v>
+      </c>
+      <c r="AR13">
+        <v>10</v>
+      </c>
+      <c r="AS13">
+        <v>13</v>
+      </c>
+      <c r="AT13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU13">
+        <v>10</v>
+      </c>
+      <c r="AV13">
+        <v>9</v>
+      </c>
+      <c r="AW13">
+        <v>12.5</v>
+      </c>
+      <c r="AX13">
+        <v>11.5</v>
+      </c>
+      <c r="AY13">
+        <v>23</v>
+      </c>
+      <c r="AZ13">
+        <v>17</v>
+      </c>
+      <c r="BA13">
+        <v>23</v>
+      </c>
+      <c r="BB13">
+        <v>12.5</v>
+      </c>
+      <c r="BC13">
+        <v>12</v>
+      </c>
+      <c r="BD13">
+        <v>11.5</v>
+      </c>
+      <c r="BE13">
+        <v>12</v>
+      </c>
+      <c r="BF13">
+        <v>11.5</v>
+      </c>
+      <c r="BG13">
+        <v>4.9</v>
+      </c>
+      <c r="BH13">
+        <v>4.7</v>
+      </c>
+      <c r="BI13">
+        <v>4.2</v>
+      </c>
+      <c r="BJ13">
+        <v>9.6</v>
+      </c>
+      <c r="BK13">
+        <v>8.4</v>
+      </c>
+      <c r="BL13">
+        <v>95</v>
+      </c>
+      <c r="BM13">
         <v>65</v>
       </c>
-      <c r="BN10">
+      <c r="BN13">
         <v>10.5</v>
       </c>
-      <c r="BO10">
+      <c r="BO13">
         <v>9.199999999999999</v>
       </c>
-      <c r="BP10">
+      <c r="BP13">
+        <v>50</v>
+      </c>
+      <c r="BQ13">
+        <v>36</v>
+      </c>
+      <c r="BR13">
         <v>48</v>
       </c>
-      <c r="BQ10">
+      <c r="BS13">
         <v>34</v>
       </c>
-      <c r="BR10">
-        <v>46</v>
-      </c>
-      <c r="BS10">
-        <v>32</v>
-      </c>
-      <c r="BT10">
+      <c r="BT13">
         <v>4.4</v>
       </c>
-      <c r="BU10">
+      <c r="BU13">
         <v>4</v>
       </c>
-      <c r="BV10">
+      <c r="BV13">
         <v>9</v>
       </c>
-      <c r="BW10">
-        <v>8</v>
-      </c>
-      <c r="BX10">
+      <c r="BW13">
+        <v>7.8</v>
+      </c>
+      <c r="BX13">
         <v>20</v>
       </c>
-      <c r="BY10">
+      <c r="BY13">
         <v>14.5</v>
       </c>
-      <c r="BZ10">
-        <v>0</v>
-      </c>
-      <c r="CA10">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="s">
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
         <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14">
+        <v>1.04</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.01</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.12</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>UEFA Nations League</t>
   </si>
   <si>
@@ -283,6 +286,9 @@
     <t>02:00:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -304,6 +310,9 @@
     <t>Costa Rica</t>
   </si>
   <si>
+    <t>Pohronie</t>
+  </si>
+  <si>
     <t>Armenia</t>
   </si>
   <si>
@@ -343,6 +352,9 @@
     <t>Curacao</t>
   </si>
   <si>
+    <t>Inter Bratislava</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
@@ -370,7 +382,7 @@
     <t>Guadeloupe</t>
   </si>
   <si>
-    <t>2026-09-23 10:07:11</t>
+    <t>2026-09-23 12:21:57</t>
   </si>
 </sst>
 </file>
@@ -702,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -952,178 +964,178 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="G2">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Z2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
+        <v>22</v>
+      </c>
+      <c r="AK2">
         <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
+        <v>210</v>
+      </c>
+      <c r="AN2">
+        <v>17</v>
+      </c>
+      <c r="AO2">
         <v>190</v>
       </c>
-      <c r="AN2">
-        <v>19</v>
-      </c>
-      <c r="AO2">
-        <v>160</v>
-      </c>
       <c r="AP2">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
+        <v>14.5</v>
+      </c>
+      <c r="AR2">
         <v>4</v>
       </c>
-      <c r="AR2">
-        <v>4.8</v>
-      </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT2">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AX2">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BB2">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF2">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1186,7 +1198,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1194,58 +1206,58 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H3">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="I3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>110</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
         <v>1.34</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
         <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1254,28 +1266,28 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="X3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
         <v>75</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
         <v>36</v>
@@ -1284,10 +1296,10 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>34</v>
@@ -1296,76 +1308,76 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3">
-        <v>2.18</v>
+        <v>4.9</v>
       </c>
       <c r="AR3">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS3">
-        <v>2.38</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>1.92</v>
+        <v>3.55</v>
       </c>
       <c r="AU3">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="AV3">
-        <v>2.22</v>
+        <v>5.3</v>
       </c>
       <c r="AW3">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="AY3">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="AZ3">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
       <c r="BA3">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="BC3">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="BD3">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE3">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="BG3">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1428,7 +1440,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1436,22 +1448,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
         <v>4.3</v>
@@ -1460,52 +1472,52 @@
         <v>4.7</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.02</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="U4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1514,46 +1526,46 @@
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
+        <v>18.5</v>
+      </c>
+      <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>22</v>
+      </c>
+      <c r="AK4">
         <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>25</v>
-      </c>
-      <c r="AK4">
-        <v>23</v>
       </c>
       <c r="AL4">
         <v>38</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP4">
         <v>15</v>
@@ -1562,22 +1574,22 @@
         <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4">
         <v>7</v>
       </c>
       <c r="AT4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
         <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1586,10 +1598,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1598,13 +1610,13 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
         <v>7</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
         <v>6.6</v>
@@ -1670,7 +1682,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1678,178 +1690,178 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F5">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF5">
+        <v>10.5</v>
+      </c>
+      <c r="AG5">
         <v>11</v>
       </c>
-      <c r="AG5">
-        <v>12.5</v>
-      </c>
       <c r="AH5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5">
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO5">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AP5">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="AS5">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AU5">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY5">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BC5">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1873,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -1912,7 +1924,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1920,306 +1932,306 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F6">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="G6">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="H6">
-        <v>5.2</v>
+        <v>2.68</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>2.68</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="G7">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2228,240 +2240,240 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA7">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF7">
         <v>11</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO7">
         <v>110</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
+        <v>18.5</v>
+      </c>
+      <c r="AW7">
+        <v>9.6</v>
+      </c>
+      <c r="AX7">
+        <v>9.4</v>
+      </c>
+      <c r="AY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>9.6</v>
+      </c>
+      <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
         <v>16.5</v>
       </c>
-      <c r="AW7">
+      <c r="BD7">
         <v>8.6</v>
       </c>
-      <c r="AX7">
-        <v>9.6</v>
-      </c>
-      <c r="AY7">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7">
-        <v>18</v>
-      </c>
-      <c r="BA7">
-        <v>8.6</v>
-      </c>
-      <c r="BB7">
-        <v>18</v>
-      </c>
-      <c r="BC7">
-        <v>18</v>
-      </c>
-      <c r="BD7">
-        <v>32</v>
-      </c>
       <c r="BE7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH7">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BI7">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN7">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS7">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BU7">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BV7">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BW7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="G8">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="R8">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>2.64</v>
+        <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2470,240 +2482,240 @@
         <v>0</v>
       </c>
       <c r="X8">
+        <v>13.5</v>
+      </c>
+      <c r="Y8">
+        <v>15.5</v>
+      </c>
+      <c r="Z8">
+        <v>46</v>
+      </c>
+      <c r="AA8">
+        <v>150</v>
+      </c>
+      <c r="AB8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8">
+        <v>8.6</v>
+      </c>
+      <c r="AD8">
+        <v>23</v>
+      </c>
+      <c r="AE8">
+        <v>80</v>
+      </c>
+      <c r="AF8">
+        <v>11</v>
+      </c>
+      <c r="AG8">
+        <v>11</v>
+      </c>
+      <c r="AH8">
+        <v>24</v>
+      </c>
+      <c r="AI8">
+        <v>80</v>
+      </c>
+      <c r="AJ8">
         <v>22</v>
       </c>
-      <c r="Y8">
-        <v>32</v>
-      </c>
-      <c r="Z8">
-        <v>70</v>
-      </c>
-      <c r="AA8">
-        <v>210</v>
-      </c>
-      <c r="AB8">
-        <v>10.5</v>
-      </c>
-      <c r="AC8">
-        <v>11</v>
-      </c>
-      <c r="AD8">
-        <v>26</v>
-      </c>
-      <c r="AE8">
-        <v>100</v>
-      </c>
-      <c r="AF8">
-        <v>10.5</v>
-      </c>
-      <c r="AG8">
-        <v>10.5</v>
-      </c>
-      <c r="AH8">
-        <v>21</v>
-      </c>
-      <c r="AI8">
-        <v>90</v>
-      </c>
-      <c r="AJ8">
-        <v>15</v>
-      </c>
       <c r="AK8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AO8">
         <v>110</v>
       </c>
       <c r="AP8">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AS8">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AU8">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AW8">
+        <v>8.6</v>
+      </c>
+      <c r="AX8">
+        <v>9.6</v>
+      </c>
+      <c r="AY8">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8">
+        <v>18</v>
+      </c>
+      <c r="BA8">
+        <v>8.6</v>
+      </c>
+      <c r="BB8">
+        <v>18</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
+        <v>32</v>
+      </c>
+      <c r="BE8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8">
+        <v>12</v>
+      </c>
+      <c r="BG8">
+        <v>9</v>
+      </c>
+      <c r="BH8">
+        <v>3.25</v>
+      </c>
+      <c r="BI8">
+        <v>2.96</v>
+      </c>
+      <c r="BJ8">
         <v>10.5</v>
-      </c>
-      <c r="AX8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>18.5</v>
-      </c>
-      <c r="BA8">
-        <v>10</v>
-      </c>
-      <c r="BB8">
-        <v>13</v>
-      </c>
-      <c r="BC8">
-        <v>13</v>
-      </c>
-      <c r="BD8">
-        <v>8.6</v>
-      </c>
-      <c r="BE8">
-        <v>10.5</v>
-      </c>
-      <c r="BF8">
-        <v>5.8</v>
-      </c>
-      <c r="BG8">
-        <v>10.5</v>
-      </c>
-      <c r="BH8">
-        <v>4.1</v>
-      </c>
-      <c r="BI8">
-        <v>3.75</v>
-      </c>
-      <c r="BJ8">
-        <v>12</v>
       </c>
       <c r="BK8">
         <v>9</v>
       </c>
       <c r="BL8">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BT8">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BU8">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BV8">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="BW8">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BX8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY8">
         <v>38</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="CB8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I9">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="S9">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="T9">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="U9">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2712,76 +2724,76 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Y9">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Z9">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AA9">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE9">
         <v>100</v>
       </c>
       <c r="AF9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>90</v>
+      </c>
+      <c r="AJ9">
+        <v>15</v>
+      </c>
+      <c r="AK9">
+        <v>15</v>
+      </c>
+      <c r="AL9">
+        <v>36</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
+        <v>6.6</v>
+      </c>
+      <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>19.5</v>
+      </c>
+      <c r="AQ9">
+        <v>20</v>
+      </c>
+      <c r="AR9">
         <v>10</v>
-      </c>
-      <c r="AH9">
-        <v>23</v>
-      </c>
-      <c r="AI9">
-        <v>95</v>
-      </c>
-      <c r="AJ9">
-        <v>20</v>
-      </c>
-      <c r="AK9">
-        <v>21</v>
-      </c>
-      <c r="AL9">
-        <v>48</v>
-      </c>
-      <c r="AM9">
-        <v>150</v>
-      </c>
-      <c r="AN9">
-        <v>12</v>
-      </c>
-      <c r="AO9">
-        <v>130</v>
-      </c>
-      <c r="AP9">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9">
-        <v>15</v>
-      </c>
-      <c r="AR9">
-        <v>9.199999999999999</v>
       </c>
       <c r="AS9">
         <v>11</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9">
         <v>19</v>
@@ -2790,7 +2802,7 @@
         <v>10.5</v>
       </c>
       <c r="AX9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
         <v>9.199999999999999</v>
@@ -2802,37 +2814,37 @@
         <v>10</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BD9">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BE9">
         <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BG9">
         <v>10.5</v>
       </c>
       <c r="BH9">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
@@ -2844,350 +2856,350 @@
         <v>3.85</v>
       </c>
       <c r="BP9">
+        <v>11</v>
+      </c>
+      <c r="BQ9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR9">
+        <v>25</v>
+      </c>
+      <c r="BS9">
+        <v>16.5</v>
+      </c>
+      <c r="BT9">
         <v>12</v>
       </c>
-      <c r="BQ9">
-        <v>10</v>
-      </c>
-      <c r="BR9">
-        <v>29</v>
-      </c>
-      <c r="BS9">
-        <v>21</v>
-      </c>
-      <c r="BT9">
+      <c r="BU9">
         <v>9</v>
       </c>
-      <c r="BU9">
-        <v>8</v>
-      </c>
       <c r="BV9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BZ9">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="CA9">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>1.73</v>
+      </c>
+      <c r="G10">
+        <v>1.76</v>
+      </c>
+      <c r="H10">
+        <v>5.4</v>
+      </c>
+      <c r="I10">
+        <v>5.8</v>
+      </c>
+      <c r="J10">
+        <v>3.95</v>
+      </c>
+      <c r="K10">
+        <v>4.1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>3.65</v>
+      </c>
+      <c r="O10">
+        <v>1.34</v>
+      </c>
+      <c r="P10">
+        <v>1.91</v>
+      </c>
+      <c r="Q10">
+        <v>2.06</v>
+      </c>
+      <c r="R10">
+        <v>1.34</v>
+      </c>
+      <c r="S10">
+        <v>3.6</v>
+      </c>
+      <c r="T10">
+        <v>1.94</v>
+      </c>
+      <c r="U10">
+        <v>1.95</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>15.5</v>
+      </c>
+      <c r="Y10">
+        <v>18</v>
+      </c>
+      <c r="Z10">
+        <v>50</v>
+      </c>
+      <c r="AA10">
+        <v>180</v>
+      </c>
+      <c r="AB10">
+        <v>8</v>
+      </c>
+      <c r="AC10">
+        <v>9</v>
+      </c>
+      <c r="AD10">
+        <v>23</v>
+      </c>
+      <c r="AE10">
         <v>100</v>
       </c>
-      <c r="E10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10">
-        <v>2.38</v>
-      </c>
-      <c r="G10">
-        <v>2.44</v>
-      </c>
-      <c r="H10">
-        <v>3.4</v>
-      </c>
-      <c r="I10">
-        <v>3.5</v>
-      </c>
-      <c r="J10">
-        <v>3.4</v>
-      </c>
-      <c r="K10">
-        <v>3.45</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>1.09</v>
-      </c>
-      <c r="N10">
-        <v>3.3</v>
-      </c>
-      <c r="O10">
-        <v>1.39</v>
-      </c>
-      <c r="P10">
-        <v>1.74</v>
-      </c>
-      <c r="Q10">
-        <v>2.2</v>
-      </c>
-      <c r="R10">
-        <v>1.29</v>
-      </c>
-      <c r="S10">
-        <v>3.9</v>
-      </c>
-      <c r="T10">
-        <v>1.89</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>12.5</v>
-      </c>
-      <c r="Y10">
-        <v>12</v>
-      </c>
-      <c r="Z10">
-        <v>23</v>
-      </c>
-      <c r="AA10">
-        <v>75</v>
-      </c>
-      <c r="AB10">
-        <v>9.4</v>
-      </c>
-      <c r="AC10">
-        <v>7.4</v>
-      </c>
-      <c r="AD10">
-        <v>15.5</v>
-      </c>
-      <c r="AE10">
-        <v>55</v>
-      </c>
       <c r="AF10">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>23</v>
       </c>
       <c r="AI10">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ10">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM10">
+        <v>150</v>
+      </c>
+      <c r="AN10">
+        <v>12</v>
+      </c>
+      <c r="AO10">
         <v>130</v>
       </c>
-      <c r="AN10">
-        <v>22</v>
-      </c>
-      <c r="AO10">
-        <v>60</v>
-      </c>
       <c r="AP10">
+        <v>12.5</v>
+      </c>
+      <c r="AQ10">
+        <v>15</v>
+      </c>
+      <c r="AR10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS10">
+        <v>11</v>
+      </c>
+      <c r="AT10">
+        <v>7</v>
+      </c>
+      <c r="AU10">
+        <v>7.8</v>
+      </c>
+      <c r="AV10">
+        <v>19</v>
+      </c>
+      <c r="AW10">
         <v>10.5</v>
       </c>
-      <c r="AQ10">
+      <c r="AX10">
+        <v>8.6</v>
+      </c>
+      <c r="AY10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10">
+        <v>19</v>
+      </c>
+      <c r="BA10">
         <v>10</v>
       </c>
-      <c r="AR10">
-        <v>19</v>
-      </c>
-      <c r="AS10">
-        <v>9.4</v>
-      </c>
-      <c r="AT10">
-        <v>8</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
-      <c r="AV10">
-        <v>13</v>
-      </c>
-      <c r="AW10">
-        <v>9</v>
-      </c>
-      <c r="AX10">
-        <v>13</v>
-      </c>
-      <c r="AY10">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10">
+      <c r="BB10">
         <v>16.5</v>
       </c>
-      <c r="BA10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB10">
-        <v>8.4</v>
-      </c>
       <c r="BC10">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD10">
         <v>9</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BG10">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BI10">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10">
+        <v>11</v>
+      </c>
+      <c r="BK10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>4.3</v>
+      </c>
+      <c r="BO10">
+        <v>3.85</v>
+      </c>
+      <c r="BP10">
         <v>12</v>
       </c>
-      <c r="BK10">
-        <v>8.4</v>
-      </c>
-      <c r="BL10">
-        <v>160</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>6.2</v>
-      </c>
-      <c r="BO10">
-        <v>4.5</v>
-      </c>
-      <c r="BP10">
-        <v>22</v>
-      </c>
       <c r="BQ10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BR10">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS10">
+        <v>21</v>
+      </c>
+      <c r="BT10">
+        <v>9</v>
+      </c>
+      <c r="BU10">
+        <v>8</v>
+      </c>
+      <c r="BV10">
+        <v>55</v>
+      </c>
+      <c r="BW10">
+        <v>36</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>42</v>
+      </c>
+      <c r="BZ10">
         <v>24</v>
       </c>
-      <c r="BT10">
-        <v>7.8</v>
-      </c>
-      <c r="BU10">
-        <v>5.7</v>
-      </c>
-      <c r="BV10">
-        <v>36</v>
-      </c>
-      <c r="BW10">
-        <v>20</v>
-      </c>
-      <c r="BX10">
-        <v>50</v>
-      </c>
-      <c r="BY10">
-        <v>30</v>
-      </c>
-      <c r="BZ10">
-        <v>38</v>
-      </c>
       <c r="CA10">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="G11">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
         <v>3.45</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
+        <v>1.38</v>
+      </c>
+      <c r="P11">
+        <v>1.74</v>
+      </c>
+      <c r="Q11">
+        <v>2.18</v>
+      </c>
+      <c r="R11">
         <v>1.29</v>
       </c>
-      <c r="P11">
-        <v>2.1</v>
-      </c>
-      <c r="Q11">
-        <v>1.86</v>
-      </c>
-      <c r="R11">
-        <v>1.42</v>
-      </c>
       <c r="S11">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3196,127 +3208,127 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA11">
         <v>75</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC11">
+        <v>7.4</v>
+      </c>
+      <c r="AD11">
+        <v>15.5</v>
+      </c>
+      <c r="AE11">
+        <v>55</v>
+      </c>
+      <c r="AF11">
+        <v>15</v>
+      </c>
+      <c r="AG11">
+        <v>12</v>
+      </c>
+      <c r="AH11">
+        <v>23</v>
+      </c>
+      <c r="AI11">
+        <v>65</v>
+      </c>
+      <c r="AJ11">
+        <v>42</v>
+      </c>
+      <c r="AK11">
+        <v>36</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>130</v>
+      </c>
+      <c r="AN11">
+        <v>26</v>
+      </c>
+      <c r="AO11">
+        <v>60</v>
+      </c>
+      <c r="AP11">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11">
+        <v>10</v>
+      </c>
+      <c r="AR11">
+        <v>20</v>
+      </c>
+      <c r="AS11">
         <v>8.4</v>
       </c>
-      <c r="AD11">
-        <v>14.5</v>
-      </c>
-      <c r="AE11">
-        <v>44</v>
-      </c>
-      <c r="AF11">
-        <v>15.5</v>
-      </c>
-      <c r="AG11">
-        <v>11.5</v>
-      </c>
-      <c r="AH11">
-        <v>19.5</v>
-      </c>
-      <c r="AI11">
-        <v>55</v>
-      </c>
-      <c r="AJ11">
-        <v>36</v>
-      </c>
-      <c r="AK11">
-        <v>24</v>
-      </c>
-      <c r="AL11">
-        <v>42</v>
-      </c>
-      <c r="AM11">
-        <v>95</v>
-      </c>
-      <c r="AN11">
-        <v>16</v>
-      </c>
-      <c r="AO11">
-        <v>38</v>
-      </c>
-      <c r="AP11">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11">
-        <v>12.5</v>
-      </c>
-      <c r="AR11">
-        <v>22</v>
-      </c>
-      <c r="AS11">
-        <v>8.6</v>
-      </c>
       <c r="AT11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AX11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BB11">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF11">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BG11">
         <v>8.199999999999999</v>
       </c>
       <c r="BH11">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BI11">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL11">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
@@ -3325,111 +3337,111 @@
         <v>6.2</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BT11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW11">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BZ11">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="CA11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="CB11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F12">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="H12">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="U12">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3438,408 +3450,408 @@
         <v>0</v>
       </c>
       <c r="X12">
+        <v>17.5</v>
+      </c>
+      <c r="Y12">
         <v>14.5</v>
       </c>
-      <c r="Y12">
-        <v>20</v>
-      </c>
       <c r="Z12">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB12">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC12">
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AF12">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL12">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AN12">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO12">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="AP12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ12">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR12">
+        <v>18.5</v>
+      </c>
+      <c r="AS12">
+        <v>8.6</v>
+      </c>
+      <c r="AT12">
+        <v>10</v>
+      </c>
+      <c r="AU12">
+        <v>7.4</v>
+      </c>
+      <c r="AV12">
+        <v>13</v>
+      </c>
+      <c r="AW12">
+        <v>8.6</v>
+      </c>
+      <c r="AX12">
+        <v>13.5</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>15</v>
+      </c>
+      <c r="BA12">
+        <v>30</v>
+      </c>
+      <c r="BB12">
+        <v>24</v>
+      </c>
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
+        <v>8.6</v>
+      </c>
+      <c r="BE12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF12">
+        <v>13.5</v>
+      </c>
+      <c r="BG12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12">
+        <v>3.65</v>
+      </c>
+      <c r="BI12">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12">
+        <v>11</v>
+      </c>
+      <c r="BK12">
+        <v>8</v>
+      </c>
+      <c r="BL12">
+        <v>130</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>6.2</v>
+      </c>
+      <c r="BO12">
+        <v>4.7</v>
+      </c>
+      <c r="BP12">
+        <v>19</v>
+      </c>
+      <c r="BQ12">
+        <v>11.5</v>
+      </c>
+      <c r="BR12">
         <v>34</v>
       </c>
-      <c r="AS12">
-        <v>9.6</v>
-      </c>
-      <c r="AT12">
-        <v>7.6</v>
-      </c>
-      <c r="AU12">
-        <v>7.8</v>
-      </c>
-      <c r="AV12">
+      <c r="BS12">
+        <v>19.5</v>
+      </c>
+      <c r="BT12">
+        <v>8</v>
+      </c>
+      <c r="BU12">
+        <v>6</v>
+      </c>
+      <c r="BV12">
+        <v>32</v>
+      </c>
+      <c r="BW12">
         <v>18.5</v>
       </c>
-      <c r="AW12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY12">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12">
-        <v>19</v>
-      </c>
-      <c r="BA12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB12">
+      <c r="BX12">
+        <v>44</v>
+      </c>
+      <c r="BY12">
+        <v>25</v>
+      </c>
+      <c r="BZ12">
+        <v>28</v>
+      </c>
+      <c r="CA12">
         <v>16</v>
       </c>
-      <c r="BC12">
-        <v>17</v>
-      </c>
-      <c r="BD12">
-        <v>8.4</v>
-      </c>
-      <c r="BE12">
-        <v>9.6</v>
-      </c>
-      <c r="BF12">
-        <v>10</v>
-      </c>
-      <c r="BG12">
-        <v>9.4</v>
-      </c>
-      <c r="BH12">
-        <v>0</v>
-      </c>
-      <c r="BI12">
-        <v>0</v>
-      </c>
-      <c r="BJ12">
-        <v>0</v>
-      </c>
-      <c r="BK12">
-        <v>0</v>
-      </c>
-      <c r="BL12">
-        <v>0</v>
-      </c>
-      <c r="BM12">
-        <v>0</v>
-      </c>
-      <c r="BN12">
-        <v>0</v>
-      </c>
-      <c r="BO12">
-        <v>0</v>
-      </c>
-      <c r="BP12">
-        <v>0</v>
-      </c>
-      <c r="BQ12">
-        <v>0</v>
-      </c>
-      <c r="BR12">
-        <v>0</v>
-      </c>
-      <c r="BS12">
-        <v>0</v>
-      </c>
-      <c r="BT12">
-        <v>0</v>
-      </c>
-      <c r="BU12">
-        <v>0</v>
-      </c>
-      <c r="BV12">
-        <v>0</v>
-      </c>
-      <c r="BW12">
-        <v>0</v>
-      </c>
-      <c r="BX12">
-        <v>0</v>
-      </c>
-      <c r="BY12">
-        <v>0</v>
-      </c>
-      <c r="BZ12">
-        <v>0</v>
-      </c>
-      <c r="CA12">
-        <v>0</v>
-      </c>
       <c r="CB12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F13">
-        <v>7.4</v>
+        <v>1.79</v>
       </c>
       <c r="G13">
+        <v>1.82</v>
+      </c>
+      <c r="H13">
+        <v>5.2</v>
+      </c>
+      <c r="I13">
+        <v>5.5</v>
+      </c>
+      <c r="J13">
+        <v>3.85</v>
+      </c>
+      <c r="K13">
+        <v>3.9</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.87</v>
+      </c>
+      <c r="Q13">
+        <v>2.04</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1.93</v>
+      </c>
+      <c r="U13">
+        <v>1.96</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>14.5</v>
+      </c>
+      <c r="Y13">
+        <v>20</v>
+      </c>
+      <c r="Z13">
+        <v>42</v>
+      </c>
+      <c r="AA13">
+        <v>170</v>
+      </c>
+      <c r="AB13">
+        <v>8.4</v>
+      </c>
+      <c r="AC13">
+        <v>8.4</v>
+      </c>
+      <c r="AD13">
+        <v>21</v>
+      </c>
+      <c r="AE13">
+        <v>95</v>
+      </c>
+      <c r="AF13">
+        <v>10.5</v>
+      </c>
+      <c r="AG13">
+        <v>10.5</v>
+      </c>
+      <c r="AH13">
+        <v>22</v>
+      </c>
+      <c r="AI13">
+        <v>95</v>
+      </c>
+      <c r="AJ13">
+        <v>21</v>
+      </c>
+      <c r="AK13">
+        <v>20</v>
+      </c>
+      <c r="AL13">
+        <v>50</v>
+      </c>
+      <c r="AM13">
+        <v>150</v>
+      </c>
+      <c r="AN13">
+        <v>12.5</v>
+      </c>
+      <c r="AO13">
+        <v>120</v>
+      </c>
+      <c r="AP13">
+        <v>12</v>
+      </c>
+      <c r="AQ13">
+        <v>15</v>
+      </c>
+      <c r="AR13">
+        <v>34</v>
+      </c>
+      <c r="AS13">
+        <v>10.5</v>
+      </c>
+      <c r="AT13">
         <v>7.6</v>
       </c>
-      <c r="H13">
-        <v>1.48</v>
-      </c>
-      <c r="I13">
-        <v>1.5</v>
-      </c>
-      <c r="J13">
-        <v>5.1</v>
-      </c>
-      <c r="K13">
-        <v>5.2</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>1.03</v>
-      </c>
-      <c r="N13">
-        <v>5.9</v>
-      </c>
-      <c r="O13">
-        <v>1.17</v>
-      </c>
-      <c r="P13">
-        <v>2.76</v>
-      </c>
-      <c r="Q13">
-        <v>1.53</v>
-      </c>
-      <c r="R13">
-        <v>1.7</v>
-      </c>
-      <c r="S13">
-        <v>2.3</v>
-      </c>
-      <c r="T13">
-        <v>1.69</v>
-      </c>
-      <c r="U13">
-        <v>2.36</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>29</v>
-      </c>
-      <c r="Y13">
-        <v>12.5</v>
-      </c>
-      <c r="Z13">
-        <v>11.5</v>
-      </c>
-      <c r="AA13">
-        <v>15</v>
-      </c>
-      <c r="AB13">
-        <v>38</v>
-      </c>
-      <c r="AC13">
-        <v>12</v>
-      </c>
-      <c r="AD13">
+      <c r="AU13">
+        <v>7.6</v>
+      </c>
+      <c r="AV13">
+        <v>18.5</v>
+      </c>
+      <c r="AW13">
+        <v>27</v>
+      </c>
+      <c r="AX13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY13">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13">
+        <v>19</v>
+      </c>
+      <c r="BA13">
         <v>10</v>
       </c>
-      <c r="AE13">
-        <v>14.5</v>
-      </c>
-      <c r="AF13">
-        <v>75</v>
-      </c>
-      <c r="AG13">
-        <v>29</v>
-      </c>
-      <c r="AH13">
-        <v>20</v>
-      </c>
-      <c r="AI13">
-        <v>27</v>
-      </c>
-      <c r="AJ13">
-        <v>210</v>
-      </c>
-      <c r="AK13">
-        <v>95</v>
-      </c>
-      <c r="AL13">
-        <v>70</v>
-      </c>
-      <c r="AM13">
-        <v>80</v>
-      </c>
-      <c r="AN13">
-        <v>80</v>
-      </c>
-      <c r="AO13">
-        <v>5.3</v>
-      </c>
-      <c r="AP13">
-        <v>23</v>
-      </c>
-      <c r="AQ13">
+      <c r="BB13">
+        <v>16.5</v>
+      </c>
+      <c r="BC13">
+        <v>17.5</v>
+      </c>
+      <c r="BD13">
+        <v>34</v>
+      </c>
+      <c r="BE13">
         <v>10.5</v>
       </c>
-      <c r="AR13">
+      <c r="BF13">
         <v>10</v>
       </c>
-      <c r="AS13">
-        <v>13</v>
-      </c>
-      <c r="AT13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU13">
+      <c r="BG13">
         <v>10</v>
       </c>
-      <c r="AV13">
-        <v>9</v>
-      </c>
-      <c r="AW13">
-        <v>12.5</v>
-      </c>
-      <c r="AX13">
-        <v>11.5</v>
-      </c>
-      <c r="AY13">
-        <v>23</v>
-      </c>
-      <c r="AZ13">
-        <v>17</v>
-      </c>
-      <c r="BA13">
-        <v>23</v>
-      </c>
-      <c r="BB13">
-        <v>12.5</v>
-      </c>
-      <c r="BC13">
-        <v>12</v>
-      </c>
-      <c r="BD13">
-        <v>11.5</v>
-      </c>
-      <c r="BE13">
-        <v>12</v>
-      </c>
-      <c r="BF13">
-        <v>11.5</v>
-      </c>
-      <c r="BG13">
-        <v>4.9</v>
-      </c>
       <c r="BH13">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL13">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BM13">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BO13">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BP13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BQ13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BR13">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BT13">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BU13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BY13">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3848,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3856,241 +3868,483 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>7.6</v>
+      </c>
+      <c r="G14">
+        <v>7.8</v>
+      </c>
+      <c r="H14">
+        <v>1.48</v>
+      </c>
+      <c r="I14">
+        <v>1.49</v>
+      </c>
+      <c r="J14">
+        <v>5.1</v>
+      </c>
+      <c r="K14">
+        <v>5.2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>5.9</v>
+      </c>
+      <c r="O14">
+        <v>1.17</v>
+      </c>
+      <c r="P14">
+        <v>2.76</v>
+      </c>
+      <c r="Q14">
+        <v>1.53</v>
+      </c>
+      <c r="R14">
+        <v>1.7</v>
+      </c>
+      <c r="S14">
+        <v>2.32</v>
+      </c>
+      <c r="T14">
+        <v>1.69</v>
+      </c>
+      <c r="U14">
+        <v>2.36</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>29</v>
+      </c>
+      <c r="Y14">
+        <v>12.5</v>
+      </c>
+      <c r="Z14">
+        <v>11.5</v>
+      </c>
+      <c r="AA14">
+        <v>15</v>
+      </c>
+      <c r="AB14">
+        <v>38</v>
+      </c>
+      <c r="AC14">
+        <v>12</v>
+      </c>
+      <c r="AD14">
+        <v>10</v>
+      </c>
+      <c r="AE14">
+        <v>14.5</v>
+      </c>
+      <c r="AF14">
+        <v>75</v>
+      </c>
+      <c r="AG14">
+        <v>29</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>27</v>
+      </c>
+      <c r="AJ14">
+        <v>210</v>
+      </c>
+      <c r="AK14">
+        <v>95</v>
+      </c>
+      <c r="AL14">
+        <v>70</v>
+      </c>
+      <c r="AM14">
+        <v>80</v>
+      </c>
+      <c r="AN14">
+        <v>80</v>
+      </c>
+      <c r="AO14">
+        <v>5.3</v>
+      </c>
+      <c r="AP14">
+        <v>24</v>
+      </c>
+      <c r="AQ14">
+        <v>10.5</v>
+      </c>
+      <c r="AR14">
+        <v>10</v>
+      </c>
+      <c r="AS14">
+        <v>13</v>
+      </c>
+      <c r="AT14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU14">
+        <v>10</v>
+      </c>
+      <c r="AV14">
+        <v>9</v>
+      </c>
+      <c r="AW14">
+        <v>12.5</v>
+      </c>
+      <c r="AX14">
+        <v>11</v>
+      </c>
+      <c r="AY14">
+        <v>23</v>
+      </c>
+      <c r="AZ14">
+        <v>17</v>
+      </c>
+      <c r="BA14">
+        <v>19</v>
+      </c>
+      <c r="BB14">
+        <v>12.5</v>
+      </c>
+      <c r="BC14">
+        <v>11.5</v>
+      </c>
+      <c r="BD14">
+        <v>11</v>
+      </c>
+      <c r="BE14">
+        <v>12</v>
+      </c>
+      <c r="BF14">
+        <v>11.5</v>
+      </c>
+      <c r="BG14">
+        <v>4.9</v>
+      </c>
+      <c r="BH14">
+        <v>4.7</v>
+      </c>
+      <c r="BI14">
+        <v>4.2</v>
+      </c>
+      <c r="BJ14">
+        <v>9.6</v>
+      </c>
+      <c r="BK14">
+        <v>8.4</v>
+      </c>
+      <c r="BL14">
+        <v>95</v>
+      </c>
+      <c r="BM14">
+        <v>65</v>
+      </c>
+      <c r="BN14">
+        <v>10.5</v>
+      </c>
+      <c r="BO14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BP14">
+        <v>50</v>
+      </c>
+      <c r="BQ14">
+        <v>34</v>
+      </c>
+      <c r="BR14">
+        <v>48</v>
+      </c>
+      <c r="BS14">
+        <v>34</v>
+      </c>
+      <c r="BT14">
+        <v>4.4</v>
+      </c>
+      <c r="BU14">
+        <v>4</v>
+      </c>
+      <c r="BV14">
+        <v>9</v>
+      </c>
+      <c r="BW14">
+        <v>7.8</v>
+      </c>
+      <c r="BX14">
+        <v>20</v>
+      </c>
+      <c r="BY14">
+        <v>14.5</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
         <v>84</v>
       </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14">
-        <v>1.04</v>
-      </c>
-      <c r="G14">
-        <v>1000</v>
-      </c>
-      <c r="H14">
-        <v>1.04</v>
-      </c>
-      <c r="I14">
-        <v>1000</v>
-      </c>
-      <c r="J14">
-        <v>1.01</v>
-      </c>
-      <c r="K14">
-        <v>1000</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15">
+        <v>1.1</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>1.1</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
         <v>1.12</v>
       </c>
-      <c r="Q14">
-        <v>1.01</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>0</v>
-      </c>
-      <c r="BC14">
-        <v>0</v>
-      </c>
-      <c r="BD14">
-        <v>0</v>
-      </c>
-      <c r="BE14">
-        <v>0</v>
-      </c>
-      <c r="BF14">
-        <v>0</v>
-      </c>
-      <c r="BG14">
-        <v>0</v>
-      </c>
-      <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <v>0</v>
-      </c>
-      <c r="BJ14">
-        <v>0</v>
-      </c>
-      <c r="BK14">
-        <v>0</v>
-      </c>
-      <c r="BL14">
-        <v>0</v>
-      </c>
-      <c r="BM14">
-        <v>0</v>
-      </c>
-      <c r="BN14">
-        <v>0</v>
-      </c>
-      <c r="BO14">
-        <v>0</v>
-      </c>
-      <c r="BP14">
-        <v>0</v>
-      </c>
-      <c r="BQ14">
-        <v>0</v>
-      </c>
-      <c r="BR14">
-        <v>0</v>
-      </c>
-      <c r="BS14">
-        <v>0</v>
-      </c>
-      <c r="BT14">
-        <v>0</v>
-      </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
-      <c r="BV14">
-        <v>0</v>
-      </c>
-      <c r="BW14">
-        <v>0</v>
-      </c>
-      <c r="BX14">
-        <v>0</v>
-      </c>
-      <c r="BY14">
-        <v>0</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>118</v>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.12</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="127">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>UEFA Nations League</t>
   </si>
   <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
     <t>CONCACAF Nations League B</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>18:45:00</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Georgia</t>
   </si>
   <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -361,6 +370,9 @@
     <t>Northern Ireland</t>
   </si>
   <si>
+    <t>IFK Stocksund</t>
+  </si>
+  <si>
     <t>Romania</t>
   </si>
   <si>
@@ -382,7 +394,7 @@
     <t>Guadeloupe</t>
   </si>
   <si>
-    <t>2026-09-23 12:21:57</t>
+    <t>2026-09-23 14:33:38</t>
   </si>
 </sst>
 </file>
@@ -714,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -964,22 +976,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F2">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
         <v>5.7</v>
@@ -988,10 +1000,10 @@
         <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1000,34 +1012,34 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1039,13 +1051,13 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB2">
         <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>29</v>
@@ -1066,19 +1078,19 @@
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>190</v>
@@ -1090,10 +1102,10 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AS2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1105,7 +1117,7 @@
         <v>20</v>
       </c>
       <c r="AW2">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX2">
         <v>8.199999999999999</v>
@@ -1117,25 +1129,25 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1198,7 +1210,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1206,28 +1218,28 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H3">
         <v>5.1</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1269,7 +1281,7 @@
         <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
         <v>13</v>
@@ -1284,7 +1296,7 @@
         <v>240</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
@@ -1293,7 +1305,7 @@
         <v>36</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF3">
         <v>9.800000000000001</v>
@@ -1302,13 +1314,13 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK3">
         <v>21</v>
@@ -1317,67 +1329,67 @@
         <v>48</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP3">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AU3">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX3">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AY3">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB3">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BC3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BD3">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF3">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1440,7 +1452,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1448,16 +1460,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F4">
         <v>1.86</v>
@@ -1469,10 +1481,10 @@
         <v>4.3</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1481,28 +1493,28 @@
         <v>1.02</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
         <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
         <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T4">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
         <v>2.2</v>
@@ -1514,22 +1526,22 @@
         <v>2.04</v>
       </c>
       <c r="X4">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA4">
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>19</v>
@@ -1556,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM4">
         <v>95</v>
@@ -1574,10 +1586,10 @@
         <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
@@ -1589,7 +1601,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1598,10 +1610,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1610,16 +1622,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1682,7 +1694,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1690,28 +1702,28 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H5">
         <v>5.2</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1720,7 +1732,7 @@
         <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1753,16 +1765,16 @@
         <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X5">
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AA5">
         <v>240</v>
@@ -1780,7 +1792,7 @@
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>11</v>
@@ -1789,10 +1801,10 @@
         <v>32</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1819,7 +1831,7 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -1831,7 +1843,7 @@
         <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5">
         <v>8.4</v>
@@ -1852,16 +1864,16 @@
         <v>18</v>
       </c>
       <c r="BD5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1885,7 +1897,7 @@
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -1924,7 +1936,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1932,16 +1944,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F6">
         <v>2.3</v>
@@ -1962,7 +1974,7 @@
         <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -2166,7 +2178,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2174,16 +2186,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>1.77</v>
@@ -2204,28 +2216,28 @@
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
         <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
         <v>1.92</v>
@@ -2234,16 +2246,16 @@
         <v>1.98</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X7">
         <v>15</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z7">
         <v>44</v>
@@ -2300,7 +2312,7 @@
         <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS7">
         <v>10</v>
@@ -2324,7 +2336,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA7">
         <v>9.6</v>
@@ -2336,7 +2348,7 @@
         <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE7">
         <v>10</v>
@@ -2345,70 +2357,70 @@
         <v>10</v>
       </c>
       <c r="BG7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2416,22 +2428,22 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G8">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -2440,13 +2452,13 @@
         <v>4.8</v>
       </c>
       <c r="J8">
+        <v>3.75</v>
+      </c>
+      <c r="K8">
         <v>3.8</v>
       </c>
-      <c r="K8">
-        <v>3.85</v>
-      </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2455,16 +2467,16 @@
         <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
         <v>2.08</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
         <v>3.85</v>
@@ -2473,46 +2485,46 @@
         <v>1.97</v>
       </c>
       <c r="U8">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8">
         <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA8">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB8">
         <v>8.199999999999999</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE8">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF8">
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8">
         <v>80</v>
@@ -2521,73 +2533,73 @@
         <v>22</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR8">
         <v>30</v>
       </c>
       <c r="AS8">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AT8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV8">
         <v>16.5</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="AX8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8">
         <v>9.4</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA8">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BB8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC8">
         <v>18</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
         <v>3.25</v>
@@ -2605,7 +2617,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
@@ -2650,249 +2662,249 @@
         <v>19</v>
       </c>
       <c r="CB8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F9">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="G9">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="H9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>130</v>
       </c>
       <c r="J9">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>5.1</v>
+        <v>2.66</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="S9">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X9">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2900,64 +2912,64 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F10">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="H10">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="U10">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2966,127 +2978,127 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Y10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Z10">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AA10">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE10">
         <v>100</v>
       </c>
       <c r="AF10">
+        <v>10.5</v>
+      </c>
+      <c r="AG10">
+        <v>10.5</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>90</v>
+      </c>
+      <c r="AJ10">
+        <v>15</v>
+      </c>
+      <c r="AK10">
+        <v>15</v>
+      </c>
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>6.6</v>
+      </c>
+      <c r="AO10">
+        <v>110</v>
+      </c>
+      <c r="AP10">
+        <v>19.5</v>
+      </c>
+      <c r="AQ10">
+        <v>23</v>
+      </c>
+      <c r="AR10">
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <v>11.5</v>
+      </c>
+      <c r="AT10">
+        <v>10</v>
+      </c>
+      <c r="AU10">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG10">
-        <v>10</v>
-      </c>
-      <c r="AH10">
+      <c r="AV10">
         <v>23</v>
-      </c>
-      <c r="AI10">
-        <v>95</v>
-      </c>
-      <c r="AJ10">
-        <v>20</v>
-      </c>
-      <c r="AK10">
-        <v>21</v>
-      </c>
-      <c r="AL10">
-        <v>48</v>
-      </c>
-      <c r="AM10">
-        <v>150</v>
-      </c>
-      <c r="AN10">
-        <v>12</v>
-      </c>
-      <c r="AO10">
-        <v>130</v>
-      </c>
-      <c r="AP10">
-        <v>12.5</v>
-      </c>
-      <c r="AQ10">
-        <v>15</v>
-      </c>
-      <c r="AR10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS10">
-        <v>11</v>
-      </c>
-      <c r="AT10">
-        <v>7</v>
-      </c>
-      <c r="AU10">
-        <v>7.8</v>
-      </c>
-      <c r="AV10">
-        <v>19</v>
       </c>
       <c r="AW10">
         <v>10.5</v>
       </c>
       <c r="AX10">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB10">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BD10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE10">
+        <v>11</v>
+      </c>
+      <c r="BF10">
+        <v>5.8</v>
+      </c>
+      <c r="BG10">
+        <v>11</v>
+      </c>
+      <c r="BH10">
+        <v>4.1</v>
+      </c>
+      <c r="BI10">
+        <v>3.75</v>
+      </c>
+      <c r="BJ10">
+        <v>12</v>
+      </c>
+      <c r="BK10">
         <v>9</v>
       </c>
-      <c r="BE10">
-        <v>10.5</v>
-      </c>
-      <c r="BF10">
-        <v>10</v>
-      </c>
-      <c r="BG10">
-        <v>10.5</v>
-      </c>
-      <c r="BH10">
-        <v>3.35</v>
-      </c>
-      <c r="BI10">
-        <v>3.1</v>
-      </c>
-      <c r="BJ10">
-        <v>11</v>
-      </c>
-      <c r="BK10">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
@@ -3098,43 +3110,43 @@
         <v>3.85</v>
       </c>
       <c r="BP10">
+        <v>11</v>
+      </c>
+      <c r="BQ10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR10">
+        <v>25</v>
+      </c>
+      <c r="BS10">
+        <v>16.5</v>
+      </c>
+      <c r="BT10">
         <v>12</v>
       </c>
-      <c r="BQ10">
-        <v>10</v>
-      </c>
-      <c r="BR10">
-        <v>29</v>
-      </c>
-      <c r="BS10">
-        <v>21</v>
-      </c>
-      <c r="BT10">
+      <c r="BU10">
         <v>9</v>
       </c>
-      <c r="BU10">
-        <v>8</v>
-      </c>
       <c r="BV10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY10">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BZ10">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="CA10">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3142,64 +3154,64 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F11">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="G11">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="I11">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3208,175 +3220,175 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Z11">
+        <v>50</v>
+      </c>
+      <c r="AA11">
+        <v>180</v>
+      </c>
+      <c r="AB11">
+        <v>8</v>
+      </c>
+      <c r="AC11">
+        <v>9</v>
+      </c>
+      <c r="AD11">
         <v>23</v>
       </c>
-      <c r="AA11">
-        <v>75</v>
-      </c>
-      <c r="AB11">
-        <v>9.4</v>
-      </c>
-      <c r="AC11">
-        <v>7.4</v>
-      </c>
-      <c r="AD11">
-        <v>15.5</v>
-      </c>
       <c r="AE11">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AF11">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH11">
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
+        <v>20</v>
+      </c>
+      <c r="AK11">
+        <v>21</v>
+      </c>
+      <c r="AL11">
+        <v>48</v>
+      </c>
+      <c r="AM11">
+        <v>140</v>
+      </c>
+      <c r="AN11">
+        <v>12</v>
+      </c>
+      <c r="AO11">
+        <v>120</v>
+      </c>
+      <c r="AP11">
+        <v>13</v>
+      </c>
+      <c r="AQ11">
+        <v>15</v>
+      </c>
+      <c r="AR11">
+        <v>9.4</v>
+      </c>
+      <c r="AS11">
+        <v>11</v>
+      </c>
+      <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>7.8</v>
+      </c>
+      <c r="AV11">
+        <v>19</v>
+      </c>
+      <c r="AW11">
+        <v>10.5</v>
+      </c>
+      <c r="AX11">
+        <v>8.6</v>
+      </c>
+      <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>19</v>
+      </c>
+      <c r="BA11">
+        <v>10.5</v>
+      </c>
+      <c r="BB11">
+        <v>16.5</v>
+      </c>
+      <c r="BC11">
+        <v>16.5</v>
+      </c>
+      <c r="BD11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE11">
+        <v>11</v>
+      </c>
+      <c r="BF11">
+        <v>10</v>
+      </c>
+      <c r="BG11">
+        <v>10.5</v>
+      </c>
+      <c r="BH11">
+        <v>3.35</v>
+      </c>
+      <c r="BI11">
+        <v>3.1</v>
+      </c>
+      <c r="BJ11">
+        <v>11</v>
+      </c>
+      <c r="BK11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>4.3</v>
+      </c>
+      <c r="BO11">
+        <v>3.85</v>
+      </c>
+      <c r="BP11">
+        <v>12</v>
+      </c>
+      <c r="BQ11">
+        <v>10</v>
+      </c>
+      <c r="BR11">
+        <v>29</v>
+      </c>
+      <c r="BS11">
+        <v>21</v>
+      </c>
+      <c r="BT11">
+        <v>9</v>
+      </c>
+      <c r="BU11">
+        <v>8</v>
+      </c>
+      <c r="BV11">
+        <v>55</v>
+      </c>
+      <c r="BW11">
+        <v>36</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
         <v>42</v>
       </c>
-      <c r="AK11">
-        <v>36</v>
-      </c>
-      <c r="AL11">
-        <v>55</v>
-      </c>
-      <c r="AM11">
-        <v>130</v>
-      </c>
-      <c r="AN11">
-        <v>26</v>
-      </c>
-      <c r="AO11">
-        <v>60</v>
-      </c>
-      <c r="AP11">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11">
-        <v>10</v>
-      </c>
-      <c r="AR11">
-        <v>20</v>
-      </c>
-      <c r="AS11">
-        <v>8.4</v>
-      </c>
-      <c r="AT11">
-        <v>8</v>
-      </c>
-      <c r="AU11">
-        <v>6.6</v>
-      </c>
-      <c r="AV11">
-        <v>13</v>
-      </c>
-      <c r="AW11">
-        <v>36</v>
-      </c>
-      <c r="AX11">
-        <v>13</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>16.5</v>
-      </c>
-      <c r="BA11">
-        <v>8.4</v>
-      </c>
-      <c r="BB11">
-        <v>8</v>
-      </c>
-      <c r="BC11">
-        <v>19.5</v>
-      </c>
-      <c r="BD11">
-        <v>36</v>
-      </c>
-      <c r="BE11">
-        <v>9</v>
-      </c>
-      <c r="BF11">
-        <v>18</v>
-      </c>
-      <c r="BG11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH11">
-        <v>3.25</v>
-      </c>
-      <c r="BI11">
-        <v>2.9</v>
-      </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>8.4</v>
-      </c>
-      <c r="BL11">
-        <v>160</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
-      </c>
-      <c r="BN11">
-        <v>6.2</v>
-      </c>
-      <c r="BO11">
-        <v>4.5</v>
-      </c>
-      <c r="BP11">
-        <v>22</v>
-      </c>
-      <c r="BQ11">
-        <v>15.5</v>
-      </c>
-      <c r="BR11">
-        <v>40</v>
-      </c>
-      <c r="BS11">
+      <c r="BZ11">
         <v>24</v>
       </c>
-      <c r="BT11">
-        <v>7.8</v>
-      </c>
-      <c r="BU11">
-        <v>5.7</v>
-      </c>
-      <c r="BV11">
-        <v>36</v>
-      </c>
-      <c r="BW11">
-        <v>20</v>
-      </c>
-      <c r="BX11">
-        <v>50</v>
-      </c>
-      <c r="BY11">
-        <v>30</v>
-      </c>
-      <c r="BZ11">
-        <v>38</v>
-      </c>
       <c r="CA11">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3384,64 +3396,64 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F12">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="G12">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I12">
         <v>3.45</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
+        <v>1.38</v>
+      </c>
+      <c r="P12">
+        <v>1.74</v>
+      </c>
+      <c r="Q12">
+        <v>2.18</v>
+      </c>
+      <c r="R12">
         <v>1.29</v>
       </c>
-      <c r="P12">
-        <v>2.1</v>
-      </c>
-      <c r="Q12">
-        <v>1.85</v>
-      </c>
-      <c r="R12">
-        <v>1.42</v>
-      </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="T12">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3450,127 +3462,127 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y12">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA12">
         <v>75</v>
       </c>
       <c r="AB12">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC12">
+        <v>7.4</v>
+      </c>
+      <c r="AD12">
+        <v>15.5</v>
+      </c>
+      <c r="AE12">
+        <v>55</v>
+      </c>
+      <c r="AF12">
+        <v>15</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>65</v>
+      </c>
+      <c r="AJ12">
+        <v>42</v>
+      </c>
+      <c r="AK12">
+        <v>36</v>
+      </c>
+      <c r="AL12">
+        <v>55</v>
+      </c>
+      <c r="AM12">
+        <v>130</v>
+      </c>
+      <c r="AN12">
+        <v>26</v>
+      </c>
+      <c r="AO12">
+        <v>60</v>
+      </c>
+      <c r="AP12">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12">
+        <v>10</v>
+      </c>
+      <c r="AR12">
+        <v>19.5</v>
+      </c>
+      <c r="AS12">
         <v>8.4</v>
       </c>
-      <c r="AD12">
-        <v>14.5</v>
-      </c>
-      <c r="AE12">
-        <v>44</v>
-      </c>
-      <c r="AF12">
-        <v>15.5</v>
-      </c>
-      <c r="AG12">
-        <v>11.5</v>
-      </c>
-      <c r="AH12">
-        <v>19.5</v>
-      </c>
-      <c r="AI12">
-        <v>55</v>
-      </c>
-      <c r="AJ12">
-        <v>36</v>
-      </c>
-      <c r="AK12">
-        <v>24</v>
-      </c>
-      <c r="AL12">
-        <v>42</v>
-      </c>
-      <c r="AM12">
-        <v>95</v>
-      </c>
-      <c r="AN12">
-        <v>16</v>
-      </c>
-      <c r="AO12">
-        <v>38</v>
-      </c>
-      <c r="AP12">
-        <v>15</v>
-      </c>
-      <c r="AQ12">
-        <v>13</v>
-      </c>
-      <c r="AR12">
-        <v>18.5</v>
-      </c>
-      <c r="AS12">
-        <v>8.6</v>
-      </c>
       <c r="AT12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU12">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV12">
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AX12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BC12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD12">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE12">
         <v>8.800000000000001</v>
       </c>
       <c r="BF12">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BG12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH12">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK12">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BL12">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="BM12">
         <v>1.01</v>
@@ -3579,46 +3591,46 @@
         <v>6.2</v>
       </c>
       <c r="BO12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BQ12">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR12">
+        <v>42</v>
+      </c>
+      <c r="BS12">
+        <v>24</v>
+      </c>
+      <c r="BT12">
+        <v>7.8</v>
+      </c>
+      <c r="BU12">
+        <v>5.7</v>
+      </c>
+      <c r="BV12">
         <v>34</v>
       </c>
-      <c r="BS12">
-        <v>19.5</v>
-      </c>
-      <c r="BT12">
-        <v>8</v>
-      </c>
-      <c r="BU12">
-        <v>6</v>
-      </c>
-      <c r="BV12">
-        <v>32</v>
-      </c>
       <c r="BW12">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BX12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BZ12">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="CA12">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="CB12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3626,64 +3638,64 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F13">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="G13">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="H13">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T13">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="U13">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3692,175 +3704,175 @@
         <v>0</v>
       </c>
       <c r="X13">
+        <v>17.5</v>
+      </c>
+      <c r="Y13">
         <v>14.5</v>
       </c>
-      <c r="Y13">
-        <v>20</v>
-      </c>
       <c r="Z13">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA13">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB13">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
+        <v>44</v>
+      </c>
+      <c r="AF13">
+        <v>15.5</v>
+      </c>
+      <c r="AG13">
+        <v>11.5</v>
+      </c>
+      <c r="AH13">
+        <v>19.5</v>
+      </c>
+      <c r="AI13">
+        <v>55</v>
+      </c>
+      <c r="AJ13">
+        <v>36</v>
+      </c>
+      <c r="AK13">
+        <v>24</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
         <v>95</v>
       </c>
-      <c r="AF13">
-        <v>10.5</v>
-      </c>
-      <c r="AG13">
-        <v>10.5</v>
-      </c>
-      <c r="AH13">
-        <v>22</v>
-      </c>
-      <c r="AI13">
-        <v>95</v>
-      </c>
-      <c r="AJ13">
-        <v>21</v>
-      </c>
-      <c r="AK13">
+      <c r="AN13">
+        <v>16</v>
+      </c>
+      <c r="AO13">
+        <v>38</v>
+      </c>
+      <c r="AP13">
+        <v>15</v>
+      </c>
+      <c r="AQ13">
+        <v>13</v>
+      </c>
+      <c r="AR13">
+        <v>18.5</v>
+      </c>
+      <c r="AS13">
+        <v>8.6</v>
+      </c>
+      <c r="AT13">
+        <v>10</v>
+      </c>
+      <c r="AU13">
+        <v>7.4</v>
+      </c>
+      <c r="AV13">
+        <v>13</v>
+      </c>
+      <c r="AW13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX13">
+        <v>13.5</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>15</v>
+      </c>
+      <c r="BA13">
+        <v>30</v>
+      </c>
+      <c r="BB13">
         <v>20</v>
-      </c>
-      <c r="AL13">
-        <v>50</v>
-      </c>
-      <c r="AM13">
-        <v>150</v>
-      </c>
-      <c r="AN13">
-        <v>12.5</v>
-      </c>
-      <c r="AO13">
-        <v>120</v>
-      </c>
-      <c r="AP13">
-        <v>12</v>
-      </c>
-      <c r="AQ13">
-        <v>15</v>
-      </c>
-      <c r="AR13">
-        <v>34</v>
-      </c>
-      <c r="AS13">
-        <v>10.5</v>
-      </c>
-      <c r="AT13">
-        <v>7.6</v>
-      </c>
-      <c r="AU13">
-        <v>7.6</v>
-      </c>
-      <c r="AV13">
-        <v>18.5</v>
-      </c>
-      <c r="AW13">
-        <v>27</v>
-      </c>
-      <c r="AX13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY13">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13">
-        <v>19</v>
-      </c>
-      <c r="BA13">
-        <v>10</v>
-      </c>
-      <c r="BB13">
-        <v>16.5</v>
       </c>
       <c r="BC13">
         <v>17.5</v>
       </c>
       <c r="BD13">
+        <v>8.6</v>
+      </c>
+      <c r="BE13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF13">
+        <v>13.5</v>
+      </c>
+      <c r="BG13">
+        <v>8.4</v>
+      </c>
+      <c r="BH13">
+        <v>3.65</v>
+      </c>
+      <c r="BI13">
+        <v>3.35</v>
+      </c>
+      <c r="BJ13">
+        <v>11</v>
+      </c>
+      <c r="BK13">
+        <v>8</v>
+      </c>
+      <c r="BL13">
+        <v>130</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>6.2</v>
+      </c>
+      <c r="BO13">
+        <v>4.7</v>
+      </c>
+      <c r="BP13">
+        <v>19</v>
+      </c>
+      <c r="BQ13">
+        <v>13.5</v>
+      </c>
+      <c r="BR13">
         <v>34</v>
       </c>
-      <c r="BE13">
-        <v>10.5</v>
-      </c>
-      <c r="BF13">
-        <v>10</v>
-      </c>
-      <c r="BG13">
-        <v>10</v>
-      </c>
-      <c r="BH13">
-        <v>0</v>
-      </c>
-      <c r="BI13">
-        <v>0</v>
-      </c>
-      <c r="BJ13">
-        <v>0</v>
-      </c>
-      <c r="BK13">
-        <v>0</v>
-      </c>
-      <c r="BL13">
-        <v>0</v>
-      </c>
-      <c r="BM13">
-        <v>0</v>
-      </c>
-      <c r="BN13">
-        <v>0</v>
-      </c>
-      <c r="BO13">
-        <v>0</v>
-      </c>
-      <c r="BP13">
-        <v>0</v>
-      </c>
-      <c r="BQ13">
-        <v>0</v>
-      </c>
-      <c r="BR13">
-        <v>0</v>
-      </c>
       <c r="BS13">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3868,232 +3880,232 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14">
+        <v>1.79</v>
+      </c>
+      <c r="G14">
+        <v>1.82</v>
+      </c>
+      <c r="H14">
+        <v>5.2</v>
+      </c>
+      <c r="I14">
+        <v>5.5</v>
+      </c>
+      <c r="J14">
+        <v>3.85</v>
+      </c>
+      <c r="K14">
+        <v>3.9</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.87</v>
+      </c>
+      <c r="Q14">
+        <v>2.04</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1.93</v>
+      </c>
+      <c r="U14">
+        <v>1.96</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>14.5</v>
+      </c>
+      <c r="Y14">
+        <v>20</v>
+      </c>
+      <c r="Z14">
+        <v>42</v>
+      </c>
+      <c r="AA14">
+        <v>170</v>
+      </c>
+      <c r="AB14">
+        <v>8.4</v>
+      </c>
+      <c r="AC14">
+        <v>8.4</v>
+      </c>
+      <c r="AD14">
+        <v>21</v>
+      </c>
+      <c r="AE14">
+        <v>95</v>
+      </c>
+      <c r="AF14">
+        <v>10.5</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>22</v>
+      </c>
+      <c r="AI14">
+        <v>95</v>
+      </c>
+      <c r="AJ14">
+        <v>21</v>
+      </c>
+      <c r="AK14">
+        <v>20</v>
+      </c>
+      <c r="AL14">
+        <v>50</v>
+      </c>
+      <c r="AM14">
+        <v>150</v>
+      </c>
+      <c r="AN14">
+        <v>12.5</v>
+      </c>
+      <c r="AO14">
         <v>120</v>
       </c>
-      <c r="F14">
+      <c r="AP14">
+        <v>12</v>
+      </c>
+      <c r="AQ14">
+        <v>15</v>
+      </c>
+      <c r="AR14">
+        <v>34</v>
+      </c>
+      <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
         <v>7.6</v>
       </c>
-      <c r="G14">
-        <v>7.8</v>
-      </c>
-      <c r="H14">
-        <v>1.48</v>
-      </c>
-      <c r="I14">
-        <v>1.49</v>
-      </c>
-      <c r="J14">
-        <v>5.1</v>
-      </c>
-      <c r="K14">
-        <v>5.2</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>1.03</v>
-      </c>
-      <c r="N14">
-        <v>5.9</v>
-      </c>
-      <c r="O14">
-        <v>1.17</v>
-      </c>
-      <c r="P14">
-        <v>2.76</v>
-      </c>
-      <c r="Q14">
-        <v>1.53</v>
-      </c>
-      <c r="R14">
-        <v>1.7</v>
-      </c>
-      <c r="S14">
-        <v>2.32</v>
-      </c>
-      <c r="T14">
-        <v>1.69</v>
-      </c>
-      <c r="U14">
-        <v>2.36</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>29</v>
-      </c>
-      <c r="Y14">
-        <v>12.5</v>
-      </c>
-      <c r="Z14">
-        <v>11.5</v>
-      </c>
-      <c r="AA14">
-        <v>15</v>
-      </c>
-      <c r="AB14">
-        <v>38</v>
-      </c>
-      <c r="AC14">
-        <v>12</v>
-      </c>
-      <c r="AD14">
+      <c r="AU14">
+        <v>7.6</v>
+      </c>
+      <c r="AV14">
+        <v>18.5</v>
+      </c>
+      <c r="AW14">
+        <v>27</v>
+      </c>
+      <c r="AX14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>19</v>
+      </c>
+      <c r="BA14">
         <v>10</v>
       </c>
-      <c r="AE14">
-        <v>14.5</v>
-      </c>
-      <c r="AF14">
-        <v>75</v>
-      </c>
-      <c r="AG14">
-        <v>29</v>
-      </c>
-      <c r="AH14">
-        <v>20</v>
-      </c>
-      <c r="AI14">
-        <v>27</v>
-      </c>
-      <c r="AJ14">
-        <v>210</v>
-      </c>
-      <c r="AK14">
-        <v>95</v>
-      </c>
-      <c r="AL14">
-        <v>70</v>
-      </c>
-      <c r="AM14">
-        <v>80</v>
-      </c>
-      <c r="AN14">
-        <v>80</v>
-      </c>
-      <c r="AO14">
-        <v>5.3</v>
-      </c>
-      <c r="AP14">
-        <v>24</v>
-      </c>
-      <c r="AQ14">
+      <c r="BB14">
+        <v>16.5</v>
+      </c>
+      <c r="BC14">
+        <v>17.5</v>
+      </c>
+      <c r="BD14">
+        <v>34</v>
+      </c>
+      <c r="BE14">
         <v>10.5</v>
       </c>
-      <c r="AR14">
+      <c r="BF14">
         <v>10</v>
       </c>
-      <c r="AS14">
-        <v>13</v>
-      </c>
-      <c r="AT14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU14">
+      <c r="BG14">
         <v>10</v>
       </c>
-      <c r="AV14">
-        <v>9</v>
-      </c>
-      <c r="AW14">
-        <v>12.5</v>
-      </c>
-      <c r="AX14">
-        <v>11</v>
-      </c>
-      <c r="AY14">
-        <v>23</v>
-      </c>
-      <c r="AZ14">
-        <v>17</v>
-      </c>
-      <c r="BA14">
-        <v>19</v>
-      </c>
-      <c r="BB14">
-        <v>12.5</v>
-      </c>
-      <c r="BC14">
-        <v>11.5</v>
-      </c>
-      <c r="BD14">
-        <v>11</v>
-      </c>
-      <c r="BE14">
-        <v>12</v>
-      </c>
-      <c r="BF14">
-        <v>11.5</v>
-      </c>
-      <c r="BG14">
-        <v>4.9</v>
-      </c>
       <c r="BH14">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4102,249 +4114,491 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15">
+        <v>7.8</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>1.46</v>
+      </c>
+      <c r="I15">
+        <v>1.48</v>
+      </c>
+      <c r="J15">
+        <v>5.1</v>
+      </c>
+      <c r="K15">
+        <v>5.2</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>6.2</v>
+      </c>
+      <c r="O15">
+        <v>1.17</v>
+      </c>
+      <c r="P15">
+        <v>2.78</v>
+      </c>
+      <c r="Q15">
+        <v>1.53</v>
+      </c>
+      <c r="R15">
+        <v>1.7</v>
+      </c>
+      <c r="S15">
+        <v>2.3</v>
+      </c>
+      <c r="T15">
+        <v>1.69</v>
+      </c>
+      <c r="U15">
+        <v>2.32</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>29</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>11.5</v>
+      </c>
+      <c r="AA15">
+        <v>14.5</v>
+      </c>
+      <c r="AB15">
+        <v>38</v>
+      </c>
+      <c r="AC15">
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <v>10</v>
+      </c>
+      <c r="AE15">
+        <v>14.5</v>
+      </c>
+      <c r="AF15">
+        <v>75</v>
+      </c>
+      <c r="AG15">
+        <v>29</v>
+      </c>
+      <c r="AH15">
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <v>27</v>
+      </c>
+      <c r="AJ15">
+        <v>210</v>
+      </c>
+      <c r="AK15">
+        <v>95</v>
+      </c>
+      <c r="AL15">
+        <v>70</v>
+      </c>
+      <c r="AM15">
+        <v>80</v>
+      </c>
+      <c r="AN15">
+        <v>80</v>
+      </c>
+      <c r="AO15">
+        <v>5.2</v>
+      </c>
+      <c r="AP15">
+        <v>24</v>
+      </c>
+      <c r="AQ15">
+        <v>10.5</v>
+      </c>
+      <c r="AR15">
+        <v>10</v>
+      </c>
+      <c r="AS15">
+        <v>13</v>
+      </c>
+      <c r="AT15">
+        <v>10.5</v>
+      </c>
+      <c r="AU15">
+        <v>10.5</v>
+      </c>
+      <c r="AV15">
+        <v>9</v>
+      </c>
+      <c r="AW15">
+        <v>12.5</v>
+      </c>
+      <c r="AX15">
+        <v>12.5</v>
+      </c>
+      <c r="AY15">
+        <v>23</v>
+      </c>
+      <c r="AZ15">
+        <v>17.5</v>
+      </c>
+      <c r="BA15">
+        <v>22</v>
+      </c>
+      <c r="BB15">
+        <v>12.5</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
+        <v>11.5</v>
+      </c>
+      <c r="BE15">
+        <v>12.5</v>
+      </c>
+      <c r="BF15">
+        <v>11.5</v>
+      </c>
+      <c r="BG15">
+        <v>4.7</v>
+      </c>
+      <c r="BH15">
+        <v>4.7</v>
+      </c>
+      <c r="BI15">
+        <v>4.2</v>
+      </c>
+      <c r="BJ15">
+        <v>9.6</v>
+      </c>
+      <c r="BK15">
+        <v>8.6</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>65</v>
+      </c>
+      <c r="BN15">
+        <v>10.5</v>
+      </c>
+      <c r="BO15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BP15">
+        <v>50</v>
+      </c>
+      <c r="BQ15">
+        <v>34</v>
+      </c>
+      <c r="BR15">
+        <v>46</v>
+      </c>
+      <c r="BS15">
+        <v>34</v>
+      </c>
+      <c r="BT15">
+        <v>4.4</v>
+      </c>
+      <c r="BU15">
+        <v>4</v>
+      </c>
+      <c r="BV15">
+        <v>9</v>
+      </c>
+      <c r="BW15">
+        <v>7.8</v>
+      </c>
+      <c r="BX15">
+        <v>20</v>
+      </c>
+      <c r="BY15">
+        <v>14.5</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>85</v>
       </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15">
-        <v>1.1</v>
-      </c>
-      <c r="G15">
-        <v>1000</v>
-      </c>
-      <c r="H15">
-        <v>1.1</v>
-      </c>
-      <c r="I15">
-        <v>1000</v>
-      </c>
-      <c r="J15">
-        <v>1.12</v>
-      </c>
-      <c r="K15">
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16">
+        <v>2.18</v>
+      </c>
+      <c r="G16">
+        <v>3.55</v>
+      </c>
+      <c r="H16">
+        <v>2.58</v>
+      </c>
+      <c r="I16">
+        <v>3.7</v>
+      </c>
+      <c r="J16">
+        <v>3.05</v>
+      </c>
+      <c r="K16">
         <v>950</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1.12</v>
-      </c>
-      <c r="Q15">
-        <v>1.01</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-      <c r="BD15">
-        <v>0</v>
-      </c>
-      <c r="BE15">
-        <v>0</v>
-      </c>
-      <c r="BF15">
-        <v>0</v>
-      </c>
-      <c r="BG15">
-        <v>0</v>
-      </c>
-      <c r="BH15">
-        <v>0</v>
-      </c>
-      <c r="BI15">
-        <v>0</v>
-      </c>
-      <c r="BJ15">
-        <v>0</v>
-      </c>
-      <c r="BK15">
-        <v>0</v>
-      </c>
-      <c r="BL15">
-        <v>0</v>
-      </c>
-      <c r="BM15">
-        <v>0</v>
-      </c>
-      <c r="BN15">
-        <v>0</v>
-      </c>
-      <c r="BO15">
-        <v>0</v>
-      </c>
-      <c r="BP15">
-        <v>0</v>
-      </c>
-      <c r="BQ15">
-        <v>0</v>
-      </c>
-      <c r="BR15">
-        <v>0</v>
-      </c>
-      <c r="BS15">
-        <v>0</v>
-      </c>
-      <c r="BT15">
-        <v>0</v>
-      </c>
-      <c r="BU15">
-        <v>0</v>
-      </c>
-      <c r="BV15">
-        <v>0</v>
-      </c>
-      <c r="BW15">
-        <v>0</v>
-      </c>
-      <c r="BX15">
-        <v>0</v>
-      </c>
-      <c r="BY15">
-        <v>0</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>122</v>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.57</v>
+      </c>
+      <c r="Q16">
+        <v>2.14</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="159">
   <si>
     <t>League</t>
   </si>
@@ -271,9 +271,27 @@
     <t>Swedish Division 1</t>
   </si>
   <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Scottish Championship</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
     <t>CONCACAF Nations League B</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
     <t>2026-09-25</t>
   </si>
   <si>
@@ -298,12 +316,18 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>18:45:00</t>
   </si>
   <si>
     <t>19:00:00</t>
   </si>
   <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
     <t>Dominican Republic</t>
   </si>
   <si>
@@ -328,27 +352,63 @@
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
     <t>Sweden</t>
   </si>
   <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Montenegro</t>
-  </si>
-  <si>
-    <t>Türkiye</t>
+    <t>Inverness CT</t>
+  </si>
+  <si>
+    <t>Galway Utd</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Raith</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Ayr</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
   </si>
   <si>
     <t>Bermuda</t>
   </si>
   <si>
+    <t>Sportivo Luqueno</t>
+  </si>
+  <si>
     <t>Nicaragua</t>
   </si>
   <si>
@@ -373,28 +433,64 @@
     <t>IFK Stocksund</t>
   </si>
   <si>
+    <t>Albacete</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
     <t>Romania</t>
   </si>
   <si>
-    <t>Bosnia</t>
-  </si>
-  <si>
-    <t>Ukraine</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Morton</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Queens Park</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
+    <t>Almere City</t>
   </si>
   <si>
     <t>Guadeloupe</t>
   </si>
   <si>
-    <t>2026-09-23 14:33:38</t>
+    <t>Guarani (Par)</t>
+  </si>
+  <si>
+    <t>2026-09-23 16:46:10</t>
   </si>
 </sst>
 </file>
@@ -726,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -976,178 +1072,178 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F2">
+        <v>1.56</v>
+      </c>
+      <c r="G2">
+        <v>1.65</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.4</v>
+      </c>
+      <c r="O2">
+        <v>1.34</v>
+      </c>
+      <c r="P2">
+        <v>1.82</v>
+      </c>
+      <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
+        <v>1.31</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>1.91</v>
+      </c>
+      <c r="U2">
         <v>1.64</v>
       </c>
-      <c r="G2">
-        <v>1.76</v>
-      </c>
-      <c r="H2">
-        <v>5.7</v>
-      </c>
-      <c r="I2">
-        <v>6.8</v>
-      </c>
-      <c r="J2">
-        <v>3.75</v>
-      </c>
-      <c r="K2">
-        <v>4.2</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.25</v>
-      </c>
-      <c r="O2">
-        <v>1.38</v>
-      </c>
-      <c r="P2">
-        <v>1.77</v>
-      </c>
-      <c r="Q2">
-        <v>2.08</v>
-      </c>
-      <c r="R2">
-        <v>1.29</v>
-      </c>
-      <c r="S2">
-        <v>3.9</v>
-      </c>
-      <c r="T2">
-        <v>2.04</v>
-      </c>
-      <c r="U2">
-        <v>1.68</v>
-      </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y2">
         <v>21</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>29</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AO2">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS2">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
+        <v>8.6</v>
+      </c>
+      <c r="AV2">
+        <v>6.2</v>
+      </c>
+      <c r="AW2">
         <v>7.6</v>
       </c>
-      <c r="AV2">
-        <v>20</v>
-      </c>
-      <c r="AW2">
-        <v>4.7</v>
-      </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BG2">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1210,7 +1306,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1218,58 +1314,58 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="F3">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="G3">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="H3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1278,91 +1374,91 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="X3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA3">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>40</v>
+      </c>
+      <c r="AE3">
+        <v>140</v>
+      </c>
+      <c r="AF3">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>36</v>
-      </c>
-      <c r="AE3">
-        <v>130</v>
-      </c>
-      <c r="AF3">
-        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>130</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
         <v>200</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX3">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>8.6</v>
@@ -1371,31 +1467,31 @@
         <v>20</v>
       </c>
       <c r="BA3">
+        <v>8.4</v>
+      </c>
+      <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>7.4</v>
+      </c>
+      <c r="BE3">
         <v>7.8</v>
       </c>
-      <c r="BB3">
-        <v>14.5</v>
-      </c>
-      <c r="BC3">
-        <v>17</v>
-      </c>
-      <c r="BD3">
-        <v>7.2</v>
-      </c>
-      <c r="BE3">
+      <c r="BF3">
         <v>8</v>
       </c>
-      <c r="BF3">
-        <v>9.6</v>
-      </c>
       <c r="BG3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1452,7 +1548,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1460,31 +1556,31 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
         <v>4.3</v>
       </c>
       <c r="I4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1496,34 +1592,34 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
         <v>2.92</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1565,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="AK4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4">
         <v>34</v>
@@ -1589,7 +1685,7 @@
         <v>7.4</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
@@ -1601,7 +1697,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1613,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1694,7 +1790,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1702,28 +1798,28 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="F5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1744,7 +1840,7 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
@@ -1762,19 +1858,19 @@
         <v>1.79</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA5">
         <v>240</v>
@@ -1792,13 +1888,13 @@
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>130</v>
@@ -1822,7 +1918,7 @@
         <v>240</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
         <v>14.5</v>
@@ -1831,7 +1927,7 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -1843,10 +1939,10 @@
         <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -1855,25 +1951,25 @@
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC5">
         <v>18</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1936,7 +2032,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1944,31 +2040,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F6">
         <v>2.3</v>
       </c>
       <c r="G6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H6">
         <v>2.68</v>
       </c>
       <c r="I6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J6">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2004,10 +2100,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2178,7 +2274,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2186,34 +2282,34 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F7">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="H7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
+        <v>3.85</v>
+      </c>
+      <c r="K7">
         <v>3.9</v>
-      </c>
-      <c r="K7">
-        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2228,7 +2324,7 @@
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
         <v>1.98</v>
@@ -2237,46 +2333,46 @@
         <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U7">
         <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
         <v>18</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2285,40 +2381,40 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
         <v>12</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP7">
         <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR7">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AS7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU7">
         <v>7.8</v>
@@ -2327,37 +2423,37 @@
         <v>18.5</v>
       </c>
       <c r="AW7">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AX7">
         <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
         <v>19</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BB7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD7">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2420,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="CB7" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2428,19 +2524,19 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
         <v>1.91</v>
@@ -2458,7 +2554,7 @@
         <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2470,7 +2566,7 @@
         <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
         <v>2.08</v>
@@ -2482,7 +2578,7 @@
         <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
         <v>1.97</v>
@@ -2539,10 +2635,10 @@
         <v>46</v>
       </c>
       <c r="AM8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO8">
         <v>90</v>
@@ -2587,7 +2683,7 @@
         <v>19</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
         <v>34</v>
@@ -2662,7 +2758,7 @@
         <v>19</v>
       </c>
       <c r="CB8" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2670,16 +2766,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F9">
         <v>1.17</v>
@@ -2904,45 +3000,45 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G10">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10">
         <v>6.6</v>
       </c>
-      <c r="I10">
-        <v>6.8</v>
-      </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
         <v>4.9</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -2954,55 +3050,55 @@
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
         <v>2.64</v>
       </c>
       <c r="T10">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y10">
         <v>27</v>
       </c>
       <c r="Z10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA10">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -3011,142 +3107,142 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
         <v>15</v>
       </c>
       <c r="AK10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR10">
+        <v>40</v>
+      </c>
+      <c r="AS10">
         <v>10</v>
       </c>
-      <c r="AS10">
-        <v>11.5</v>
-      </c>
       <c r="AT10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW10">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY10">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD10">
+        <v>21</v>
+      </c>
+      <c r="BE10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF10">
+        <v>6</v>
+      </c>
+      <c r="BG10">
+        <v>9.6</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>3.45</v>
+      </c>
+      <c r="BJ10">
+        <v>12.5</v>
+      </c>
+      <c r="BK10">
+        <v>7.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>21</v>
+      </c>
+      <c r="BN10">
+        <v>5</v>
+      </c>
+      <c r="BO10">
+        <v>3.55</v>
+      </c>
+      <c r="BP10">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10">
+        <v>7</v>
+      </c>
+      <c r="BR10">
+        <v>30</v>
+      </c>
+      <c r="BS10">
+        <v>13.5</v>
+      </c>
+      <c r="BT10">
+        <v>12.5</v>
+      </c>
+      <c r="BU10">
+        <v>7.4</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>21</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>21</v>
+      </c>
+      <c r="BZ10">
+        <v>20</v>
+      </c>
+      <c r="CA10">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE10">
-        <v>11</v>
-      </c>
-      <c r="BF10">
-        <v>5.8</v>
-      </c>
-      <c r="BG10">
-        <v>11</v>
-      </c>
-      <c r="BH10">
-        <v>4.1</v>
-      </c>
-      <c r="BI10">
-        <v>3.75</v>
-      </c>
-      <c r="BJ10">
-        <v>12</v>
-      </c>
-      <c r="BK10">
-        <v>9</v>
-      </c>
-      <c r="BL10">
-        <v>130</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>4.3</v>
-      </c>
-      <c r="BO10">
-        <v>3.85</v>
-      </c>
-      <c r="BP10">
-        <v>11</v>
-      </c>
-      <c r="BQ10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR10">
-        <v>25</v>
-      </c>
-      <c r="BS10">
-        <v>16.5</v>
-      </c>
-      <c r="BT10">
-        <v>12</v>
-      </c>
-      <c r="BU10">
-        <v>9</v>
-      </c>
-      <c r="BV10">
-        <v>60</v>
-      </c>
-      <c r="BW10">
-        <v>38</v>
-      </c>
-      <c r="BX10">
-        <v>60</v>
-      </c>
-      <c r="BY10">
-        <v>38</v>
-      </c>
-      <c r="BZ10">
-        <v>16.5</v>
-      </c>
-      <c r="CA10">
-        <v>10.5</v>
-      </c>
       <c r="CB10" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3154,241 +3250,241 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F11">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>5.4</v>
+        <v>1.47</v>
       </c>
       <c r="I11">
-        <v>5.8</v>
+        <v>1.48</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
-        <v>1.89</v>
+        <v>2.78</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="S11">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="U11">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Y11">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="Z11">
+        <v>11</v>
+      </c>
+      <c r="AA11">
+        <v>14</v>
+      </c>
+      <c r="AB11">
+        <v>38</v>
+      </c>
+      <c r="AC11">
+        <v>12</v>
+      </c>
+      <c r="AD11">
+        <v>10.5</v>
+      </c>
+      <c r="AE11">
+        <v>14</v>
+      </c>
+      <c r="AF11">
+        <v>85</v>
+      </c>
+      <c r="AG11">
+        <v>28</v>
+      </c>
+      <c r="AH11">
+        <v>20</v>
+      </c>
+      <c r="AI11">
+        <v>26</v>
+      </c>
+      <c r="AJ11">
+        <v>220</v>
+      </c>
+      <c r="AK11">
+        <v>95</v>
+      </c>
+      <c r="AL11">
+        <v>75</v>
+      </c>
+      <c r="AM11">
+        <v>80</v>
+      </c>
+      <c r="AN11">
+        <v>75</v>
+      </c>
+      <c r="AO11">
+        <v>5.2</v>
+      </c>
+      <c r="AP11">
+        <v>24</v>
+      </c>
+      <c r="AQ11">
+        <v>11</v>
+      </c>
+      <c r="AR11">
+        <v>10</v>
+      </c>
+      <c r="AS11">
+        <v>13</v>
+      </c>
+      <c r="AT11">
+        <v>32</v>
+      </c>
+      <c r="AU11">
+        <v>11</v>
+      </c>
+      <c r="AV11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11">
+        <v>12.5</v>
+      </c>
+      <c r="AX11">
+        <v>16</v>
+      </c>
+      <c r="AY11">
+        <v>25</v>
+      </c>
+      <c r="AZ11">
+        <v>18.5</v>
+      </c>
+      <c r="BA11">
+        <v>23</v>
+      </c>
+      <c r="BB11">
+        <v>15</v>
+      </c>
+      <c r="BC11">
+        <v>13.5</v>
+      </c>
+      <c r="BD11">
+        <v>60</v>
+      </c>
+      <c r="BE11">
+        <v>16.5</v>
+      </c>
+      <c r="BF11">
+        <v>60</v>
+      </c>
+      <c r="BG11">
+        <v>4.8</v>
+      </c>
+      <c r="BH11">
+        <v>4.7</v>
+      </c>
+      <c r="BI11">
+        <v>4.2</v>
+      </c>
+      <c r="BJ11">
+        <v>9.6</v>
+      </c>
+      <c r="BK11">
+        <v>8.6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>21</v>
+      </c>
+      <c r="BN11">
+        <v>10.5</v>
+      </c>
+      <c r="BO11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BP11">
         <v>50</v>
       </c>
-      <c r="AA11">
-        <v>180</v>
-      </c>
-      <c r="AB11">
-        <v>8</v>
-      </c>
-      <c r="AC11">
+      <c r="BQ11">
+        <v>34</v>
+      </c>
+      <c r="BR11">
+        <v>46</v>
+      </c>
+      <c r="BS11">
+        <v>34</v>
+      </c>
+      <c r="BT11">
+        <v>4.4</v>
+      </c>
+      <c r="BU11">
+        <v>4</v>
+      </c>
+      <c r="BV11">
         <v>9</v>
       </c>
-      <c r="AD11">
-        <v>23</v>
-      </c>
-      <c r="AE11">
-        <v>100</v>
-      </c>
-      <c r="AF11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG11">
-        <v>10</v>
-      </c>
-      <c r="AH11">
-        <v>23</v>
-      </c>
-      <c r="AI11">
-        <v>95</v>
-      </c>
-      <c r="AJ11">
-        <v>20</v>
-      </c>
-      <c r="AK11">
-        <v>21</v>
-      </c>
-      <c r="AL11">
-        <v>48</v>
-      </c>
-      <c r="AM11">
-        <v>140</v>
-      </c>
-      <c r="AN11">
-        <v>12</v>
-      </c>
-      <c r="AO11">
-        <v>120</v>
-      </c>
-      <c r="AP11">
-        <v>13</v>
-      </c>
-      <c r="AQ11">
-        <v>15</v>
-      </c>
-      <c r="AR11">
-        <v>9.4</v>
-      </c>
-      <c r="AS11">
-        <v>11</v>
-      </c>
-      <c r="AT11">
-        <v>7</v>
-      </c>
-      <c r="AU11">
+      <c r="BW11">
         <v>7.8</v>
       </c>
-      <c r="AV11">
+      <c r="BX11">
         <v>19</v>
       </c>
-      <c r="AW11">
-        <v>10.5</v>
-      </c>
-      <c r="AX11">
-        <v>8.6</v>
-      </c>
-      <c r="AY11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11">
-        <v>19</v>
-      </c>
-      <c r="BA11">
-        <v>10.5</v>
-      </c>
-      <c r="BB11">
-        <v>16.5</v>
-      </c>
-      <c r="BC11">
-        <v>16.5</v>
-      </c>
-      <c r="BD11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11">
-        <v>11</v>
-      </c>
-      <c r="BF11">
-        <v>10</v>
-      </c>
-      <c r="BG11">
-        <v>10.5</v>
-      </c>
-      <c r="BH11">
-        <v>3.35</v>
-      </c>
-      <c r="BI11">
-        <v>3.1</v>
-      </c>
-      <c r="BJ11">
-        <v>11</v>
-      </c>
-      <c r="BK11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
-      </c>
-      <c r="BN11">
-        <v>4.3</v>
-      </c>
-      <c r="BO11">
-        <v>3.85</v>
-      </c>
-      <c r="BP11">
-        <v>12</v>
-      </c>
-      <c r="BQ11">
-        <v>10</v>
-      </c>
-      <c r="BR11">
-        <v>29</v>
-      </c>
-      <c r="BS11">
-        <v>21</v>
-      </c>
-      <c r="BT11">
-        <v>9</v>
-      </c>
-      <c r="BU11">
-        <v>8</v>
-      </c>
-      <c r="BV11">
-        <v>55</v>
-      </c>
-      <c r="BW11">
-        <v>36</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
       <c r="BY11">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="BZ11">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3396,241 +3492,241 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="F12">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="G12">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="H12">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X12">
+        <v>13.5</v>
+      </c>
+      <c r="Y12">
+        <v>18</v>
+      </c>
+      <c r="Z12">
+        <v>42</v>
+      </c>
+      <c r="AA12">
+        <v>160</v>
+      </c>
+      <c r="AB12">
+        <v>8.4</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>21</v>
+      </c>
+      <c r="AE12">
+        <v>90</v>
+      </c>
+      <c r="AF12">
+        <v>10.5</v>
+      </c>
+      <c r="AG12">
+        <v>10.5</v>
+      </c>
+      <c r="AH12">
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <v>90</v>
+      </c>
+      <c r="AJ12">
+        <v>19</v>
+      </c>
+      <c r="AK12">
+        <v>20</v>
+      </c>
+      <c r="AL12">
+        <v>44</v>
+      </c>
+      <c r="AM12">
+        <v>140</v>
+      </c>
+      <c r="AN12">
         <v>12.5</v>
       </c>
-      <c r="Y12">
+      <c r="AO12">
+        <v>100</v>
+      </c>
+      <c r="AP12">
+        <v>11.5</v>
+      </c>
+      <c r="AQ12">
+        <v>16</v>
+      </c>
+      <c r="AR12">
+        <v>34</v>
+      </c>
+      <c r="AS12">
+        <v>13</v>
+      </c>
+      <c r="AT12">
+        <v>7.6</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>18.5</v>
+      </c>
+      <c r="AW12">
+        <v>27</v>
+      </c>
+      <c r="AX12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>65</v>
+      </c>
+      <c r="BB12">
+        <v>16.5</v>
+      </c>
+      <c r="BC12">
+        <v>17.5</v>
+      </c>
+      <c r="BD12">
+        <v>34</v>
+      </c>
+      <c r="BE12">
+        <v>13</v>
+      </c>
+      <c r="BF12">
+        <v>11</v>
+      </c>
+      <c r="BG12">
+        <v>12.5</v>
+      </c>
+      <c r="BH12">
+        <v>3.6</v>
+      </c>
+      <c r="BI12">
+        <v>2.84</v>
+      </c>
+      <c r="BJ12">
+        <v>14.5</v>
+      </c>
+      <c r="BK12">
+        <v>7.8</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>3.75</v>
+      </c>
+      <c r="BN12">
+        <v>5.8</v>
+      </c>
+      <c r="BO12">
+        <v>3.4</v>
+      </c>
+      <c r="BP12">
+        <v>18</v>
+      </c>
+      <c r="BQ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR12">
+        <v>44</v>
+      </c>
+      <c r="BS12">
+        <v>3.45</v>
+      </c>
+      <c r="BT12">
         <v>12</v>
       </c>
-      <c r="Z12">
-        <v>23</v>
-      </c>
-      <c r="AA12">
-        <v>75</v>
-      </c>
-      <c r="AB12">
-        <v>9.4</v>
-      </c>
-      <c r="AC12">
-        <v>7.4</v>
-      </c>
-      <c r="AD12">
-        <v>15.5</v>
-      </c>
-      <c r="AE12">
-        <v>55</v>
-      </c>
-      <c r="AF12">
-        <v>15</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>23</v>
-      </c>
-      <c r="AI12">
-        <v>65</v>
-      </c>
-      <c r="AJ12">
-        <v>42</v>
-      </c>
-      <c r="AK12">
+      <c r="BU12">
+        <v>6.4</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>3.55</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>3.6</v>
+      </c>
+      <c r="BZ12">
         <v>36</v>
       </c>
-      <c r="AL12">
-        <v>55</v>
-      </c>
-      <c r="AM12">
-        <v>130</v>
-      </c>
-      <c r="AN12">
-        <v>26</v>
-      </c>
-      <c r="AO12">
-        <v>60</v>
-      </c>
-      <c r="AP12">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12">
-        <v>10</v>
-      </c>
-      <c r="AR12">
-        <v>19.5</v>
-      </c>
-      <c r="AS12">
-        <v>8.4</v>
-      </c>
-      <c r="AT12">
-        <v>8</v>
-      </c>
-      <c r="AU12">
-        <v>6.6</v>
-      </c>
-      <c r="AV12">
-        <v>13</v>
-      </c>
-      <c r="AW12">
-        <v>8</v>
-      </c>
-      <c r="AX12">
-        <v>13</v>
-      </c>
-      <c r="AY12">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12">
-        <v>16.5</v>
-      </c>
-      <c r="BA12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB12">
-        <v>7.8</v>
-      </c>
-      <c r="BC12">
-        <v>19.5</v>
-      </c>
-      <c r="BD12">
-        <v>8</v>
-      </c>
-      <c r="BE12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF12">
-        <v>18</v>
-      </c>
-      <c r="BG12">
-        <v>7.8</v>
-      </c>
-      <c r="BH12">
-        <v>3.25</v>
-      </c>
-      <c r="BI12">
-        <v>2.88</v>
-      </c>
-      <c r="BJ12">
-        <v>12</v>
-      </c>
-      <c r="BK12">
-        <v>8.6</v>
-      </c>
-      <c r="BL12">
-        <v>170</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
-        <v>6.2</v>
-      </c>
-      <c r="BO12">
-        <v>4.6</v>
-      </c>
-      <c r="BP12">
-        <v>23</v>
-      </c>
-      <c r="BQ12">
-        <v>13.5</v>
-      </c>
-      <c r="BR12">
-        <v>42</v>
-      </c>
-      <c r="BS12">
-        <v>24</v>
-      </c>
-      <c r="BT12">
-        <v>7.8</v>
-      </c>
-      <c r="BU12">
-        <v>5.7</v>
-      </c>
-      <c r="BV12">
-        <v>34</v>
-      </c>
-      <c r="BW12">
-        <v>20</v>
-      </c>
-      <c r="BX12">
-        <v>50</v>
-      </c>
-      <c r="BY12">
-        <v>29</v>
-      </c>
-      <c r="BZ12">
-        <v>38</v>
-      </c>
       <c r="CA12">
-        <v>22</v>
+        <v>3.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3638,16 +3734,16 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="F13">
         <v>2.28</v>
@@ -3656,7 +3752,7 @@
         <v>2.3</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I13">
         <v>3.45</v>
@@ -3668,64 +3764,64 @@
         <v>3.75</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
         <v>1.29</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q13">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R13">
         <v>1.42</v>
       </c>
       <c r="S13">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U13">
         <v>2.3</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y13">
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB13">
         <v>11.5</v>
       </c>
       <c r="AC13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
         <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF13">
         <v>15.5</v>
@@ -3737,49 +3833,49 @@
         <v>19.5</v>
       </c>
       <c r="AI13">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ13">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK13">
         <v>24</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO13">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP13">
         <v>15</v>
       </c>
       <c r="AQ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR13">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV13">
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3791,25 +3887,25 @@
         <v>15</v>
       </c>
       <c r="BA13">
+        <v>40</v>
+      </c>
+      <c r="BB13">
+        <v>26</v>
+      </c>
+      <c r="BC13">
+        <v>21</v>
+      </c>
+      <c r="BD13">
         <v>30</v>
       </c>
-      <c r="BB13">
-        <v>20</v>
-      </c>
-      <c r="BC13">
-        <v>17.5</v>
-      </c>
-      <c r="BD13">
-        <v>8.6</v>
-      </c>
       <c r="BE13">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF13">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG13">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BH13">
         <v>3.65</v>
@@ -3827,31 +3923,31 @@
         <v>130</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BR13">
         <v>34</v>
       </c>
       <c r="BS13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BT13">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV13">
         <v>32</v>
@@ -3860,7 +3956,7 @@
         <v>18.5</v>
       </c>
       <c r="BX13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY13">
         <v>25</v>
@@ -3869,10 +3965,10 @@
         <v>28</v>
       </c>
       <c r="CA13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3880,241 +3976,241 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="F14">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="H14">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P14">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X14">
+        <v>12</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>23</v>
+      </c>
+      <c r="AA14">
+        <v>65</v>
+      </c>
+      <c r="AB14">
+        <v>9.4</v>
+      </c>
+      <c r="AC14">
+        <v>7.4</v>
+      </c>
+      <c r="AD14">
+        <v>15</v>
+      </c>
+      <c r="AE14">
+        <v>46</v>
+      </c>
+      <c r="AF14">
+        <v>15</v>
+      </c>
+      <c r="AG14">
         <v>14.5</v>
       </c>
-      <c r="Y14">
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>60</v>
+      </c>
+      <c r="AJ14">
+        <v>36</v>
+      </c>
+      <c r="AK14">
+        <v>34</v>
+      </c>
+      <c r="AL14">
+        <v>55</v>
+      </c>
+      <c r="AM14">
+        <v>130</v>
+      </c>
+      <c r="AN14">
+        <v>26</v>
+      </c>
+      <c r="AO14">
+        <v>60</v>
+      </c>
+      <c r="AP14">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14">
+        <v>10.5</v>
+      </c>
+      <c r="AR14">
         <v>20</v>
       </c>
-      <c r="Z14">
+      <c r="AS14">
+        <v>55</v>
+      </c>
+      <c r="AT14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>13</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>13</v>
+      </c>
+      <c r="AY14">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14">
+        <v>17</v>
+      </c>
+      <c r="BA14">
+        <v>48</v>
+      </c>
+      <c r="BB14">
+        <v>30</v>
+      </c>
+      <c r="BC14">
+        <v>25</v>
+      </c>
+      <c r="BD14">
+        <v>38</v>
+      </c>
+      <c r="BE14">
+        <v>12</v>
+      </c>
+      <c r="BF14">
+        <v>19.5</v>
+      </c>
+      <c r="BG14">
+        <v>38</v>
+      </c>
+      <c r="BH14">
+        <v>3.25</v>
+      </c>
+      <c r="BI14">
+        <v>2.88</v>
+      </c>
+      <c r="BJ14">
+        <v>12</v>
+      </c>
+      <c r="BK14">
+        <v>8.6</v>
+      </c>
+      <c r="BL14">
+        <v>160</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>5.3</v>
+      </c>
+      <c r="BO14">
+        <v>4.6</v>
+      </c>
+      <c r="BP14">
+        <v>23</v>
+      </c>
+      <c r="BQ14">
+        <v>16</v>
+      </c>
+      <c r="BR14">
         <v>42</v>
       </c>
-      <c r="AA14">
-        <v>170</v>
-      </c>
-      <c r="AB14">
-        <v>8.4</v>
-      </c>
-      <c r="AC14">
-        <v>8.4</v>
-      </c>
-      <c r="AD14">
-        <v>21</v>
-      </c>
-      <c r="AE14">
-        <v>95</v>
-      </c>
-      <c r="AF14">
-        <v>10.5</v>
-      </c>
-      <c r="AG14">
-        <v>10.5</v>
-      </c>
-      <c r="AH14">
+      <c r="BS14">
+        <v>24</v>
+      </c>
+      <c r="BT14">
+        <v>7.6</v>
+      </c>
+      <c r="BU14">
+        <v>5.7</v>
+      </c>
+      <c r="BV14">
+        <v>34</v>
+      </c>
+      <c r="BW14">
+        <v>20</v>
+      </c>
+      <c r="BX14">
+        <v>50</v>
+      </c>
+      <c r="BY14">
+        <v>29</v>
+      </c>
+      <c r="BZ14">
+        <v>38</v>
+      </c>
+      <c r="CA14">
         <v>22</v>
       </c>
-      <c r="AI14">
-        <v>95</v>
-      </c>
-      <c r="AJ14">
-        <v>21</v>
-      </c>
-      <c r="AK14">
-        <v>20</v>
-      </c>
-      <c r="AL14">
-        <v>50</v>
-      </c>
-      <c r="AM14">
-        <v>150</v>
-      </c>
-      <c r="AN14">
-        <v>12.5</v>
-      </c>
-      <c r="AO14">
-        <v>120</v>
-      </c>
-      <c r="AP14">
-        <v>12</v>
-      </c>
-      <c r="AQ14">
-        <v>15</v>
-      </c>
-      <c r="AR14">
-        <v>34</v>
-      </c>
-      <c r="AS14">
-        <v>10.5</v>
-      </c>
-      <c r="AT14">
-        <v>7.6</v>
-      </c>
-      <c r="AU14">
-        <v>7.6</v>
-      </c>
-      <c r="AV14">
-        <v>18.5</v>
-      </c>
-      <c r="AW14">
-        <v>27</v>
-      </c>
-      <c r="AX14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14">
-        <v>19</v>
-      </c>
-      <c r="BA14">
-        <v>10</v>
-      </c>
-      <c r="BB14">
-        <v>16.5</v>
-      </c>
-      <c r="BC14">
-        <v>17.5</v>
-      </c>
-      <c r="BD14">
-        <v>34</v>
-      </c>
-      <c r="BE14">
-        <v>10.5</v>
-      </c>
-      <c r="BF14">
-        <v>10</v>
-      </c>
-      <c r="BG14">
-        <v>10</v>
-      </c>
-      <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <v>0</v>
-      </c>
-      <c r="BJ14">
-        <v>0</v>
-      </c>
-      <c r="BK14">
-        <v>0</v>
-      </c>
-      <c r="BL14">
-        <v>0</v>
-      </c>
-      <c r="BM14">
-        <v>0</v>
-      </c>
-      <c r="BN14">
-        <v>0</v>
-      </c>
-      <c r="BO14">
-        <v>0</v>
-      </c>
-      <c r="BP14">
-        <v>0</v>
-      </c>
-      <c r="BQ14">
-        <v>0</v>
-      </c>
-      <c r="BR14">
-        <v>0</v>
-      </c>
-      <c r="BS14">
-        <v>0</v>
-      </c>
-      <c r="BT14">
-        <v>0</v>
-      </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
-      <c r="BV14">
-        <v>0</v>
-      </c>
-      <c r="BW14">
-        <v>0</v>
-      </c>
-      <c r="BX14">
-        <v>0</v>
-      </c>
-      <c r="BY14">
-        <v>0</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
       <c r="CB14" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4122,483 +4218,3387 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="F15">
+        <v>1.73</v>
+      </c>
+      <c r="G15">
+        <v>1.76</v>
+      </c>
+      <c r="H15">
+        <v>5.4</v>
+      </c>
+      <c r="I15">
+        <v>5.8</v>
+      </c>
+      <c r="J15">
+        <v>3.95</v>
+      </c>
+      <c r="K15">
+        <v>4.1</v>
+      </c>
+      <c r="L15">
+        <v>1.37</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.7</v>
+      </c>
+      <c r="O15">
+        <v>1.34</v>
+      </c>
+      <c r="P15">
+        <v>1.89</v>
+      </c>
+      <c r="Q15">
+        <v>2.04</v>
+      </c>
+      <c r="R15">
+        <v>1.35</v>
+      </c>
+      <c r="S15">
+        <v>3.65</v>
+      </c>
+      <c r="T15">
+        <v>1.94</v>
+      </c>
+      <c r="U15">
+        <v>1.96</v>
+      </c>
+      <c r="V15">
+        <v>1.21</v>
+      </c>
+      <c r="W15">
+        <v>2.3</v>
+      </c>
+      <c r="X15">
+        <v>15.5</v>
+      </c>
+      <c r="Y15">
+        <v>18</v>
+      </c>
+      <c r="Z15">
+        <v>55</v>
+      </c>
+      <c r="AA15">
+        <v>180</v>
+      </c>
+      <c r="AB15">
+        <v>8</v>
+      </c>
+      <c r="AC15">
+        <v>9</v>
+      </c>
+      <c r="AD15">
+        <v>23</v>
+      </c>
+      <c r="AE15">
+        <v>100</v>
+      </c>
+      <c r="AF15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>85</v>
+      </c>
+      <c r="AJ15">
+        <v>20</v>
+      </c>
+      <c r="AK15">
+        <v>21</v>
+      </c>
+      <c r="AL15">
+        <v>50</v>
+      </c>
+      <c r="AM15">
+        <v>140</v>
+      </c>
+      <c r="AN15">
+        <v>12</v>
+      </c>
+      <c r="AO15">
+        <v>120</v>
+      </c>
+      <c r="AP15">
+        <v>13</v>
+      </c>
+      <c r="AQ15">
+        <v>15</v>
+      </c>
+      <c r="AR15">
+        <v>9.4</v>
+      </c>
+      <c r="AS15">
+        <v>11</v>
+      </c>
+      <c r="AT15">
+        <v>7</v>
+      </c>
+      <c r="AU15">
         <v>7.8</v>
       </c>
-      <c r="G15">
+      <c r="AV15">
+        <v>19</v>
+      </c>
+      <c r="AW15">
+        <v>10.5</v>
+      </c>
+      <c r="AX15">
+        <v>8.6</v>
+      </c>
+      <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>19</v>
+      </c>
+      <c r="BA15">
+        <v>10.5</v>
+      </c>
+      <c r="BB15">
+        <v>16.5</v>
+      </c>
+      <c r="BC15">
+        <v>16.5</v>
+      </c>
+      <c r="BD15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE15">
+        <v>11</v>
+      </c>
+      <c r="BF15">
+        <v>10</v>
+      </c>
+      <c r="BG15">
+        <v>10.5</v>
+      </c>
+      <c r="BH15">
+        <v>3.35</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>11</v>
+      </c>
+      <c r="BK15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>21</v>
+      </c>
+      <c r="BN15">
+        <v>4.3</v>
+      </c>
+      <c r="BO15">
+        <v>3.85</v>
+      </c>
+      <c r="BP15">
+        <v>12</v>
+      </c>
+      <c r="BQ15">
+        <v>10</v>
+      </c>
+      <c r="BR15">
+        <v>29</v>
+      </c>
+      <c r="BS15">
+        <v>21</v>
+      </c>
+      <c r="BT15">
+        <v>9</v>
+      </c>
+      <c r="BU15">
         <v>8</v>
       </c>
-      <c r="H15">
-        <v>1.46</v>
-      </c>
-      <c r="I15">
-        <v>1.48</v>
-      </c>
-      <c r="J15">
-        <v>5.1</v>
-      </c>
-      <c r="K15">
-        <v>5.2</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>1.03</v>
-      </c>
-      <c r="N15">
-        <v>6.2</v>
-      </c>
-      <c r="O15">
-        <v>1.17</v>
-      </c>
-      <c r="P15">
-        <v>2.78</v>
-      </c>
-      <c r="Q15">
-        <v>1.53</v>
-      </c>
-      <c r="R15">
-        <v>1.7</v>
-      </c>
-      <c r="S15">
-        <v>2.3</v>
-      </c>
-      <c r="T15">
-        <v>1.69</v>
-      </c>
-      <c r="U15">
-        <v>2.32</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>29</v>
-      </c>
-      <c r="Y15">
-        <v>12.5</v>
-      </c>
-      <c r="Z15">
-        <v>11.5</v>
-      </c>
-      <c r="AA15">
-        <v>14.5</v>
-      </c>
-      <c r="AB15">
-        <v>38</v>
-      </c>
-      <c r="AC15">
-        <v>12.5</v>
-      </c>
-      <c r="AD15">
-        <v>10</v>
-      </c>
-      <c r="AE15">
-        <v>14.5</v>
-      </c>
-      <c r="AF15">
-        <v>75</v>
-      </c>
-      <c r="AG15">
-        <v>29</v>
-      </c>
-      <c r="AH15">
-        <v>20</v>
-      </c>
-      <c r="AI15">
-        <v>27</v>
-      </c>
-      <c r="AJ15">
-        <v>210</v>
-      </c>
-      <c r="AK15">
-        <v>95</v>
-      </c>
-      <c r="AL15">
-        <v>70</v>
-      </c>
-      <c r="AM15">
-        <v>80</v>
-      </c>
-      <c r="AN15">
-        <v>80</v>
-      </c>
-      <c r="AO15">
-        <v>5.2</v>
-      </c>
-      <c r="AP15">
+      <c r="BV15">
+        <v>55</v>
+      </c>
+      <c r="BW15">
+        <v>36</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>42</v>
+      </c>
+      <c r="BZ15">
         <v>24</v>
       </c>
-      <c r="AQ15">
-        <v>10.5</v>
-      </c>
-      <c r="AR15">
-        <v>10</v>
-      </c>
-      <c r="AS15">
-        <v>13</v>
-      </c>
-      <c r="AT15">
-        <v>10.5</v>
-      </c>
-      <c r="AU15">
-        <v>10.5</v>
-      </c>
-      <c r="AV15">
-        <v>9</v>
-      </c>
-      <c r="AW15">
-        <v>12.5</v>
-      </c>
-      <c r="AX15">
-        <v>12.5</v>
-      </c>
-      <c r="AY15">
-        <v>23</v>
-      </c>
-      <c r="AZ15">
+      <c r="CA15">
         <v>17.5</v>
       </c>
-      <c r="BA15">
-        <v>22</v>
-      </c>
-      <c r="BB15">
-        <v>12.5</v>
-      </c>
-      <c r="BC15">
-        <v>12</v>
-      </c>
-      <c r="BD15">
-        <v>11.5</v>
-      </c>
-      <c r="BE15">
-        <v>12.5</v>
-      </c>
-      <c r="BF15">
-        <v>11.5</v>
-      </c>
-      <c r="BG15">
-        <v>4.7</v>
-      </c>
-      <c r="BH15">
-        <v>4.7</v>
-      </c>
-      <c r="BI15">
-        <v>4.2</v>
-      </c>
-      <c r="BJ15">
-        <v>9.6</v>
-      </c>
-      <c r="BK15">
-        <v>8.6</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>65</v>
-      </c>
-      <c r="BN15">
-        <v>10.5</v>
-      </c>
-      <c r="BO15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BP15">
-        <v>50</v>
-      </c>
-      <c r="BQ15">
-        <v>34</v>
-      </c>
-      <c r="BR15">
-        <v>46</v>
-      </c>
-      <c r="BS15">
-        <v>34</v>
-      </c>
-      <c r="BT15">
-        <v>4.4</v>
-      </c>
-      <c r="BU15">
-        <v>4</v>
-      </c>
-      <c r="BV15">
-        <v>9</v>
-      </c>
-      <c r="BW15">
-        <v>7.8</v>
-      </c>
-      <c r="BX15">
-        <v>20</v>
-      </c>
-      <c r="BY15">
-        <v>14.5</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
       <c r="CB15" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16">
+        <v>1.55</v>
+      </c>
+      <c r="G16">
+        <v>1.56</v>
+      </c>
+      <c r="H16">
+        <v>6.6</v>
+      </c>
+      <c r="I16">
+        <v>6.8</v>
+      </c>
+      <c r="J16">
+        <v>4.7</v>
+      </c>
+      <c r="K16">
+        <v>4.9</v>
+      </c>
+      <c r="L16">
+        <v>1.3</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>5.1</v>
+      </c>
+      <c r="O16">
+        <v>1.22</v>
+      </c>
+      <c r="P16">
+        <v>2.38</v>
+      </c>
+      <c r="Q16">
+        <v>1.66</v>
+      </c>
+      <c r="R16">
+        <v>1.56</v>
+      </c>
+      <c r="S16">
+        <v>2.64</v>
+      </c>
+      <c r="T16">
+        <v>1.81</v>
+      </c>
+      <c r="U16">
+        <v>2.14</v>
+      </c>
+      <c r="V16">
+        <v>1.17</v>
+      </c>
+      <c r="W16">
+        <v>2.78</v>
+      </c>
+      <c r="X16">
+        <v>22</v>
+      </c>
+      <c r="Y16">
+        <v>26</v>
+      </c>
+      <c r="Z16">
+        <v>60</v>
+      </c>
+      <c r="AA16">
+        <v>200</v>
+      </c>
+      <c r="AB16">
+        <v>10.5</v>
+      </c>
+      <c r="AC16">
+        <v>11</v>
+      </c>
+      <c r="AD16">
+        <v>25</v>
+      </c>
+      <c r="AE16">
         <v>85</v>
       </c>
-      <c r="B16" t="s">
+      <c r="AF16">
+        <v>10.5</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+      <c r="AH16">
+        <v>21</v>
+      </c>
+      <c r="AI16">
+        <v>80</v>
+      </c>
+      <c r="AJ16">
+        <v>15</v>
+      </c>
+      <c r="AK16">
+        <v>15</v>
+      </c>
+      <c r="AL16">
+        <v>30</v>
+      </c>
+      <c r="AM16">
+        <v>110</v>
+      </c>
+      <c r="AN16">
+        <v>6.6</v>
+      </c>
+      <c r="AO16">
+        <v>90</v>
+      </c>
+      <c r="AP16">
+        <v>19.5</v>
+      </c>
+      <c r="AQ16">
+        <v>25</v>
+      </c>
+      <c r="AR16">
+        <v>50</v>
+      </c>
+      <c r="AS16">
+        <v>15</v>
+      </c>
+      <c r="AT16">
+        <v>10</v>
+      </c>
+      <c r="AU16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV16">
+        <v>22</v>
+      </c>
+      <c r="AW16">
+        <v>15.5</v>
+      </c>
+      <c r="AX16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16">
+        <v>18.5</v>
+      </c>
+      <c r="BA16">
+        <v>65</v>
+      </c>
+      <c r="BB16">
+        <v>13.5</v>
+      </c>
+      <c r="BC16">
+        <v>13.5</v>
+      </c>
+      <c r="BD16">
+        <v>26</v>
+      </c>
+      <c r="BE16">
+        <v>16.5</v>
+      </c>
+      <c r="BF16">
+        <v>5.9</v>
+      </c>
+      <c r="BG16">
+        <v>16</v>
+      </c>
+      <c r="BH16">
+        <v>4.1</v>
+      </c>
+      <c r="BI16">
+        <v>3.75</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>9</v>
+      </c>
+      <c r="BL16">
+        <v>130</v>
+      </c>
+      <c r="BM16">
+        <v>21</v>
+      </c>
+      <c r="BN16">
+        <v>4.3</v>
+      </c>
+      <c r="BO16">
+        <v>3.85</v>
+      </c>
+      <c r="BP16">
+        <v>11</v>
+      </c>
+      <c r="BQ16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR16">
+        <v>25</v>
+      </c>
+      <c r="BS16">
+        <v>16.5</v>
+      </c>
+      <c r="BT16">
+        <v>12</v>
+      </c>
+      <c r="BU16">
+        <v>9</v>
+      </c>
+      <c r="BV16">
+        <v>60</v>
+      </c>
+      <c r="BW16">
+        <v>38</v>
+      </c>
+      <c r="BX16">
+        <v>60</v>
+      </c>
+      <c r="BY16">
+        <v>38</v>
+      </c>
+      <c r="BZ16">
+        <v>16.5</v>
+      </c>
+      <c r="CA16">
+        <v>10.5</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
         <v>86</v>
       </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17">
+        <v>1.37</v>
+      </c>
+      <c r="G17">
+        <v>1.43</v>
+      </c>
+      <c r="H17">
+        <v>9.6</v>
+      </c>
+      <c r="I17">
+        <v>11.5</v>
+      </c>
+      <c r="J17">
+        <v>4.8</v>
+      </c>
+      <c r="K17">
+        <v>5.6</v>
+      </c>
+      <c r="L17">
+        <v>1.29</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
+      <c r="O17">
+        <v>1.25</v>
+      </c>
+      <c r="P17">
+        <v>2.1</v>
+      </c>
+      <c r="Q17">
+        <v>1.79</v>
+      </c>
+      <c r="R17">
+        <v>1.37</v>
+      </c>
+      <c r="S17">
+        <v>2.94</v>
+      </c>
+      <c r="T17">
+        <v>2.14</v>
+      </c>
+      <c r="U17">
+        <v>1.79</v>
+      </c>
+      <c r="V17">
+        <v>1.1</v>
+      </c>
+      <c r="W17">
+        <v>3.25</v>
+      </c>
+      <c r="X17">
+        <v>21</v>
+      </c>
+      <c r="Y17">
+        <v>32</v>
+      </c>
+      <c r="Z17">
+        <v>120</v>
+      </c>
+      <c r="AA17">
+        <v>510</v>
+      </c>
+      <c r="AB17">
+        <v>8</v>
+      </c>
+      <c r="AC17">
+        <v>14</v>
+      </c>
+      <c r="AD17">
+        <v>40</v>
+      </c>
+      <c r="AE17">
+        <v>230</v>
+      </c>
+      <c r="AF17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>32</v>
+      </c>
+      <c r="AI17">
+        <v>190</v>
+      </c>
+      <c r="AJ17">
+        <v>13.5</v>
+      </c>
+      <c r="AK17">
+        <v>19.5</v>
+      </c>
+      <c r="AL17">
+        <v>55</v>
+      </c>
+      <c r="AM17">
+        <v>230</v>
+      </c>
+      <c r="AN17">
+        <v>7</v>
+      </c>
+      <c r="AO17">
+        <v>350</v>
+      </c>
+      <c r="AP17">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17">
+        <v>21</v>
+      </c>
+      <c r="AR17">
+        <v>6</v>
+      </c>
+      <c r="AS17">
+        <v>6.2</v>
+      </c>
+      <c r="AT17">
+        <v>6.8</v>
+      </c>
+      <c r="AU17">
+        <v>10</v>
+      </c>
+      <c r="AV17">
+        <v>5.6</v>
+      </c>
+      <c r="AW17">
+        <v>6.2</v>
+      </c>
+      <c r="AX17">
+        <v>7</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>6</v>
+      </c>
+      <c r="BB17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC17">
+        <v>13.5</v>
+      </c>
+      <c r="BD17">
+        <v>5.8</v>
+      </c>
+      <c r="BE17">
+        <v>6.2</v>
+      </c>
+      <c r="BF17">
+        <v>6</v>
+      </c>
+      <c r="BG17">
+        <v>6.2</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>18</v>
+      </c>
+      <c r="BK17">
+        <v>7.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>21</v>
+      </c>
+      <c r="BN17">
+        <v>5.1</v>
+      </c>
+      <c r="BO17">
+        <v>2.64</v>
+      </c>
+      <c r="BP17">
+        <v>12</v>
+      </c>
+      <c r="BQ17">
+        <v>5.3</v>
+      </c>
+      <c r="BR17">
+        <v>38</v>
+      </c>
+      <c r="BS17">
+        <v>15.5</v>
+      </c>
+      <c r="BT17">
+        <v>19</v>
+      </c>
+      <c r="BU17">
+        <v>8</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>21</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>21</v>
+      </c>
+      <c r="BZ17">
+        <v>21</v>
+      </c>
+      <c r="CA17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18">
+        <v>2.7</v>
+      </c>
+      <c r="G18">
+        <v>2.84</v>
+      </c>
+      <c r="H18">
+        <v>2.58</v>
+      </c>
+      <c r="I18">
+        <v>2.66</v>
+      </c>
+      <c r="J18">
+        <v>3.65</v>
+      </c>
+      <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.05</v>
+      </c>
+      <c r="N18">
+        <v>4.4</v>
+      </c>
+      <c r="O18">
+        <v>1.24</v>
+      </c>
+      <c r="P18">
+        <v>2.22</v>
+      </c>
+      <c r="Q18">
+        <v>1.71</v>
+      </c>
+      <c r="R18">
+        <v>1.45</v>
+      </c>
+      <c r="S18">
+        <v>2.7</v>
+      </c>
+      <c r="T18">
+        <v>1.63</v>
+      </c>
+      <c r="U18">
+        <v>2.28</v>
+      </c>
+      <c r="V18">
+        <v>1.6</v>
+      </c>
+      <c r="W18">
+        <v>1.54</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>27</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>29</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>7.8</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>4.3</v>
+      </c>
+      <c r="BI18">
+        <v>3.1</v>
+      </c>
+      <c r="BJ18">
+        <v>12.5</v>
+      </c>
+      <c r="BK18">
+        <v>5.6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO18">
+        <v>4.8</v>
+      </c>
+      <c r="BP18">
+        <v>28</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>40</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU18">
+        <v>4.7</v>
+      </c>
+      <c r="BV18">
+        <v>28</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>40</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>29</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19">
+        <v>1.83</v>
+      </c>
+      <c r="G19">
+        <v>1.93</v>
+      </c>
+      <c r="H19">
+        <v>5.4</v>
+      </c>
+      <c r="I19">
+        <v>6.2</v>
+      </c>
+      <c r="J19">
+        <v>3.35</v>
+      </c>
+      <c r="K19">
+        <v>3.6</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.06</v>
+      </c>
+      <c r="N19">
+        <v>2.98</v>
+      </c>
+      <c r="O19">
+        <v>1.45</v>
+      </c>
+      <c r="P19">
+        <v>1.64</v>
+      </c>
+      <c r="Q19">
+        <v>2.38</v>
+      </c>
+      <c r="R19">
+        <v>1.2</v>
+      </c>
+      <c r="S19">
+        <v>4.7</v>
+      </c>
+      <c r="T19">
+        <v>1.99</v>
+      </c>
+      <c r="U19">
+        <v>1.72</v>
+      </c>
+      <c r="V19">
+        <v>1.19</v>
+      </c>
+      <c r="W19">
+        <v>2.06</v>
+      </c>
+      <c r="X19">
+        <v>17.5</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC19">
+        <v>11</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>17</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>20</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>16.5</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>16.5</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>17.5</v>
+      </c>
+      <c r="BC19">
+        <v>17</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>10.5</v>
+      </c>
+      <c r="BG19">
+        <v>90</v>
+      </c>
+      <c r="BH19">
+        <v>3.5</v>
+      </c>
+      <c r="BI19">
+        <v>2.4</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.41</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.41</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.41</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.41</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.41</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.41</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.41</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.41</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.41</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20">
+        <v>2.46</v>
+      </c>
+      <c r="G20">
+        <v>2.78</v>
+      </c>
+      <c r="H20">
+        <v>2.8</v>
+      </c>
+      <c r="I20">
+        <v>3.25</v>
+      </c>
+      <c r="J20">
+        <v>3.3</v>
+      </c>
+      <c r="K20">
+        <v>3.75</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.05</v>
+      </c>
+      <c r="N20">
+        <v>3.15</v>
+      </c>
+      <c r="O20">
+        <v>1.27</v>
+      </c>
+      <c r="P20">
+        <v>1.89</v>
+      </c>
+      <c r="Q20">
+        <v>1.94</v>
+      </c>
+      <c r="R20">
+        <v>1.23</v>
+      </c>
+      <c r="S20">
+        <v>2.5</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>1.78</v>
+      </c>
+      <c r="V20">
+        <v>1.44</v>
+      </c>
+      <c r="W20">
+        <v>1.56</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>17.5</v>
+      </c>
+      <c r="Z20">
+        <v>30</v>
+      </c>
+      <c r="AA20">
+        <v>70</v>
+      </c>
+      <c r="AB20">
+        <v>15.5</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>19</v>
+      </c>
+      <c r="AE20">
+        <v>50</v>
+      </c>
+      <c r="AF20">
+        <v>25</v>
+      </c>
+      <c r="AG20">
+        <v>17.5</v>
+      </c>
+      <c r="AH20">
+        <v>25</v>
+      </c>
+      <c r="AI20">
+        <v>65</v>
+      </c>
+      <c r="AJ20">
+        <v>55</v>
+      </c>
+      <c r="AK20">
+        <v>44</v>
+      </c>
+      <c r="AL20">
+        <v>60</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>34</v>
+      </c>
+      <c r="AO20">
+        <v>46</v>
+      </c>
+      <c r="AP20">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20">
+        <v>7.4</v>
+      </c>
+      <c r="AR20">
+        <v>12.5</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>6.8</v>
+      </c>
+      <c r="AU20">
+        <v>5.1</v>
+      </c>
+      <c r="AV20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW20">
+        <v>1.03</v>
+      </c>
+      <c r="AX20">
+        <v>10.5</v>
+      </c>
+      <c r="AY20">
+        <v>7.4</v>
+      </c>
+      <c r="AZ20">
+        <v>10.5</v>
+      </c>
+      <c r="BA20">
+        <v>1.03</v>
+      </c>
+      <c r="BB20">
+        <v>1.03</v>
+      </c>
+      <c r="BC20">
+        <v>16.5</v>
+      </c>
+      <c r="BD20">
+        <v>1.03</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>14</v>
+      </c>
+      <c r="BG20">
+        <v>18.5</v>
+      </c>
+      <c r="BH20">
+        <v>4.2</v>
+      </c>
+      <c r="BI20">
+        <v>2.7</v>
+      </c>
+      <c r="BJ20">
+        <v>13.5</v>
+      </c>
+      <c r="BK20">
+        <v>5.9</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>21</v>
+      </c>
+      <c r="BN20">
+        <v>7.8</v>
+      </c>
+      <c r="BO20">
+        <v>3.6</v>
+      </c>
+      <c r="BP20">
+        <v>29</v>
+      </c>
+      <c r="BQ20">
+        <v>12</v>
+      </c>
+      <c r="BR20">
+        <v>48</v>
+      </c>
+      <c r="BS20">
+        <v>19</v>
+      </c>
+      <c r="BT20">
+        <v>8.6</v>
+      </c>
+      <c r="BU20">
+        <v>3.95</v>
+      </c>
+      <c r="BV20">
+        <v>34</v>
+      </c>
+      <c r="BW20">
+        <v>14</v>
+      </c>
+      <c r="BX20">
+        <v>50</v>
+      </c>
+      <c r="BY20">
+        <v>21</v>
+      </c>
+      <c r="BZ20">
+        <v>40</v>
+      </c>
+      <c r="CA20">
+        <v>16.5</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21">
+        <v>2.92</v>
+      </c>
+      <c r="G21">
+        <v>3.4</v>
+      </c>
+      <c r="H21">
+        <v>2.3</v>
+      </c>
+      <c r="I21">
+        <v>2.62</v>
+      </c>
+      <c r="J21">
+        <v>3.4</v>
+      </c>
+      <c r="K21">
+        <v>4.5</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.02</v>
+      </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <v>1.25</v>
+      </c>
+      <c r="P21">
+        <v>1.99</v>
+      </c>
+      <c r="Q21">
+        <v>1.79</v>
+      </c>
+      <c r="R21">
+        <v>1.37</v>
+      </c>
+      <c r="S21">
+        <v>2.8</v>
+      </c>
+      <c r="T21">
+        <v>1.63</v>
+      </c>
+      <c r="U21">
+        <v>2.14</v>
+      </c>
+      <c r="V21">
+        <v>1.63</v>
+      </c>
+      <c r="W21">
+        <v>1.4</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>12.5</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.03</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.03</v>
+      </c>
+      <c r="AX21">
+        <v>1.01</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.03</v>
+      </c>
+      <c r="BB21">
+        <v>1.03</v>
+      </c>
+      <c r="BC21">
+        <v>1.03</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.03</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>4.5</v>
+      </c>
+      <c r="BI21">
+        <v>2.88</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.29</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.29</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.29</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.29</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.29</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.29</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.29</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.29</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.29</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22">
+        <v>2.7</v>
+      </c>
+      <c r="G22">
+        <v>3.4</v>
+      </c>
+      <c r="H22">
+        <v>2.18</v>
+      </c>
+      <c r="I22">
+        <v>2.6</v>
+      </c>
+      <c r="J22">
+        <v>3.55</v>
+      </c>
+      <c r="K22">
+        <v>5.9</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>2.56</v>
+      </c>
+      <c r="O22">
+        <v>1.15</v>
+      </c>
+      <c r="P22">
+        <v>2.52</v>
+      </c>
+      <c r="Q22">
+        <v>1.45</v>
+      </c>
+      <c r="R22">
+        <v>1.64</v>
+      </c>
+      <c r="S22">
+        <v>2.12</v>
+      </c>
+      <c r="T22">
+        <v>1.43</v>
+      </c>
+      <c r="U22">
+        <v>2.6</v>
+      </c>
+      <c r="V22">
+        <v>1.63</v>
+      </c>
+      <c r="W22">
+        <v>1.42</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>23</v>
+      </c>
+      <c r="AP22">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22">
+        <v>1.03</v>
+      </c>
+      <c r="AR22">
+        <v>1.03</v>
+      </c>
+      <c r="AS22">
+        <v>1.03</v>
+      </c>
+      <c r="AT22">
+        <v>1.03</v>
+      </c>
+      <c r="AU22">
+        <v>1.03</v>
+      </c>
+      <c r="AV22">
+        <v>1.03</v>
+      </c>
+      <c r="AW22">
+        <v>1.03</v>
+      </c>
+      <c r="AX22">
+        <v>1.03</v>
+      </c>
+      <c r="AY22">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22">
+        <v>1.03</v>
+      </c>
+      <c r="BA22">
+        <v>1.03</v>
+      </c>
+      <c r="BB22">
+        <v>1.03</v>
+      </c>
+      <c r="BC22">
+        <v>1.03</v>
+      </c>
+      <c r="BD22">
+        <v>1.03</v>
+      </c>
+      <c r="BE22">
+        <v>1.03</v>
+      </c>
+      <c r="BF22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG22">
+        <v>7.6</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
         <v>125</v>
       </c>
-      <c r="F16">
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23">
+        <v>2.48</v>
+      </c>
+      <c r="G23">
+        <v>2.98</v>
+      </c>
+      <c r="H23">
+        <v>2.58</v>
+      </c>
+      <c r="I23">
+        <v>3.15</v>
+      </c>
+      <c r="J23">
+        <v>3.5</v>
+      </c>
+      <c r="K23">
+        <v>3.85</v>
+      </c>
+      <c r="L23">
+        <v>1.28</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="N23">
+        <v>3.85</v>
+      </c>
+      <c r="O23">
+        <v>1.26</v>
+      </c>
+      <c r="P23">
+        <v>1.97</v>
+      </c>
+      <c r="Q23">
+        <v>1.76</v>
+      </c>
+      <c r="R23">
+        <v>1.42</v>
+      </c>
+      <c r="S23">
+        <v>2.92</v>
+      </c>
+      <c r="T23">
+        <v>1.65</v>
+      </c>
+      <c r="U23">
+        <v>2.1</v>
+      </c>
+      <c r="V23">
+        <v>1.48</v>
+      </c>
+      <c r="W23">
+        <v>1.51</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>34</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>36</v>
+      </c>
+      <c r="AC23">
+        <v>13</v>
+      </c>
+      <c r="AD23">
+        <v>38</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>38</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23">
+        <v>1.18</v>
+      </c>
+      <c r="AR23">
+        <v>1.22</v>
+      </c>
+      <c r="AS23">
+        <v>1.22</v>
+      </c>
+      <c r="AT23">
+        <v>1.18</v>
+      </c>
+      <c r="AU23">
+        <v>1.12</v>
+      </c>
+      <c r="AV23">
+        <v>1.19</v>
+      </c>
+      <c r="AW23">
+        <v>1.22</v>
+      </c>
+      <c r="AX23">
+        <v>1.22</v>
+      </c>
+      <c r="AY23">
+        <v>1.19</v>
+      </c>
+      <c r="AZ23">
+        <v>1.22</v>
+      </c>
+      <c r="BA23">
+        <v>1.22</v>
+      </c>
+      <c r="BB23">
+        <v>1.22</v>
+      </c>
+      <c r="BC23">
+        <v>1.22</v>
+      </c>
+      <c r="BD23">
+        <v>1.22</v>
+      </c>
+      <c r="BE23">
+        <v>1.22</v>
+      </c>
+      <c r="BF23">
+        <v>1.22</v>
+      </c>
+      <c r="BG23">
+        <v>1.22</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>2.88</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24">
+        <v>1.68</v>
+      </c>
+      <c r="G24">
+        <v>1.95</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>6.2</v>
+      </c>
+      <c r="J24">
+        <v>3.65</v>
+      </c>
+      <c r="K24">
+        <v>5.1</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.02</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24">
+        <v>1.24</v>
+      </c>
+      <c r="P24">
+        <v>2.04</v>
+      </c>
+      <c r="Q24">
+        <v>1.7</v>
+      </c>
+      <c r="R24">
+        <v>1.4</v>
+      </c>
+      <c r="S24">
+        <v>2.78</v>
+      </c>
+      <c r="T24">
+        <v>1.69</v>
+      </c>
+      <c r="U24">
+        <v>2.08</v>
+      </c>
+      <c r="V24">
+        <v>1.19</v>
+      </c>
+      <c r="W24">
+        <v>2.06</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>17.5</v>
+      </c>
+      <c r="AC24">
+        <v>15</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>1000</v>
+      </c>
+      <c r="AG24">
+        <v>18</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>16</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.31</v>
+      </c>
+      <c r="AQ24">
+        <v>1.31</v>
+      </c>
+      <c r="AR24">
+        <v>1.31</v>
+      </c>
+      <c r="AS24">
+        <v>1.31</v>
+      </c>
+      <c r="AT24">
+        <v>1.22</v>
+      </c>
+      <c r="AU24">
+        <v>6.6</v>
+      </c>
+      <c r="AV24">
+        <v>1.31</v>
+      </c>
+      <c r="AW24">
+        <v>1.31</v>
+      </c>
+      <c r="AX24">
+        <v>1.31</v>
+      </c>
+      <c r="AY24">
+        <v>7.2</v>
+      </c>
+      <c r="AZ24">
+        <v>1.31</v>
+      </c>
+      <c r="BA24">
+        <v>1.31</v>
+      </c>
+      <c r="BB24">
+        <v>1.31</v>
+      </c>
+      <c r="BC24">
+        <v>1.31</v>
+      </c>
+      <c r="BD24">
+        <v>1.31</v>
+      </c>
+      <c r="BE24">
+        <v>1.31</v>
+      </c>
+      <c r="BF24">
+        <v>1.21</v>
+      </c>
+      <c r="BG24">
+        <v>1.31</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25">
+        <v>2.3</v>
+      </c>
+      <c r="G25">
+        <v>2.52</v>
+      </c>
+      <c r="H25">
+        <v>3.35</v>
+      </c>
+      <c r="I25">
+        <v>3.65</v>
+      </c>
+      <c r="J25">
+        <v>3.3</v>
+      </c>
+      <c r="K25">
+        <v>3.45</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.09</v>
+      </c>
+      <c r="N25">
+        <v>2.94</v>
+      </c>
+      <c r="O25">
+        <v>1.4</v>
+      </c>
+      <c r="P25">
+        <v>1.69</v>
+      </c>
+      <c r="Q25">
         <v>2.18</v>
       </c>
-      <c r="G16">
-        <v>3.55</v>
-      </c>
-      <c r="H16">
-        <v>2.58</v>
-      </c>
-      <c r="I16">
-        <v>3.7</v>
-      </c>
-      <c r="J16">
+      <c r="R25">
+        <v>1.26</v>
+      </c>
+      <c r="S25">
+        <v>4.1</v>
+      </c>
+      <c r="T25">
+        <v>1.89</v>
+      </c>
+      <c r="U25">
+        <v>1.92</v>
+      </c>
+      <c r="V25">
+        <v>1.38</v>
+      </c>
+      <c r="W25">
+        <v>1.66</v>
+      </c>
+      <c r="X25">
+        <v>13</v>
+      </c>
+      <c r="Y25">
+        <v>13</v>
+      </c>
+      <c r="Z25">
+        <v>27</v>
+      </c>
+      <c r="AA25">
+        <v>80</v>
+      </c>
+      <c r="AB25">
+        <v>9</v>
+      </c>
+      <c r="AC25">
+        <v>8</v>
+      </c>
+      <c r="AD25">
+        <v>17</v>
+      </c>
+      <c r="AE25">
+        <v>55</v>
+      </c>
+      <c r="AF25">
+        <v>16.5</v>
+      </c>
+      <c r="AG25">
+        <v>13.5</v>
+      </c>
+      <c r="AH25">
+        <v>23</v>
+      </c>
+      <c r="AI25">
+        <v>70</v>
+      </c>
+      <c r="AJ25">
+        <v>36</v>
+      </c>
+      <c r="AK25">
+        <v>34</v>
+      </c>
+      <c r="AL25">
+        <v>55</v>
+      </c>
+      <c r="AM25">
+        <v>140</v>
+      </c>
+      <c r="AN25">
+        <v>30</v>
+      </c>
+      <c r="AO25">
+        <v>65</v>
+      </c>
+      <c r="AP25">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25">
+        <v>9.6</v>
+      </c>
+      <c r="AR25">
+        <v>20</v>
+      </c>
+      <c r="AS25">
+        <v>6</v>
+      </c>
+      <c r="AT25">
+        <v>7.6</v>
+      </c>
+      <c r="AU25">
+        <v>6.6</v>
+      </c>
+      <c r="AV25">
+        <v>13</v>
+      </c>
+      <c r="AW25">
+        <v>5.9</v>
+      </c>
+      <c r="AX25">
+        <v>12.5</v>
+      </c>
+      <c r="AY25">
+        <v>10</v>
+      </c>
+      <c r="AZ25">
+        <v>17</v>
+      </c>
+      <c r="BA25">
+        <v>6</v>
+      </c>
+      <c r="BB25">
+        <v>5.6</v>
+      </c>
+      <c r="BC25">
+        <v>5.5</v>
+      </c>
+      <c r="BD25">
+        <v>38</v>
+      </c>
+      <c r="BE25">
+        <v>6</v>
+      </c>
+      <c r="BF25">
+        <v>5.4</v>
+      </c>
+      <c r="BG25">
+        <v>6</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>2.44</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>3.45</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26">
         <v>3.05</v>
       </c>
-      <c r="K16">
-        <v>950</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>1.57</v>
-      </c>
-      <c r="Q16">
+      <c r="G26">
+        <v>3.3</v>
+      </c>
+      <c r="H26">
+        <v>2.1</v>
+      </c>
+      <c r="I26">
+        <v>2.24</v>
+      </c>
+      <c r="J26">
+        <v>4.2</v>
+      </c>
+      <c r="K26">
+        <v>4.6</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.02</v>
+      </c>
+      <c r="N26">
+        <v>3.1</v>
+      </c>
+      <c r="O26">
+        <v>1.1</v>
+      </c>
+      <c r="P26">
+        <v>3.1</v>
+      </c>
+      <c r="Q26">
+        <v>1.41</v>
+      </c>
+      <c r="R26">
+        <v>1.77</v>
+      </c>
+      <c r="S26">
+        <v>1.94</v>
+      </c>
+      <c r="T26">
+        <v>1.39</v>
+      </c>
+      <c r="U26">
+        <v>2.76</v>
+      </c>
+      <c r="V26">
+        <v>1.8</v>
+      </c>
+      <c r="W26">
+        <v>1.43</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>22</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>38</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>38</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>38</v>
+      </c>
+      <c r="AL26">
+        <v>38</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>12</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>11.5</v>
+      </c>
+      <c r="AR26">
+        <v>12</v>
+      </c>
+      <c r="AS26">
+        <v>20</v>
+      </c>
+      <c r="AT26">
+        <v>16.5</v>
+      </c>
+      <c r="AU26">
+        <v>7.8</v>
+      </c>
+      <c r="AV26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW26">
+        <v>11.5</v>
+      </c>
+      <c r="AX26">
+        <v>21</v>
+      </c>
+      <c r="AY26">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA26">
+        <v>16</v>
+      </c>
+      <c r="BB26">
+        <v>34</v>
+      </c>
+      <c r="BC26">
+        <v>19</v>
+      </c>
+      <c r="BD26">
+        <v>20</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>9.6</v>
+      </c>
+      <c r="BG26">
+        <v>6</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27">
+        <v>3.15</v>
+      </c>
+      <c r="G27">
+        <v>4.4</v>
+      </c>
+      <c r="H27">
         <v>2.14</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>0</v>
-      </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <v>0</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <v>0</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>0</v>
-      </c>
-      <c r="BT16">
-        <v>0</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>0</v>
-      </c>
-      <c r="BY16">
-        <v>0</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>126</v>
+      <c r="I27">
+        <v>2.5</v>
+      </c>
+      <c r="J27">
+        <v>3.25</v>
+      </c>
+      <c r="K27">
+        <v>3.65</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>1.38</v>
+      </c>
+      <c r="P27">
+        <v>1.6</v>
+      </c>
+      <c r="Q27">
+        <v>2.06</v>
+      </c>
+      <c r="R27">
+        <v>1.17</v>
+      </c>
+      <c r="S27">
+        <v>2.44</v>
+      </c>
+      <c r="T27">
+        <v>1.01</v>
+      </c>
+      <c r="U27">
+        <v>1.01</v>
+      </c>
+      <c r="V27">
+        <v>1.78</v>
+      </c>
+      <c r="W27">
+        <v>1.28</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27">
+        <v>1.01</v>
+      </c>
+      <c r="AR27">
+        <v>1.01</v>
+      </c>
+      <c r="AS27">
+        <v>1.01</v>
+      </c>
+      <c r="AT27">
+        <v>1.01</v>
+      </c>
+      <c r="AU27">
+        <v>1.01</v>
+      </c>
+      <c r="AV27">
+        <v>1.01</v>
+      </c>
+      <c r="AW27">
+        <v>1.01</v>
+      </c>
+      <c r="AX27">
+        <v>1.01</v>
+      </c>
+      <c r="AY27">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27">
+        <v>1.01</v>
+      </c>
+      <c r="BA27">
+        <v>1.01</v>
+      </c>
+      <c r="BB27">
+        <v>1.01</v>
+      </c>
+      <c r="BC27">
+        <v>1.01</v>
+      </c>
+      <c r="BD27">
+        <v>1.01</v>
+      </c>
+      <c r="BE27">
+        <v>1.01</v>
+      </c>
+      <c r="BF27">
+        <v>1.01</v>
+      </c>
+      <c r="BG27">
+        <v>1.01</v>
+      </c>
+      <c r="BH27">
+        <v>3.75</v>
+      </c>
+      <c r="BI27">
+        <v>2.54</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.07</v>
+      </c>
+      <c r="Q28">
+        <v>1.01</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -490,7 +490,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-09-23 16:46:10</t>
+    <t>2026-09-23 18:58:20</t>
   </si>
 </sst>
 </file>
@@ -1084,22 +1084,22 @@
         <v>131</v>
       </c>
       <c r="F2">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1108,34 +1108,34 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X2">
         <v>17</v>
@@ -1147,7 +1147,7 @@
         <v>75</v>
       </c>
       <c r="AA2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB2">
         <v>7.4</v>
@@ -1171,7 +1171,7 @@
         <v>27</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>15</v>
@@ -1183,37 +1183,37 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>8.6</v>
       </c>
       <c r="AV2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>7.6</v>
@@ -1222,28 +1222,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1326,16 +1326,16 @@
         <v>132</v>
       </c>
       <c r="F3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1347,16 +1347,16 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q3">
         <v>1.81</v>
@@ -1374,13 +1374,13 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -1389,19 +1389,19 @@
         <v>85</v>
       </c>
       <c r="AA3">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF3">
         <v>9.199999999999999</v>
@@ -1431,61 +1431,61 @@
         <v>12</v>
       </c>
       <c r="AO3">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR3">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AV3">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AW3">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY3">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BA3">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BF3">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BG3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1571,7 +1571,7 @@
         <v>1.87</v>
       </c>
       <c r="G4">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
         <v>4.3</v>
@@ -1601,13 +1601,13 @@
         <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
         <v>1.72</v>
@@ -1619,7 +1619,7 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1664,7 +1664,7 @@
         <v>20</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM4">
         <v>95</v>
@@ -1688,7 +1688,7 @@
         <v>8.6</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
@@ -1810,19 +1810,19 @@
         <v>134</v>
       </c>
       <c r="F5">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G5">
         <v>1.8</v>
       </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
         <v>3.95</v>
@@ -1834,31 +1834,31 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>2.24</v>
@@ -1867,34 +1867,34 @@
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA5">
         <v>240</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC5">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AE5">
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI5">
         <v>130</v>
@@ -1903,10 +1903,10 @@
         <v>19</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM5">
         <v>230</v>
@@ -1915,10 +1915,10 @@
         <v>15.5</v>
       </c>
       <c r="AO5">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
         <v>14.5</v>
@@ -1927,7 +1927,7 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -1936,13 +1936,13 @@
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -1951,25 +1951,25 @@
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>18</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF5">
         <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2061,7 +2061,7 @@
         <v>2.68</v>
       </c>
       <c r="I6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J6">
         <v>3.3</v>
@@ -2070,16 +2070,16 @@
         <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
         <v>1.96</v>
@@ -2088,10 +2088,10 @@
         <v>1.74</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S6">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2303,13 +2303,13 @@
         <v>5.1</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2324,7 +2324,7 @@
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
         <v>1.98</v>
@@ -2351,13 +2351,13 @@
         <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
         <v>42</v>
       </c>
       <c r="AA7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB7">
         <v>8.4</v>
@@ -2369,7 +2369,7 @@
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF7">
         <v>10.5</v>
@@ -2408,10 +2408,10 @@
         <v>15</v>
       </c>
       <c r="AR7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT7">
         <v>7.8</v>
@@ -2423,7 +2423,7 @@
         <v>18.5</v>
       </c>
       <c r="AW7">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="AX7">
         <v>9.4</v>
@@ -2435,7 +2435,7 @@
         <v>19</v>
       </c>
       <c r="BA7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2447,13 +2447,13 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF7">
         <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="BO7">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP7">
         <v>14.5</v>
@@ -2495,7 +2495,7 @@
         <v>10.5</v>
       </c>
       <c r="BU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2539,7 +2539,7 @@
         <v>1.9</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -2578,7 +2578,7 @@
         <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U8">
         <v>1.97</v>
@@ -2599,7 +2599,7 @@
         <v>36</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB8">
         <v>8.199999999999999</v>
@@ -2617,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
         <v>23</v>
@@ -2662,7 +2662,7 @@
         <v>7.6</v>
       </c>
       <c r="AV8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW8">
         <v>55</v>
@@ -2671,13 +2671,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
         <v>19</v>
       </c>
       <c r="BA8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB8">
         <v>19</v>
@@ -2689,7 +2689,7 @@
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
@@ -3020,7 +3020,7 @@
         <v>139</v>
       </c>
       <c r="F10">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
         <v>1.61</v>
@@ -3029,7 +3029,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
         <v>4.5</v>
@@ -3044,13 +3044,13 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>1.65</v>
@@ -3059,13 +3059,13 @@
         <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
         <v>1.78</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.17</v>
@@ -3095,7 +3095,7 @@
         <v>25</v>
       </c>
       <c r="AE10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3125,7 +3125,7 @@
         <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP10">
         <v>20</v>
@@ -3140,7 +3140,7 @@
         <v>10</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
@@ -3158,13 +3158,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
         <v>14</v>
@@ -3173,7 +3173,7 @@
         <v>21</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>6</v>
@@ -3185,7 +3185,7 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
@@ -3197,7 +3197,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>21</v>
+        <v>2.26</v>
       </c>
       <c r="BN10">
         <v>5</v>
@@ -3215,7 +3215,7 @@
         <v>30</v>
       </c>
       <c r="BS10">
-        <v>13.5</v>
+        <v>2.12</v>
       </c>
       <c r="BT10">
         <v>12.5</v>
@@ -3227,19 +3227,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>21</v>
+        <v>2.2</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>21</v>
+        <v>2.2</v>
       </c>
       <c r="BZ10">
         <v>20</v>
       </c>
       <c r="CA10">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="CB10" t="s">
         <v>158</v>
@@ -3262,7 +3262,7 @@
         <v>140</v>
       </c>
       <c r="F11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -3274,13 +3274,13 @@
         <v>1.48</v>
       </c>
       <c r="J11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5.2</v>
       </c>
       <c r="L11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3292,16 +3292,16 @@
         <v>1.17</v>
       </c>
       <c r="P11">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q11">
         <v>1.53</v>
       </c>
       <c r="R11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
         <v>1.7</v>
@@ -3319,13 +3319,13 @@
         <v>28</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AB11">
         <v>38</v>
@@ -3355,13 +3355,13 @@
         <v>220</v>
       </c>
       <c r="AK11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL11">
         <v>75</v>
       </c>
       <c r="AM11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN11">
         <v>75</v>
@@ -3370,7 +3370,7 @@
         <v>5.2</v>
       </c>
       <c r="AP11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AQ11">
         <v>11</v>
@@ -3394,28 +3394,28 @@
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY11">
         <v>25</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
         <v>23</v>
       </c>
       <c r="BB11">
+        <v>14.5</v>
+      </c>
+      <c r="BC11">
         <v>15</v>
-      </c>
-      <c r="BC11">
-        <v>13.5</v>
       </c>
       <c r="BD11">
         <v>60</v>
       </c>
       <c r="BE11">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BF11">
         <v>60</v>
@@ -3424,58 +3424,58 @@
         <v>4.8</v>
       </c>
       <c r="BH11">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BP11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BV11">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3615,7 +3615,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR12">
         <v>34</v>
@@ -3666,64 +3666,64 @@
         <v>12.5</v>
       </c>
       <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.25</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.94</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.94</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
         <v>3.6</v>
       </c>
-      <c r="BI12">
-        <v>2.84</v>
-      </c>
-      <c r="BJ12">
-        <v>14.5</v>
-      </c>
-      <c r="BK12">
-        <v>7.8</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>3.75</v>
-      </c>
-      <c r="BN12">
-        <v>5.8</v>
-      </c>
-      <c r="BO12">
-        <v>3.4</v>
-      </c>
       <c r="BP12">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="BR12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BT12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>6.4</v>
+        <v>1.94</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>3.55</v>
+        <v>1.94</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="BZ12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -3746,19 +3746,19 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
         <v>3.35</v>
       </c>
       <c r="I13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
         <v>3.75</v>
@@ -3776,28 +3776,28 @@
         <v>1.29</v>
       </c>
       <c r="P13">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R13">
         <v>1.42</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -3806,7 +3806,7 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA13">
         <v>60</v>
@@ -3815,43 +3815,43 @@
         <v>11.5</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH13">
         <v>19.5</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ13">
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM13">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP13">
         <v>15</v>
@@ -3866,28 +3866,28 @@
         <v>50</v>
       </c>
       <c r="AT13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU13">
         <v>7.6</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
         <v>32</v>
       </c>
       <c r="AX13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB13">
         <v>26</v>
@@ -3899,16 +3899,16 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG13">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI13">
         <v>3.35</v>
@@ -3929,7 +3929,7 @@
         <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP13">
         <v>19.5</v>
@@ -3947,7 +3947,7 @@
         <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV13">
         <v>32</v>
@@ -3959,10 +3959,10 @@
         <v>42</v>
       </c>
       <c r="BY13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BZ13">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CA13">
         <v>16.5</v>
@@ -3988,7 +3988,7 @@
         <v>143</v>
       </c>
       <c r="F14">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G14">
         <v>2.44</v>
@@ -4030,13 +4030,13 @@
         <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U14">
         <v>2</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
         <v>1.69</v>
@@ -4069,16 +4069,16 @@
         <v>15</v>
       </c>
       <c r="AG14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI14">
         <v>60</v>
       </c>
       <c r="AJ14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK14">
         <v>34</v>
@@ -4087,7 +4087,7 @@
         <v>55</v>
       </c>
       <c r="AM14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN14">
         <v>26</v>
@@ -4108,7 +4108,7 @@
         <v>55</v>
       </c>
       <c r="AT14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
@@ -4263,7 +4263,7 @@
         <v>1.89</v>
       </c>
       <c r="Q15">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R15">
         <v>1.35</v>
@@ -4275,7 +4275,7 @@
         <v>1.94</v>
       </c>
       <c r="U15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V15">
         <v>1.21</v>
@@ -4407,7 +4407,7 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
         <v>4.3</v>
@@ -4431,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="BU15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV15">
         <v>55</v>
@@ -4490,7 +4490,7 @@
         <v>4.9</v>
       </c>
       <c r="L16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M16">
         <v>1.04</v>
@@ -4565,10 +4565,10 @@
         <v>15</v>
       </c>
       <c r="AK16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM16">
         <v>110</v>
@@ -4580,22 +4580,22 @@
         <v>90</v>
       </c>
       <c r="AP16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR16">
         <v>50</v>
       </c>
       <c r="AS16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT16">
         <v>10</v>
       </c>
       <c r="AU16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV16">
         <v>22</v>
@@ -4610,10 +4610,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA16">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="BB16">
         <v>13.5</v>
@@ -4643,7 +4643,7 @@
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL16">
         <v>130</v>
@@ -4658,13 +4658,13 @@
         <v>3.85</v>
       </c>
       <c r="BP16">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BQ16">
         <v>8.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS16">
         <v>16.5</v>
@@ -4691,7 +4691,7 @@
         <v>16.5</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -4714,7 +4714,7 @@
         <v>146</v>
       </c>
       <c r="F17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G17">
         <v>1.43</v>
@@ -4726,10 +4726,10 @@
         <v>11.5</v>
       </c>
       <c r="J17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K17">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4879,25 +4879,25 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BJ17">
         <v>18</v>
       </c>
       <c r="BK17">
-        <v>7.6</v>
+        <v>1.69</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO17">
-        <v>2.64</v>
+        <v>1.36</v>
       </c>
       <c r="BP17">
         <v>12</v>
@@ -4909,31 +4909,31 @@
         <v>38</v>
       </c>
       <c r="BS17">
-        <v>15.5</v>
+        <v>1.78</v>
       </c>
       <c r="BT17">
         <v>19</v>
       </c>
       <c r="BU17">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BZ17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA17">
-        <v>8.800000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
@@ -4956,7 +4956,7 @@
         <v>147</v>
       </c>
       <c r="F18">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G18">
         <v>2.84</v>
@@ -4965,7 +4965,7 @@
         <v>2.58</v>
       </c>
       <c r="I18">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="J18">
         <v>3.65</v>
@@ -4995,16 +4995,16 @@
         <v>1.45</v>
       </c>
       <c r="S18">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T18">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="U18">
         <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.54</v>
@@ -5064,64 +5064,64 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AU18">
         <v>7.8</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BH18">
         <v>4.3</v>
       </c>
       <c r="BI18">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ18">
         <v>12.5</v>
@@ -5133,49 +5133,49 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BN18">
         <v>8.199999999999999</v>
       </c>
       <c r="BO18">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BR18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BT18">
         <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="BV18">
         <v>28</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BX18">
         <v>40</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BZ18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -5207,13 +5207,13 @@
         <v>5.4</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J19">
         <v>3.35</v>
       </c>
       <c r="K19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5231,10 +5231,10 @@
         <v>1.64</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
         <v>4.7</v>
@@ -5246,13 +5246,13 @@
         <v>1.72</v>
       </c>
       <c r="V19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W19">
         <v>2.06</v>
       </c>
       <c r="X19">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
         <v>1000</v>
@@ -5264,10 +5264,10 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC19">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5276,10 +5276,10 @@
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>1000</v>
@@ -5306,40 +5306,40 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AV19">
         <v>16.5</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AX19">
         <v>8.800000000000001</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AZ19">
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BB19">
         <v>17.5</v>
@@ -5348,16 +5348,16 @@
         <v>17</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BF19">
-        <v>10.5</v>
+        <v>1.72</v>
       </c>
       <c r="BG19">
-        <v>90</v>
+        <v>1.88</v>
       </c>
       <c r="BH19">
         <v>3.5</v>
@@ -5485,7 +5485,7 @@
         <v>1.5</v>
       </c>
       <c r="U20">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -5557,7 +5557,7 @@
         <v>12.5</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
         <v>6.8</v>
@@ -5581,7 +5581,7 @@
         <v>10.5</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
         <v>1.03</v>
@@ -5593,7 +5593,7 @@
         <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>14</v>
@@ -5611,13 +5611,13 @@
         <v>13.5</v>
       </c>
       <c r="BK20">
-        <v>5.9</v>
+        <v>2.58</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>3.15</v>
       </c>
       <c r="BN20">
         <v>7.8</v>
@@ -5629,13 +5629,13 @@
         <v>29</v>
       </c>
       <c r="BQ20">
-        <v>12</v>
+        <v>2.88</v>
       </c>
       <c r="BR20">
         <v>48</v>
       </c>
       <c r="BS20">
-        <v>19</v>
+        <v>2.98</v>
       </c>
       <c r="BT20">
         <v>8.6</v>
@@ -5647,19 +5647,19 @@
         <v>34</v>
       </c>
       <c r="BW20">
-        <v>14</v>
+        <v>2.92</v>
       </c>
       <c r="BX20">
         <v>50</v>
       </c>
       <c r="BY20">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="BZ20">
         <v>40</v>
       </c>
       <c r="CA20">
-        <v>16.5</v>
+        <v>2.96</v>
       </c>
       <c r="CB20" t="s">
         <v>158</v>
@@ -5682,22 +5682,22 @@
         <v>150</v>
       </c>
       <c r="F21">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="G21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H21">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I21">
         <v>2.62</v>
       </c>
       <c r="J21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5706,13 +5706,13 @@
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O21">
         <v>1.25</v>
       </c>
       <c r="P21">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q21">
         <v>1.79</v>
@@ -5721,7 +5721,7 @@
         <v>1.37</v>
       </c>
       <c r="S21">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T21">
         <v>1.63</v>
@@ -5730,10 +5730,10 @@
         <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5751,7 +5751,7 @@
         <v>1000</v>
       </c>
       <c r="AC21">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5930,7 +5930,7 @@
         <v>3.4</v>
       </c>
       <c r="H22">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="I22">
         <v>2.6</v>
@@ -5939,7 +5939,7 @@
         <v>3.55</v>
       </c>
       <c r="K22">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5948,25 +5948,25 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="O22">
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R22">
         <v>1.64</v>
       </c>
       <c r="S22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T22">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U22">
         <v>2.6</v>
@@ -6032,58 +6032,58 @@
         <v>23</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF22">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BG22">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6193,13 +6193,13 @@
         <v>3.85</v>
       </c>
       <c r="O23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P23">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R23">
         <v>1.42</v>
@@ -6235,7 +6235,7 @@
         <v>36</v>
       </c>
       <c r="AC23">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD23">
         <v>38</v>
@@ -6462,7 +6462,7 @@
         <v>2.06</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y24">
         <v>1000</v>
@@ -6474,10 +6474,10 @@
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC24">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD24">
         <v>1000</v>
@@ -6486,10 +6486,10 @@
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG24">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH24">
         <v>1000</v>
@@ -6510,64 +6510,64 @@
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
+        <v>1.38</v>
+      </c>
+      <c r="AQ24">
+        <v>1.41</v>
+      </c>
+      <c r="AR24">
+        <v>1.41</v>
+      </c>
+      <c r="AS24">
+        <v>1.41</v>
+      </c>
+      <c r="AT24">
         <v>1.31</v>
-      </c>
-      <c r="AQ24">
-        <v>1.31</v>
-      </c>
-      <c r="AR24">
-        <v>1.31</v>
-      </c>
-      <c r="AS24">
-        <v>1.31</v>
-      </c>
-      <c r="AT24">
-        <v>1.22</v>
       </c>
       <c r="AU24">
         <v>6.6</v>
       </c>
       <c r="AV24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AW24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AX24">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AY24">
         <v>7.2</v>
       </c>
       <c r="AZ24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BA24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BB24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BC24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BD24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BE24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BF24">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BG24">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6650,10 +6650,10 @@
         <v>154</v>
       </c>
       <c r="F25">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G25">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H25">
         <v>3.35</v>
@@ -6668,13 +6668,13 @@
         <v>3.45</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25">
         <v>1.09</v>
       </c>
       <c r="N25">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>1.4</v>
@@ -6698,10 +6698,10 @@
         <v>1.92</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X25">
         <v>13</v>
@@ -6815,7 +6815,7 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
@@ -6833,7 +6833,7 @@
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
         <v>1000</v>
@@ -6901,7 +6901,7 @@
         <v>2.1</v>
       </c>
       <c r="I26">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J26">
         <v>4.2</v>
@@ -6916,10 +6916,10 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P26">
         <v>3.1</v>
@@ -6928,7 +6928,7 @@
         <v>1.41</v>
       </c>
       <c r="R26">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="S26">
         <v>1.94</v>
@@ -6940,7 +6940,7 @@
         <v>2.76</v>
       </c>
       <c r="V26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W26">
         <v>1.43</v>
@@ -6997,61 +6997,61 @@
         <v>1000</v>
       </c>
       <c r="AO26">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AQ26">
-        <v>11.5</v>
+        <v>1.23</v>
       </c>
       <c r="AR26">
-        <v>12</v>
+        <v>1.3</v>
       </c>
       <c r="AS26">
-        <v>20</v>
+        <v>1.26</v>
       </c>
       <c r="AT26">
         <v>16.5</v>
       </c>
       <c r="AU26">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="AV26">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="AW26">
-        <v>11.5</v>
+        <v>1.3</v>
       </c>
       <c r="AX26">
-        <v>21</v>
+        <v>1.26</v>
       </c>
       <c r="AY26">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="AZ26">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="BA26">
         <v>16</v>
       </c>
       <c r="BB26">
-        <v>34</v>
+        <v>1.3</v>
       </c>
       <c r="BC26">
         <v>19</v>
       </c>
       <c r="BD26">
-        <v>20</v>
+        <v>1.26</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BF26">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="BG26">
-        <v>6</v>
+        <v>1.17</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7134,22 +7134,22 @@
         <v>156</v>
       </c>
       <c r="F27">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="G27">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="H27">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="I27">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="J27">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7158,22 +7158,22 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q27">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
         <v>1.01</v>
@@ -7182,10 +7182,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7242,52 +7242,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7394,208 +7394,208 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
         <v>158</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -490,7 +490,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-09-23 18:58:20</t>
+    <t>2026-09-23 21:10:53</t>
   </si>
 </sst>
 </file>
@@ -1087,10 +1087,10 @@
         <v>1.54</v>
       </c>
       <c r="G2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -1102,22 +1102,22 @@
         <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
         <v>1.33</v>
@@ -1126,7 +1126,7 @@
         <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
         <v>1.81</v>
@@ -1135,7 +1135,7 @@
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
         <v>17</v>
@@ -1144,25 +1144,25 @@
         <v>21</v>
       </c>
       <c r="Z2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>10</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1192,25 +1192,25 @@
         <v>210</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AW2">
         <v>8.199999999999999</v>
@@ -1222,10 +1222,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1234,16 +1234,16 @@
         <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
         <v>7.4</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1329,13 +1329,13 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
         <v>6</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1356,10 +1356,10 @@
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q3">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
         <v>1.3</v>
@@ -1374,10 +1374,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X3">
         <v>17</v>
@@ -1425,7 +1425,7 @@
         <v>65</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN3">
         <v>12</v>
@@ -1434,10 +1434,10 @@
         <v>180</v>
       </c>
       <c r="AP3">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="AR3">
         <v>6.6</v>
@@ -1446,43 +1446,43 @@
         <v>7.2</v>
       </c>
       <c r="AT3">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="AW3">
         <v>7</v>
       </c>
       <c r="AX3">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>7</v>
       </c>
       <c r="BB3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BC3">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
         <v>7</v>
       </c>
       <c r="BF3">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
         <v>7</v>
@@ -1568,10 +1568,10 @@
         <v>133</v>
       </c>
       <c r="F4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H4">
         <v>4.3</v>
@@ -1589,7 +1589,7 @@
         <v>1.02</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
         <v>4.5</v>
@@ -1601,13 +1601,13 @@
         <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T4">
         <v>1.72</v>
@@ -1619,7 +1619,7 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1810,22 +1810,22 @@
         <v>134</v>
       </c>
       <c r="F5">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1834,142 +1834,142 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AA5">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB5">
         <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AI5">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AP5">
         <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
+        <v>7</v>
+      </c>
+      <c r="AY5">
+        <v>8.6</v>
+      </c>
+      <c r="AZ5">
+        <v>7.2</v>
+      </c>
+      <c r="BA5">
         <v>9</v>
       </c>
-      <c r="AY5">
-        <v>9</v>
-      </c>
-      <c r="AZ5">
-        <v>20</v>
-      </c>
-      <c r="BA5">
-        <v>10.5</v>
-      </c>
       <c r="BB5">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BC5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BE5">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2294,7 +2294,7 @@
         <v>136</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G7">
         <v>1.82</v>
@@ -2303,7 +2303,7 @@
         <v>5.1</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
         <v>3.9</v>
@@ -2327,7 +2327,7 @@
         <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R7">
         <v>1.35</v>
@@ -2548,10 +2548,10 @@
         <v>4.8</v>
       </c>
       <c r="J8">
+        <v>3.7</v>
+      </c>
+      <c r="K8">
         <v>3.75</v>
-      </c>
-      <c r="K8">
-        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.44</v>
@@ -2578,7 +2578,7 @@
         <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
         <v>1.97</v>
@@ -2602,10 +2602,10 @@
         <v>120</v>
       </c>
       <c r="AB8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>20</v>
@@ -2623,7 +2623,7 @@
         <v>23</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ8">
         <v>22</v>
@@ -2653,7 +2653,7 @@
         <v>30</v>
       </c>
       <c r="AS8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT8">
         <v>7.4</v>
@@ -2677,13 +2677,13 @@
         <v>19</v>
       </c>
       <c r="BA8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB8">
         <v>19</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD8">
         <v>34</v>
@@ -2692,10 +2692,10 @@
         <v>12.5</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH8">
         <v>3.25</v>
@@ -2722,22 +2722,22 @@
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
         <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS8">
         <v>21</v>
       </c>
       <c r="BT8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV8">
         <v>44</v>
@@ -2752,10 +2752,10 @@
         <v>38</v>
       </c>
       <c r="BZ8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -2826,7 +2826,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
         <v>3.1</v>
@@ -3044,40 +3044,40 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
         <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z10">
         <v>65</v>
@@ -3128,7 +3128,7 @@
         <v>85</v>
       </c>
       <c r="AP10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10">
         <v>22</v>
@@ -3137,7 +3137,7 @@
         <v>40</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
         <v>9.199999999999999</v>
@@ -3149,7 +3149,7 @@
         <v>21</v>
       </c>
       <c r="AW10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3161,7 +3161,7 @@
         <v>18</v>
       </c>
       <c r="BA10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3179,7 +3179,7 @@
         <v>6</v>
       </c>
       <c r="BG10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3298,10 +3298,10 @@
         <v>1.53</v>
       </c>
       <c r="R11">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
         <v>1.7</v>
@@ -3322,7 +3322,7 @@
         <v>12</v>
       </c>
       <c r="Z11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA11">
         <v>14.5</v>
@@ -3370,10 +3370,10 @@
         <v>5.2</v>
       </c>
       <c r="AP11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR11">
         <v>10</v>
@@ -3400,16 +3400,16 @@
         <v>25</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
         <v>23</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD11">
         <v>60</v>
@@ -3421,7 +3421,7 @@
         <v>60</v>
       </c>
       <c r="BG11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3504,13 +3504,13 @@
         <v>141</v>
       </c>
       <c r="F12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G12">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I12">
         <v>5.5</v>
@@ -3546,7 +3546,7 @@
         <v>3.7</v>
       </c>
       <c r="T12">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U12">
         <v>1.96</v>
@@ -3555,7 +3555,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -3582,7 +3582,7 @@
         <v>90</v>
       </c>
       <c r="AF12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -3612,16 +3612,16 @@
         <v>100</v>
       </c>
       <c r="AP12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR12">
         <v>34</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT12">
         <v>7.6</v>
@@ -3657,13 +3657,13 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
         <v>11</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3681,13 +3681,13 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -3746,16 +3746,16 @@
         <v>142</v>
       </c>
       <c r="F13">
+        <v>2.26</v>
+      </c>
+      <c r="G13">
         <v>2.3</v>
       </c>
-      <c r="G13">
-        <v>2.32</v>
-      </c>
       <c r="H13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
         <v>3.7</v>
@@ -3782,10 +3782,10 @@
         <v>1.84</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
         <v>1.7</v>
@@ -3794,10 +3794,10 @@
         <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -3830,7 +3830,7 @@
         <v>11</v>
       </c>
       <c r="AH13">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
         <v>44</v>
@@ -3839,7 +3839,7 @@
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL13">
         <v>34</v>
@@ -3872,7 +3872,7 @@
         <v>7.6</v>
       </c>
       <c r="AV13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW13">
         <v>32</v>
@@ -3887,10 +3887,10 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BB13">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BC13">
         <v>21</v>
@@ -3959,7 +3959,7 @@
         <v>42</v>
       </c>
       <c r="BY13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BZ13">
         <v>23</v>
@@ -3988,7 +3988,7 @@
         <v>143</v>
       </c>
       <c r="F14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
         <v>2.44</v>
@@ -4030,13 +4030,13 @@
         <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
         <v>1.69</v>
@@ -4069,7 +4069,7 @@
         <v>15</v>
       </c>
       <c r="AG14">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
         <v>21</v>
@@ -4093,7 +4093,7 @@
         <v>26</v>
       </c>
       <c r="AO14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP14">
         <v>10.5</v>
@@ -4108,7 +4108,7 @@
         <v>55</v>
       </c>
       <c r="AT14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
@@ -4150,64 +4150,64 @@
         <v>38</v>
       </c>
       <c r="BH14">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL14">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BR14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>158</v>
@@ -4260,7 +4260,7 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4356,7 +4356,7 @@
         <v>7.8</v>
       </c>
       <c r="AV15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW15">
         <v>10.5</v>
@@ -4643,7 +4643,7 @@
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL16">
         <v>130</v>
@@ -4664,7 +4664,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS16">
         <v>16.5</v>
@@ -4691,7 +4691,7 @@
         <v>16.5</v>
       </c>
       <c r="CA16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -4714,22 +4714,22 @@
         <v>146</v>
       </c>
       <c r="F17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H17">
         <v>9.6</v>
       </c>
       <c r="I17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J17">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4741,7 +4741,7 @@
         <v>4</v>
       </c>
       <c r="O17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P17">
         <v>2.1</v>
@@ -4750,7 +4750,7 @@
         <v>1.79</v>
       </c>
       <c r="R17">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
         <v>2.94</v>
@@ -4759,10 +4759,10 @@
         <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W17">
         <v>3.25</v>
@@ -4804,7 +4804,7 @@
         <v>190</v>
       </c>
       <c r="AJ17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK17">
         <v>19.5</v>
@@ -4828,7 +4828,7 @@
         <v>21</v>
       </c>
       <c r="AR17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AS17">
         <v>6.2</v>
@@ -4840,10 +4840,10 @@
         <v>10</v>
       </c>
       <c r="AV17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX17">
         <v>7</v>
@@ -4858,22 +4858,22 @@
         <v>6</v>
       </c>
       <c r="BB17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC17">
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF17">
         <v>6</v>
       </c>
       <c r="BG17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4897,7 +4897,7 @@
         <v>5</v>
       </c>
       <c r="BO17">
-        <v>1.36</v>
+        <v>2.64</v>
       </c>
       <c r="BP17">
         <v>12</v>
@@ -4956,22 +4956,22 @@
         <v>147</v>
       </c>
       <c r="F18">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G18">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="H18">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I18">
         <v>2.76</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4980,7 +4980,7 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
         <v>1.24</v>
@@ -4989,7 +4989,7 @@
         <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R18">
         <v>1.45</v>
@@ -5004,10 +5004,10 @@
         <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W18">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5043,7 +5043,7 @@
         <v>1000</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
@@ -5052,7 +5052,7 @@
         <v>1000</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM18">
         <v>1000</v>
@@ -5064,61 +5064,61 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AS18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AT18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU18">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AW18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AX18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
       </c>
       <c r="AZ18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BA18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BB18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BD18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BE18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BF18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BG18">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BH18">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
         <v>3.3</v>
@@ -5127,55 +5127,55 @@
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>5.6</v>
+        <v>2.76</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="BN18">
         <v>8.199999999999999</v>
       </c>
       <c r="BO18">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="BP18">
         <v>29</v>
       </c>
       <c r="BQ18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BR18">
         <v>44</v>
       </c>
       <c r="BS18">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BT18">
         <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BV18">
         <v>28</v>
       </c>
       <c r="BW18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BX18">
         <v>40</v>
       </c>
       <c r="BY18">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BZ18">
         <v>30</v>
       </c>
       <c r="CA18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -5222,19 +5222,19 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R19">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S19">
         <v>4.7</v>
@@ -5243,7 +5243,7 @@
         <v>1.99</v>
       </c>
       <c r="U19">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V19">
         <v>1.2</v>
@@ -5252,7 +5252,7 @@
         <v>2.06</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
         <v>1000</v>
@@ -5267,7 +5267,7 @@
         <v>7.8</v>
       </c>
       <c r="AC19">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5276,7 +5276,7 @@
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG19">
         <v>11.5</v>
@@ -5306,40 +5306,40 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AQ19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AS19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AT19">
-        <v>5.9</v>
+        <v>1.59</v>
       </c>
       <c r="AU19">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AV19">
         <v>16.5</v>
       </c>
       <c r="AW19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AX19">
         <v>8.800000000000001</v>
       </c>
       <c r="AY19">
-        <v>1.61</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BB19">
         <v>17.5</v>
@@ -5348,16 +5348,16 @@
         <v>17</v>
       </c>
       <c r="BD19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BE19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BF19">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="BG19">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BH19">
         <v>3.5</v>
@@ -5446,7 +5446,7 @@
         <v>2.78</v>
       </c>
       <c r="H20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I20">
         <v>3.25</v>
@@ -5488,7 +5488,7 @@
         <v>1.79</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
         <v>1.56</v>
@@ -5682,46 +5682,46 @@
         <v>150</v>
       </c>
       <c r="F21">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H21">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I21">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J21">
         <v>3.5</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
         <v>4.1</v>
       </c>
       <c r="O21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P21">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q21">
         <v>1.79</v>
       </c>
       <c r="R21">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S21">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T21">
         <v>1.63</v>
@@ -5730,7 +5730,7 @@
         <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W21">
         <v>1.42</v>
@@ -6166,7 +6166,7 @@
         <v>152</v>
       </c>
       <c r="F23">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G23">
         <v>2.98</v>
@@ -6181,7 +6181,7 @@
         <v>3.5</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>1.28</v>
@@ -6196,10 +6196,10 @@
         <v>1.25</v>
       </c>
       <c r="P23">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q23">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R23">
         <v>1.42</v>
@@ -6414,13 +6414,13 @@
         <v>1.95</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24">
         <v>6.2</v>
       </c>
       <c r="J24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24">
         <v>5.1</v>
@@ -6432,22 +6432,22 @@
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O24">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P24">
         <v>2.04</v>
       </c>
       <c r="Q24">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R24">
         <v>1.4</v>
       </c>
       <c r="S24">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T24">
         <v>1.69</v>
@@ -6653,13 +6653,13 @@
         <v>2.32</v>
       </c>
       <c r="G25">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H25">
         <v>3.35</v>
       </c>
       <c r="I25">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J25">
         <v>3.3</v>
@@ -6698,10 +6698,10 @@
         <v>1.92</v>
       </c>
       <c r="V25">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X25">
         <v>13</v>
@@ -6907,7 +6907,7 @@
         <v>4.2</v>
       </c>
       <c r="K26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6919,7 +6919,7 @@
         <v>3.75</v>
       </c>
       <c r="O26">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P26">
         <v>3.1</v>
@@ -6928,13 +6928,13 @@
         <v>1.41</v>
       </c>
       <c r="R26">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S26">
         <v>1.94</v>
       </c>
       <c r="T26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U26">
         <v>2.76</v>
@@ -7000,13 +7000,13 @@
         <v>970</v>
       </c>
       <c r="AP26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AQ26">
         <v>1.23</v>
       </c>
       <c r="AR26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AS26">
         <v>1.26</v>
@@ -7015,28 +7015,28 @@
         <v>16.5</v>
       </c>
       <c r="AU26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AV26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AW26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AX26">
         <v>1.26</v>
       </c>
       <c r="AY26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AZ26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BA26">
         <v>16</v>
       </c>
       <c r="BB26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BC26">
         <v>19</v>
@@ -7045,10 +7045,10 @@
         <v>1.26</v>
       </c>
       <c r="BE26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BG26">
         <v>1.17</v>
@@ -7134,19 +7134,19 @@
         <v>156</v>
       </c>
       <c r="F27">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="G27">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="H27">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="I27">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7155,91 +7155,91 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P27">
         <v>1.65</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V27">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP27">
         <v>1.03</v>
@@ -7293,7 +7293,7 @@
         <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH27">
         <v>3.75</v>
@@ -7400,13 +7400,13 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O28">
         <v>1.37</v>
       </c>
       <c r="P28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q28">
         <v>1.37</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -490,7 +490,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-09-23 21:10:53</t>
+    <t>2026-09-23 23:23:35</t>
   </si>
 </sst>
 </file>
@@ -1084,19 +1084,19 @@
         <v>131</v>
       </c>
       <c r="F2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H2">
         <v>6.6</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
         <v>4.7</v>
@@ -1108,37 +1108,37 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>21</v>
@@ -1195,13 +1195,13 @@
         <v>13</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1210,22 +1210,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2">
         <v>7.6</v>
       </c>
       <c r="AY2">
+        <v>9</v>
+      </c>
+      <c r="AZ2">
+        <v>7.2</v>
+      </c>
+      <c r="BA2">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>6.6</v>
-      </c>
-      <c r="BA2">
-        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1234,16 +1234,16 @@
         <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1326,58 +1326,58 @@
         <v>132</v>
       </c>
       <c r="F3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
         <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X3">
         <v>17</v>
@@ -1392,7 +1392,7 @@
         <v>250</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>9.800000000000001</v>
@@ -1404,10 +1404,10 @@
         <v>130</v>
       </c>
       <c r="AF3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1428,34 +1428,34 @@
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
         <v>180</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3">
         <v>17</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
         <v>21</v>
       </c>
       <c r="AW3">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1467,7 +1467,7 @@
         <v>20</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1476,16 +1476,16 @@
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1571,10 +1571,10 @@
         <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
         <v>4.7</v>
@@ -1607,7 +1607,7 @@
         <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
         <v>1.72</v>
@@ -1619,7 +1619,7 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1661,16 +1661,16 @@
         <v>22</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM4">
         <v>95</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
         <v>55</v>
@@ -1682,10 +1682,10 @@
         <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4">
         <v>9.4</v>
@@ -1697,7 +1697,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1718,16 +1718,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1810,166 +1810,166 @@
         <v>134</v>
       </c>
       <c r="F5">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="G5">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
+        <v>2.08</v>
+      </c>
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.9</v>
+      </c>
+      <c r="T5">
         <v>1.97</v>
       </c>
-      <c r="R5">
-        <v>1.31</v>
-      </c>
-      <c r="S5">
-        <v>3.55</v>
-      </c>
-      <c r="T5">
-        <v>1.98</v>
-      </c>
       <c r="U5">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="AB5">
         <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>130</v>
+      </c>
+      <c r="AJ5">
+        <v>20</v>
+      </c>
+      <c r="AK5">
+        <v>26</v>
+      </c>
+      <c r="AL5">
+        <v>46</v>
+      </c>
+      <c r="AM5">
+        <v>160</v>
+      </c>
+      <c r="AN5">
+        <v>14.5</v>
+      </c>
+      <c r="AO5">
+        <v>120</v>
+      </c>
+      <c r="AP5">
+        <v>11</v>
+      </c>
+      <c r="AQ5">
+        <v>14</v>
+      </c>
+      <c r="AR5">
         <v>34</v>
       </c>
-      <c r="AI5">
-        <v>170</v>
-      </c>
-      <c r="AJ5">
-        <v>17</v>
-      </c>
-      <c r="AK5">
-        <v>19.5</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>240</v>
-      </c>
-      <c r="AN5">
-        <v>11.5</v>
-      </c>
-      <c r="AO5">
-        <v>180</v>
-      </c>
-      <c r="AP5">
+      <c r="AS5">
+        <v>10</v>
+      </c>
+      <c r="AT5">
+        <v>6.8</v>
+      </c>
+      <c r="AU5">
+        <v>7.6</v>
+      </c>
+      <c r="AV5">
+        <v>18</v>
+      </c>
+      <c r="AW5">
         <v>10.5</v>
       </c>
-      <c r="AQ5">
-        <v>15.5</v>
-      </c>
-      <c r="AR5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS5">
+      <c r="AX5">
+        <v>9</v>
+      </c>
+      <c r="AY5">
         <v>9.4</v>
       </c>
-      <c r="AT5">
-        <v>4.5</v>
-      </c>
-      <c r="AU5">
-        <v>5.1</v>
-      </c>
-      <c r="AV5">
-        <v>7.4</v>
-      </c>
-      <c r="AW5">
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB5">
+        <v>16.5</v>
+      </c>
+      <c r="BC5">
+        <v>18</v>
+      </c>
+      <c r="BD5">
         <v>9.6</v>
       </c>
-      <c r="AX5">
-        <v>7</v>
-      </c>
-      <c r="AY5">
-        <v>8.6</v>
-      </c>
-      <c r="AZ5">
-        <v>7.2</v>
-      </c>
-      <c r="BA5">
-        <v>9</v>
-      </c>
-      <c r="BB5">
-        <v>6.2</v>
-      </c>
-      <c r="BC5">
-        <v>15</v>
-      </c>
-      <c r="BD5">
-        <v>8</v>
-      </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2055,7 +2055,7 @@
         <v>2.3</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
         <v>2.68</v>
@@ -2091,7 +2091,7 @@
         <v>1.37</v>
       </c>
       <c r="S6">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2103,7 +2103,7 @@
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2297,19 +2297,19 @@
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I7">
         <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2336,7 +2336,7 @@
         <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
         <v>1.98</v>
@@ -2345,7 +2345,7 @@
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X7">
         <v>14.5</v>
@@ -2369,7 +2369,7 @@
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF7">
         <v>10.5</v>
@@ -2429,7 +2429,7 @@
         <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
         <v>19</v>
@@ -2536,10 +2536,10 @@
         <v>137</v>
       </c>
       <c r="F8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -2548,52 +2548,52 @@
         <v>4.8</v>
       </c>
       <c r="J8">
+        <v>3.65</v>
+      </c>
+      <c r="K8">
         <v>3.7</v>
-      </c>
-      <c r="K8">
-        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.44</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V8">
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
         <v>36</v>
@@ -2602,16 +2602,16 @@
         <v>120</v>
       </c>
       <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
         <v>8.4</v>
-      </c>
-      <c r="AC8">
-        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>20</v>
       </c>
       <c r="AE8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF8">
         <v>11</v>
@@ -2623,10 +2623,10 @@
         <v>23</v>
       </c>
       <c r="AI8">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -2635,19 +2635,19 @@
         <v>46</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN8">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO8">
         <v>90</v>
       </c>
       <c r="AP8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
         <v>30</v>
@@ -2656,13 +2656,13 @@
         <v>12.5</v>
       </c>
       <c r="AT8">
+        <v>7.2</v>
+      </c>
+      <c r="AU8">
         <v>7.4</v>
       </c>
-      <c r="AU8">
-        <v>7.6</v>
-      </c>
       <c r="AV8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW8">
         <v>55</v>
@@ -2674,40 +2674,40 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BB8">
         <v>19</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE8">
         <v>12.5</v>
       </c>
       <c r="BF8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BH8">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI8">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2725,7 +2725,7 @@
         <v>14</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR8">
         <v>32</v>
@@ -2740,19 +2740,19 @@
         <v>7</v>
       </c>
       <c r="BV8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW8">
         <v>30</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY8">
         <v>38</v>
       </c>
       <c r="BZ8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="CA8">
         <v>19.5</v>
@@ -3262,10 +3262,10 @@
         <v>140</v>
       </c>
       <c r="F11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H11">
         <v>1.47</v>
@@ -3277,7 +3277,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
         <v>1.27</v>
@@ -3295,7 +3295,7 @@
         <v>2.76</v>
       </c>
       <c r="Q11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
         <v>1.71</v>
@@ -3382,7 +3382,7 @@
         <v>13</v>
       </c>
       <c r="AT11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AU11">
         <v>11</v>
@@ -3394,7 +3394,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY11">
         <v>25</v>
@@ -3418,7 +3418,7 @@
         <v>65</v>
       </c>
       <c r="BF11">
-        <v>60</v>
+        <v>14.5</v>
       </c>
       <c r="BG11">
         <v>4.7</v>
@@ -3504,13 +3504,13 @@
         <v>141</v>
       </c>
       <c r="F12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
         <v>5.5</v>
@@ -3549,13 +3549,13 @@
         <v>1.94</v>
       </c>
       <c r="U12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -3564,7 +3564,7 @@
         <v>18</v>
       </c>
       <c r="Z12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA12">
         <v>160</v>
@@ -3579,7 +3579,7 @@
         <v>21</v>
       </c>
       <c r="AE12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF12">
         <v>10</v>
@@ -3621,13 +3621,13 @@
         <v>34</v>
       </c>
       <c r="AS12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT12">
         <v>7.6</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>18.5</v>
@@ -3648,7 +3648,7 @@
         <v>65</v>
       </c>
       <c r="BB12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC12">
         <v>17.5</v>
@@ -3746,13 +3746,13 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I13">
         <v>3.45</v>
@@ -3794,10 +3794,10 @@
         <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -3872,7 +3872,7 @@
         <v>7.6</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
         <v>32</v>
@@ -3881,13 +3881,13 @@
         <v>14</v>
       </c>
       <c r="AY13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BB13">
         <v>11.5</v>
@@ -3988,16 +3988,16 @@
         <v>143</v>
       </c>
       <c r="F14">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G14">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I14">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J14">
         <v>3.4</v>
@@ -4021,7 +4021,7 @@
         <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
         <v>1.29</v>
@@ -4033,13 +4033,13 @@
         <v>1.88</v>
       </c>
       <c r="U14">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X14">
         <v>12</v>
@@ -4048,7 +4048,7 @@
         <v>12</v>
       </c>
       <c r="Z14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA14">
         <v>65</v>
@@ -4069,16 +4069,16 @@
         <v>15</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI14">
         <v>60</v>
       </c>
       <c r="AJ14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK14">
         <v>34</v>
@@ -4090,10 +4090,10 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP14">
         <v>10.5</v>
@@ -4102,7 +4102,7 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS14">
         <v>55</v>
@@ -4141,7 +4141,7 @@
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF14">
         <v>19.5</v>
@@ -4260,7 +4260,7 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4290,7 +4290,7 @@
         <v>18</v>
       </c>
       <c r="Z15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA15">
         <v>180</v>
@@ -4356,7 +4356,7 @@
         <v>7.8</v>
       </c>
       <c r="AV15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW15">
         <v>10.5</v>
@@ -4580,7 +4580,7 @@
         <v>90</v>
       </c>
       <c r="AP16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16">
         <v>23</v>
@@ -4628,7 +4628,7 @@
         <v>16.5</v>
       </c>
       <c r="BF16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG16">
         <v>16</v>
@@ -4658,13 +4658,13 @@
         <v>3.85</v>
       </c>
       <c r="BP16">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BQ16">
         <v>8.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS16">
         <v>16.5</v>
@@ -4691,7 +4691,7 @@
         <v>16.5</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="s">
         <v>158</v>
@@ -4750,7 +4750,7 @@
         <v>1.79</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17">
         <v>2.94</v>
@@ -4897,7 +4897,7 @@
         <v>5</v>
       </c>
       <c r="BO17">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BP17">
         <v>12</v>
@@ -4959,7 +4959,7 @@
         <v>2.66</v>
       </c>
       <c r="G18">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H18">
         <v>2.54</v>
@@ -4971,7 +4971,7 @@
         <v>3.55</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4980,7 +4980,7 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
         <v>1.24</v>
@@ -4995,7 +4995,7 @@
         <v>1.45</v>
       </c>
       <c r="S18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T18">
         <v>1.57</v>
@@ -5121,19 +5121,19 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18">
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>2.76</v>
+        <v>5.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BN18">
         <v>8.199999999999999</v>
@@ -5172,7 +5172,7 @@
         <v>3.25</v>
       </c>
       <c r="BZ18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA18">
         <v>3.15</v>
@@ -5252,7 +5252,7 @@
         <v>2.06</v>
       </c>
       <c r="X19">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y19">
         <v>1000</v>
@@ -5264,7 +5264,7 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC19">
         <v>970</v>
@@ -5279,7 +5279,7 @@
         <v>970</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH19">
         <v>1000</v>
@@ -5306,40 +5306,40 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AS19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AT19">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AU19">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="AV19">
         <v>16.5</v>
       </c>
       <c r="AW19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AX19">
         <v>8.800000000000001</v>
       </c>
       <c r="AY19">
-        <v>8.800000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="AZ19">
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BB19">
         <v>17.5</v>
@@ -5348,16 +5348,16 @@
         <v>17</v>
       </c>
       <c r="BD19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BE19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BF19">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="BG19">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BH19">
         <v>3.5</v>
@@ -5440,58 +5440,58 @@
         <v>149</v>
       </c>
       <c r="F20">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G20">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H20">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J20">
+        <v>3.35</v>
+      </c>
+      <c r="K20">
+        <v>3.7</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
+        <v>3.55</v>
+      </c>
+      <c r="O20">
+        <v>1.32</v>
+      </c>
+      <c r="P20">
+        <v>1.88</v>
+      </c>
+      <c r="Q20">
+        <v>1.87</v>
+      </c>
+      <c r="R20">
+        <v>1.37</v>
+      </c>
+      <c r="S20">
         <v>3.3</v>
       </c>
-      <c r="K20">
-        <v>3.75</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.05</v>
-      </c>
-      <c r="N20">
-        <v>3.15</v>
-      </c>
-      <c r="O20">
-        <v>1.27</v>
-      </c>
-      <c r="P20">
-        <v>1.89</v>
-      </c>
-      <c r="Q20">
-        <v>1.94</v>
-      </c>
-      <c r="R20">
-        <v>1.23</v>
-      </c>
-      <c r="S20">
-        <v>2.5</v>
-      </c>
       <c r="T20">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="U20">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
         <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5548,7 +5548,7 @@
         <v>46</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
         <v>7.4</v>
@@ -5557,7 +5557,7 @@
         <v>12.5</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AT20">
         <v>6.8</v>
@@ -5569,7 +5569,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AX20">
         <v>10.5</v>
@@ -5581,19 +5581,19 @@
         <v>10.5</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BC20">
         <v>16.5</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BF20">
         <v>14</v>
@@ -5602,7 +5602,7 @@
         <v>18.5</v>
       </c>
       <c r="BH20">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
         <v>2.7</v>
@@ -5611,13 +5611,13 @@
         <v>13.5</v>
       </c>
       <c r="BK20">
-        <v>2.58</v>
+        <v>1.6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="BN20">
         <v>7.8</v>
@@ -5629,13 +5629,13 @@
         <v>29</v>
       </c>
       <c r="BQ20">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="BR20">
         <v>48</v>
       </c>
       <c r="BS20">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="BT20">
         <v>8.6</v>
@@ -5647,19 +5647,19 @@
         <v>34</v>
       </c>
       <c r="BW20">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="BX20">
         <v>50</v>
       </c>
       <c r="BY20">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="BZ20">
         <v>40</v>
       </c>
       <c r="CA20">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="CB20" t="s">
         <v>158</v>
@@ -5694,10 +5694,10 @@
         <v>2.68</v>
       </c>
       <c r="J21">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5706,22 +5706,22 @@
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R21">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T21">
         <v>1.63</v>
@@ -5748,7 +5748,7 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC21">
         <v>970</v>
@@ -5790,61 +5790,61 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS21">
+        <v>1.12</v>
+      </c>
+      <c r="AT21">
+        <v>1.08</v>
+      </c>
+      <c r="AU21">
         <v>1.03</v>
       </c>
-      <c r="AT21">
-        <v>1.01</v>
-      </c>
-      <c r="AU21">
-        <v>1.01</v>
-      </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH21">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
         <v>2.88</v>
@@ -5853,55 +5853,55 @@
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>158</v>
@@ -5930,16 +5930,16 @@
         <v>3.4</v>
       </c>
       <c r="H22">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I22">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J22">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5948,13 +5948,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
@@ -5963,7 +5963,7 @@
         <v>1.64</v>
       </c>
       <c r="S22">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T22">
         <v>1.45</v>
@@ -5972,7 +5972,7 @@
         <v>2.6</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W22">
         <v>1.42</v>
@@ -6029,58 +6029,58 @@
         <v>1000</v>
       </c>
       <c r="AO22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AQ22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AR22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AS22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AT22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AU22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AV22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AW22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AX22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AY22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AZ22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BA22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BB22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BC22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BD22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BE22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BF22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG22">
         <v>1.01</v>
@@ -6193,13 +6193,13 @@
         <v>3.85</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P23">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R23">
         <v>1.42</v>
@@ -6411,7 +6411,7 @@
         <v>1.68</v>
       </c>
       <c r="G24">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H24">
         <v>4.1</v>
@@ -6420,7 +6420,7 @@
         <v>6.2</v>
       </c>
       <c r="J24">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
         <v>5.1</v>
@@ -6447,13 +6447,13 @@
         <v>1.4</v>
       </c>
       <c r="S24">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="T24">
         <v>1.69</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V24">
         <v>1.19</v>
@@ -6650,13 +6650,13 @@
         <v>154</v>
       </c>
       <c r="F25">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G25">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I25">
         <v>3.7</v>
@@ -6674,13 +6674,13 @@
         <v>1.09</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P25">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q25">
         <v>2.18</v>
@@ -6701,7 +6701,7 @@
         <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X25">
         <v>13</v>
@@ -6901,7 +6901,7 @@
         <v>2.1</v>
       </c>
       <c r="I26">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J26">
         <v>4.2</v>
@@ -6919,7 +6919,7 @@
         <v>3.75</v>
       </c>
       <c r="O26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P26">
         <v>3.1</v>
@@ -6928,19 +6928,19 @@
         <v>1.41</v>
       </c>
       <c r="R26">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S26">
         <v>1.94</v>
       </c>
       <c r="T26">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U26">
         <v>2.76</v>
       </c>
       <c r="V26">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W26">
         <v>1.43</v>
@@ -6976,7 +6976,7 @@
         <v>1000</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI26">
         <v>1000</v>
@@ -7000,34 +7000,34 @@
         <v>970</v>
       </c>
       <c r="AP26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ26">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>1.31</v>
+        <v>16.5</v>
       </c>
       <c r="AS26">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT26">
         <v>16.5</v>
       </c>
       <c r="AU26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AV26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AW26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AX26">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AY26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26">
         <v>1.31</v>
@@ -7036,22 +7036,22 @@
         <v>16</v>
       </c>
       <c r="BB26">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BC26">
         <v>19</v>
       </c>
       <c r="BD26">
+        <v>1.36</v>
+      </c>
+      <c r="BE26">
+        <v>1.41</v>
+      </c>
+      <c r="BF26">
+        <v>1.41</v>
+      </c>
+      <c r="BG26">
         <v>1.26</v>
-      </c>
-      <c r="BE26">
-        <v>1.31</v>
-      </c>
-      <c r="BF26">
-        <v>1.31</v>
-      </c>
-      <c r="BG26">
-        <v>1.17</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7173,13 +7173,13 @@
         <v>1.24</v>
       </c>
       <c r="S27">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U27">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="V27">
         <v>1.62</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="178">
   <si>
     <t>League</t>
   </si>
@@ -283,15 +283,21 @@
     <t>Irish Division 1</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
-    <t>CONCACAF Nations League B</t>
-  </si>
-  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Argentinian Primera B Metropolitana</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-09-25</t>
   </si>
   <si>
@@ -328,6 +334,21 @@
     <t>19:30:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:10:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Dominican Republic</t>
   </si>
   <si>
@@ -376,15 +397,18 @@
     <t>Inverness CT</t>
   </si>
   <si>
+    <t>Ayr</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Raith</t>
+  </si>
+  <si>
     <t>Galway Utd</t>
   </si>
   <si>
-    <t>Arbroath</t>
-  </si>
-  <si>
-    <t>Raith</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
@@ -397,18 +421,33 @@
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Ayr</t>
+    <t>Bermuda</t>
   </si>
   <si>
     <t>FC Dordrecht</t>
   </si>
   <si>
-    <t>Bermuda</t>
-  </si>
-  <si>
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>CA Ituzaingo</t>
+  </si>
+  <si>
+    <t>Nacional (Par)</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Excursionistas</t>
+  </si>
+  <si>
+    <t>Boyaca Chico</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>Nicaragua</t>
   </si>
   <si>
@@ -457,15 +496,18 @@
     <t>Morton</t>
   </si>
   <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
+    <t>Queens Park</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Queens Park</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
     <t>Athlone Town</t>
   </si>
   <si>
@@ -478,19 +520,34 @@
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Stenhousemuir</t>
+    <t>Guadeloupe</t>
   </si>
   <si>
     <t>Almere City</t>
   </si>
   <si>
-    <t>Guadeloupe</t>
-  </si>
-  <si>
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-09-23 23:23:35</t>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Club Sportivo Ameliano</t>
+  </si>
+  <si>
+    <t>Sao Bernardo</t>
+  </si>
+  <si>
+    <t>Real Pilar FC</t>
+  </si>
+  <si>
+    <t>Deportivo Pasto</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>2026-09-24 01:37:00</t>
   </si>
 </sst>
 </file>
@@ -822,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1072,58 +1129,58 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F2">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -1132,118 +1189,118 @@
         <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z2">
         <v>70</v>
       </c>
       <c r="AA2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2">
         <v>140</v>
       </c>
       <c r="AF2">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV2">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1306,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1314,19 +1371,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G3">
         <v>1.67</v>
@@ -1335,94 +1392,94 @@
         <v>6.2</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
         <v>2.48</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y3">
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA3">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE3">
         <v>130</v>
       </c>
       <c r="AF3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>180</v>
@@ -1431,7 +1488,7 @@
         <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP3">
         <v>12.5</v>
@@ -1440,10 +1497,10 @@
         <v>17</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="AS3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1452,16 +1509,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AW3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
         <v>20</v>
@@ -1473,25 +1530,25 @@
         <v>13</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD3">
         <v>29</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
         <v>8.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1548,7 +1605,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1556,22 +1613,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F4">
         <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H4">
         <v>4.4</v>
@@ -1580,40 +1637,40 @@
         <v>4.7</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
         <v>1.27</v>
@@ -1631,16 +1688,16 @@
         <v>36</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4">
         <v>11</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
         <v>60</v>
@@ -1649,22 +1706,22 @@
         <v>13</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK4">
         <v>19.5</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM4">
         <v>95</v>
@@ -1673,31 +1730,31 @@
         <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP4">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4">
+        <v>16</v>
+      </c>
+      <c r="AR4">
+        <v>28</v>
+      </c>
+      <c r="AS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT4">
+        <v>9.6</v>
+      </c>
+      <c r="AU4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4">
         <v>15</v>
       </c>
-      <c r="AQ4">
-        <v>15.5</v>
-      </c>
-      <c r="AR4">
-        <v>7.8</v>
-      </c>
-      <c r="AS4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT4">
-        <v>9.4</v>
-      </c>
-      <c r="AU4">
-        <v>7.8</v>
-      </c>
-      <c r="AV4">
-        <v>15.5</v>
-      </c>
       <c r="AW4">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1709,25 +1766,25 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
         <v>18</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1790,7 +1847,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1798,94 +1855,94 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>1.97</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X5">
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB5">
         <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
@@ -1894,31 +1951,31 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AJ5">
         <v>20</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
         <v>14</v>
@@ -1927,7 +1984,7 @@
         <v>34</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT5">
         <v>6.8</v>
@@ -1936,40 +1993,40 @@
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW5">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AX5">
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2032,7 +2089,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2040,16 +2097,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F6">
         <v>2.3</v>
@@ -2091,7 +2148,7 @@
         <v>1.37</v>
       </c>
       <c r="S6">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2274,7 +2331,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2282,25 +2339,25 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F7">
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I7">
         <v>5.4</v>
@@ -2324,7 +2381,7 @@
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q7">
         <v>1.97</v>
@@ -2345,7 +2402,7 @@
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X7">
         <v>14.5</v>
@@ -2354,13 +2411,13 @@
         <v>17.5</v>
       </c>
       <c r="Z7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA7">
         <v>140</v>
       </c>
       <c r="AB7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
@@ -2384,7 +2441,7 @@
         <v>80</v>
       </c>
       <c r="AJ7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK7">
         <v>19.5</v>
@@ -2393,7 +2450,7 @@
         <v>38</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7">
         <v>12</v>
@@ -2429,7 +2486,7 @@
         <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
         <v>19</v>
@@ -2441,7 +2498,7 @@
         <v>17</v>
       </c>
       <c r="BC7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD7">
         <v>32</v>
@@ -2453,7 +2510,7 @@
         <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2462,61 +2519,61 @@
         <v>2.88</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
         <v>3.7</v>
       </c>
       <c r="BP7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2524,22 +2581,22 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>1.91</v>
       </c>
       <c r="G8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -2554,7 +2611,7 @@
         <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
         <v>1.09</v>
@@ -2566,10 +2623,10 @@
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
         <v>1.3</v>
@@ -2587,7 +2644,7 @@
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X8">
         <v>12</v>
@@ -2602,13 +2659,13 @@
         <v>120</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
         <v>75</v>
@@ -2617,10 +2674,10 @@
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8">
         <v>85</v>
@@ -2629,16 +2686,16 @@
         <v>23</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL8">
         <v>46</v>
       </c>
       <c r="AM8">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO8">
         <v>90</v>
@@ -2647,49 +2704,49 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR8">
         <v>30</v>
       </c>
       <c r="AS8">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AT8">
         <v>7.2</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD8">
         <v>38</v>
       </c>
       <c r="BE8">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF8">
         <v>14.5</v>
@@ -2698,25 +2755,25 @@
         <v>70</v>
       </c>
       <c r="BH8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI8">
         <v>2.84</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8">
         <v>4</v>
@@ -2731,34 +2788,34 @@
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BT8">
         <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV8">
         <v>46</v>
       </c>
       <c r="BW8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BX8">
         <v>60</v>
       </c>
       <c r="BY8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BZ8">
         <v>30</v>
       </c>
       <c r="CA8">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="CB8" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2766,16 +2823,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F9">
         <v>1.17</v>
@@ -3000,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3008,28 +3065,28 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F10">
         <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H10">
         <v>6</v>
       </c>
       <c r="I10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>4.5</v>
@@ -3038,7 +3095,7 @@
         <v>4.9</v>
       </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -3050,7 +3107,7 @@
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
         <v>1.66</v>
@@ -3062,7 +3119,7 @@
         <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
         <v>2.16</v>
@@ -3071,7 +3128,7 @@
         <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3122,22 +3179,22 @@
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO10">
         <v>85</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR10">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT10">
         <v>9.199999999999999</v>
@@ -3146,10 +3203,10 @@
         <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3161,7 +3218,7 @@
         <v>18</v>
       </c>
       <c r="BA10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3173,13 +3230,13 @@
         <v>21</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3242,7 +3299,7 @@
         <v>3.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3250,22 +3307,22 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>7.8</v>
       </c>
       <c r="G11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H11">
         <v>1.47</v>
@@ -3301,7 +3358,7 @@
         <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
         <v>1.7</v>
@@ -3325,7 +3382,7 @@
         <v>11</v>
       </c>
       <c r="AA11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB11">
         <v>38</v>
@@ -3340,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="AF11">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AG11">
         <v>28</v>
@@ -3361,28 +3418,28 @@
         <v>75</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN11">
         <v>75</v>
       </c>
       <c r="AO11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AP11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11">
         <v>10</v>
       </c>
       <c r="AS11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU11">
         <v>11</v>
@@ -3394,7 +3451,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AY11">
         <v>25</v>
@@ -3406,10 +3463,10 @@
         <v>23</v>
       </c>
       <c r="BB11">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="BD11">
         <v>60</v>
@@ -3418,64 +3475,64 @@
         <v>65</v>
       </c>
       <c r="BF11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG11">
+        <v>4.8</v>
+      </c>
+      <c r="BH11">
         <v>4.7</v>
       </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
       <c r="BI11">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO11">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU11">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW11">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY11">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3484,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3492,31 +3549,31 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I12">
         <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3528,7 +3585,7 @@
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
         <v>1.35</v>
@@ -3543,7 +3600,7 @@
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T12">
         <v>1.94</v>
@@ -3555,22 +3612,22 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X12">
         <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA12">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB12">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12">
         <v>8.4</v>
@@ -3579,10 +3636,10 @@
         <v>21</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -3597,10 +3654,10 @@
         <v>19</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM12">
         <v>140</v>
@@ -3618,22 +3675,22 @@
         <v>16</v>
       </c>
       <c r="AR12">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU12">
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW12">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AX12">
         <v>9.199999999999999</v>
@@ -3642,13 +3699,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="BB12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC12">
         <v>17.5</v>
@@ -3657,13 +3714,13 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF12">
         <v>11</v>
       </c>
       <c r="BG12">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3681,7 +3738,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>3.6</v>
+        <v>1.77</v>
       </c>
       <c r="BN12">
         <v>1000</v>
@@ -3699,7 +3756,7 @@
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="BT12">
         <v>1000</v>
@@ -3723,10 +3780,10 @@
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="CB12" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3734,16 +3791,16 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F13">
         <v>2.28</v>
@@ -3755,7 +3812,7 @@
         <v>3.35</v>
       </c>
       <c r="I13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J13">
         <v>3.7</v>
@@ -3764,7 +3821,7 @@
         <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
         <v>1.06</v>
@@ -3773,7 +3830,7 @@
         <v>4.2</v>
       </c>
       <c r="O13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P13">
         <v>2.12</v>
@@ -3785,7 +3842,7 @@
         <v>1.44</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T13">
         <v>1.7</v>
@@ -3806,10 +3863,10 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA13">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB13">
         <v>11.5</v>
@@ -3821,10 +3878,10 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3836,13 +3893,13 @@
         <v>44</v>
       </c>
       <c r="AJ13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK13">
         <v>24</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM13">
         <v>80</v>
@@ -3887,10 +3944,10 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB13">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="BC13">
         <v>21</v>
@@ -3899,76 +3956,76 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="BF13">
         <v>14</v>
       </c>
       <c r="BG13">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BH13">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BL13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BR13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3976,28 +4033,28 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F14">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G14">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J14">
         <v>3.4</v>
@@ -4018,7 +4075,7 @@
         <v>1.38</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4036,10 +4093,10 @@
         <v>2</v>
       </c>
       <c r="V14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X14">
         <v>12</v>
@@ -4054,7 +4111,7 @@
         <v>65</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
@@ -4066,10 +4123,10 @@
         <v>46</v>
       </c>
       <c r="AF14">
+        <v>15.5</v>
+      </c>
+      <c r="AG14">
         <v>15</v>
-      </c>
-      <c r="AG14">
-        <v>14.5</v>
       </c>
       <c r="AH14">
         <v>23</v>
@@ -4078,10 +4135,10 @@
         <v>60</v>
       </c>
       <c r="AJ14">
+        <v>44</v>
+      </c>
+      <c r="AK14">
         <v>36</v>
-      </c>
-      <c r="AK14">
-        <v>34</v>
       </c>
       <c r="AL14">
         <v>55</v>
@@ -4090,7 +4147,7 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO14">
         <v>48</v>
@@ -4141,7 +4198,7 @@
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BF14">
         <v>19.5</v>
@@ -4210,7 +4267,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4218,28 +4275,28 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>1.73</v>
       </c>
       <c r="G15">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H15">
         <v>5.4</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
         <v>3.95</v>
@@ -4254,7 +4311,7 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O15">
         <v>1.34</v>
@@ -4263,34 +4320,34 @@
         <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R15">
         <v>1.35</v>
       </c>
       <c r="S15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T15">
         <v>1.94</v>
       </c>
       <c r="U15">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
         <v>1.21</v>
       </c>
       <c r="W15">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA15">
         <v>180</v>
@@ -4299,7 +4356,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
         <v>23</v>
@@ -4308,7 +4365,7 @@
         <v>100</v>
       </c>
       <c r="AF15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -4317,16 +4374,16 @@
         <v>23</v>
       </c>
       <c r="AI15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ15">
+        <v>19.5</v>
+      </c>
+      <c r="AK15">
         <v>20</v>
       </c>
-      <c r="AK15">
-        <v>21</v>
-      </c>
       <c r="AL15">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM15">
         <v>140</v>
@@ -4338,19 +4395,19 @@
         <v>120</v>
       </c>
       <c r="AP15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15">
         <v>15</v>
       </c>
       <c r="AR15">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU15">
         <v>7.8</v>
@@ -4359,7 +4416,7 @@
         <v>19</v>
       </c>
       <c r="AW15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX15">
         <v>8.6</v>
@@ -4368,10 +4425,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB15">
         <v>16.5</v>
@@ -4380,28 +4437,28 @@
         <v>16.5</v>
       </c>
       <c r="BD15">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF15">
         <v>10</v>
       </c>
       <c r="BG15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH15">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BJ15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4410,49 +4467,49 @@
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BR15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4460,16 +4517,16 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F16">
         <v>1.55</v>
@@ -4481,7 +4538,7 @@
         <v>6.6</v>
       </c>
       <c r="I16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>4.7</v>
@@ -4502,13 +4559,13 @@
         <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
         <v>2.64</v>
@@ -4559,19 +4616,19 @@
         <v>21</v>
       </c>
       <c r="AI16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK16">
         <v>15.5</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN16">
         <v>6.6</v>
@@ -4580,7 +4637,7 @@
         <v>90</v>
       </c>
       <c r="AP16">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16">
         <v>23</v>
@@ -4589,10 +4646,10 @@
         <v>50</v>
       </c>
       <c r="AS16">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU16">
         <v>9.6</v>
@@ -4601,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AW16">
-        <v>15.5</v>
+        <v>70</v>
       </c>
       <c r="AX16">
         <v>9.199999999999999</v>
@@ -4610,10 +4667,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA16">
-        <v>15.5</v>
+        <v>65</v>
       </c>
       <c r="BB16">
         <v>13.5</v>
@@ -4622,79 +4679,79 @@
         <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE16">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="BF16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BH16">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BL16">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BP16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BR16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BV16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4702,25 +4759,25 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F17">
         <v>1.37</v>
       </c>
       <c r="G17">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17">
         <v>12</v>
@@ -4729,7 +4786,7 @@
         <v>4.9</v>
       </c>
       <c r="K17">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4738,7 +4795,7 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O17">
         <v>1.26</v>
@@ -4747,25 +4804,25 @@
         <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R17">
         <v>1.41</v>
       </c>
       <c r="S17">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T17">
         <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V17">
         <v>1.09</v>
       </c>
       <c r="W17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X17">
         <v>21</v>
@@ -4780,7 +4837,7 @@
         <v>510</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17">
         <v>14</v>
@@ -4792,13 +4849,13 @@
         <v>230</v>
       </c>
       <c r="AF17">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG17">
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI17">
         <v>190</v>
@@ -4816,7 +4873,7 @@
         <v>230</v>
       </c>
       <c r="AN17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO17">
         <v>350</v>
@@ -4828,22 +4885,22 @@
         <v>21</v>
       </c>
       <c r="AR17">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS17">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU17">
         <v>10</v>
       </c>
       <c r="AV17">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW17">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AX17">
         <v>7</v>
@@ -4855,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BB17">
         <v>10</v>
@@ -4864,321 +4921,321 @@
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BE17">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BF17">
         <v>6</v>
       </c>
       <c r="BG17">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F18">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="G18">
+        <v>2.54</v>
+      </c>
+      <c r="H18">
+        <v>3.3</v>
+      </c>
+      <c r="I18">
+        <v>3.7</v>
+      </c>
+      <c r="J18">
+        <v>3.3</v>
+      </c>
+      <c r="K18">
+        <v>3.45</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
         <v>2.98</v>
       </c>
-      <c r="H18">
-        <v>2.54</v>
-      </c>
-      <c r="I18">
-        <v>2.76</v>
-      </c>
-      <c r="J18">
-        <v>3.55</v>
-      </c>
-      <c r="K18">
-        <v>4</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.05</v>
-      </c>
-      <c r="N18">
-        <v>4.4</v>
-      </c>
       <c r="O18">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="P18">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="R18">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S18">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="T18">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="V18">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="W18">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG18">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI18">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP18">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR18">
-        <v>1.3</v>
+        <v>18</v>
       </c>
       <c r="AS18">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="AT18">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV18">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX18">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="AY18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="BA18">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="BB18">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC18">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD18">
-        <v>1.26</v>
+        <v>5.9</v>
       </c>
       <c r="BE18">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF18">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG18">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5186,19 +5243,19 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F19">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G19">
         <v>1.93</v>
@@ -5207,10 +5264,10 @@
         <v>5.4</v>
       </c>
       <c r="I19">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5219,25 +5276,25 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O19">
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q19">
         <v>2.28</v>
       </c>
       <c r="R19">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
         <v>1.99</v>
@@ -5249,7 +5306,7 @@
         <v>1.2</v>
       </c>
       <c r="W19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5300,64 +5357,64 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AR19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AT19">
+        <v>1.34</v>
+      </c>
+      <c r="AU19">
+        <v>1.36</v>
+      </c>
+      <c r="AV19">
+        <v>1.56</v>
+      </c>
+      <c r="AW19">
+        <v>1.56</v>
+      </c>
+      <c r="AX19">
+        <v>1.43</v>
+      </c>
+      <c r="AY19">
         <v>1.44</v>
       </c>
-      <c r="AU19">
-        <v>1.46</v>
-      </c>
-      <c r="AV19">
-        <v>16.5</v>
-      </c>
-      <c r="AW19">
-        <v>1.69</v>
-      </c>
-      <c r="AX19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY19">
-        <v>1.55</v>
-      </c>
       <c r="AZ19">
-        <v>16.5</v>
+        <v>1.56</v>
       </c>
       <c r="BA19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BB19">
-        <v>17.5</v>
+        <v>1.56</v>
       </c>
       <c r="BC19">
-        <v>17</v>
+        <v>1.56</v>
       </c>
       <c r="BD19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BE19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BG19">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BH19">
         <v>3.5</v>
@@ -5420,7 +5477,7 @@
         <v>1.41</v>
       </c>
       <c r="CB19" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5428,31 +5485,31 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F20">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G20">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="H20">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K20">
         <v>3.7</v>
@@ -5464,7 +5521,7 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
         <v>1.32</v>
@@ -5473,133 +5530,133 @@
         <v>1.88</v>
       </c>
       <c r="Q20">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R20">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S20">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD20">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AQ20">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR20">
-        <v>12.5</v>
+        <v>1.31</v>
       </c>
       <c r="AS20">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AT20">
-        <v>6.8</v>
+        <v>1.23</v>
       </c>
       <c r="AU20">
-        <v>5.1</v>
+        <v>1.16</v>
       </c>
       <c r="AV20">
-        <v>8.199999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AW20">
-        <v>2.38</v>
+        <v>1.31</v>
       </c>
       <c r="AX20">
-        <v>10.5</v>
+        <v>1.31</v>
       </c>
       <c r="AY20">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AZ20">
-        <v>10.5</v>
+        <v>1.31</v>
       </c>
       <c r="BA20">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="BB20">
-        <v>2.38</v>
+        <v>1.31</v>
       </c>
       <c r="BC20">
-        <v>16.5</v>
+        <v>1.31</v>
       </c>
       <c r="BD20">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="BE20">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="BF20">
-        <v>14</v>
+        <v>1.31</v>
       </c>
       <c r="BG20">
-        <v>18.5</v>
+        <v>1.31</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5608,303 +5665,303 @@
         <v>2.7</v>
       </c>
       <c r="BJ20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F21">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="G21">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="H21">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="I21">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J21">
+        <v>3.6</v>
+      </c>
+      <c r="K21">
+        <v>3.9</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>4.5</v>
+      </c>
+      <c r="O21">
+        <v>1.24</v>
+      </c>
+      <c r="P21">
+        <v>2.22</v>
+      </c>
+      <c r="Q21">
+        <v>1.72</v>
+      </c>
+      <c r="R21">
+        <v>1.48</v>
+      </c>
+      <c r="S21">
+        <v>2.78</v>
+      </c>
+      <c r="T21">
+        <v>1.62</v>
+      </c>
+      <c r="U21">
+        <v>2.44</v>
+      </c>
+      <c r="V21">
+        <v>1.57</v>
+      </c>
+      <c r="W21">
+        <v>1.54</v>
+      </c>
+      <c r="X21">
+        <v>23</v>
+      </c>
+      <c r="Y21">
+        <v>14</v>
+      </c>
+      <c r="Z21">
+        <v>24</v>
+      </c>
+      <c r="AA21">
+        <v>46</v>
+      </c>
+      <c r="AB21">
+        <v>17.5</v>
+      </c>
+      <c r="AC21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>13</v>
+      </c>
+      <c r="AE21">
+        <v>27</v>
+      </c>
+      <c r="AF21">
+        <v>25</v>
+      </c>
+      <c r="AG21">
+        <v>13</v>
+      </c>
+      <c r="AH21">
+        <v>18.5</v>
+      </c>
+      <c r="AI21">
+        <v>36</v>
+      </c>
+      <c r="AJ21">
+        <v>50</v>
+      </c>
+      <c r="AK21">
+        <v>34</v>
+      </c>
+      <c r="AL21">
+        <v>36</v>
+      </c>
+      <c r="AM21">
+        <v>80</v>
+      </c>
+      <c r="AN21">
+        <v>23</v>
+      </c>
+      <c r="AO21">
+        <v>23</v>
+      </c>
+      <c r="AP21">
+        <v>16.5</v>
+      </c>
+      <c r="AQ21">
+        <v>12</v>
+      </c>
+      <c r="AR21">
+        <v>17.5</v>
+      </c>
+      <c r="AS21">
+        <v>5.9</v>
+      </c>
+      <c r="AT21">
+        <v>12.5</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>11</v>
+      </c>
+      <c r="AW21">
+        <v>19.5</v>
+      </c>
+      <c r="AX21">
+        <v>17.5</v>
+      </c>
+      <c r="AY21">
+        <v>11</v>
+      </c>
+      <c r="AZ21">
+        <v>13</v>
+      </c>
+      <c r="BA21">
+        <v>5.7</v>
+      </c>
+      <c r="BB21">
+        <v>32</v>
+      </c>
+      <c r="BC21">
+        <v>20</v>
+      </c>
+      <c r="BD21">
+        <v>5.7</v>
+      </c>
+      <c r="BE21">
+        <v>6.2</v>
+      </c>
+      <c r="BF21">
+        <v>16.5</v>
+      </c>
+      <c r="BG21">
+        <v>16</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
         <v>3.25</v>
       </c>
-      <c r="K21">
-        <v>4.5</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.06</v>
-      </c>
-      <c r="N21">
-        <v>3.9</v>
-      </c>
-      <c r="O21">
-        <v>1.25</v>
-      </c>
-      <c r="P21">
-        <v>1.97</v>
-      </c>
-      <c r="Q21">
-        <v>1.78</v>
-      </c>
-      <c r="R21">
-        <v>1.38</v>
-      </c>
-      <c r="S21">
-        <v>2.84</v>
-      </c>
-      <c r="T21">
-        <v>1.63</v>
-      </c>
-      <c r="U21">
-        <v>2.14</v>
-      </c>
-      <c r="V21">
-        <v>1.59</v>
-      </c>
-      <c r="W21">
-        <v>1.42</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>34</v>
-      </c>
-      <c r="AC21">
-        <v>970</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>1000</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>1000</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>1.12</v>
-      </c>
-      <c r="AQ21">
-        <v>1.12</v>
-      </c>
-      <c r="AR21">
-        <v>1.12</v>
-      </c>
-      <c r="AS21">
-        <v>1.12</v>
-      </c>
-      <c r="AT21">
-        <v>1.08</v>
-      </c>
-      <c r="AU21">
-        <v>1.03</v>
-      </c>
-      <c r="AV21">
-        <v>1.12</v>
-      </c>
-      <c r="AW21">
-        <v>1.12</v>
-      </c>
-      <c r="AX21">
-        <v>1.12</v>
-      </c>
-      <c r="AY21">
-        <v>1.12</v>
-      </c>
-      <c r="AZ21">
-        <v>1.12</v>
-      </c>
-      <c r="BA21">
-        <v>1.12</v>
-      </c>
-      <c r="BB21">
-        <v>1.12</v>
-      </c>
-      <c r="BC21">
-        <v>1.12</v>
-      </c>
-      <c r="BD21">
-        <v>1.12</v>
-      </c>
-      <c r="BE21">
-        <v>1.12</v>
-      </c>
-      <c r="BF21">
-        <v>1.12</v>
-      </c>
-      <c r="BG21">
-        <v>1.12</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>2.88</v>
-      </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="CB21" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5912,67 +5969,67 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F22">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="G22">
         <v>3.4</v>
       </c>
       <c r="H22">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I22">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K22">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
         <v>4.1</v>
       </c>
       <c r="O22">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="P22">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="R22">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
-        <v>2.06</v>
+        <v>2.84</v>
       </c>
       <c r="T22">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="U22">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="V22">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
         <v>1.42</v>
@@ -5990,10 +6047,10 @@
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD22">
         <v>1000</v>
@@ -6029,67 +6086,67 @@
         <v>1000</v>
       </c>
       <c r="AO22">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AQ22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AR22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AS22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AT22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AU22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AW22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AX22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AY22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AZ22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BA22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BB22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BC22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BD22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BE22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BF22">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -6146,7 +6203,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6154,76 +6211,76 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F23">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="G23">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="H23">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="I23">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="O23">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="P23">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="R23">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="S23">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="T23">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="W23">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X23">
         <v>1000</v>
       </c>
       <c r="Y23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
         <v>1000</v>
@@ -6232,13 +6289,13 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
         <v>1000</v>
@@ -6247,7 +6304,7 @@
         <v>1000</v>
       </c>
       <c r="AG23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
         <v>1000</v>
@@ -6271,67 +6328,67 @@
         <v>1000</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AQ23">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AS23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AT23">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AU23">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AV23">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AW23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AX23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AY23">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AZ23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BA23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BB23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BC23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BD23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BE23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BF23">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BG23">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
@@ -6382,13 +6439,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6396,76 +6453,76 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F24">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="G24">
-        <v>1.94</v>
+        <v>2.98</v>
       </c>
       <c r="H24">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="I24">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P24">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q24">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S24">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T24">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U24">
         <v>2.12</v>
       </c>
       <c r="V24">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="X24">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z24">
         <v>1000</v>
@@ -6474,22 +6531,22 @@
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AC24">
         <v>970</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AH24">
         <v>1000</v>
@@ -6510,70 +6567,70 @@
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AR24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AS24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AT24">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AU24">
-        <v>6.6</v>
+        <v>1.12</v>
       </c>
       <c r="AV24">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AW24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AX24">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AY24">
-        <v>7.2</v>
+        <v>1.19</v>
       </c>
       <c r="AZ24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BA24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BB24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BC24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BD24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BE24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BF24">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BG24">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
@@ -6624,192 +6681,192 @@
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F25">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="G25">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="H25">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I25">
+        <v>6.4</v>
+      </c>
+      <c r="J25">
         <v>3.7</v>
       </c>
-      <c r="J25">
-        <v>3.3</v>
-      </c>
       <c r="K25">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L25">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="R25">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="T25">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="U25">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="X25">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="Y25">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD25">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AG25">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AO25">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>9.6</v>
+        <v>1.39</v>
       </c>
       <c r="AQ25">
-        <v>9.6</v>
+        <v>1.42</v>
       </c>
       <c r="AR25">
-        <v>20</v>
+        <v>1.42</v>
       </c>
       <c r="AS25">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="AT25">
-        <v>7.6</v>
+        <v>1.32</v>
       </c>
       <c r="AU25">
         <v>6.6</v>
       </c>
       <c r="AV25">
-        <v>13</v>
+        <v>1.42</v>
       </c>
       <c r="AW25">
-        <v>5.9</v>
+        <v>1.42</v>
       </c>
       <c r="AX25">
-        <v>12.5</v>
+        <v>1.35</v>
       </c>
       <c r="AY25">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AZ25">
-        <v>17</v>
+        <v>1.42</v>
       </c>
       <c r="BA25">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="BB25">
-        <v>5.6</v>
+        <v>1.42</v>
       </c>
       <c r="BC25">
-        <v>5.5</v>
+        <v>1.42</v>
       </c>
       <c r="BD25">
-        <v>38</v>
+        <v>1.42</v>
       </c>
       <c r="BE25">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="BF25">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="BG25">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6872,7 +6929,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6880,184 +6937,184 @@
         <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F26">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="G26">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="H26">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="I26">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J26">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="K26">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
+        <v>2.8</v>
+      </c>
+      <c r="O26">
+        <v>1.39</v>
+      </c>
+      <c r="P26">
+        <v>1.66</v>
+      </c>
+      <c r="Q26">
+        <v>2.14</v>
+      </c>
+      <c r="R26">
+        <v>1.26</v>
+      </c>
+      <c r="S26">
+        <v>3.85</v>
+      </c>
+      <c r="T26">
+        <v>1.9</v>
+      </c>
+      <c r="U26">
+        <v>1.89</v>
+      </c>
+      <c r="V26">
+        <v>1.78</v>
+      </c>
+      <c r="W26">
+        <v>1.29</v>
+      </c>
+      <c r="X26">
+        <v>12.5</v>
+      </c>
+      <c r="Y26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z26">
+        <v>14.5</v>
+      </c>
+      <c r="AA26">
+        <v>32</v>
+      </c>
+      <c r="AB26">
+        <v>14</v>
+      </c>
+      <c r="AC26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26">
+        <v>12.5</v>
+      </c>
+      <c r="AE26">
+        <v>30</v>
+      </c>
+      <c r="AF26">
+        <v>32</v>
+      </c>
+      <c r="AG26">
+        <v>19</v>
+      </c>
+      <c r="AH26">
+        <v>24</v>
+      </c>
+      <c r="AI26">
+        <v>55</v>
+      </c>
+      <c r="AJ26">
+        <v>110</v>
+      </c>
+      <c r="AK26">
+        <v>70</v>
+      </c>
+      <c r="AL26">
+        <v>80</v>
+      </c>
+      <c r="AM26">
+        <v>160</v>
+      </c>
+      <c r="AN26">
+        <v>85</v>
+      </c>
+      <c r="AO26">
+        <v>25</v>
+      </c>
+      <c r="AP26">
+        <v>1.03</v>
+      </c>
+      <c r="AQ26">
+        <v>1.03</v>
+      </c>
+      <c r="AR26">
+        <v>1.03</v>
+      </c>
+      <c r="AS26">
+        <v>1.03</v>
+      </c>
+      <c r="AT26">
+        <v>1.03</v>
+      </c>
+      <c r="AU26">
+        <v>1.03</v>
+      </c>
+      <c r="AV26">
+        <v>1.03</v>
+      </c>
+      <c r="AW26">
+        <v>1.03</v>
+      </c>
+      <c r="AX26">
+        <v>1.03</v>
+      </c>
+      <c r="AY26">
+        <v>1.03</v>
+      </c>
+      <c r="AZ26">
+        <v>1.03</v>
+      </c>
+      <c r="BA26">
+        <v>1.03</v>
+      </c>
+      <c r="BB26">
+        <v>1.03</v>
+      </c>
+      <c r="BC26">
+        <v>1.03</v>
+      </c>
+      <c r="BD26">
+        <v>1.03</v>
+      </c>
+      <c r="BE26">
+        <v>1.03</v>
+      </c>
+      <c r="BF26">
+        <v>1.01</v>
+      </c>
+      <c r="BG26">
+        <v>17.5</v>
+      </c>
+      <c r="BH26">
         <v>3.75</v>
       </c>
-      <c r="O26">
-        <v>1.1</v>
-      </c>
-      <c r="P26">
-        <v>3.1</v>
-      </c>
-      <c r="Q26">
-        <v>1.41</v>
-      </c>
-      <c r="R26">
-        <v>1.78</v>
-      </c>
-      <c r="S26">
-        <v>1.94</v>
-      </c>
-      <c r="T26">
-        <v>1.39</v>
-      </c>
-      <c r="U26">
-        <v>2.76</v>
-      </c>
-      <c r="V26">
-        <v>1.79</v>
-      </c>
-      <c r="W26">
-        <v>1.43</v>
-      </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>22</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>38</v>
-      </c>
-      <c r="AB26">
-        <v>1000</v>
-      </c>
-      <c r="AC26">
-        <v>1000</v>
-      </c>
-      <c r="AD26">
-        <v>1000</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>38</v>
-      </c>
-      <c r="AG26">
-        <v>1000</v>
-      </c>
-      <c r="AH26">
-        <v>970</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>1000</v>
-      </c>
-      <c r="AK26">
-        <v>38</v>
-      </c>
-      <c r="AL26">
-        <v>38</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>1000</v>
-      </c>
-      <c r="AO26">
-        <v>970</v>
-      </c>
-      <c r="AP26">
-        <v>1.41</v>
-      </c>
-      <c r="AQ26">
-        <v>1.33</v>
-      </c>
-      <c r="AR26">
-        <v>16.5</v>
-      </c>
-      <c r="AS26">
-        <v>1.36</v>
-      </c>
-      <c r="AT26">
-        <v>16.5</v>
-      </c>
-      <c r="AU26">
-        <v>1.41</v>
-      </c>
-      <c r="AV26">
-        <v>1.41</v>
-      </c>
-      <c r="AW26">
-        <v>1.41</v>
-      </c>
-      <c r="AX26">
-        <v>1.36</v>
-      </c>
-      <c r="AY26">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26">
-        <v>1.31</v>
-      </c>
-      <c r="BA26">
-        <v>16</v>
-      </c>
-      <c r="BB26">
-        <v>1.41</v>
-      </c>
-      <c r="BC26">
-        <v>19</v>
-      </c>
-      <c r="BD26">
-        <v>1.36</v>
-      </c>
-      <c r="BE26">
-        <v>1.41</v>
-      </c>
-      <c r="BF26">
-        <v>1.41</v>
-      </c>
-      <c r="BG26">
-        <v>1.26</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
@@ -7114,7 +7171,7 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7122,184 +7179,184 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F27">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H27">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="I27">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="J27">
+        <v>3.95</v>
+      </c>
+      <c r="K27">
+        <v>5.4</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
         <v>3.05</v>
       </c>
-      <c r="K27">
-        <v>3.6</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.08</v>
-      </c>
-      <c r="N27">
-        <v>2.72</v>
-      </c>
       <c r="O27">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="P27">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="R27">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>1.94</v>
       </c>
       <c r="T27">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="U27">
-        <v>1.89</v>
+        <v>2.76</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W27">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X27">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG27">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
@@ -7356,7 +7413,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7364,16 +7421,16 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -7598,7 +7655,1459 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>158</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29">
+        <v>1.1</v>
+      </c>
+      <c r="G29">
+        <v>1000</v>
+      </c>
+      <c r="H29">
+        <v>1.1</v>
+      </c>
+      <c r="I29">
+        <v>110</v>
+      </c>
+      <c r="J29">
+        <v>1.12</v>
+      </c>
+      <c r="K29">
+        <v>950</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>1.08</v>
+      </c>
+      <c r="O29">
+        <v>1.02</v>
+      </c>
+      <c r="P29">
+        <v>1.08</v>
+      </c>
+      <c r="Q29">
+        <v>1.02</v>
+      </c>
+      <c r="R29">
+        <v>1.08</v>
+      </c>
+      <c r="S29">
+        <v>1.02</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
+        <v>1.04</v>
+      </c>
+      <c r="W29">
+        <v>1.03</v>
+      </c>
+      <c r="X29">
+        <v>1000</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29">
+        <v>1000</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>1000</v>
+      </c>
+      <c r="AG29">
+        <v>1000</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29">
+        <v>1.03</v>
+      </c>
+      <c r="AR29">
+        <v>1.03</v>
+      </c>
+      <c r="AS29">
+        <v>1.03</v>
+      </c>
+      <c r="AT29">
+        <v>1.03</v>
+      </c>
+      <c r="AU29">
+        <v>1.03</v>
+      </c>
+      <c r="AV29">
+        <v>1.03</v>
+      </c>
+      <c r="AW29">
+        <v>1.03</v>
+      </c>
+      <c r="AX29">
+        <v>1.03</v>
+      </c>
+      <c r="AY29">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29">
+        <v>1.03</v>
+      </c>
+      <c r="BA29">
+        <v>1.03</v>
+      </c>
+      <c r="BB29">
+        <v>1.03</v>
+      </c>
+      <c r="BC29">
+        <v>1.03</v>
+      </c>
+      <c r="BD29">
+        <v>1.03</v>
+      </c>
+      <c r="BE29">
+        <v>1.03</v>
+      </c>
+      <c r="BF29">
+        <v>1.01</v>
+      </c>
+      <c r="BG29">
+        <v>1.01</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.01</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.01</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.01</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.01</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.01</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.01</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.01</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.01</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>1.09</v>
+      </c>
+      <c r="O30">
+        <v>1.01</v>
+      </c>
+      <c r="P30">
+        <v>1.09</v>
+      </c>
+      <c r="Q30">
+        <v>1.41</v>
+      </c>
+      <c r="R30">
+        <v>1.08</v>
+      </c>
+      <c r="S30">
+        <v>1.42</v>
+      </c>
+      <c r="T30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>1.01</v>
+      </c>
+      <c r="V30">
+        <v>1.01</v>
+      </c>
+      <c r="W30">
+        <v>1.01</v>
+      </c>
+      <c r="X30">
+        <v>1000</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>1000</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>1000</v>
+      </c>
+      <c r="AG30">
+        <v>1000</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>1000</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>1000</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30">
+        <v>1.03</v>
+      </c>
+      <c r="AR30">
+        <v>1.03</v>
+      </c>
+      <c r="AS30">
+        <v>1.03</v>
+      </c>
+      <c r="AT30">
+        <v>1.03</v>
+      </c>
+      <c r="AU30">
+        <v>1.03</v>
+      </c>
+      <c r="AV30">
+        <v>1.03</v>
+      </c>
+      <c r="AW30">
+        <v>1.03</v>
+      </c>
+      <c r="AX30">
+        <v>1.03</v>
+      </c>
+      <c r="AY30">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30">
+        <v>1.03</v>
+      </c>
+      <c r="BA30">
+        <v>1.03</v>
+      </c>
+      <c r="BB30">
+        <v>1.03</v>
+      </c>
+      <c r="BC30">
+        <v>1.03</v>
+      </c>
+      <c r="BD30">
+        <v>1.03</v>
+      </c>
+      <c r="BE30">
+        <v>1.03</v>
+      </c>
+      <c r="BF30">
+        <v>1.01</v>
+      </c>
+      <c r="BG30">
+        <v>1.01</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.01</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.01</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.01</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.01</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.01</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31">
+        <v>1.59</v>
+      </c>
+      <c r="G31">
+        <v>1.7</v>
+      </c>
+      <c r="H31">
+        <v>5.8</v>
+      </c>
+      <c r="I31">
+        <v>7.2</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31">
+        <v>4.4</v>
+      </c>
+      <c r="L31">
+        <v>1.36</v>
+      </c>
+      <c r="M31">
+        <v>1.06</v>
+      </c>
+      <c r="N31">
+        <v>3.75</v>
+      </c>
+      <c r="O31">
+        <v>1.29</v>
+      </c>
+      <c r="P31">
+        <v>2.06</v>
+      </c>
+      <c r="Q31">
+        <v>1.76</v>
+      </c>
+      <c r="R31">
+        <v>1.41</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
+        <v>1.83</v>
+      </c>
+      <c r="U31">
+        <v>1.92</v>
+      </c>
+      <c r="V31">
+        <v>1.17</v>
+      </c>
+      <c r="W31">
+        <v>2.44</v>
+      </c>
+      <c r="X31">
+        <v>1000</v>
+      </c>
+      <c r="Y31">
+        <v>1000</v>
+      </c>
+      <c r="Z31">
+        <v>1000</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>970</v>
+      </c>
+      <c r="AC31">
+        <v>970</v>
+      </c>
+      <c r="AD31">
+        <v>1000</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
+        <v>970</v>
+      </c>
+      <c r="AG31">
+        <v>970</v>
+      </c>
+      <c r="AH31">
+        <v>1000</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>1000</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>970</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>10</v>
+      </c>
+      <c r="AQ31">
+        <v>1.49</v>
+      </c>
+      <c r="AR31">
+        <v>1.49</v>
+      </c>
+      <c r="AS31">
+        <v>1.49</v>
+      </c>
+      <c r="AT31">
+        <v>7</v>
+      </c>
+      <c r="AU31">
+        <v>7.2</v>
+      </c>
+      <c r="AV31">
+        <v>1.49</v>
+      </c>
+      <c r="AW31">
+        <v>1.49</v>
+      </c>
+      <c r="AX31">
+        <v>7</v>
+      </c>
+      <c r="AY31">
+        <v>7.2</v>
+      </c>
+      <c r="AZ31">
+        <v>1.49</v>
+      </c>
+      <c r="BA31">
+        <v>1.49</v>
+      </c>
+      <c r="BB31">
+        <v>10</v>
+      </c>
+      <c r="BC31">
+        <v>10.5</v>
+      </c>
+      <c r="BD31">
+        <v>1.49</v>
+      </c>
+      <c r="BE31">
+        <v>1.49</v>
+      </c>
+      <c r="BF31">
+        <v>6.6</v>
+      </c>
+      <c r="BG31">
+        <v>1.49</v>
+      </c>
+      <c r="BH31">
+        <v>4.5</v>
+      </c>
+      <c r="BI31">
+        <v>2.84</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.29</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.29</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.34</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.29</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.29</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.29</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.29</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.29</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.29</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32">
+        <v>1.1</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+      <c r="H32">
+        <v>1.1</v>
+      </c>
+      <c r="I32">
+        <v>1000</v>
+      </c>
+      <c r="J32">
+        <v>1.12</v>
+      </c>
+      <c r="K32">
+        <v>950</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>1.07</v>
+      </c>
+      <c r="O32">
+        <v>1.02</v>
+      </c>
+      <c r="P32">
+        <v>1.07</v>
+      </c>
+      <c r="Q32">
+        <v>1.02</v>
+      </c>
+      <c r="R32">
+        <v>1.07</v>
+      </c>
+      <c r="S32">
+        <v>1.02</v>
+      </c>
+      <c r="T32">
+        <v>1.01</v>
+      </c>
+      <c r="U32">
+        <v>1.01</v>
+      </c>
+      <c r="V32">
+        <v>1.03</v>
+      </c>
+      <c r="W32">
+        <v>1.03</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32">
+        <v>1.03</v>
+      </c>
+      <c r="AR32">
+        <v>1.03</v>
+      </c>
+      <c r="AS32">
+        <v>1.03</v>
+      </c>
+      <c r="AT32">
+        <v>1.03</v>
+      </c>
+      <c r="AU32">
+        <v>1.03</v>
+      </c>
+      <c r="AV32">
+        <v>1.03</v>
+      </c>
+      <c r="AW32">
+        <v>1.03</v>
+      </c>
+      <c r="AX32">
+        <v>1.03</v>
+      </c>
+      <c r="AY32">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32">
+        <v>1.03</v>
+      </c>
+      <c r="BA32">
+        <v>1.03</v>
+      </c>
+      <c r="BB32">
+        <v>1.03</v>
+      </c>
+      <c r="BC32">
+        <v>1.03</v>
+      </c>
+      <c r="BD32">
+        <v>1.03</v>
+      </c>
+      <c r="BE32">
+        <v>1.03</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.01</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.01</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.01</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.01</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" t="s">
+        <v>175</v>
+      </c>
+      <c r="F33">
+        <v>2.6</v>
+      </c>
+      <c r="G33">
+        <v>2.8</v>
+      </c>
+      <c r="H33">
+        <v>3.05</v>
+      </c>
+      <c r="I33">
+        <v>3.35</v>
+      </c>
+      <c r="J33">
+        <v>3.1</v>
+      </c>
+      <c r="K33">
+        <v>3.3</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.12</v>
+      </c>
+      <c r="N33">
+        <v>2.74</v>
+      </c>
+      <c r="O33">
+        <v>1.5</v>
+      </c>
+      <c r="P33">
+        <v>1.58</v>
+      </c>
+      <c r="Q33">
+        <v>2.5</v>
+      </c>
+      <c r="R33">
+        <v>1.21</v>
+      </c>
+      <c r="S33">
+        <v>5</v>
+      </c>
+      <c r="T33">
+        <v>2.02</v>
+      </c>
+      <c r="U33">
+        <v>1.84</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.52</v>
+      </c>
+      <c r="X33">
+        <v>9.4</v>
+      </c>
+      <c r="Y33">
+        <v>9.4</v>
+      </c>
+      <c r="Z33">
+        <v>21</v>
+      </c>
+      <c r="AA33">
+        <v>70</v>
+      </c>
+      <c r="AB33">
+        <v>8.6</v>
+      </c>
+      <c r="AC33">
+        <v>7.4</v>
+      </c>
+      <c r="AD33">
+        <v>15</v>
+      </c>
+      <c r="AE33">
+        <v>55</v>
+      </c>
+      <c r="AF33">
+        <v>16.5</v>
+      </c>
+      <c r="AG33">
+        <v>13.5</v>
+      </c>
+      <c r="AH33">
+        <v>23</v>
+      </c>
+      <c r="AI33">
+        <v>80</v>
+      </c>
+      <c r="AJ33">
+        <v>65</v>
+      </c>
+      <c r="AK33">
+        <v>50</v>
+      </c>
+      <c r="AL33">
+        <v>75</v>
+      </c>
+      <c r="AM33">
+        <v>190</v>
+      </c>
+      <c r="AN33">
+        <v>48</v>
+      </c>
+      <c r="AO33">
+        <v>70</v>
+      </c>
+      <c r="AP33">
+        <v>8</v>
+      </c>
+      <c r="AQ33">
+        <v>8</v>
+      </c>
+      <c r="AR33">
+        <v>17</v>
+      </c>
+      <c r="AS33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT33">
+        <v>7.4</v>
+      </c>
+      <c r="AU33">
+        <v>6.4</v>
+      </c>
+      <c r="AV33">
+        <v>12.5</v>
+      </c>
+      <c r="AW33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX33">
+        <v>13.5</v>
+      </c>
+      <c r="AY33">
+        <v>11.5</v>
+      </c>
+      <c r="AZ33">
+        <v>18.5</v>
+      </c>
+      <c r="BA33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB33">
+        <v>8.4</v>
+      </c>
+      <c r="BC33">
+        <v>8</v>
+      </c>
+      <c r="BD33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE33">
+        <v>10</v>
+      </c>
+      <c r="BF33">
+        <v>8.6</v>
+      </c>
+      <c r="BG33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34">
+        <v>1.62</v>
+      </c>
+      <c r="G34">
+        <v>1.72</v>
+      </c>
+      <c r="H34">
+        <v>6.2</v>
+      </c>
+      <c r="I34">
+        <v>7.4</v>
+      </c>
+      <c r="J34">
+        <v>3.7</v>
+      </c>
+      <c r="K34">
+        <v>4.1</v>
+      </c>
+      <c r="L34">
+        <v>1.44</v>
+      </c>
+      <c r="M34">
+        <v>1.09</v>
+      </c>
+      <c r="N34">
+        <v>2.96</v>
+      </c>
+      <c r="O34">
+        <v>1.4</v>
+      </c>
+      <c r="P34">
+        <v>1.66</v>
+      </c>
+      <c r="Q34">
+        <v>2.16</v>
+      </c>
+      <c r="R34">
+        <v>1.23</v>
+      </c>
+      <c r="S34">
+        <v>4</v>
+      </c>
+      <c r="T34">
+        <v>2.06</v>
+      </c>
+      <c r="U34">
+        <v>1.67</v>
+      </c>
+      <c r="V34">
+        <v>1.15</v>
+      </c>
+      <c r="W34">
+        <v>2.38</v>
+      </c>
+      <c r="X34">
+        <v>970</v>
+      </c>
+      <c r="Y34">
+        <v>19</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>970</v>
+      </c>
+      <c r="AC34">
+        <v>970</v>
+      </c>
+      <c r="AD34">
+        <v>30</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>970</v>
+      </c>
+      <c r="AG34">
+        <v>970</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>970</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>7.8</v>
+      </c>
+      <c r="AQ34">
+        <v>1.75</v>
+      </c>
+      <c r="AR34">
+        <v>1.93</v>
+      </c>
+      <c r="AS34">
+        <v>1.93</v>
+      </c>
+      <c r="AT34">
+        <v>5.2</v>
+      </c>
+      <c r="AU34">
+        <v>6.4</v>
+      </c>
+      <c r="AV34">
+        <v>1.8</v>
+      </c>
+      <c r="AW34">
+        <v>1.93</v>
+      </c>
+      <c r="AX34">
+        <v>6.4</v>
+      </c>
+      <c r="AY34">
+        <v>7.4</v>
+      </c>
+      <c r="AZ34">
+        <v>1.93</v>
+      </c>
+      <c r="BA34">
+        <v>1.93</v>
+      </c>
+      <c r="BB34">
+        <v>1.92</v>
+      </c>
+      <c r="BC34">
+        <v>1.93</v>
+      </c>
+      <c r="BD34">
+        <v>1.93</v>
+      </c>
+      <c r="BE34">
+        <v>1.93</v>
+      </c>
+      <c r="BF34">
+        <v>1.81</v>
+      </c>
+      <c r="BG34">
+        <v>1.93</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.29</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.43</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -547,7 +547,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-24 01:37:00</t>
+    <t>2026-09-24 03:51:14</t>
   </si>
 </sst>
 </file>
@@ -1141,10 +1141,10 @@
         <v>144</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G2">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -1174,37 +1174,37 @@
         <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X2">
         <v>17</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AB2">
         <v>7.4</v>
@@ -1213,10 +1213,10 @@
         <v>11</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF2">
         <v>10.5</v>
@@ -1228,7 +1228,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>17.5</v>
@@ -1237,28 +1237,28 @@
         <v>19</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP2">
         <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR2">
+        <v>6.4</v>
+      </c>
+      <c r="AS2">
         <v>6.8</v>
-      </c>
-      <c r="AS2">
-        <v>7</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1267,13 +1267,13 @@
         <v>8.6</v>
       </c>
       <c r="AV2">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY2">
         <v>9</v>
@@ -1282,37 +1282,37 @@
         <v>5.9</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BE2">
         <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>6.8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1321,46 +1321,46 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,7 +1383,7 @@
         <v>145</v>
       </c>
       <c r="F3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
         <v>1.67</v>
@@ -1425,10 +1425,10 @@
         <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
         <v>1.17</v>
@@ -1449,7 +1449,7 @@
         <v>240</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>9.800000000000001</v>
@@ -1461,19 +1461,19 @@
         <v>130</v>
       </c>
       <c r="AF3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>120</v>
       </c>
       <c r="AJ3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK3">
         <v>20</v>
@@ -1494,10 +1494,10 @@
         <v>12.5</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="AS3">
         <v>10.5</v>
@@ -1506,10 +1506,10 @@
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW3">
         <v>10</v>
@@ -1521,40 +1521,40 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>10</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3">
         <v>29</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF3">
         <v>8.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI3">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1563,46 +1563,46 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,226 +1625,226 @@
         <v>146</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
       </c>
       <c r="AD4">
+        <v>20</v>
+      </c>
+      <c r="AE4">
+        <v>80</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
+        <v>80</v>
+      </c>
+      <c r="AJ4">
+        <v>20</v>
+      </c>
+      <c r="AK4">
         <v>18.5</v>
       </c>
-      <c r="AE4">
-        <v>60</v>
-      </c>
-      <c r="AF4">
-        <v>13</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>70</v>
-      </c>
-      <c r="AJ4">
-        <v>23</v>
-      </c>
-      <c r="AK4">
-        <v>19.5</v>
-      </c>
       <c r="AL4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN4">
         <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AP4">
+        <v>14.5</v>
+      </c>
+      <c r="AQ4">
+        <v>17</v>
+      </c>
+      <c r="AR4">
+        <v>8</v>
+      </c>
+      <c r="AS4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>8.4</v>
+      </c>
+      <c r="AU4">
+        <v>7.8</v>
+      </c>
+      <c r="AV4">
+        <v>16</v>
+      </c>
+      <c r="AW4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX4">
+        <v>10</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
         <v>15.5</v>
       </c>
-      <c r="AQ4">
-        <v>16</v>
-      </c>
-      <c r="AR4">
-        <v>28</v>
-      </c>
-      <c r="AS4">
+      <c r="BA4">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT4">
-        <v>9.6</v>
-      </c>
-      <c r="AU4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4">
+      <c r="BB4">
+        <v>17</v>
+      </c>
+      <c r="BC4">
         <v>15</v>
       </c>
-      <c r="AW4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX4">
-        <v>10.5</v>
-      </c>
-      <c r="AY4">
+      <c r="BD4">
+        <v>27</v>
+      </c>
+      <c r="BE4">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
-      <c r="BA4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB4">
-        <v>18</v>
-      </c>
-      <c r="BC4">
-        <v>16</v>
-      </c>
-      <c r="BD4">
+      <c r="BF4">
+        <v>9</v>
+      </c>
+      <c r="BG4">
+        <v>42</v>
+      </c>
+      <c r="BH4">
+        <v>4.1</v>
+      </c>
+      <c r="BI4">
+        <v>3.05</v>
+      </c>
+      <c r="BJ4">
+        <v>10</v>
+      </c>
+      <c r="BK4">
+        <v>4.7</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>8.4</v>
+      </c>
+      <c r="BN4">
+        <v>4.7</v>
+      </c>
+      <c r="BO4">
+        <v>3.95</v>
+      </c>
+      <c r="BP4">
+        <v>12.5</v>
+      </c>
+      <c r="BQ4">
+        <v>5.2</v>
+      </c>
+      <c r="BR4">
+        <v>27</v>
+      </c>
+      <c r="BS4">
+        <v>6.6</v>
+      </c>
+      <c r="BT4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU4">
+        <v>4.4</v>
+      </c>
+      <c r="BV4">
+        <v>44</v>
+      </c>
+      <c r="BW4">
         <v>7.4</v>
       </c>
-      <c r="BE4">
-        <v>8.6</v>
-      </c>
-      <c r="BF4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG4">
-        <v>8</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.01</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.01</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.01</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.01</v>
-      </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1870,7 +1870,7 @@
         <v>1.8</v>
       </c>
       <c r="G5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H5">
         <v>5.1</v>
@@ -1897,7 +1897,7 @@
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1924,7 +1924,7 @@
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z5">
         <v>40</v>
@@ -1933,16 +1933,16 @@
         <v>150</v>
       </c>
       <c r="AB5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
@@ -1954,7 +1954,7 @@
         <v>23</v>
       </c>
       <c r="AI5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
         <v>20</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
         <v>14</v>
@@ -1984,22 +1984,22 @@
         <v>34</v>
       </c>
       <c r="AS5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU5">
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
@@ -2008,37 +2008,37 @@
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BB5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD5">
         <v>34</v>
       </c>
       <c r="BE5">
+        <v>11.5</v>
+      </c>
+      <c r="BF5">
         <v>12</v>
-      </c>
-      <c r="BF5">
-        <v>12.5</v>
       </c>
       <c r="BG5">
         <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2047,46 +2047,46 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2148,7 +2148,7 @@
         <v>1.37</v>
       </c>
       <c r="S6">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2378,34 +2378,34 @@
         <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y7">
         <v>17.5</v>
@@ -2426,7 +2426,7 @@
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF7">
         <v>10.5</v>
@@ -2486,13 +2486,13 @@
         <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
         <v>19</v>
       </c>
       <c r="BA7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2552,7 +2552,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>1.91</v>
       </c>
       <c r="G8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -2623,13 +2623,13 @@
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q8">
         <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S8">
         <v>4.1</v>
@@ -2644,7 +2644,7 @@
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X8">
         <v>12</v>
@@ -2665,7 +2665,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE8">
         <v>75</v>
@@ -2683,7 +2683,7 @@
         <v>85</v>
       </c>
       <c r="AJ8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK8">
         <v>23</v>
@@ -2692,7 +2692,7 @@
         <v>46</v>
       </c>
       <c r="AM8">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN8">
         <v>16.5</v>
@@ -2701,7 +2701,7 @@
         <v>90</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2719,7 +2719,7 @@
         <v>7.6</v>
       </c>
       <c r="AV8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW8">
         <v>60</v>
@@ -3086,7 +3086,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
         <v>4.5</v>
@@ -3107,22 +3107,22 @@
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
         <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.17</v>
@@ -3131,7 +3131,7 @@
         <v>2.6</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y10">
         <v>26</v>
@@ -3179,7 +3179,7 @@
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
         <v>85</v>
@@ -3188,25 +3188,25 @@
         <v>19</v>
       </c>
       <c r="AQ10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR10">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3218,7 +3218,7 @@
         <v>18</v>
       </c>
       <c r="BA10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3230,13 +3230,13 @@
         <v>21</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>6.2</v>
       </c>
       <c r="BG10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3319,22 +3319,22 @@
         <v>153</v>
       </c>
       <c r="F11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I11">
         <v>1.48</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L11">
         <v>1.27</v>
@@ -3355,7 +3355,7 @@
         <v>1.52</v>
       </c>
       <c r="R11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S11">
         <v>2.28</v>
@@ -3388,7 +3388,7 @@
         <v>38</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD11">
         <v>10.5</v>
@@ -3397,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="AF11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG11">
         <v>28</v>
@@ -3415,7 +3415,7 @@
         <v>90</v>
       </c>
       <c r="AL11">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AM11">
         <v>80</v>
@@ -3424,13 +3424,13 @@
         <v>75</v>
       </c>
       <c r="AO11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AP11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>12.5</v>
       </c>
       <c r="AT11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AU11">
         <v>11</v>
@@ -3460,7 +3460,7 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB11">
         <v>17.5</v>
@@ -3561,10 +3561,10 @@
         <v>154</v>
       </c>
       <c r="F12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H12">
         <v>5.3</v>
@@ -3585,7 +3585,7 @@
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
         <v>1.35</v>
@@ -3600,10 +3600,10 @@
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U12">
         <v>1.95</v>
@@ -3612,7 +3612,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -3624,7 +3624,7 @@
         <v>42</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB12">
         <v>8.199999999999999</v>
@@ -3639,7 +3639,7 @@
         <v>80</v>
       </c>
       <c r="AF12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -3651,10 +3651,10 @@
         <v>90</v>
       </c>
       <c r="AJ12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL12">
         <v>42</v>
@@ -3678,7 +3678,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT12">
         <v>7.4</v>
@@ -3687,10 +3687,10 @@
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW12">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="AX12">
         <v>9.199999999999999</v>
@@ -3714,13 +3714,13 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF12">
         <v>11</v>
       </c>
       <c r="BG12">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3803,19 +3803,19 @@
         <v>155</v>
       </c>
       <c r="F13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H13">
+        <v>3.3</v>
+      </c>
+      <c r="I13">
         <v>3.35</v>
       </c>
-      <c r="I13">
-        <v>3.4</v>
-      </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
         <v>3.75</v>
@@ -3827,10 +3827,10 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
         <v>2.12</v>
@@ -3842,7 +3842,7 @@
         <v>1.44</v>
       </c>
       <c r="S13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
         <v>1.7</v>
@@ -3851,10 +3851,10 @@
         <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -3863,10 +3863,10 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA13">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB13">
         <v>11.5</v>
@@ -3878,10 +3878,10 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3899,7 +3899,7 @@
         <v>24</v>
       </c>
       <c r="AL13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM13">
         <v>80</v>
@@ -3917,7 +3917,7 @@
         <v>13.5</v>
       </c>
       <c r="AR13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS13">
         <v>50</v>
@@ -3944,10 +3944,10 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC13">
         <v>21</v>
@@ -3959,10 +3959,10 @@
         <v>65</v>
       </c>
       <c r="BF13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
@@ -4048,19 +4048,19 @@
         <v>2.42</v>
       </c>
       <c r="G14">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H14">
         <v>3.3</v>
       </c>
       <c r="I14">
+        <v>3.4</v>
+      </c>
+      <c r="J14">
         <v>3.45</v>
       </c>
-      <c r="J14">
-        <v>3.4</v>
-      </c>
       <c r="K14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L14">
         <v>1.41</v>
@@ -4069,16 +4069,16 @@
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
         <v>1.38</v>
       </c>
       <c r="P14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R14">
         <v>1.29</v>
@@ -4087,16 +4087,16 @@
         <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X14">
         <v>12</v>
@@ -4120,25 +4120,25 @@
         <v>15</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI14">
         <v>60</v>
       </c>
       <c r="AJ14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL14">
         <v>55</v>
@@ -4147,7 +4147,7 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14">
         <v>48</v>
@@ -4159,10 +4159,10 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT14">
         <v>8.4</v>
@@ -4174,7 +4174,7 @@
         <v>13</v>
       </c>
       <c r="AW14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4186,7 +4186,7 @@
         <v>17</v>
       </c>
       <c r="BA14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB14">
         <v>30</v>
@@ -4198,7 +4198,7 @@
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BF14">
         <v>19.5</v>
@@ -4287,37 +4287,37 @@
         <v>157</v>
       </c>
       <c r="F15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M15">
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
         <v>2.04</v>
@@ -4329,7 +4329,7 @@
         <v>3.7</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U15">
         <v>1.97</v>
@@ -4338,7 +4338,7 @@
         <v>1.21</v>
       </c>
       <c r="W15">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X15">
         <v>16</v>
@@ -4374,7 +4374,7 @@
         <v>23</v>
       </c>
       <c r="AI15">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
         <v>19.5</v>
@@ -4401,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="AR15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AS15">
         <v>12</v>
@@ -4416,7 +4416,7 @@
         <v>19</v>
       </c>
       <c r="AW15">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AX15">
         <v>8.6</v>
@@ -4425,10 +4425,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BA15">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BB15">
         <v>16.5</v>
@@ -4437,7 +4437,7 @@
         <v>16.5</v>
       </c>
       <c r="BD15">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BE15">
         <v>11.5</v>
@@ -4449,64 +4449,64 @@
         <v>11.5</v>
       </c>
       <c r="BH15">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BI15">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK15">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ15">
+        <v>10</v>
+      </c>
+      <c r="BR15">
+        <v>29</v>
+      </c>
+      <c r="BS15">
+        <v>23</v>
+      </c>
+      <c r="BT15">
+        <v>9</v>
+      </c>
+      <c r="BU15">
         <v>8</v>
       </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>6.4</v>
-      </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4538,7 +4538,7 @@
         <v>6.6</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
         <v>4.7</v>
@@ -4565,10 +4565,10 @@
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S16">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
         <v>1.81</v>
@@ -4652,7 +4652,7 @@
         <v>9.4</v>
       </c>
       <c r="AU16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16">
         <v>22</v>
@@ -4688,7 +4688,7 @@
         <v>6.2</v>
       </c>
       <c r="BG16">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4795,19 +4795,19 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S17">
         <v>3.05</v>
@@ -4816,7 +4816,7 @@
         <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
         <v>1.09</v>
@@ -4828,7 +4828,7 @@
         <v>21</v>
       </c>
       <c r="Y17">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z17">
         <v>120</v>
@@ -4843,13 +4843,13 @@
         <v>14</v>
       </c>
       <c r="AD17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE17">
         <v>230</v>
       </c>
       <c r="AF17">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG17">
         <v>13</v>
@@ -4873,34 +4873,34 @@
         <v>230</v>
       </c>
       <c r="AN17">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO17">
         <v>350</v>
       </c>
       <c r="AP17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17">
         <v>21</v>
       </c>
       <c r="AR17">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS17">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU17">
         <v>10</v>
       </c>
       <c r="AV17">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW17">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX17">
         <v>7</v>
@@ -4912,25 +4912,25 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17">
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE17">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF17">
         <v>6</v>
       </c>
       <c r="BG17">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5019,7 +5019,7 @@
         <v>2.54</v>
       </c>
       <c r="H18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I18">
         <v>3.7</v>
@@ -5037,7 +5037,7 @@
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O18">
         <v>1.41</v>
@@ -5058,13 +5058,13 @@
         <v>1.89</v>
       </c>
       <c r="U18">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V18">
         <v>1.39</v>
       </c>
       <c r="W18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X18">
         <v>13</v>
@@ -5073,7 +5073,7 @@
         <v>13</v>
       </c>
       <c r="Z18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA18">
         <v>80</v>
@@ -5127,10 +5127,10 @@
         <v>9.4</v>
       </c>
       <c r="AR18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT18">
         <v>7.6</v>
@@ -5142,10 +5142,10 @@
         <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY18">
         <v>10</v>
@@ -5154,22 +5154,22 @@
         <v>17</v>
       </c>
       <c r="BA18">
+        <v>6.2</v>
+      </c>
+      <c r="BB18">
+        <v>5.7</v>
+      </c>
+      <c r="BC18">
+        <v>5.6</v>
+      </c>
+      <c r="BD18">
+        <v>38</v>
+      </c>
+      <c r="BE18">
         <v>6</v>
       </c>
-      <c r="BB18">
-        <v>5.6</v>
-      </c>
-      <c r="BC18">
-        <v>5.5</v>
-      </c>
-      <c r="BD18">
-        <v>5.9</v>
-      </c>
-      <c r="BE18">
-        <v>5.9</v>
-      </c>
       <c r="BF18">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BG18">
         <v>6</v>
@@ -5258,16 +5258,16 @@
         <v>1.82</v>
       </c>
       <c r="G19">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="H19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I19">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5279,10 +5279,10 @@
         <v>1.1</v>
       </c>
       <c r="N19">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P19">
         <v>1.62</v>
@@ -5294,10 +5294,10 @@
         <v>1.19</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T19">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U19">
         <v>1.73</v>
@@ -5306,7 +5306,7 @@
         <v>1.2</v>
       </c>
       <c r="W19">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5497,58 +5497,58 @@
         <v>162</v>
       </c>
       <c r="F20">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G20">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H20">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I20">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
         <v>1.32</v>
       </c>
       <c r="P20">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q20">
         <v>1.92</v>
       </c>
       <c r="R20">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
         <v>3.15</v>
       </c>
       <c r="T20">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="U20">
         <v>2.08</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5659,7 +5659,7 @@
         <v>1.31</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI20">
         <v>2.7</v>
@@ -5668,55 +5668,55 @@
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5739,7 +5739,7 @@
         <v>163</v>
       </c>
       <c r="F21">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G21">
         <v>2.86</v>
@@ -5748,7 +5748,7 @@
         <v>2.6</v>
       </c>
       <c r="I21">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J21">
         <v>3.6</v>
@@ -5772,25 +5772,25 @@
         <v>2.22</v>
       </c>
       <c r="Q21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R21">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U21">
         <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X21">
         <v>23</v>
@@ -5847,13 +5847,13 @@
         <v>23</v>
       </c>
       <c r="AP21">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21">
         <v>12</v>
       </c>
       <c r="AR21">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS21">
         <v>5.9</v>
@@ -5862,7 +5862,7 @@
         <v>12.5</v>
       </c>
       <c r="AU21">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV21">
         <v>11</v>
@@ -5901,7 +5901,7 @@
         <v>16</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI21">
         <v>3.25</v>
@@ -5916,49 +5916,49 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="BN21">
         <v>8.199999999999999</v>
       </c>
       <c r="BO21">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="BP21">
         <v>29</v>
       </c>
       <c r="BQ21">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BR21">
         <v>44</v>
       </c>
       <c r="BS21">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BT21">
         <v>8.199999999999999</v>
       </c>
       <c r="BU21">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="BV21">
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BX21">
         <v>40</v>
       </c>
       <c r="BY21">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BZ21">
         <v>30</v>
       </c>
       <c r="CA21">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5987,13 +5987,13 @@
         <v>3.4</v>
       </c>
       <c r="H22">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="I22">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
         <v>4.5</v>
@@ -6005,19 +6005,19 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q22">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
         <v>2.84</v>
@@ -6029,7 +6029,7 @@
         <v>2.14</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
         <v>1.42</v>
@@ -6223,19 +6223,19 @@
         <v>165</v>
       </c>
       <c r="F23">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G23">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="H23">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I23">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>5.4</v>
@@ -6262,7 +6262,7 @@
         <v>1.64</v>
       </c>
       <c r="S23">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T23">
         <v>1.45</v>
@@ -6271,10 +6271,10 @@
         <v>2.6</v>
       </c>
       <c r="V23">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="W23">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6707,10 +6707,10 @@
         <v>167</v>
       </c>
       <c r="F25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G25">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H25">
         <v>4.3</v>
@@ -6719,10 +6719,10 @@
         <v>6.4</v>
       </c>
       <c r="J25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6731,7 +6731,7 @@
         <v>1.02</v>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
         <v>1.26</v>
@@ -6746,7 +6746,7 @@
         <v>1.4</v>
       </c>
       <c r="S25">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T25">
         <v>1.69</v>
@@ -6758,10 +6758,10 @@
         <v>1.2</v>
       </c>
       <c r="W25">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
         <v>1000</v>
@@ -6818,55 +6818,55 @@
         <v>1.39</v>
       </c>
       <c r="AQ25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AR25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT25">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU25">
         <v>6.6</v>
       </c>
       <c r="AV25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AW25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AX25">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AY25">
         <v>7.2</v>
       </c>
       <c r="AZ25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BA25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BB25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BC25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BD25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BE25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BF25">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BG25">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6949,19 +6949,19 @@
         <v>168</v>
       </c>
       <c r="F26">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H26">
         <v>2.02</v>
       </c>
       <c r="I26">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J26">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K26">
         <v>3.75</v>
@@ -6970,43 +6970,43 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N26">
         <v>2.8</v>
       </c>
       <c r="O26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P26">
         <v>1.66</v>
       </c>
       <c r="Q26">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R26">
         <v>1.26</v>
       </c>
       <c r="S26">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U26">
         <v>1.89</v>
       </c>
       <c r="V26">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W26">
         <v>1.29</v>
       </c>
       <c r="X26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y26">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z26">
         <v>14.5</v>
@@ -7015,10 +7015,10 @@
         <v>32</v>
       </c>
       <c r="AB26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC26">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD26">
         <v>12.5</v>
@@ -7027,10 +7027,10 @@
         <v>30</v>
       </c>
       <c r="AF26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG26">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH26">
         <v>24</v>
@@ -7108,7 +7108,7 @@
         <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH26">
         <v>3.75</v>
@@ -7200,13 +7200,13 @@
         <v>2.1</v>
       </c>
       <c r="I27">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K27">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7215,19 +7215,19 @@
         <v>1.02</v>
       </c>
       <c r="N27">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="O27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R27">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S27">
         <v>1.94</v>
@@ -7239,10 +7239,10 @@
         <v>2.76</v>
       </c>
       <c r="V27">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7263,7 +7263,7 @@
         <v>1000</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE27">
         <v>1000</v>
@@ -7302,10 +7302,10 @@
         <v>1.09</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AR27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AS27">
         <v>1.09</v>
@@ -7314,22 +7314,22 @@
         <v>1.09</v>
       </c>
       <c r="AU27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AV27">
         <v>1.09</v>
       </c>
       <c r="AW27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AX27">
         <v>1.09</v>
       </c>
       <c r="AY27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AZ27">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="BA27">
         <v>1.09</v>
@@ -7347,10 +7347,10 @@
         <v>1.09</v>
       </c>
       <c r="BF27">
+        <v>1.21</v>
+      </c>
+      <c r="BG27">
         <v>1.09</v>
-      </c>
-      <c r="BG27">
-        <v>1.01</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7678,7 +7678,7 @@
         <v>1.1</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H29">
         <v>1.1</v>
@@ -7723,10 +7723,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
+        <v>1.05</v>
+      </c>
+      <c r="W29">
         <v>1.04</v>
-      </c>
-      <c r="W29">
-        <v>1.03</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -8159,22 +8159,22 @@
         <v>173</v>
       </c>
       <c r="F31">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H31">
         <v>5.8</v>
       </c>
       <c r="I31">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>4</v>
       </c>
       <c r="K31">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L31">
         <v>1.36</v>
@@ -8183,7 +8183,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
         <v>1.29</v>
@@ -8192,133 +8192,133 @@
         <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R31">
         <v>1.41</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T31">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U31">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V31">
         <v>1.17</v>
       </c>
       <c r="W31">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB31">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC31">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF31">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG31">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN31">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP31">
+        <v>14.5</v>
+      </c>
+      <c r="AQ31">
+        <v>17.5</v>
+      </c>
+      <c r="AR31">
+        <v>36</v>
+      </c>
+      <c r="AS31">
         <v>10</v>
       </c>
-      <c r="AQ31">
-        <v>1.49</v>
-      </c>
-      <c r="AR31">
-        <v>1.49</v>
-      </c>
-      <c r="AS31">
-        <v>1.49</v>
-      </c>
       <c r="AT31">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU31">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV31">
-        <v>1.49</v>
+        <v>19.5</v>
       </c>
       <c r="AW31">
-        <v>1.49</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX31">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AY31">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>1.49</v>
+        <v>7.6</v>
       </c>
       <c r="BA31">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="BB31">
+        <v>13.5</v>
+      </c>
+      <c r="BC31">
+        <v>15</v>
+      </c>
+      <c r="BD31">
+        <v>9</v>
+      </c>
+      <c r="BE31">
         <v>10</v>
       </c>
-      <c r="BC31">
-        <v>10.5</v>
-      </c>
-      <c r="BD31">
-        <v>1.49</v>
-      </c>
-      <c r="BE31">
-        <v>1.49</v>
-      </c>
       <c r="BF31">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG31">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="BH31">
         <v>4.5</v>
@@ -8404,13 +8404,13 @@
         <v>1.1</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H32">
         <v>1.1</v>
       </c>
       <c r="I32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J32">
         <v>1.12</v>
@@ -8449,10 +8449,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8643,19 +8643,19 @@
         <v>175</v>
       </c>
       <c r="F33">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G33">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33">
+        <v>3.25</v>
+      </c>
+      <c r="J33">
         <v>3.05</v>
-      </c>
-      <c r="I33">
-        <v>3.35</v>
-      </c>
-      <c r="J33">
-        <v>3.1</v>
       </c>
       <c r="K33">
         <v>3.3</v>
@@ -8667,25 +8667,25 @@
         <v>1.12</v>
       </c>
       <c r="N33">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O33">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P33">
         <v>1.58</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S33">
         <v>5</v>
       </c>
       <c r="T33">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
         <v>1.84</v>
@@ -8694,10 +8694,10 @@
         <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X33">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y33">
         <v>9.4</v>
@@ -8709,19 +8709,19 @@
         <v>70</v>
       </c>
       <c r="AB33">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33">
         <v>7.4</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE33">
         <v>55</v>
       </c>
       <c r="AF33">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG33">
         <v>13.5</v>
@@ -8748,7 +8748,7 @@
         <v>48</v>
       </c>
       <c r="AO33">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP33">
         <v>8</v>
@@ -8763,7 +8763,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU33">
         <v>6.4</v>
@@ -8784,16 +8784,16 @@
         <v>18.5</v>
       </c>
       <c r="BA33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC33">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE33">
         <v>10</v>
@@ -8888,16 +8888,16 @@
         <v>1.62</v>
       </c>
       <c r="G34">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H34">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I34">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K34">
         <v>4.1</v>
@@ -8909,142 +8909,142 @@
         <v>1.09</v>
       </c>
       <c r="N34">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O34">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P34">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q34">
+        <v>2.22</v>
+      </c>
+      <c r="R34">
+        <v>1.27</v>
+      </c>
+      <c r="S34">
+        <v>4.3</v>
+      </c>
+      <c r="T34">
         <v>2.16</v>
       </c>
-      <c r="R34">
-        <v>1.23</v>
-      </c>
-      <c r="S34">
-        <v>4</v>
-      </c>
-      <c r="T34">
-        <v>2.06</v>
-      </c>
       <c r="U34">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V34">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X34">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y34">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB34">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF34">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG34">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN34">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP34">
+        <v>10</v>
+      </c>
+      <c r="AQ34">
+        <v>15.5</v>
+      </c>
+      <c r="AR34">
+        <v>7.6</v>
+      </c>
+      <c r="AS34">
+        <v>8</v>
+      </c>
+      <c r="AT34">
+        <v>6</v>
+      </c>
+      <c r="AU34">
         <v>7.8</v>
       </c>
-      <c r="AQ34">
-        <v>1.75</v>
-      </c>
-      <c r="AR34">
-        <v>1.93</v>
-      </c>
-      <c r="AS34">
-        <v>1.93</v>
-      </c>
-      <c r="AT34">
-        <v>5.2</v>
-      </c>
-      <c r="AU34">
-        <v>6.4</v>
-      </c>
       <c r="AV34">
-        <v>1.8</v>
+        <v>23</v>
       </c>
       <c r="AW34">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="AX34">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY34">
+        <v>9</v>
+      </c>
+      <c r="AZ34">
+        <v>23</v>
+      </c>
+      <c r="BA34">
+        <v>8</v>
+      </c>
+      <c r="BB34">
+        <v>14</v>
+      </c>
+      <c r="BC34">
+        <v>18</v>
+      </c>
+      <c r="BD34">
         <v>7.4</v>
       </c>
-      <c r="AZ34">
-        <v>1.93</v>
-      </c>
-      <c r="BA34">
-        <v>1.93</v>
-      </c>
-      <c r="BB34">
-        <v>1.92</v>
-      </c>
-      <c r="BC34">
-        <v>1.93</v>
-      </c>
-      <c r="BD34">
-        <v>1.93</v>
-      </c>
       <c r="BE34">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="BF34">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="BG34">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="BH34">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -616,7 +616,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-24 08:19:37</t>
+    <t>2026-09-24 10:35:23</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G2">
         <v>1.63</v>
@@ -1240,7 +1240,7 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -1255,7 +1255,7 @@
         <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.16</v>
@@ -1267,10 +1267,10 @@
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA2">
         <v>260</v>
@@ -1279,7 +1279,7 @@
         <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
         <v>26</v>
@@ -1300,10 +1300,10 @@
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1312,7 +1312,7 @@
         <v>210</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
         <v>200</v>
@@ -1324,10 +1324,10 @@
         <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1339,7 +1339,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1348,10 +1348,10 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>13</v>
@@ -1360,28 +1360,28 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>9</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
         <v>2.68</v>
       </c>
       <c r="BJ2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1390,46 +1390,46 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>200</v>
@@ -1452,73 +1452,73 @@
         <v>161</v>
       </c>
       <c r="F3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G3">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="H3">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="I3">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
         <v>1.37</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="W3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X3">
         <v>21</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC3">
         <v>11</v>
@@ -1527,25 +1527,25 @@
         <v>11</v>
       </c>
       <c r="AE3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AF3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AG3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3">
         <v>50</v>
       </c>
       <c r="AJ3">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AK3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL3">
         <v>120</v>
@@ -1554,28 +1554,28 @@
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AO3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
         <v>8.800000000000001</v>
@@ -1584,46 +1584,46 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1632,46 +1632,46 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>200</v>
@@ -1697,55 +1697,55 @@
         <v>1.63</v>
       </c>
       <c r="G4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>6.8</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X4">
         <v>18</v>
@@ -1763,22 +1763,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1793,49 +1793,49 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO4">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AS4">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
         <v>21</v>
       </c>
       <c r="AW4">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1844,28 +1844,28 @@
         <v>15</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1883,13 +1883,13 @@
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BT4">
         <v>10.5</v>
@@ -1901,19 +1901,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="s">
         <v>200</v>
@@ -1939,22 +1939,22 @@
         <v>1.85</v>
       </c>
       <c r="G5">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
         <v>4.9</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.06</v>
@@ -1963,22 +1963,22 @@
         <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
         <v>2.22</v>
@@ -1993,25 +1993,25 @@
         <v>17.5</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA5">
         <v>130</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -2020,40 +2020,40 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
         <v>22</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
         <v>70</v>
       </c>
       <c r="AP5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -2062,100 +2062,100 @@
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>200</v>
@@ -2178,22 +2178,22 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I6">
         <v>5.6</v>
       </c>
       <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
         <v>3.7</v>
-      </c>
-      <c r="K6">
-        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.47</v>
@@ -2202,13 +2202,13 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
         <v>2.16</v>
@@ -2223,28 +2223,28 @@
         <v>1.98</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y6">
         <v>16</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA6">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AB6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
@@ -2253,7 +2253,7 @@
         <v>21</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF6">
         <v>10.5</v>
@@ -2286,7 +2286,7 @@
         <v>120</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
         <v>14</v>
@@ -2295,7 +2295,7 @@
         <v>34</v>
       </c>
       <c r="AS6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2307,7 +2307,7 @@
         <v>18.5</v>
       </c>
       <c r="AW6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX6">
         <v>9</v>
@@ -2319,22 +2319,22 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BB6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC6">
         <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG6">
         <v>12.5</v>
@@ -2343,7 +2343,7 @@
         <v>3.3</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2364,10 +2364,10 @@
         <v>3.3</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2379,7 +2379,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2394,10 +2394,10 @@
         <v>44</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CB6" t="s">
         <v>200</v>
@@ -2420,58 +2420,58 @@
         <v>165</v>
       </c>
       <c r="F7">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3.35</v>
+      </c>
+      <c r="H7">
+        <v>2.28</v>
+      </c>
+      <c r="I7">
+        <v>2.52</v>
+      </c>
+      <c r="J7">
         <v>3.5</v>
       </c>
-      <c r="H7">
-        <v>2.2</v>
-      </c>
-      <c r="I7">
-        <v>2.62</v>
-      </c>
-      <c r="J7">
-        <v>2.96</v>
-      </c>
       <c r="K7">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
         <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q7">
         <v>1.7</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S7">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U7">
         <v>2.16</v>
       </c>
       <c r="V7">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2489,7 +2489,7 @@
         <v>1000</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2528,58 +2528,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2662,13 +2662,13 @@
         <v>166</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="G8">
         <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="I8">
         <v>1000</v>
@@ -2686,16 +2686,16 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O8">
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="R8">
         <v>1.08</v>
@@ -2931,19 +2931,19 @@
         <v>1.08</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
         <v>1.08</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
         <v>1.08</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3152,7 +3152,7 @@
         <v>2.3</v>
       </c>
       <c r="H10">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
         <v>3.5</v>
@@ -3161,7 +3161,7 @@
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3170,28 +3170,28 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
         <v>1.4</v>
       </c>
       <c r="S10">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V10">
         <v>1.4</v>
@@ -3388,37 +3388,37 @@
         <v>169</v>
       </c>
       <c r="F11">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G11">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H11">
         <v>5.1</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -3427,28 +3427,28 @@
         <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T11">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y11">
         <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA11">
         <v>170</v>
@@ -3472,13 +3472,13 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11">
         <v>85</v>
       </c>
       <c r="AJ11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK11">
         <v>20</v>
@@ -3487,13 +3487,13 @@
         <v>42</v>
       </c>
       <c r="AM11">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN11">
         <v>13</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3505,10 +3505,10 @@
         <v>34</v>
       </c>
       <c r="AS11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
@@ -3520,13 +3520,13 @@
         <v>17</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY11">
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
         <v>17</v>
@@ -3541,7 +3541,7 @@
         <v>36</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF11">
         <v>11.5</v>
@@ -3577,7 +3577,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BR11">
         <v>1000</v>
@@ -3630,22 +3630,22 @@
         <v>170</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="G12">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="H12">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3654,7 +3654,7 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.4</v>
@@ -3672,70 +3672,70 @@
         <v>4.1</v>
       </c>
       <c r="T12">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="X12">
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA12">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE12">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF12">
+        <v>10.5</v>
+      </c>
+      <c r="AG12">
         <v>11</v>
       </c>
-      <c r="AG12">
-        <v>10.5</v>
-      </c>
       <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>90</v>
+      </c>
+      <c r="AJ12">
+        <v>21</v>
+      </c>
+      <c r="AK12">
         <v>22</v>
-      </c>
-      <c r="AI12">
-        <v>85</v>
-      </c>
-      <c r="AJ12">
-        <v>22</v>
-      </c>
-      <c r="AK12">
-        <v>23</v>
       </c>
       <c r="AL12">
         <v>44</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO12">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP12">
         <v>10.5</v>
@@ -3744,52 +3744,52 @@
         <v>13</v>
       </c>
       <c r="AR12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS12">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX12">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12">
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
         <v>70</v>
       </c>
       <c r="BB12">
+        <v>18</v>
+      </c>
+      <c r="BC12">
         <v>19</v>
-      </c>
-      <c r="BC12">
-        <v>19.5</v>
       </c>
       <c r="BD12">
         <v>38</v>
       </c>
       <c r="BE12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH12">
         <v>3.1</v>
@@ -3804,7 +3804,7 @@
         <v>9.4</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM12">
         <v>15.5</v>
@@ -3813,13 +3813,13 @@
         <v>4.4</v>
       </c>
       <c r="BO12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
         <v>32</v>
@@ -3828,13 +3828,13 @@
         <v>11</v>
       </c>
       <c r="BT12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW12">
         <v>12.5</v>
@@ -3846,10 +3846,10 @@
         <v>13.5</v>
       </c>
       <c r="BZ12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
         <v>200</v>
@@ -3872,22 +3872,22 @@
         <v>171</v>
       </c>
       <c r="F13">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>1.75</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>8.199999999999999</v>
+        <v>190</v>
       </c>
       <c r="J13">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3896,22 +3896,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.32</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3920,10 +3920,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4114,19 +4114,19 @@
         <v>172</v>
       </c>
       <c r="F14">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="G14">
-        <v>1.45</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
         <v>130</v>
       </c>
       <c r="J14">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4138,22 +4138,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>2.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
         <v>1.02</v>
       </c>
       <c r="R14">
-        <v>1.87</v>
+        <v>1.08</v>
       </c>
       <c r="S14">
-        <v>1.59</v>
+        <v>1.03</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4165,7 +4165,7 @@
         <v>1.01</v>
       </c>
       <c r="W14">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4356,22 +4356,22 @@
         <v>173</v>
       </c>
       <c r="F15">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
         <v>1000</v>
       </c>
       <c r="H15">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="I15">
-        <v>1.68</v>
+        <v>110</v>
       </c>
       <c r="J15">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="K15">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4380,22 +4380,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.74</v>
+        <v>1.08</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="Q15">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="S15">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4404,7 +4404,7 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
         <v>1.01</v>
@@ -4598,166 +4598,166 @@
         <v>174</v>
       </c>
       <c r="F16">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G16">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I16">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P16">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
         <v>1.74</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="T16">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W16">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD16">
+        <v>12</v>
+      </c>
+      <c r="AE16">
+        <v>29</v>
+      </c>
+      <c r="AF16">
         <v>24</v>
       </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
       <c r="AG16">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>1.17</v>
+        <v>14</v>
       </c>
       <c r="AS16">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="AT16">
-        <v>1.17</v>
+        <v>12.5</v>
       </c>
       <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>17</v>
+      </c>
+      <c r="AX16">
+        <v>17</v>
+      </c>
+      <c r="AY16">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16">
+        <v>13.5</v>
+      </c>
+      <c r="BA16">
         <v>6</v>
       </c>
-      <c r="AV16">
-        <v>1.12</v>
-      </c>
-      <c r="AW16">
-        <v>1.17</v>
-      </c>
-      <c r="AX16">
-        <v>1.17</v>
-      </c>
-      <c r="AY16">
-        <v>1.14</v>
-      </c>
-      <c r="AZ16">
-        <v>1.17</v>
-      </c>
-      <c r="BA16">
-        <v>1.17</v>
-      </c>
       <c r="BB16">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="BC16">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="BD16">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="BE16">
-        <v>1.17</v>
+        <v>6.4</v>
       </c>
       <c r="BF16">
-        <v>1.17</v>
+        <v>19</v>
       </c>
       <c r="BG16">
-        <v>1.17</v>
+        <v>13.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4852,7 +4852,7 @@
         <v>6.6</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17">
         <v>4.8</v>
@@ -4870,16 +4870,16 @@
         <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q17">
         <v>1.66</v>
       </c>
       <c r="R17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T17">
         <v>1.77</v>
@@ -4912,7 +4912,7 @@
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE17">
         <v>90</v>
@@ -5017,7 +5017,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="BN17">
         <v>1000</v>
@@ -5059,7 +5059,7 @@
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="CB17" t="s">
         <v>200</v>
@@ -5082,22 +5082,22 @@
         <v>176</v>
       </c>
       <c r="F18">
+        <v>1.53</v>
+      </c>
+      <c r="G18">
         <v>1.54</v>
       </c>
-      <c r="G18">
-        <v>1.55</v>
-      </c>
       <c r="H18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L18">
         <v>1.29</v>
@@ -5112,40 +5112,40 @@
         <v>1.22</v>
       </c>
       <c r="P18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
         <v>1.66</v>
       </c>
       <c r="R18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T18">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U18">
         <v>2.14</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W18">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z18">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA18">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB18">
         <v>10.5</v>
@@ -5157,10 +5157,10 @@
         <v>26</v>
       </c>
       <c r="AE18">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5172,10 +5172,10 @@
         <v>80</v>
       </c>
       <c r="AJ18">
+        <v>13.5</v>
+      </c>
+      <c r="AK18">
         <v>14.5</v>
-      </c>
-      <c r="AK18">
-        <v>15</v>
       </c>
       <c r="AL18">
         <v>32</v>
@@ -5193,34 +5193,34 @@
         <v>19.5</v>
       </c>
       <c r="AQ18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS18">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AT18">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV18">
         <v>23</v>
       </c>
       <c r="AW18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18">
         <v>65</v>
@@ -5229,13 +5229,13 @@
         <v>12.5</v>
       </c>
       <c r="BC18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD18">
         <v>28</v>
       </c>
       <c r="BE18">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="BF18">
         <v>5.9</v>
@@ -5262,16 +5262,16 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR18">
         <v>1000</v>
@@ -5283,7 +5283,7 @@
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV18">
         <v>1000</v>
@@ -5330,16 +5330,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H19">
+        <v>1.44</v>
+      </c>
+      <c r="I19">
         <v>1.45</v>
       </c>
-      <c r="I19">
-        <v>1.46</v>
-      </c>
       <c r="J19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L19">
         <v>1.26</v>
@@ -5351,34 +5351,34 @@
         <v>6.6</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P19">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q19">
         <v>1.48</v>
       </c>
       <c r="R19">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S19">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y19">
         <v>13</v>
@@ -5393,7 +5393,7 @@
         <v>40</v>
       </c>
       <c r="AC19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD19">
         <v>10.5</v>
@@ -5402,22 +5402,22 @@
         <v>14</v>
       </c>
       <c r="AF19">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AG19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH19">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI19">
         <v>26</v>
       </c>
       <c r="AJ19">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AK19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL19">
         <v>75</v>
@@ -5429,7 +5429,7 @@
         <v>75</v>
       </c>
       <c r="AO19">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AP19">
         <v>27</v>
@@ -5447,19 +5447,19 @@
         <v>34</v>
       </c>
       <c r="AU19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV19">
         <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX19">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AY19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ19">
         <v>19</v>
@@ -5468,22 +5468,22 @@
         <v>23</v>
       </c>
       <c r="BB19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC19">
-        <v>75</v>
+        <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE19">
         <v>65</v>
       </c>
       <c r="BF19">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BG19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH19">
         <v>4.9</v>
@@ -5525,13 +5525,13 @@
         <v>4.4</v>
       </c>
       <c r="BU19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV19">
         <v>8.6</v>
       </c>
       <c r="BW19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX19">
         <v>19</v>
@@ -5566,10 +5566,10 @@
         <v>178</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G20">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H20">
         <v>5.3</v>
@@ -5578,10 +5578,10 @@
         <v>5.5</v>
       </c>
       <c r="J20">
+        <v>3.8</v>
+      </c>
+      <c r="K20">
         <v>3.85</v>
-      </c>
-      <c r="K20">
-        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.39</v>
@@ -5593,7 +5593,7 @@
         <v>3.55</v>
       </c>
       <c r="O20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P20">
         <v>1.85</v>
@@ -5608,7 +5608,7 @@
         <v>3.8</v>
       </c>
       <c r="T20">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U20">
         <v>1.94</v>
@@ -5617,7 +5617,7 @@
         <v>1.22</v>
       </c>
       <c r="W20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X20">
         <v>13.5</v>
@@ -5653,10 +5653,10 @@
         <v>22</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK20">
         <v>21</v>
@@ -5674,7 +5674,7 @@
         <v>100</v>
       </c>
       <c r="AP20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
         <v>15</v>
@@ -5683,7 +5683,7 @@
         <v>36</v>
       </c>
       <c r="AS20">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT20">
         <v>7.4</v>
@@ -5695,7 +5695,7 @@
         <v>18.5</v>
       </c>
       <c r="AW20">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX20">
         <v>9.199999999999999</v>
@@ -5716,52 +5716,52 @@
         <v>18</v>
       </c>
       <c r="BD20">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="BE20">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF20">
         <v>11</v>
       </c>
       <c r="BG20">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BT20">
         <v>1000</v>
@@ -5773,19 +5773,19 @@
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="CB20" t="s">
         <v>200</v>
@@ -5817,7 +5817,7 @@
         <v>3.25</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J21">
         <v>3.65</v>
@@ -5835,7 +5835,7 @@
         <v>4.3</v>
       </c>
       <c r="O21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P21">
         <v>2.12</v>
@@ -5856,7 +5856,7 @@
         <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
         <v>1.73</v>
@@ -5904,7 +5904,7 @@
         <v>24</v>
       </c>
       <c r="AL21">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM21">
         <v>80</v>
@@ -5928,7 +5928,7 @@
         <v>50</v>
       </c>
       <c r="AT21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
         <v>7.6</v>
@@ -5952,7 +5952,7 @@
         <v>38</v>
       </c>
       <c r="BB21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC21">
         <v>21</v>
@@ -6074,13 +6074,13 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P22">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q22">
         <v>2.18</v>
@@ -6089,13 +6089,13 @@
         <v>1.3</v>
       </c>
       <c r="S22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T22">
         <v>1.89</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
         <v>1.42</v>
@@ -6128,7 +6128,7 @@
         <v>55</v>
       </c>
       <c r="AF22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG22">
         <v>12</v>
@@ -6155,7 +6155,7 @@
         <v>24</v>
       </c>
       <c r="AO22">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP22">
         <v>12</v>
@@ -6221,55 +6221,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>11</v>
+        <v>2.64</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="CB22" t="s">
         <v>200</v>
@@ -6292,22 +6292,22 @@
         <v>181</v>
       </c>
       <c r="F23">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G23">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H23">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.42</v>
@@ -6319,13 +6319,13 @@
         <v>3.75</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P23">
         <v>1.94</v>
       </c>
       <c r="Q23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R23">
         <v>1.36</v>
@@ -6334,7 +6334,7 @@
         <v>3.55</v>
       </c>
       <c r="T23">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U23">
         <v>1.97</v>
@@ -6343,7 +6343,7 @@
         <v>1.21</v>
       </c>
       <c r="W23">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X23">
         <v>15</v>
@@ -6352,7 +6352,7 @@
         <v>18</v>
       </c>
       <c r="Z23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA23">
         <v>180</v>
@@ -6370,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="AF23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -6382,7 +6382,7 @@
         <v>85</v>
       </c>
       <c r="AJ23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK23">
         <v>19</v>
@@ -6409,13 +6409,13 @@
         <v>38</v>
       </c>
       <c r="AS23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT23">
         <v>7.4</v>
       </c>
       <c r="AU23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV23">
         <v>19.5</v>
@@ -6445,13 +6445,13 @@
         <v>34</v>
       </c>
       <c r="BE23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF23">
         <v>10.5</v>
       </c>
       <c r="BG23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH23">
         <v>3.4</v>
@@ -6487,7 +6487,7 @@
         <v>29</v>
       </c>
       <c r="BS23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT23">
         <v>9</v>
@@ -6511,7 +6511,7 @@
         <v>24</v>
       </c>
       <c r="CA23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB23" t="s">
         <v>200</v>
@@ -6552,7 +6552,7 @@
         <v>5.3</v>
       </c>
       <c r="L24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6561,28 +6561,28 @@
         <v>3.95</v>
       </c>
       <c r="O24">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P24">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q24">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R24">
         <v>1.39</v>
       </c>
       <c r="S24">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="T24">
         <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W24">
         <v>3.25</v>
@@ -6600,25 +6600,25 @@
         <v>510</v>
       </c>
       <c r="AB24">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC24">
         <v>14</v>
       </c>
       <c r="AD24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AE24">
         <v>230</v>
       </c>
       <c r="AF24">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH24">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI24">
         <v>190</v>
@@ -6636,7 +6636,7 @@
         <v>230</v>
       </c>
       <c r="AN24">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO24">
         <v>350</v>
@@ -6648,10 +6648,10 @@
         <v>21</v>
       </c>
       <c r="AR24">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AS24">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AT24">
         <v>6.8</v>
@@ -6660,10 +6660,10 @@
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AW24">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AX24">
         <v>7</v>
@@ -6675,7 +6675,7 @@
         <v>21</v>
       </c>
       <c r="BA24">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB24">
         <v>10</v>
@@ -6684,16 +6684,16 @@
         <v>13.5</v>
       </c>
       <c r="BD24">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BE24">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BF24">
         <v>6</v>
       </c>
       <c r="BG24">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6779,13 +6779,13 @@
         <v>2.96</v>
       </c>
       <c r="G25">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H25">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I25">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J25">
         <v>3.3</v>
@@ -6800,7 +6800,7 @@
         <v>1.06</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O25">
         <v>1.25</v>
@@ -7021,7 +7021,7 @@
         <v>1.83</v>
       </c>
       <c r="G26">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H26">
         <v>5.1</v>
@@ -7030,7 +7030,7 @@
         <v>5.8</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
         <v>3.65</v>
@@ -7048,7 +7048,7 @@
         <v>1.44</v>
       </c>
       <c r="P26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q26">
         <v>2.26</v>
@@ -7060,16 +7060,16 @@
         <v>3.9</v>
       </c>
       <c r="T26">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
         <v>1.2</v>
       </c>
       <c r="W26">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X26">
         <v>970</v>
@@ -7263,7 +7263,7 @@
         <v>2.5</v>
       </c>
       <c r="G27">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H27">
         <v>2.88</v>
@@ -7272,7 +7272,7 @@
         <v>3.1</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7284,19 +7284,19 @@
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
         <v>1.31</v>
       </c>
       <c r="P27">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q27">
         <v>1.92</v>
       </c>
       <c r="R27">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
         <v>3.15</v>
@@ -7329,7 +7329,7 @@
         <v>970</v>
       </c>
       <c r="AC27">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD27">
         <v>970</v>
@@ -7368,19 +7368,19 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AQ27">
+        <v>1.26</v>
+      </c>
+      <c r="AR27">
+        <v>1.32</v>
+      </c>
+      <c r="AS27">
+        <v>1.32</v>
+      </c>
+      <c r="AT27">
         <v>1.25</v>
-      </c>
-      <c r="AR27">
-        <v>1.31</v>
-      </c>
-      <c r="AS27">
-        <v>1.31</v>
-      </c>
-      <c r="AT27">
-        <v>1.23</v>
       </c>
       <c r="AU27">
         <v>5.8</v>
@@ -7389,97 +7389,97 @@
         <v>1.27</v>
       </c>
       <c r="AW27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AX27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AY27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AZ27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BA27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BB27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BC27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BD27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BE27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BG27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BH27">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>200</v>
@@ -7511,7 +7511,7 @@
         <v>2.66</v>
       </c>
       <c r="I28">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J28">
         <v>3.5</v>
@@ -7523,7 +7523,7 @@
         <v>1.3</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N28">
         <v>4.5</v>
@@ -7538,16 +7538,16 @@
         <v>1.74</v>
       </c>
       <c r="R28">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S28">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
         <v>1.56</v>
@@ -7595,16 +7595,16 @@
         <v>50</v>
       </c>
       <c r="AK28">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL28">
         <v>44</v>
       </c>
       <c r="AM28">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO28">
         <v>21</v>
@@ -7655,7 +7655,7 @@
         <v>6.6</v>
       </c>
       <c r="BE28">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF28">
         <v>17</v>
@@ -7780,10 +7780,10 @@
         <v>1.47</v>
       </c>
       <c r="R29">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S29">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T29">
         <v>1.49</v>
@@ -7801,13 +7801,13 @@
         <v>34</v>
       </c>
       <c r="Y29">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z29">
         <v>23</v>
       </c>
       <c r="AA29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB29">
         <v>25</v>
@@ -7819,7 +7819,7 @@
         <v>14</v>
       </c>
       <c r="AE29">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF29">
         <v>34</v>
@@ -7837,19 +7837,19 @@
         <v>60</v>
       </c>
       <c r="AK29">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL29">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM29">
         <v>55</v>
       </c>
       <c r="AN29">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP29">
         <v>21</v>
@@ -7861,10 +7861,10 @@
         <v>16.5</v>
       </c>
       <c r="AS29">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT29">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -7876,31 +7876,31 @@
         <v>17.5</v>
       </c>
       <c r="AX29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ29">
         <v>12</v>
       </c>
       <c r="BA29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB29">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC29">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BD29">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE29">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BF29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG29">
         <v>8.800000000000001</v>
@@ -7986,19 +7986,19 @@
         <v>188</v>
       </c>
       <c r="F30">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G30">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H30">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I30">
         <v>2.88</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K30">
         <v>3.85</v>
@@ -8010,22 +8010,22 @@
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q30">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R30">
         <v>1.41</v>
       </c>
       <c r="S30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T30">
         <v>1.67</v>
@@ -8043,13 +8043,13 @@
         <v>17</v>
       </c>
       <c r="Y30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z30">
         <v>20</v>
       </c>
       <c r="AA30">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB30">
         <v>13</v>
@@ -8061,34 +8061,34 @@
         <v>13</v>
       </c>
       <c r="AE30">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF30">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG30">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH30">
         <v>17</v>
       </c>
       <c r="AI30">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ30">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK30">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AL30">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM30">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO30">
         <v>23</v>
@@ -8100,19 +8100,19 @@
         <v>11</v>
       </c>
       <c r="AR30">
+        <v>16.5</v>
+      </c>
+      <c r="AS30">
         <v>7</v>
       </c>
-      <c r="AS30">
-        <v>8.4</v>
-      </c>
       <c r="AT30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU30">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW30">
         <v>20</v>
@@ -8124,49 +8124,49 @@
         <v>10.5</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA30">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB30">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BC30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD30">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BE30">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF30">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG30">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BH30">
         <v>3.8</v>
       </c>
       <c r="BI30">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ30">
         <v>9.4</v>
       </c>
       <c r="BK30">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN30">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO30">
         <v>4.5</v>
@@ -8175,31 +8175,31 @@
         <v>21</v>
       </c>
       <c r="BQ30">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR30">
         <v>32</v>
       </c>
       <c r="BS30">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT30">
         <v>6.2</v>
       </c>
       <c r="BU30">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV30">
         <v>21</v>
       </c>
       <c r="BW30">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX30">
         <v>32</v>
       </c>
       <c r="BY30">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ30">
         <v>0</v>
@@ -8228,22 +8228,22 @@
         <v>189</v>
       </c>
       <c r="F31">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="G31">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="H31">
         <v>4.5</v>
       </c>
       <c r="I31">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="J31">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K31">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8261,25 +8261,25 @@
         <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R31">
         <v>1.41</v>
       </c>
       <c r="S31">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T31">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U31">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8336,58 +8336,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AS31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT31">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AU31">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AV31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AW31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AX31">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AY31">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AZ31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BA31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BB31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BC31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BD31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BE31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BF31">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="BG31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8473,7 +8473,7 @@
         <v>2.34</v>
       </c>
       <c r="G32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H32">
         <v>3.25</v>
@@ -8482,34 +8482,34 @@
         <v>3.5</v>
       </c>
       <c r="J32">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K32">
         <v>3.45</v>
       </c>
       <c r="L32">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
         <v>1.09</v>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P32">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R32">
         <v>1.26</v>
       </c>
       <c r="S32">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T32">
         <v>1.89</v>
@@ -8521,7 +8521,7 @@
         <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X32">
         <v>13</v>
@@ -8560,10 +8560,10 @@
         <v>70</v>
       </c>
       <c r="AJ32">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL32">
         <v>60</v>
@@ -8587,7 +8587,7 @@
         <v>17.5</v>
       </c>
       <c r="AS32">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT32">
         <v>7.6</v>
@@ -8599,7 +8599,7 @@
         <v>12.5</v>
       </c>
       <c r="AW32">
-        <v>36</v>
+        <v>5.9</v>
       </c>
       <c r="AX32">
         <v>12.5</v>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="BA32">
+        <v>6</v>
+      </c>
+      <c r="BB32">
+        <v>5.6</v>
+      </c>
+      <c r="BC32">
+        <v>5.5</v>
+      </c>
+      <c r="BD32">
+        <v>5.9</v>
+      </c>
+      <c r="BE32">
         <v>6.2</v>
-      </c>
-      <c r="BB32">
-        <v>5.7</v>
-      </c>
-      <c r="BC32">
-        <v>5.6</v>
-      </c>
-      <c r="BD32">
-        <v>6</v>
-      </c>
-      <c r="BE32">
-        <v>6.4</v>
       </c>
       <c r="BF32">
         <v>20</v>
@@ -8712,22 +8712,22 @@
         <v>191</v>
       </c>
       <c r="F33">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="G33">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="H33">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="I33">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="J33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8736,13 +8736,13 @@
         <v>1.09</v>
       </c>
       <c r="N33">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>1.4</v>
       </c>
       <c r="P33">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q33">
         <v>2.18</v>
@@ -8751,127 +8751,127 @@
         <v>1.25</v>
       </c>
       <c r="S33">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="X33">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y33">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z33">
+        <v>19</v>
+      </c>
+      <c r="AA33">
+        <v>48</v>
+      </c>
+      <c r="AB33">
+        <v>11.5</v>
+      </c>
+      <c r="AC33">
+        <v>7.6</v>
+      </c>
+      <c r="AD33">
+        <v>14</v>
+      </c>
+      <c r="AE33">
+        <v>38</v>
+      </c>
+      <c r="AF33">
+        <v>21</v>
+      </c>
+      <c r="AG33">
+        <v>14</v>
+      </c>
+      <c r="AH33">
+        <v>19.5</v>
+      </c>
+      <c r="AI33">
+        <v>60</v>
+      </c>
+      <c r="AJ33">
+        <v>65</v>
+      </c>
+      <c r="AK33">
+        <v>40</v>
+      </c>
+      <c r="AL33">
+        <v>70</v>
+      </c>
+      <c r="AM33">
+        <v>130</v>
+      </c>
+      <c r="AN33">
+        <v>44</v>
+      </c>
+      <c r="AO33">
+        <v>38</v>
+      </c>
+      <c r="AP33">
+        <v>4.7</v>
+      </c>
+      <c r="AQ33">
+        <v>7</v>
+      </c>
+      <c r="AR33">
+        <v>11</v>
+      </c>
+      <c r="AS33">
+        <v>25</v>
+      </c>
+      <c r="AT33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU33">
+        <v>6.4</v>
+      </c>
+      <c r="AV33">
+        <v>9</v>
+      </c>
+      <c r="AW33">
+        <v>21</v>
+      </c>
+      <c r="AX33">
+        <v>14</v>
+      </c>
+      <c r="AY33">
+        <v>5.1</v>
+      </c>
+      <c r="AZ33">
         <v>16.5</v>
       </c>
-      <c r="AA33">
-        <v>38</v>
-      </c>
-      <c r="AB33">
-        <v>13.5</v>
-      </c>
-      <c r="AC33">
-        <v>8.6</v>
-      </c>
-      <c r="AD33">
-        <v>13.5</v>
-      </c>
-      <c r="AE33">
+      <c r="BA33">
         <v>34</v>
       </c>
-      <c r="AF33">
-        <v>29</v>
-      </c>
-      <c r="AG33">
-        <v>18</v>
-      </c>
-      <c r="AH33">
-        <v>23</v>
-      </c>
-      <c r="AI33">
-        <v>55</v>
-      </c>
-      <c r="AJ33">
-        <v>85</v>
-      </c>
-      <c r="AK33">
-        <v>60</v>
-      </c>
-      <c r="AL33">
-        <v>75</v>
-      </c>
-      <c r="AM33">
-        <v>150</v>
-      </c>
-      <c r="AN33">
-        <v>70</v>
-      </c>
-      <c r="AO33">
-        <v>30</v>
-      </c>
-      <c r="AP33">
-        <v>1.03</v>
-      </c>
-      <c r="AQ33">
-        <v>1.03</v>
-      </c>
-      <c r="AR33">
-        <v>1.03</v>
-      </c>
-      <c r="AS33">
-        <v>1.03</v>
-      </c>
-      <c r="AT33">
-        <v>1.03</v>
-      </c>
-      <c r="AU33">
-        <v>1.03</v>
-      </c>
-      <c r="AV33">
-        <v>1.03</v>
-      </c>
-      <c r="AW33">
-        <v>1.03</v>
-      </c>
-      <c r="AX33">
-        <v>1.03</v>
-      </c>
-      <c r="AY33">
-        <v>1.03</v>
-      </c>
-      <c r="AZ33">
-        <v>1.03</v>
-      </c>
-      <c r="BA33">
-        <v>1.03</v>
-      </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG33">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH33">
         <v>3.75</v>
@@ -8883,55 +8883,55 @@
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB33" t="s">
         <v>200</v>
@@ -8978,10 +8978,10 @@
         <v>1.02</v>
       </c>
       <c r="N34">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="O34">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P34">
         <v>2.88</v>
@@ -9038,7 +9038,7 @@
         <v>1000</v>
       </c>
       <c r="AH34">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
         <v>1000</v>
@@ -9062,58 +9062,58 @@
         <v>970</v>
       </c>
       <c r="AP34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AQ34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AR34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AU34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AV34">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AW34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AX34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AY34">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AZ34">
         <v>1.27</v>
       </c>
       <c r="BA34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BB34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BC34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BD34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BE34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BF34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BG34">
-        <v>6.2</v>
+        <v>1.15</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9220,7 +9220,7 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="O35">
         <v>1.37</v>
@@ -9235,7 +9235,7 @@
         <v>1.08</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T35">
         <v>1.83</v>
@@ -9450,7 +9450,7 @@
         <v>110</v>
       </c>
       <c r="J36">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="K36">
         <v>950</v>
@@ -9722,10 +9722,10 @@
         <v>1.42</v>
       </c>
       <c r="T37">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U37">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V37">
         <v>1.01</v>
@@ -9800,10 +9800,10 @@
         <v>1.03</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV37">
         <v>1.03</v>
@@ -9812,7 +9812,7 @@
         <v>1.03</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY37">
         <v>1.01</v>
@@ -9922,16 +9922,16 @@
         <v>196</v>
       </c>
       <c r="F38">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G38">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H38">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I38">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J38">
         <v>4.1</v>
@@ -9940,16 +9940,16 @@
         <v>4.5</v>
       </c>
       <c r="L38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M38">
         <v>1.06</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P38">
         <v>2.06</v>
@@ -9961,22 +9961,22 @@
         <v>1.39</v>
       </c>
       <c r="S38">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T38">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U38">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W38">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X38">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y38">
         <v>22</v>
@@ -9991,16 +9991,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD38">
         <v>25</v>
       </c>
       <c r="AE38">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF38">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG38">
         <v>10.5</v>
@@ -10024,7 +10024,7 @@
         <v>140</v>
       </c>
       <c r="AN38">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO38">
         <v>130</v>
@@ -10033,13 +10033,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ38">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AR38">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT38">
         <v>7.6</v>
@@ -10051,7 +10051,7 @@
         <v>20</v>
       </c>
       <c r="AW38">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AX38">
         <v>8.6</v>
@@ -10060,46 +10060,46 @@
         <v>9</v>
       </c>
       <c r="AZ38">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA38">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC38">
         <v>15</v>
       </c>
       <c r="BD38">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE38">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF38">
         <v>7.8</v>
       </c>
       <c r="BG38">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH38">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>2.84</v>
+        <v>1.27</v>
       </c>
       <c r="BJ38">
         <v>1000</v>
       </c>
       <c r="BK38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BN38">
         <v>1000</v>
@@ -10111,37 +10111,37 @@
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BT38">
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="s">
         <v>200</v>
@@ -10176,7 +10176,7 @@
         <v>110</v>
       </c>
       <c r="J39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K39">
         <v>950</v>
@@ -10409,7 +10409,7 @@
         <v>2.66</v>
       </c>
       <c r="G40">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -10421,7 +10421,7 @@
         <v>3.05</v>
       </c>
       <c r="K40">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10433,7 +10433,7 @@
         <v>2.72</v>
       </c>
       <c r="O40">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P40">
         <v>1.58</v>
@@ -10448,7 +10448,7 @@
         <v>5.1</v>
       </c>
       <c r="T40">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U40">
         <v>1.84</v>
@@ -10466,10 +10466,10 @@
         <v>9.4</v>
       </c>
       <c r="Z40">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA40">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB40">
         <v>8.800000000000001</v>
@@ -10478,7 +10478,7 @@
         <v>7.4</v>
       </c>
       <c r="AD40">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE40">
         <v>55</v>
@@ -10490,13 +10490,13 @@
         <v>13.5</v>
       </c>
       <c r="AH40">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI40">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ40">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK40">
         <v>46</v>
@@ -10508,22 +10508,22 @@
         <v>200</v>
       </c>
       <c r="AN40">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO40">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP40">
         <v>8</v>
       </c>
       <c r="AQ40">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AR40">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS40">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AT40">
         <v>7.6</v>
@@ -10535,7 +10535,7 @@
         <v>12.5</v>
       </c>
       <c r="AW40">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AX40">
         <v>14</v>
@@ -10544,28 +10544,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ40">
+        <v>6.2</v>
+      </c>
+      <c r="BA40">
         <v>7.4</v>
       </c>
-      <c r="BA40">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BB40">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BC40">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BD40">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BF40">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BG40">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10648,13 +10648,13 @@
         <v>199</v>
       </c>
       <c r="F41">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G41">
         <v>1.69</v>
       </c>
       <c r="H41">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I41">
         <v>7.2</v>
@@ -10663,31 +10663,31 @@
         <v>3.75</v>
       </c>
       <c r="K41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L41">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M41">
         <v>1.09</v>
       </c>
       <c r="N41">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O41">
         <v>1.4</v>
       </c>
       <c r="P41">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R41">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T41">
         <v>2.16</v>
@@ -10699,13 +10699,13 @@
         <v>1.16</v>
       </c>
       <c r="W41">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="X41">
         <v>12.5</v>
       </c>
       <c r="Y41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z41">
         <v>65</v>
@@ -10717,10 +10717,10 @@
         <v>7</v>
       </c>
       <c r="AC41">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD41">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE41">
         <v>140</v>
@@ -10738,10 +10738,10 @@
         <v>140</v>
       </c>
       <c r="AJ41">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK41">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL41">
         <v>60</v>
@@ -10759,16 +10759,16 @@
         <v>10</v>
       </c>
       <c r="AQ41">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR41">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS41">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT41">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -10777,7 +10777,7 @@
         <v>23</v>
       </c>
       <c r="AW41">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX41">
         <v>7.8</v>
@@ -10786,10 +10786,10 @@
         <v>9</v>
       </c>
       <c r="AZ41">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA41">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB41">
         <v>14</v>
@@ -10798,16 +10798,16 @@
         <v>17.5</v>
       </c>
       <c r="BD41">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE41">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF41">
         <v>11</v>
       </c>
       <c r="BG41">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10819,7 +10819,7 @@
         <v>1000</v>
       </c>
       <c r="BK41">
-        <v>1.28</v>
+        <v>2.06</v>
       </c>
       <c r="BL41">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -616,7 +616,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-24 12:51:43</t>
+    <t>2026-09-24 15:20:46</t>
   </si>
 </sst>
 </file>
@@ -1210,22 +1210,22 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1237,7 +1237,7 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
         <v>1.89</v>
@@ -1249,10 +1249,10 @@
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
         <v>1.81</v>
@@ -1261,7 +1261,7 @@
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1288,7 +1288,7 @@
         <v>140</v>
       </c>
       <c r="AF2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1306,7 +1306,7 @@
         <v>18.5</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>210</v>
@@ -1318,13 +1318,13 @@
         <v>200</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
         <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS2">
         <v>10.5</v>
@@ -1345,7 +1345,7 @@
         <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
         <v>21</v>
@@ -1360,7 +1360,7 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE2">
         <v>100</v>
@@ -1420,7 +1420,7 @@
         <v>50</v>
       </c>
       <c r="BX2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY2">
         <v>50</v>
@@ -1452,7 +1452,7 @@
         <v>161</v>
       </c>
       <c r="F3">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G3">
         <v>6.4</v>
@@ -1461,13 +1461,13 @@
         <v>1.58</v>
       </c>
       <c r="I3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1476,7 +1476,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
         <v>1.33</v>
@@ -1494,13 +1494,13 @@
         <v>3.55</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="W3">
         <v>1.18</v>
@@ -1515,7 +1515,7 @@
         <v>9.4</v>
       </c>
       <c r="AA3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AB3">
         <v>22</v>
@@ -1527,7 +1527,7 @@
         <v>11</v>
       </c>
       <c r="AE3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AF3">
         <v>65</v>
@@ -1548,22 +1548,22 @@
         <v>120</v>
       </c>
       <c r="AL3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM3">
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO3">
         <v>11</v>
       </c>
       <c r="AP3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
         <v>7.8</v>
@@ -1581,10 +1581,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX3">
-        <v>34</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
         <v>20</v>
@@ -1596,25 +1596,25 @@
         <v>32</v>
       </c>
       <c r="BB3">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>6.6</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
+        <v>6</v>
+      </c>
+      <c r="BF3">
+        <v>6</v>
+      </c>
+      <c r="BG3">
         <v>7.8</v>
       </c>
-      <c r="BF3">
-        <v>70</v>
-      </c>
-      <c r="BG3">
-        <v>7.6</v>
-      </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI3">
         <v>2.82</v>
@@ -1632,7 +1632,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO3">
         <v>7.8</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BT3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU3">
         <v>3.1</v>
@@ -1659,19 +1659,19 @@
         <v>12</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>32</v>
       </c>
       <c r="BY3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>200</v>
@@ -1694,148 +1694,148 @@
         <v>162</v>
       </c>
       <c r="F4">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="G4">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
         <v>3.9</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
         <v>36</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB4">
         <v>17.5</v>
@@ -1844,76 +1844,76 @@
         <v>16</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE4">
         <v>65</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BH4">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>200</v>
@@ -1936,13 +1936,13 @@
         <v>163</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
         <v>5.7</v>
@@ -1960,7 +1960,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.39</v>
@@ -1969,7 +1969,7 @@
         <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1978,7 +1978,7 @@
         <v>4.1</v>
       </c>
       <c r="T5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U5">
         <v>1.86</v>
@@ -1987,7 +1987,7 @@
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
         <v>12</v>
@@ -2008,13 +2008,13 @@
         <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE5">
         <v>90</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -2032,7 +2032,7 @@
         <v>22</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>160</v>
@@ -2044,7 +2044,7 @@
         <v>120</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
         <v>14</v>
@@ -2053,7 +2053,7 @@
         <v>34</v>
       </c>
       <c r="AS5">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="AT5">
         <v>7</v>
@@ -2065,7 +2065,7 @@
         <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX5">
         <v>9</v>
@@ -2074,10 +2074,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -2089,16 +2089,16 @@
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="BF5">
         <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
         <v>2.86</v>
@@ -2137,7 +2137,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2181,16 +2181,16 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H6">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I6">
         <v>2.52</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
         <v>3.95</v>
@@ -2202,34 +2202,34 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
         <v>2.98</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W6">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X6">
         <v>19.5</v>
@@ -2256,31 +2256,31 @@
         <v>28</v>
       </c>
       <c r="AF6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO6">
         <v>19.5</v>
@@ -2295,7 +2295,7 @@
         <v>14</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT6">
         <v>12</v>
@@ -2304,7 +2304,7 @@
         <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW6">
         <v>18.5</v>
@@ -2319,19 +2319,19 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB6">
+        <v>5.7</v>
+      </c>
+      <c r="BC6">
         <v>5.4</v>
       </c>
-      <c r="BC6">
-        <v>5.1</v>
-      </c>
       <c r="BD6">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF6">
         <v>21</v>
@@ -2343,7 +2343,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2432,7 +2432,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2453,7 +2453,7 @@
         <v>1.09</v>
       </c>
       <c r="Q7">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="R7">
         <v>1.08</v>
@@ -2674,7 +2674,7 @@
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2904,22 +2904,22 @@
         <v>167</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G9">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J9">
         <v>3.6</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2928,25 +2928,25 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P9">
         <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="T9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U9">
         <v>2.32</v>
@@ -2955,7 +2955,7 @@
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3149,7 +3149,7 @@
         <v>1.83</v>
       </c>
       <c r="G10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H10">
         <v>5.1</v>
@@ -3161,43 +3161,43 @@
         <v>3.8</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
         <v>3.75</v>
       </c>
       <c r="T10">
+        <v>1.96</v>
+      </c>
+      <c r="U10">
         <v>1.95</v>
       </c>
-      <c r="U10">
-        <v>1.96</v>
-      </c>
       <c r="V10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
         <v>13.5</v>
@@ -3215,7 +3215,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
         <v>20</v>
@@ -3233,22 +3233,22 @@
         <v>22</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ10">
         <v>19.5</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM10">
         <v>130</v>
       </c>
       <c r="AN10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO10">
         <v>90</v>
@@ -3263,10 +3263,10 @@
         <v>34</v>
       </c>
       <c r="AS10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU10">
         <v>7.8</v>
@@ -3275,7 +3275,7 @@
         <v>18</v>
       </c>
       <c r="AW10">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AX10">
         <v>9.6</v>
@@ -3287,7 +3287,7 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -3296,40 +3296,40 @@
         <v>18</v>
       </c>
       <c r="BD10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF10">
         <v>11.5</v>
       </c>
       <c r="BG10">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP10">
         <v>1000</v>
@@ -3341,31 +3341,31 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="CB10" t="s">
         <v>200</v>
@@ -3391,13 +3391,13 @@
         <v>1.82</v>
       </c>
       <c r="G11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H11">
+        <v>5.1</v>
+      </c>
+      <c r="I11">
         <v>5.2</v>
-      </c>
-      <c r="I11">
-        <v>5.3</v>
       </c>
       <c r="J11">
         <v>3.8</v>
@@ -3412,25 +3412,25 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
         <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q11">
         <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
         <v>4.1</v>
       </c>
       <c r="T11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U11">
         <v>1.89</v>
@@ -3439,7 +3439,7 @@
         <v>1.23</v>
       </c>
       <c r="W11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X11">
         <v>12</v>
@@ -3454,7 +3454,7 @@
         <v>150</v>
       </c>
       <c r="AB11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC11">
         <v>8.6</v>
@@ -3484,7 +3484,7 @@
         <v>22</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM11">
         <v>150</v>
@@ -3496,19 +3496,19 @@
         <v>120</v>
       </c>
       <c r="AP11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR11">
         <v>32</v>
       </c>
       <c r="AS11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -3541,13 +3541,13 @@
         <v>38</v>
       </c>
       <c r="BE11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BH11">
         <v>3.1</v>
@@ -3559,13 +3559,13 @@
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL11">
         <v>170</v>
       </c>
       <c r="BM11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3577,16 +3577,16 @@
         <v>13.5</v>
       </c>
       <c r="BQ11">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
         <v>32</v>
       </c>
       <c r="BS11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU11">
         <v>7.4</v>
@@ -3595,19 +3595,19 @@
         <v>50</v>
       </c>
       <c r="BW11">
+        <v>13</v>
+      </c>
+      <c r="BX11">
+        <v>65</v>
+      </c>
+      <c r="BY11">
         <v>13.5</v>
-      </c>
-      <c r="BX11">
-        <v>60</v>
-      </c>
-      <c r="BY11">
-        <v>14.5</v>
       </c>
       <c r="BZ11">
         <v>29</v>
       </c>
       <c r="CA11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>200</v>
@@ -3633,16 +3633,16 @@
         <v>1.55</v>
       </c>
       <c r="G12">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>180</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>7.2</v>
@@ -3678,10 +3678,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3881,7 +3881,7 @@
         <v>7.2</v>
       </c>
       <c r="I13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J13">
         <v>6.2</v>
@@ -3896,16 +3896,16 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
         <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R13">
         <v>1.89</v>
@@ -4114,22 +4114,22 @@
         <v>172</v>
       </c>
       <c r="F14">
-        <v>5.3</v>
+        <v>1.12</v>
       </c>
       <c r="G14">
         <v>1000</v>
       </c>
       <c r="H14">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="I14">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="J14">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4138,7 +4138,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="O14">
         <v>1.02</v>
@@ -4147,22 +4147,22 @@
         <v>2.2</v>
       </c>
       <c r="Q14">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S14">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U14">
         <v>2.08</v>
       </c>
       <c r="V14">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -4359,7 +4359,7 @@
         <v>3</v>
       </c>
       <c r="G15">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H15">
         <v>2.28</v>
@@ -4368,7 +4368,7 @@
         <v>2.48</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
         <v>3.9</v>
@@ -4389,13 +4389,13 @@
         <v>2.12</v>
       </c>
       <c r="Q15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
         <v>1.44</v>
       </c>
       <c r="S15">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
         <v>1.64</v>
@@ -4404,16 +4404,16 @@
         <v>2.32</v>
       </c>
       <c r="V15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
         <v>1.42</v>
       </c>
       <c r="X15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
         <v>17.5</v>
@@ -4479,7 +4479,7 @@
         <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV15">
         <v>10</v>
@@ -4503,13 +4503,13 @@
         <v>7.8</v>
       </c>
       <c r="BC15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15">
         <v>19</v>
@@ -4598,7 +4598,7 @@
         <v>174</v>
       </c>
       <c r="F16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G16">
         <v>1.61</v>
@@ -4631,7 +4631,7 @@
         <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
         <v>1.56</v>
@@ -4643,7 +4643,7 @@
         <v>1.78</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
         <v>1.18</v>
@@ -4652,7 +4652,7 @@
         <v>2.62</v>
       </c>
       <c r="X16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y16">
         <v>26</v>
@@ -4667,7 +4667,7 @@
         <v>11</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD16">
         <v>24</v>
@@ -4685,10 +4685,10 @@
         <v>20</v>
       </c>
       <c r="AI16">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16">
         <v>15.5</v>
@@ -4712,10 +4712,10 @@
         <v>22</v>
       </c>
       <c r="AR16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT16">
         <v>9.6</v>
@@ -4748,10 +4748,10 @@
         <v>14</v>
       </c>
       <c r="BD16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE16">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BF16">
         <v>6.2</v>
@@ -4763,31 +4763,31 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO16">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="BR16">
         <v>1000</v>
@@ -4805,13 +4805,13 @@
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
@@ -4840,7 +4840,7 @@
         <v>175</v>
       </c>
       <c r="F17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G17">
         <v>1.54</v>
@@ -4849,7 +4849,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>4.8</v>
@@ -4864,31 +4864,31 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O17">
         <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R17">
         <v>1.57</v>
       </c>
       <c r="S17">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T17">
         <v>1.82</v>
       </c>
       <c r="U17">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W17">
         <v>2.84</v>
@@ -4903,7 +4903,7 @@
         <v>65</v>
       </c>
       <c r="AA17">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB17">
         <v>10.5</v>
@@ -4915,13 +4915,13 @@
         <v>26</v>
       </c>
       <c r="AE17">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF17">
         <v>9.800000000000001</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17">
         <v>21</v>
@@ -4951,13 +4951,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR17">
         <v>55</v>
       </c>
       <c r="AS17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -4969,13 +4969,13 @@
         <v>23</v>
       </c>
       <c r="AW17">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="AX17">
         <v>9.4</v>
       </c>
       <c r="AY17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
         <v>19.5</v>
@@ -4987,13 +4987,13 @@
         <v>12.5</v>
       </c>
       <c r="BC17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD17">
         <v>28</v>
       </c>
       <c r="BE17">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="BF17">
         <v>6</v>
@@ -5023,13 +5023,13 @@
         <v>4.9</v>
       </c>
       <c r="BO17">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
@@ -5097,10 +5097,10 @@
         <v>5.4</v>
       </c>
       <c r="K18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
         <v>1.03</v>
@@ -5109,10 +5109,10 @@
         <v>6.8</v>
       </c>
       <c r="O18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q18">
         <v>1.47</v>
@@ -5124,7 +5124,7 @@
         <v>2.16</v>
       </c>
       <c r="T18">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U18">
         <v>2.36</v>
@@ -5136,7 +5136,7 @@
         <v>1.13</v>
       </c>
       <c r="X18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y18">
         <v>13</v>
@@ -5172,7 +5172,7 @@
         <v>26</v>
       </c>
       <c r="AJ18">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AK18">
         <v>95</v>
@@ -5187,7 +5187,7 @@
         <v>75</v>
       </c>
       <c r="AO18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP18">
         <v>27</v>
@@ -5199,7 +5199,7 @@
         <v>10</v>
       </c>
       <c r="AS18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT18">
         <v>34</v>
@@ -5223,28 +5223,28 @@
         <v>19</v>
       </c>
       <c r="BA18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18">
         <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>14.5</v>
+        <v>80</v>
       </c>
       <c r="BD18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE18">
         <v>65</v>
       </c>
       <c r="BF18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BG18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI18">
         <v>4.5</v>
@@ -5262,19 +5262,19 @@
         <v>13</v>
       </c>
       <c r="BN18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BP18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BQ18">
         <v>12</v>
       </c>
       <c r="BR18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS18">
         <v>11.5</v>
@@ -5283,16 +5283,16 @@
         <v>4.4</v>
       </c>
       <c r="BU18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW18">
         <v>7.6</v>
       </c>
       <c r="BX18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BY18">
         <v>8.800000000000001</v>
@@ -5324,16 +5324,16 @@
         <v>177</v>
       </c>
       <c r="F19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G19">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H19">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J19">
         <v>3.8</v>
@@ -5354,34 +5354,34 @@
         <v>1.36</v>
       </c>
       <c r="P19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S19">
         <v>3.8</v>
       </c>
       <c r="T19">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U19">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V19">
         <v>1.22</v>
       </c>
       <c r="W19">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z19">
         <v>40</v>
@@ -5390,10 +5390,10 @@
         <v>170</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD19">
         <v>21</v>
@@ -5405,13 +5405,13 @@
         <v>10</v>
       </c>
       <c r="AG19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ19">
         <v>19</v>
@@ -5432,7 +5432,7 @@
         <v>100</v>
       </c>
       <c r="AP19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
         <v>15</v>
@@ -5441,7 +5441,7 @@
         <v>36</v>
       </c>
       <c r="AS19">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT19">
         <v>7.4</v>
@@ -5453,19 +5453,19 @@
         <v>18.5</v>
       </c>
       <c r="AW19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AX19">
         <v>9.199999999999999</v>
       </c>
       <c r="AY19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19">
         <v>20</v>
       </c>
       <c r="BA19">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB19">
         <v>17</v>
@@ -5477,13 +5477,13 @@
         <v>15.5</v>
       </c>
       <c r="BE19">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BF19">
         <v>11</v>
       </c>
       <c r="BG19">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5566,16 +5566,16 @@
         <v>178</v>
       </c>
       <c r="F20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H20">
         <v>3.25</v>
       </c>
       <c r="I20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
         <v>3.65</v>
@@ -5584,7 +5584,7 @@
         <v>3.7</v>
       </c>
       <c r="L20">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M20">
         <v>1.06</v>
@@ -5596,28 +5596,28 @@
         <v>1.28</v>
       </c>
       <c r="P20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R20">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
         <v>1.7</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X20">
         <v>17</v>
@@ -5677,7 +5677,7 @@
         <v>15</v>
       </c>
       <c r="AQ20">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR20">
         <v>21</v>
@@ -5719,7 +5719,7 @@
         <v>30</v>
       </c>
       <c r="BE20">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF20">
         <v>14.5</v>
@@ -5728,16 +5728,16 @@
         <v>26</v>
       </c>
       <c r="BH20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI20">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
@@ -5817,37 +5817,37 @@
         <v>3.35</v>
       </c>
       <c r="I21">
+        <v>3.45</v>
+      </c>
+      <c r="J21">
         <v>3.4</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>3.45</v>
       </c>
-      <c r="K21">
-        <v>3.5</v>
-      </c>
       <c r="L21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M21">
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O21">
         <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q21">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T21">
         <v>1.89</v>
@@ -5856,7 +5856,7 @@
         <v>2.04</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
         <v>1.69</v>
@@ -5868,7 +5868,7 @@
         <v>12</v>
       </c>
       <c r="Z21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA21">
         <v>65</v>
@@ -5892,7 +5892,7 @@
         <v>12</v>
       </c>
       <c r="AH21">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI21">
         <v>55</v>
@@ -5907,7 +5907,7 @@
         <v>44</v>
       </c>
       <c r="AM21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21">
         <v>24</v>
@@ -5928,7 +5928,7 @@
         <v>50</v>
       </c>
       <c r="AT21">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU21">
         <v>6.8</v>
@@ -5961,7 +5961,7 @@
         <v>38</v>
       </c>
       <c r="BE21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF21">
         <v>20</v>
@@ -5973,7 +5973,7 @@
         <v>3.5</v>
       </c>
       <c r="BI21">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -6050,37 +6050,37 @@
         <v>180</v>
       </c>
       <c r="F22">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G22">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H22">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M22">
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
         <v>1.33</v>
       </c>
       <c r="P22">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q22">
         <v>2.02</v>
@@ -6089,19 +6089,19 @@
         <v>1.36</v>
       </c>
       <c r="S22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T22">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V22">
         <v>1.21</v>
       </c>
       <c r="W22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X22">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>42</v>
       </c>
       <c r="AA22">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AB22">
         <v>8.199999999999999</v>
@@ -6122,7 +6122,7 @@
         <v>8.6</v>
       </c>
       <c r="AD22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE22">
         <v>100</v>
@@ -6131,19 +6131,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH22">
         <v>22</v>
       </c>
       <c r="AI22">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ22">
         <v>19</v>
       </c>
       <c r="AK22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL22">
         <v>38</v>
@@ -6164,34 +6164,34 @@
         <v>16.5</v>
       </c>
       <c r="AR22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS22">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT22">
         <v>7.4</v>
       </c>
       <c r="AU22">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV22">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX22">
         <v>9</v>
       </c>
       <c r="AY22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22">
         <v>20</v>
       </c>
       <c r="BA22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22">
         <v>16.5</v>
@@ -6203,16 +6203,16 @@
         <v>34</v>
       </c>
       <c r="BE22">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BF22">
         <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI22">
         <v>3.15</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="BK22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6269,7 +6269,7 @@
         <v>24</v>
       </c>
       <c r="CA22">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="s">
         <v>200</v>
@@ -6292,16 +6292,16 @@
         <v>181</v>
       </c>
       <c r="F23">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G23">
         <v>1.41</v>
       </c>
       <c r="H23">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J23">
         <v>4.9</v>
@@ -6310,7 +6310,7 @@
         <v>5.4</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M23">
         <v>1.05</v>
@@ -6325,19 +6325,19 @@
         <v>2.04</v>
       </c>
       <c r="Q23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R23">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S23">
         <v>2.88</v>
       </c>
       <c r="T23">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V23">
         <v>1.09</v>
@@ -6361,7 +6361,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD23">
         <v>42</v>
@@ -6370,10 +6370,10 @@
         <v>230</v>
       </c>
       <c r="AF23">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG23">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH23">
         <v>32</v>
@@ -6400,28 +6400,28 @@
         <v>350</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23">
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AT23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU23">
         <v>10</v>
       </c>
       <c r="AV23">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW23">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX23">
         <v>7</v>
@@ -6433,7 +6433,7 @@
         <v>21</v>
       </c>
       <c r="BA23">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB23">
         <v>10</v>
@@ -6445,13 +6445,13 @@
         <v>34</v>
       </c>
       <c r="BE23">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF23">
         <v>6</v>
       </c>
       <c r="BG23">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6540,22 +6540,22 @@
         <v>2.9</v>
       </c>
       <c r="H24">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I24">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L24">
         <v>1.3</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
         <v>4.5</v>
@@ -6579,10 +6579,10 @@
         <v>1.63</v>
       </c>
       <c r="U24">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
         <v>1.53</v>
@@ -6594,10 +6594,10 @@
         <v>14</v>
       </c>
       <c r="Z24">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA24">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB24">
         <v>14.5</v>
@@ -6606,40 +6606,40 @@
         <v>8.4</v>
       </c>
       <c r="AD24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE24">
         <v>28</v>
       </c>
       <c r="AF24">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH24">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI24">
         <v>36</v>
       </c>
       <c r="AJ24">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK24">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM24">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN24">
         <v>24</v>
       </c>
       <c r="AO24">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP24">
         <v>15</v>
@@ -6651,19 +6651,19 @@
         <v>17</v>
       </c>
       <c r="AS24">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="AT24">
         <v>12.5</v>
       </c>
       <c r="AU24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
         <v>11</v>
       </c>
       <c r="AW24">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX24">
         <v>18</v>
@@ -6672,22 +6672,22 @@
         <v>11</v>
       </c>
       <c r="AZ24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA24">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BB24">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD24">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE24">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BF24">
         <v>17</v>
@@ -6776,19 +6776,19 @@
         <v>183</v>
       </c>
       <c r="F25">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G25">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H25">
         <v>5.1</v>
       </c>
       <c r="I25">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
         <v>3.65</v>
@@ -6800,40 +6800,40 @@
         <v>1.1</v>
       </c>
       <c r="N25">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="O25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P25">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q25">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R25">
+        <v>1.2</v>
+      </c>
+      <c r="S25">
+        <v>2.64</v>
+      </c>
+      <c r="T25">
+        <v>2.06</v>
+      </c>
+      <c r="U25">
+        <v>1.75</v>
+      </c>
+      <c r="V25">
         <v>1.21</v>
       </c>
-      <c r="S25">
-        <v>3.9</v>
-      </c>
-      <c r="T25">
-        <v>2</v>
-      </c>
-      <c r="U25">
-        <v>1.72</v>
-      </c>
-      <c r="V25">
-        <v>1.2</v>
-      </c>
       <c r="W25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X25">
         <v>970</v>
       </c>
       <c r="Y25">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z25">
         <v>1000</v>
@@ -6884,58 +6884,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AR25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AT25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU25">
         <v>1.4</v>
       </c>
       <c r="AV25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AW25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AX25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AY25">
         <v>1.48</v>
       </c>
       <c r="AZ25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BA25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BB25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BC25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BD25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BE25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF25">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="BG25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7021,10 +7021,10 @@
         <v>2.48</v>
       </c>
       <c r="G26">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H26">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="I26">
         <v>3.15</v>
@@ -7045,10 +7045,10 @@
         <v>3.6</v>
       </c>
       <c r="O26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P26">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
         <v>1.94</v>
@@ -7060,16 +7060,16 @@
         <v>3.35</v>
       </c>
       <c r="T26">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U26">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V26">
         <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7087,7 +7087,7 @@
         <v>970</v>
       </c>
       <c r="AC26">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD26">
         <v>970</v>
@@ -7126,58 +7126,58 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AQ26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AR26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AS26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT26">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU26">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV26">
         <v>1.27</v>
       </c>
       <c r="AW26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AX26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AY26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AZ26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BA26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BB26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BC26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BD26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BE26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BF26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BG26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7260,7 +7260,7 @@
         <v>185</v>
       </c>
       <c r="F27">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G27">
         <v>2.54</v>
@@ -7275,7 +7275,7 @@
         <v>3.25</v>
       </c>
       <c r="K27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7284,13 +7284,13 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P27">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -7305,13 +7305,13 @@
         <v>1.89</v>
       </c>
       <c r="U27">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V27">
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X27">
         <v>13</v>
@@ -7350,10 +7350,10 @@
         <v>70</v>
       </c>
       <c r="AJ27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7374,10 +7374,10 @@
         <v>9.6</v>
       </c>
       <c r="AR27">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS27">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT27">
         <v>7.6</v>
@@ -7389,7 +7389,7 @@
         <v>12.5</v>
       </c>
       <c r="AW27">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="AX27">
         <v>12.5</v>
@@ -7401,25 +7401,25 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB27">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC27">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD27">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BE27">
+        <v>6.4</v>
+      </c>
+      <c r="BF27">
+        <v>21</v>
+      </c>
+      <c r="BG27">
         <v>6.2</v>
-      </c>
-      <c r="BF27">
-        <v>20</v>
-      </c>
-      <c r="BG27">
-        <v>6</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7502,22 +7502,22 @@
         <v>186</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G28">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="H28">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="I28">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="J28">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7526,40 +7526,40 @@
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="O28">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P28">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q28">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S28">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T28">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U28">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V28">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X28">
         <v>1000</v>
       </c>
       <c r="Y28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z28">
         <v>1000</v>
@@ -7568,13 +7568,13 @@
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AC28">
         <v>970</v>
       </c>
       <c r="AD28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE28">
         <v>1000</v>
@@ -7583,7 +7583,7 @@
         <v>1000</v>
       </c>
       <c r="AG28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
         <v>1000</v>
@@ -7610,58 +7610,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>8</v>
+        <v>1.18</v>
       </c>
       <c r="AR28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AS28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AT28">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AU28">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AV28">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AW28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AX28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AY28">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="AZ28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BA28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BB28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BD28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BE28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BF28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BG28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BH28">
         <v>4.5</v>
@@ -7744,19 +7744,19 @@
         <v>187</v>
       </c>
       <c r="F29">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="G29">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="H29">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="I29">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K29">
         <v>4.3</v>
@@ -7786,22 +7786,22 @@
         <v>2.2</v>
       </c>
       <c r="T29">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U29">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W29">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X29">
         <v>34</v>
       </c>
       <c r="Y29">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z29">
         <v>22</v>
@@ -7810,22 +7810,22 @@
         <v>34</v>
       </c>
       <c r="AB29">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD29">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE29">
         <v>23</v>
       </c>
       <c r="AF29">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AG29">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH29">
         <v>16</v>
@@ -7834,43 +7834,43 @@
         <v>29</v>
       </c>
       <c r="AJ29">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK29">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AM29">
         <v>55</v>
       </c>
       <c r="AN29">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO29">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP29">
         <v>21</v>
       </c>
       <c r="AQ29">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR29">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS29">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT29">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AU29">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV29">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW29">
         <v>17.5</v>
@@ -7879,7 +7879,7 @@
         <v>21</v>
       </c>
       <c r="AY29">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ29">
         <v>12</v>
@@ -7888,22 +7888,22 @@
         <v>19</v>
       </c>
       <c r="BB29">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC29">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE29">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF29">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG29">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7986,10 +7986,10 @@
         <v>188</v>
       </c>
       <c r="F30">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G30">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H30">
         <v>2.64</v>
@@ -8004,7 +8004,7 @@
         <v>3.85</v>
       </c>
       <c r="L30">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M30">
         <v>1.06</v>
@@ -8013,7 +8013,7 @@
         <v>4.1</v>
       </c>
       <c r="O30">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P30">
         <v>2.08</v>
@@ -8022,13 +8022,13 @@
         <v>1.81</v>
       </c>
       <c r="R30">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S30">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T30">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U30">
         <v>2.3</v>
@@ -8037,7 +8037,7 @@
         <v>1.53</v>
       </c>
       <c r="W30">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X30">
         <v>17</v>
@@ -8046,7 +8046,7 @@
         <v>13</v>
       </c>
       <c r="Z30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA30">
         <v>44</v>
@@ -8064,7 +8064,7 @@
         <v>30</v>
       </c>
       <c r="AF30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG30">
         <v>13</v>
@@ -8088,64 +8088,64 @@
         <v>95</v>
       </c>
       <c r="AN30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30">
         <v>23</v>
       </c>
       <c r="AP30">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AQ30">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AR30">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AS30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT30">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AU30">
         <v>7.4</v>
       </c>
       <c r="AV30">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AW30">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AX30">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="AY30">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC30">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BD30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF30">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BG30">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BH30">
         <v>3.8</v>
@@ -8228,22 +8228,22 @@
         <v>189</v>
       </c>
       <c r="F31">
+        <v>1.7</v>
+      </c>
+      <c r="G31">
         <v>1.79</v>
       </c>
-      <c r="G31">
-        <v>1.86</v>
-      </c>
       <c r="H31">
+        <v>4.9</v>
+      </c>
+      <c r="I31">
+        <v>5.6</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31">
         <v>4.5</v>
-      </c>
-      <c r="I31">
-        <v>5</v>
-      </c>
-      <c r="J31">
-        <v>3.85</v>
-      </c>
-      <c r="K31">
-        <v>4.3</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8258,28 +8258,28 @@
         <v>1.23</v>
       </c>
       <c r="P31">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q31">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
         <v>2.74</v>
       </c>
       <c r="T31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U31">
         <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8336,58 +8336,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AR31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AS31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT31">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AU31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AV31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AW31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AX31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AY31">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AZ31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BA31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BB31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BC31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BD31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BE31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF31">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="BG31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8473,7 +8473,7 @@
         <v>3.05</v>
       </c>
       <c r="G32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H32">
         <v>2.1</v>
@@ -8485,7 +8485,7 @@
         <v>4.2</v>
       </c>
       <c r="K32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8494,16 +8494,16 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O32">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P32">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R32">
         <v>1.82</v>
@@ -8512,16 +8512,16 @@
         <v>2</v>
       </c>
       <c r="T32">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U32">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V32">
         <v>1.81</v>
       </c>
       <c r="W32">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8539,7 +8539,7 @@
         <v>1000</v>
       </c>
       <c r="AC32">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD32">
         <v>970</v>
@@ -8578,58 +8578,58 @@
         <v>970</v>
       </c>
       <c r="AP32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AS32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AU32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AV32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AW32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AX32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AY32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AZ32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BA32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BB32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BD32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BE32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BF32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BG32">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8712,22 +8712,22 @@
         <v>191</v>
       </c>
       <c r="F33">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="G33">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="H33">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="I33">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8736,76 +8736,76 @@
         <v>1.09</v>
       </c>
       <c r="N33">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P33">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S33">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T33">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X33">
+        <v>11.5</v>
+      </c>
+      <c r="Y33">
         <v>12.5</v>
       </c>
-      <c r="Y33">
-        <v>11.5</v>
-      </c>
       <c r="Z33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA33">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB33">
         <v>10.5</v>
       </c>
       <c r="AC33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD33">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE33">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF33">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG33">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH33">
         <v>19</v>
       </c>
       <c r="AI33">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ33">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL33">
         <v>50</v>
@@ -8814,37 +8814,37 @@
         <v>130</v>
       </c>
       <c r="AN33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO33">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AP33">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ33">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR33">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS33">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AT33">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU33">
         <v>6.4</v>
       </c>
       <c r="AV33">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AX33">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY33">
         <v>10.5</v>
@@ -8853,25 +8853,25 @@
         <v>15.5</v>
       </c>
       <c r="BA33">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC33">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BD33">
         <v>40</v>
       </c>
       <c r="BE33">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF33">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BG33">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH33">
         <v>3.75</v>
@@ -8996,10 +8996,10 @@
         <v>1.01</v>
       </c>
       <c r="T34">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U34">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V34">
         <v>1.01</v>
@@ -9008,7 +9008,7 @@
         <v>1.01</v>
       </c>
       <c r="X34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y34">
         <v>970</v>
@@ -9020,13 +9020,13 @@
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC34">
         <v>970</v>
       </c>
       <c r="AD34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE34">
         <v>1000</v>
@@ -9196,7 +9196,7 @@
         <v>193</v>
       </c>
       <c r="F35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G35">
         <v>110</v>
@@ -9480,10 +9480,10 @@
         <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U36">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V36">
         <v>1.01</v>
@@ -9492,7 +9492,7 @@
         <v>1.01</v>
       </c>
       <c r="X36">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y36">
         <v>1000</v>
@@ -9519,7 +9519,7 @@
         <v>970</v>
       </c>
       <c r="AG36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH36">
         <v>1000</v>
@@ -9558,7 +9558,7 @@
         <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU36">
         <v>1.03</v>
@@ -9680,7 +9680,7 @@
         <v>195</v>
       </c>
       <c r="F37">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G37">
         <v>1.63</v>
@@ -9692,31 +9692,31 @@
         <v>7.2</v>
       </c>
       <c r="J37">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K37">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L37">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M37">
         <v>1.06</v>
       </c>
       <c r="N37">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O37">
         <v>1.29</v>
       </c>
       <c r="P37">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q37">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S37">
         <v>3.1</v>
@@ -9734,7 +9734,7 @@
         <v>2.56</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y37">
         <v>22</v>
@@ -9770,7 +9770,7 @@
         <v>95</v>
       </c>
       <c r="AJ37">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK37">
         <v>17.5</v>
@@ -9782,7 +9782,7 @@
         <v>140</v>
       </c>
       <c r="AN37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO37">
         <v>130</v>
@@ -9794,13 +9794,13 @@
         <v>19</v>
       </c>
       <c r="AR37">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS37">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AT37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU37">
         <v>8.6</v>
@@ -9809,7 +9809,7 @@
         <v>20</v>
       </c>
       <c r="AW37">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AX37">
         <v>8.6</v>
@@ -9818,10 +9818,10 @@
         <v>9</v>
       </c>
       <c r="AZ37">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="BA37">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BB37">
         <v>13</v>
@@ -9830,16 +9830,16 @@
         <v>15</v>
       </c>
       <c r="BD37">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BE37">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF37">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG37">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9851,7 +9851,7 @@
         <v>1000</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BL37">
         <v>1000</v>
@@ -9863,13 +9863,13 @@
         <v>1000</v>
       </c>
       <c r="BO37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BP37">
         <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="BR37">
         <v>1000</v>
@@ -9881,7 +9881,7 @@
         <v>1000</v>
       </c>
       <c r="BU37">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="BV37">
         <v>1000</v>
@@ -10167,163 +10167,163 @@
         <v>2.94</v>
       </c>
       <c r="G39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H39">
         <v>2.26</v>
       </c>
       <c r="I39">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J39">
         <v>3.75</v>
       </c>
       <c r="K39">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L39">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N39">
         <v>4.4</v>
       </c>
       <c r="O39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P39">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
         <v>1.71</v>
       </c>
       <c r="R39">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S39">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T39">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X39">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y39">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AD39">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK39">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL39">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM39">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO39">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA39">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10406,7 +10406,7 @@
         <v>198</v>
       </c>
       <c r="F40">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G40">
         <v>2.88</v>
@@ -10415,13 +10415,13 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J40">
         <v>3.05</v>
       </c>
       <c r="K40">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10457,7 +10457,7 @@
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X40">
         <v>9.199999999999999</v>
@@ -10466,7 +10466,7 @@
         <v>9.4</v>
       </c>
       <c r="Z40">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA40">
         <v>70</v>
@@ -10478,7 +10478,7 @@
         <v>7.4</v>
       </c>
       <c r="AD40">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE40">
         <v>55</v>
@@ -10523,7 +10523,7 @@
         <v>17</v>
       </c>
       <c r="AS40">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT40">
         <v>7.6</v>
@@ -10535,7 +10535,7 @@
         <v>12.5</v>
       </c>
       <c r="AW40">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX40">
         <v>14.5</v>
@@ -10544,28 +10544,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ40">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA40">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB40">
+        <v>6.8</v>
+      </c>
+      <c r="BC40">
+        <v>6.6</v>
+      </c>
+      <c r="BD40">
+        <v>7</v>
+      </c>
+      <c r="BE40">
         <v>7.2</v>
       </c>
-      <c r="BC40">
+      <c r="BF40">
         <v>6.8</v>
       </c>
-      <c r="BD40">
-        <v>7.4</v>
-      </c>
-      <c r="BE40">
-        <v>7.6</v>
-      </c>
-      <c r="BF40">
-        <v>7.2</v>
-      </c>
       <c r="BG40">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10648,25 +10648,25 @@
         <v>199</v>
       </c>
       <c r="F41">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G41">
         <v>1.69</v>
       </c>
       <c r="H41">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J41">
         <v>3.75</v>
       </c>
       <c r="K41">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L41">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M41">
         <v>1.09</v>
@@ -10693,7 +10693,7 @@
         <v>2.16</v>
       </c>
       <c r="U41">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V41">
         <v>1.16</v>
@@ -10705,7 +10705,7 @@
         <v>12.5</v>
       </c>
       <c r="Y41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z41">
         <v>65</v>
@@ -10726,10 +10726,10 @@
         <v>140</v>
       </c>
       <c r="AF41">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH41">
         <v>29</v>
@@ -10750,7 +10750,7 @@
         <v>230</v>
       </c>
       <c r="AN41">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AO41">
         <v>230</v>
@@ -10762,13 +10762,13 @@
         <v>16</v>
       </c>
       <c r="AR41">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS41">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT41">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -10777,19 +10777,19 @@
         <v>23</v>
       </c>
       <c r="AW41">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX41">
         <v>8</v>
       </c>
       <c r="AY41">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ41">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BA41">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB41">
         <v>14</v>
@@ -10798,76 +10798,76 @@
         <v>17.5</v>
       </c>
       <c r="BD41">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BE41">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF41">
         <v>11</v>
       </c>
       <c r="BG41">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH41">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI41">
-        <v>2.86</v>
+        <v>1.29</v>
       </c>
       <c r="BJ41">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK41">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO41">
-        <v>3.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP41">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="BR41">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS41">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU41">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="BV41">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW41">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX41">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BY41">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA41">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="s">
         <v>200</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -625,7 +625,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-24 17:37:21</t>
+    <t>2026-09-24 19:53:31</t>
   </si>
 </sst>
 </file>
@@ -1219,226 +1219,226 @@
         <v>162</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>120</v>
       </c>
       <c r="AJ2">
+        <v>17</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
+        <v>180</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2">
+        <v>160</v>
+      </c>
+      <c r="AP2">
+        <v>13</v>
+      </c>
+      <c r="AQ2">
         <v>14.5</v>
       </c>
-      <c r="AK2">
-        <v>18.5</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>200</v>
-      </c>
-      <c r="AN2">
-        <v>11</v>
-      </c>
-      <c r="AO2">
-        <v>230</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>16</v>
-      </c>
       <c r="AR2">
+        <v>34</v>
+      </c>
+      <c r="AS2">
+        <v>13</v>
+      </c>
+      <c r="AT2">
+        <v>6.8</v>
+      </c>
+      <c r="AU2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>20</v>
+      </c>
+      <c r="AW2">
+        <v>70</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>23</v>
+      </c>
+      <c r="BA2">
+        <v>13.5</v>
+      </c>
+      <c r="BB2">
+        <v>15</v>
+      </c>
+      <c r="BC2">
+        <v>17</v>
+      </c>
+      <c r="BD2">
         <v>38</v>
       </c>
-      <c r="AS2">
-        <v>11.5</v>
-      </c>
-      <c r="AT2">
-        <v>6.4</v>
-      </c>
-      <c r="AU2">
-        <v>9</v>
-      </c>
-      <c r="AV2">
-        <v>21</v>
-      </c>
-      <c r="AW2">
-        <v>60</v>
-      </c>
-      <c r="AX2">
-        <v>7.6</v>
-      </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>25</v>
-      </c>
-      <c r="BA2">
-        <v>55</v>
-      </c>
-      <c r="BB2">
-        <v>13</v>
-      </c>
-      <c r="BC2">
-        <v>16</v>
-      </c>
-      <c r="BD2">
-        <v>27</v>
-      </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>120</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>90</v>
+        <v>13.5</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2">
         <v>14</v>
       </c>
       <c r="BK2">
+        <v>5.3</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>140</v>
+      </c>
+      <c r="BN2">
+        <v>4.1</v>
+      </c>
+      <c r="BO2">
+        <v>3.7</v>
+      </c>
+      <c r="BP2">
+        <v>13.5</v>
+      </c>
+      <c r="BQ2">
+        <v>5.3</v>
+      </c>
+      <c r="BR2">
+        <v>36</v>
+      </c>
+      <c r="BS2">
+        <v>6.4</v>
+      </c>
+      <c r="BT2">
+        <v>12</v>
+      </c>
+      <c r="BU2">
         <v>8.6</v>
       </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>4.6</v>
-      </c>
-      <c r="BO2">
-        <v>3.1</v>
-      </c>
-      <c r="BP2">
-        <v>13</v>
-      </c>
-      <c r="BQ2">
-        <v>8</v>
-      </c>
-      <c r="BR2">
-        <v>38</v>
-      </c>
-      <c r="BS2">
-        <v>21</v>
-      </c>
-      <c r="BT2">
-        <v>12.5</v>
-      </c>
-      <c r="BU2">
-        <v>7.6</v>
-      </c>
       <c r="BV2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BW2">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BY2">
-        <v>55</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="s">
         <v>203</v>
@@ -1461,22 +1461,22 @@
         <v>163</v>
       </c>
       <c r="F3">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="I3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="J3">
         <v>4.5</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1485,202 +1485,202 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
         <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="W3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X3">
+        <v>16.5</v>
+      </c>
+      <c r="Y3">
+        <v>8.4</v>
+      </c>
+      <c r="Z3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA3">
+        <v>16</v>
+      </c>
+      <c r="AB3">
         <v>21</v>
       </c>
-      <c r="Y3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>9.4</v>
-      </c>
-      <c r="AA3">
-        <v>18</v>
-      </c>
-      <c r="AB3">
-        <v>23</v>
-      </c>
       <c r="AC3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>11</v>
       </c>
       <c r="AE3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AK3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU3">
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX3">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="AY3">
         <v>20</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>65</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>100</v>
       </c>
       <c r="BF3">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BG3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BN3">
         <v>12.5</v>
       </c>
       <c r="BO3">
+        <v>4.1</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>4.5</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>4.5</v>
+      </c>
+      <c r="BT3">
+        <v>4.7</v>
+      </c>
+      <c r="BU3">
+        <v>3.5</v>
+      </c>
+      <c r="BV3">
+        <v>12.5</v>
+      </c>
+      <c r="BW3">
         <v>7.8</v>
       </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>48</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>50</v>
-      </c>
-      <c r="BT3">
-        <v>4.6</v>
-      </c>
-      <c r="BU3">
-        <v>3.15</v>
-      </c>
-      <c r="BV3">
-        <v>12</v>
-      </c>
-      <c r="BW3">
-        <v>7.6</v>
-      </c>
       <c r="BX3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>3.95</v>
       </c>
       <c r="CB3" t="s">
         <v>203</v>
@@ -1703,10 +1703,10 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="G4">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H4">
         <v>6.4</v>
@@ -1715,10 +1715,10 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>1.4</v>
@@ -1727,37 +1727,37 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
         <v>3.45</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="X4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y4">
         <v>21</v>
@@ -1766,100 +1766,100 @@
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB4">
         <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
         <v>26</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF4">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
         <v>17.5</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN4">
         <v>9.4</v>
       </c>
       <c r="AO4">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AS4">
-        <v>12.5</v>
+        <v>120</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV4">
+        <v>22</v>
+      </c>
+      <c r="AW4">
+        <v>60</v>
+      </c>
+      <c r="AX4">
+        <v>7.6</v>
+      </c>
+      <c r="AY4">
         <v>8.6</v>
       </c>
-      <c r="AV4">
-        <v>21</v>
-      </c>
-      <c r="AW4">
-        <v>55</v>
-      </c>
-      <c r="AX4">
-        <v>8</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC4">
         <v>15</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG4">
         <v>70</v>
@@ -1868,61 +1868,61 @@
         <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BN4">
         <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>27</v>
       </c>
       <c r="BS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT4">
+        <v>11</v>
+      </c>
+      <c r="BU4">
+        <v>8</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>11</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>11</v>
+      </c>
+      <c r="BZ4">
         <v>19</v>
       </c>
-      <c r="BT4">
-        <v>10.5</v>
-      </c>
-      <c r="BU4">
+      <c r="CA4">
         <v>7.6</v>
-      </c>
-      <c r="BV4">
-        <v>65</v>
-      </c>
-      <c r="BW4">
-        <v>44</v>
-      </c>
-      <c r="BX4">
-        <v>70</v>
-      </c>
-      <c r="BY4">
-        <v>46</v>
-      </c>
-      <c r="BZ4">
-        <v>20</v>
-      </c>
-      <c r="CA4">
-        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>203</v>
@@ -1975,22 +1975,22 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
         <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.24</v>
@@ -1999,64 +1999,64 @@
         <v>2.22</v>
       </c>
       <c r="X5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA5">
         <v>120</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>12</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
         <v>19.5</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5">
         <v>17</v>
       </c>
       <c r="AQ5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5">
         <v>34</v>
@@ -2077,64 +2077,64 @@
         <v>48</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BF5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
         <v>46</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>25</v>
@@ -2146,7 +2146,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BV5">
         <v>40</v>
@@ -2161,7 +2161,7 @@
         <v>7.4</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
         <v>6</v>
@@ -2187,88 +2187,88 @@
         <v>166</v>
       </c>
       <c r="F6">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="H6">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P6">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T6">
         <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA6">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB6">
         <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH6">
         <v>24</v>
@@ -2277,64 +2277,64 @@
         <v>110</v>
       </c>
       <c r="AJ6">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL6">
         <v>44</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV6">
         <v>19</v>
       </c>
       <c r="AW6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
         <v>20</v>
       </c>
       <c r="BA6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD6">
         <v>36</v>
@@ -2343,70 +2343,70 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI6">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BT6">
         <v>9.199999999999999</v>
       </c>
       <c r="BU6">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="s">
         <v>203</v>
@@ -2435,13 +2435,13 @@
         <v>3.25</v>
       </c>
       <c r="H7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I7">
         <v>2.52</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
         <v>3.95</v>
@@ -2474,7 +2474,7 @@
         <v>1.67</v>
       </c>
       <c r="U7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
         <v>1.66</v>
@@ -2489,52 +2489,52 @@
         <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF7">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG7">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM7">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AN7">
         <v>30</v>
       </c>
       <c r="AO7">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP7">
         <v>14.5</v>
@@ -2546,7 +2546,7 @@
         <v>14</v>
       </c>
       <c r="AS7">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT7">
         <v>12</v>
@@ -2570,19 +2570,19 @@
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BB7">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC7">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
         <v>21</v>
@@ -2779,52 +2779,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2955,7 +2955,7 @@
         <v>1.03</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U9">
         <v>1.01</v>
@@ -3021,55 +3021,55 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -3155,22 +3155,22 @@
         <v>170</v>
       </c>
       <c r="F10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G10">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3182,7 +3182,7 @@
         <v>4.3</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
         <v>2.16</v>
@@ -3194,10 +3194,10 @@
         <v>1.43</v>
       </c>
       <c r="S10">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="T10">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U10">
         <v>2.32</v>
@@ -3206,7 +3206,7 @@
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
         <v>24</v>
@@ -3254,7 +3254,7 @@
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN10">
         <v>17.5</v>
@@ -3263,46 +3263,46 @@
         <v>32</v>
       </c>
       <c r="AP10">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="AQ10">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AR10">
-        <v>17.5</v>
+        <v>3.7</v>
       </c>
       <c r="AS10">
         <v>3.95</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="AV10">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="AW10">
         <v>3.85</v>
       </c>
       <c r="AX10">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="AY10">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="AZ10">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="BA10">
         <v>3.9</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="BC10">
-        <v>16.5</v>
+        <v>3.65</v>
       </c>
       <c r="BD10">
         <v>3.8</v>
@@ -3311,10 +3311,10 @@
         <v>4</v>
       </c>
       <c r="BF10">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="BG10">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3397,85 +3397,85 @@
         <v>171</v>
       </c>
       <c r="F11">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="G11">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="H11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I11">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J11">
+        <v>3.75</v>
+      </c>
+      <c r="K11">
         <v>3.85</v>
       </c>
-      <c r="K11">
-        <v>3.9</v>
-      </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P11">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
         <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W11">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA11">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB11">
         <v>8.199999999999999</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
         <v>20</v>
       </c>
       <c r="AE11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -3484,79 +3484,79 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11">
         <v>42</v>
       </c>
       <c r="AM11">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN11">
+        <v>14.5</v>
+      </c>
+      <c r="AO11">
+        <v>90</v>
+      </c>
+      <c r="AP11">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11">
         <v>13.5</v>
       </c>
-      <c r="AO11">
-        <v>95</v>
-      </c>
-      <c r="AP11">
-        <v>12</v>
-      </c>
-      <c r="AQ11">
-        <v>15</v>
-      </c>
       <c r="AR11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
         <v>7.4</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW11">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AX11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11">
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BB11">
         <v>17</v>
       </c>
       <c r="BC11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BE11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BF11">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH11">
         <v>3.55</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BN11">
         <v>1000</v>
@@ -3586,37 +3586,37 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="CB11" t="s">
         <v>203</v>
@@ -3639,22 +3639,22 @@
         <v>172</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3669,52 +3669,52 @@
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U12">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="X12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y12">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF12">
         <v>10.5</v>
@@ -3723,82 +3723,82 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
+        <v>21</v>
+      </c>
+      <c r="AI12">
+        <v>80</v>
+      </c>
+      <c r="AJ12">
+        <v>22</v>
+      </c>
+      <c r="AK12">
         <v>23</v>
       </c>
-      <c r="AI12">
-        <v>90</v>
-      </c>
-      <c r="AJ12">
-        <v>20</v>
-      </c>
-      <c r="AK12">
-        <v>22</v>
-      </c>
       <c r="AL12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM12">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12">
         <v>13.5</v>
       </c>
       <c r="AR12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS12">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="AT12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AW12">
+        <v>55</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12">
+        <v>20</v>
+      </c>
+      <c r="BA12">
         <v>65</v>
       </c>
-      <c r="AX12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY12">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12">
-        <v>21</v>
-      </c>
-      <c r="BA12">
+      <c r="BB12">
+        <v>19.5</v>
+      </c>
+      <c r="BC12">
+        <v>20</v>
+      </c>
+      <c r="BD12">
+        <v>40</v>
+      </c>
+      <c r="BE12">
+        <v>29</v>
+      </c>
+      <c r="BF12">
+        <v>15</v>
+      </c>
+      <c r="BG12">
         <v>70</v>
-      </c>
-      <c r="BB12">
-        <v>17.5</v>
-      </c>
-      <c r="BC12">
-        <v>18.5</v>
-      </c>
-      <c r="BD12">
-        <v>38</v>
-      </c>
-      <c r="BE12">
-        <v>14.5</v>
-      </c>
-      <c r="BF12">
-        <v>13</v>
-      </c>
-      <c r="BG12">
-        <v>85</v>
       </c>
       <c r="BH12">
         <v>3.1</v>
@@ -3810,55 +3810,55 @@
         <v>11</v>
       </c>
       <c r="BK12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL12">
         <v>170</v>
       </c>
       <c r="BM12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO12">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY12">
         <v>13</v>
       </c>
       <c r="BZ12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
         <v>203</v>
@@ -3884,7 +3884,7 @@
         <v>1.56</v>
       </c>
       <c r="G13">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H13">
         <v>4.8</v>
@@ -3896,13 +3896,13 @@
         <v>4.2</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
         <v>2.78</v>
@@ -3929,16 +3929,16 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X13">
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3947,10 +3947,10 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD13">
         <v>1000</v>
@@ -3959,88 +3959,88 @@
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI13">
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BF13">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4123,7 +4123,7 @@
         <v>174</v>
       </c>
       <c r="F14">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G14">
         <v>1.37</v>
@@ -4147,13 +4147,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
         <v>1.23</v>
@@ -4168,7 +4168,7 @@
         <v>1.01</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V14">
         <v>1.05</v>
@@ -4225,64 +4225,64 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>3.4</v>
+        <v>29</v>
       </c>
       <c r="AO14">
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG14">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4365,7 +4365,7 @@
         <v>175</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="G15">
         <v>110</v>
@@ -4374,13 +4374,13 @@
         <v>1.5</v>
       </c>
       <c r="I15">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>3.05</v>
       </c>
       <c r="K15">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4389,34 +4389,34 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
         <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="T15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4473,58 +4473,58 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4613,10 +4613,10 @@
         <v>3.35</v>
       </c>
       <c r="H16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J16">
         <v>3.6</v>
@@ -4631,7 +4631,7 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.26</v>
@@ -4643,19 +4643,19 @@
         <v>1.75</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16">
         <v>2.88</v>
       </c>
       <c r="T16">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U16">
         <v>2.32</v>
       </c>
       <c r="V16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W16">
         <v>1.42</v>
@@ -4682,7 +4682,7 @@
         <v>12</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF16">
         <v>24</v>
@@ -4697,13 +4697,13 @@
         <v>34</v>
       </c>
       <c r="AJ16">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK16">
         <v>36</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM16">
         <v>90</v>
@@ -4724,7 +4724,7 @@
         <v>14</v>
       </c>
       <c r="AS16">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AT16">
         <v>12.5</v>
@@ -4748,19 +4748,19 @@
         <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BB16">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC16">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BE16">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16">
         <v>19</v>
@@ -4849,7 +4849,7 @@
         <v>177</v>
       </c>
       <c r="F17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G17">
         <v>1.6</v>
@@ -4858,10 +4858,10 @@
         <v>6.2</v>
       </c>
       <c r="I17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17">
         <v>4.7</v>
@@ -4873,13 +4873,13 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O17">
         <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q17">
         <v>1.66</v>
@@ -4891,7 +4891,7 @@
         <v>2.66</v>
       </c>
       <c r="T17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U17">
         <v>2.22</v>
@@ -4903,16 +4903,16 @@
         <v>2.66</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17">
         <v>26</v>
       </c>
       <c r="Z17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA17">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB17">
         <v>11</v>
@@ -4924,19 +4924,19 @@
         <v>24</v>
       </c>
       <c r="AE17">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF17">
         <v>11</v>
       </c>
       <c r="AG17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI17">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ17">
         <v>15</v>
@@ -4945,70 +4945,70 @@
         <v>15.5</v>
       </c>
       <c r="AL17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM17">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO17">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP17">
         <v>19.5</v>
       </c>
       <c r="AQ17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR17">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AS17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AT17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17">
         <v>9.6</v>
       </c>
       <c r="AV17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW17">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AX17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA17">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BB17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC17">
         <v>14</v>
       </c>
       <c r="BD17">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BE17">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BF17">
         <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5044,7 +5044,7 @@
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="BT17">
         <v>1000</v>
@@ -5091,10 +5091,10 @@
         <v>178</v>
       </c>
       <c r="F18">
+        <v>1.51</v>
+      </c>
+      <c r="G18">
         <v>1.52</v>
-      </c>
-      <c r="G18">
-        <v>1.53</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -5103,10 +5103,10 @@
         <v>7.2</v>
       </c>
       <c r="J18">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
         <v>1.27</v>
@@ -5115,13 +5115,13 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q18">
         <v>1.65</v>
@@ -5130,34 +5130,34 @@
         <v>1.57</v>
       </c>
       <c r="S18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T18">
         <v>1.83</v>
       </c>
       <c r="U18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18">
         <v>1.16</v>
       </c>
       <c r="W18">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z18">
         <v>65</v>
       </c>
       <c r="AA18">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>11</v>
@@ -5166,19 +5166,19 @@
         <v>26</v>
       </c>
       <c r="AE18">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH18">
         <v>22</v>
       </c>
       <c r="AI18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ18">
         <v>13.5</v>
@@ -5193,25 +5193,25 @@
         <v>100</v>
       </c>
       <c r="AN18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR18">
         <v>55</v>
       </c>
       <c r="AS18">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AT18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU18">
         <v>10</v>
@@ -5220,16 +5220,16 @@
         <v>23</v>
       </c>
       <c r="AW18">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AX18">
         <v>9.4</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
         <v>65</v>
@@ -5241,7 +5241,7 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE18">
         <v>85</v>
@@ -5333,64 +5333,64 @@
         <v>179</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I19">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M19">
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P19">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q19">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="T19">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z19">
         <v>11.5</v>
@@ -5399,88 +5399,88 @@
         <v>14</v>
       </c>
       <c r="AB19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF19">
         <v>85</v>
       </c>
       <c r="AG19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI19">
         <v>26</v>
       </c>
       <c r="AJ19">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AK19">
         <v>95</v>
       </c>
       <c r="AL19">
+        <v>70</v>
+      </c>
+      <c r="AM19">
         <v>75</v>
       </c>
-      <c r="AM19">
+      <c r="AN19">
         <v>80</v>
       </c>
-      <c r="AN19">
-        <v>75</v>
-      </c>
       <c r="AO19">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AP19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ19">
+        <v>13</v>
+      </c>
+      <c r="AR19">
+        <v>10.5</v>
+      </c>
+      <c r="AS19">
+        <v>13</v>
+      </c>
+      <c r="AT19">
+        <v>38</v>
+      </c>
+      <c r="AU19">
         <v>12</v>
       </c>
-      <c r="AR19">
+      <c r="AV19">
         <v>10</v>
-      </c>
-      <c r="AS19">
-        <v>12.5</v>
-      </c>
-      <c r="AT19">
-        <v>34</v>
-      </c>
-      <c r="AU19">
-        <v>11.5</v>
-      </c>
-      <c r="AV19">
-        <v>9.6</v>
       </c>
       <c r="AW19">
         <v>12</v>
       </c>
       <c r="AX19">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AY19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ19">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB19">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC19">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="BD19">
         <v>60</v>
@@ -5489,64 +5489,64 @@
         <v>65</v>
       </c>
       <c r="BF19">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BG19">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ19">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL19">
         <v>90</v>
       </c>
       <c r="BM19">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BN19">
         <v>11.5</v>
       </c>
       <c r="BO19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BP19">
         <v>55</v>
       </c>
       <c r="BQ19">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BR19">
         <v>48</v>
       </c>
       <c r="BS19">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BT19">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV19">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BW19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY19">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5575,22 +5575,22 @@
         <v>180</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H20">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I20">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
         <v>3.9</v>
-      </c>
-      <c r="K20">
-        <v>3.95</v>
       </c>
       <c r="L20">
         <v>1.39</v>
@@ -5608,25 +5608,25 @@
         <v>1.87</v>
       </c>
       <c r="Q20">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W20">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X20">
         <v>13</v>
@@ -5638,13 +5638,13 @@
         <v>40</v>
       </c>
       <c r="AA20">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
         <v>21</v>
@@ -5653,25 +5653,25 @@
         <v>80</v>
       </c>
       <c r="AF20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ20">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK20">
         <v>21</v>
       </c>
       <c r="AL20">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM20">
         <v>140</v>
@@ -5680,7 +5680,7 @@
         <v>12.5</v>
       </c>
       <c r="AO20">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AP20">
         <v>12</v>
@@ -5689,10 +5689,10 @@
         <v>15</v>
       </c>
       <c r="AR20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS20">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AT20">
         <v>7.4</v>
@@ -5704,19 +5704,19 @@
         <v>18.5</v>
       </c>
       <c r="AW20">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="AX20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
         <v>20</v>
       </c>
       <c r="BA20">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BB20">
         <v>17</v>
@@ -5725,16 +5725,16 @@
         <v>18</v>
       </c>
       <c r="BD20">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BE20">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BF20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG20">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5817,16 +5817,16 @@
         <v>181</v>
       </c>
       <c r="F21">
+        <v>2.3</v>
+      </c>
+      <c r="G21">
         <v>2.34</v>
       </c>
-      <c r="G21">
-        <v>2.36</v>
-      </c>
       <c r="H21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
         <v>3.65</v>
@@ -5835,7 +5835,7 @@
         <v>3.7</v>
       </c>
       <c r="L21">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M21">
         <v>1.06</v>
@@ -5844,49 +5844,49 @@
         <v>4.3</v>
       </c>
       <c r="O21">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P21">
         <v>2.12</v>
       </c>
       <c r="Q21">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
         <v>1.43</v>
       </c>
       <c r="S21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T21">
         <v>1.7</v>
       </c>
       <c r="U21">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X21">
         <v>17</v>
       </c>
       <c r="Y21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z21">
         <v>24</v>
       </c>
       <c r="AA21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB21">
         <v>12</v>
       </c>
       <c r="AC21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21">
         <v>14</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
         <v>11.5</v>
@@ -5922,13 +5922,13 @@
         <v>16.5</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP21">
         <v>15</v>
       </c>
       <c r="AQ21">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR21">
         <v>21</v>
@@ -5940,19 +5940,19 @@
         <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21">
         <v>15</v>
@@ -5973,7 +5973,7 @@
         <v>65</v>
       </c>
       <c r="BF21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG21">
         <v>26</v>
@@ -6059,10 +6059,10 @@
         <v>182</v>
       </c>
       <c r="F22">
+        <v>2.4</v>
+      </c>
+      <c r="G22">
         <v>2.42</v>
-      </c>
-      <c r="G22">
-        <v>2.46</v>
       </c>
       <c r="H22">
         <v>3.35</v>
@@ -6083,16 +6083,16 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O22">
         <v>1.38</v>
       </c>
       <c r="P22">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q22">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R22">
         <v>1.3</v>
@@ -6104,16 +6104,16 @@
         <v>1.86</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y22">
         <v>12</v>
@@ -6128,7 +6128,7 @@
         <v>9.4</v>
       </c>
       <c r="AC22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD22">
         <v>14.5</v>
@@ -6137,7 +6137,7 @@
         <v>55</v>
       </c>
       <c r="AF22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG22">
         <v>12</v>
@@ -6161,10 +6161,10 @@
         <v>110</v>
       </c>
       <c r="AN22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP22">
         <v>11</v>
@@ -6212,7 +6212,7 @@
         <v>38</v>
       </c>
       <c r="BE22">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BF22">
         <v>20</v>
@@ -6304,22 +6304,22 @@
         <v>1.75</v>
       </c>
       <c r="G23">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H23">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J23">
         <v>3.95</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M23">
         <v>1.07</v>
@@ -6328,31 +6328,31 @@
         <v>3.8</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P23">
+        <v>1.98</v>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23">
+        <v>1.37</v>
+      </c>
+      <c r="S23">
+        <v>3.5</v>
+      </c>
+      <c r="T23">
         <v>1.94</v>
       </c>
-      <c r="Q23">
+      <c r="U23">
         <v>2.02</v>
-      </c>
-      <c r="R23">
-        <v>1.36</v>
-      </c>
-      <c r="S23">
-        <v>3.55</v>
-      </c>
-      <c r="T23">
-        <v>1.95</v>
-      </c>
-      <c r="U23">
-        <v>1.99</v>
       </c>
       <c r="V23">
         <v>1.21</v>
       </c>
       <c r="W23">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X23">
         <v>15</v>
@@ -6361,13 +6361,13 @@
         <v>18</v>
       </c>
       <c r="Z23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA23">
         <v>150</v>
       </c>
       <c r="AB23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC23">
         <v>8.800000000000001</v>
@@ -6379,7 +6379,7 @@
         <v>100</v>
       </c>
       <c r="AF23">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG23">
         <v>9.800000000000001</v>
@@ -6388,25 +6388,25 @@
         <v>22</v>
       </c>
       <c r="AI23">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ23">
+        <v>18</v>
+      </c>
+      <c r="AK23">
         <v>18.5</v>
-      </c>
-      <c r="AK23">
-        <v>19</v>
       </c>
       <c r="AL23">
         <v>38</v>
       </c>
       <c r="AM23">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN23">
         <v>11.5</v>
       </c>
       <c r="AO23">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP23">
         <v>13</v>
@@ -6415,22 +6415,22 @@
         <v>16.5</v>
       </c>
       <c r="AR23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU23">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV23">
         <v>19</v>
       </c>
       <c r="AW23">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX23">
         <v>9</v>
@@ -6445,7 +6445,7 @@
         <v>17.5</v>
       </c>
       <c r="BB23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC23">
         <v>17</v>
@@ -6454,16 +6454,16 @@
         <v>34</v>
       </c>
       <c r="BE23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BF23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG23">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BH23">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI23">
         <v>3.1</v>
@@ -6478,7 +6478,7 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN23">
         <v>4.2</v>
@@ -6493,10 +6493,10 @@
         <v>10</v>
       </c>
       <c r="BR23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT23">
         <v>9</v>
@@ -6508,19 +6508,19 @@
         <v>55</v>
       </c>
       <c r="BW23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX23">
         <v>60</v>
       </c>
       <c r="BY23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA23">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="s">
         <v>203</v>
@@ -6543,16 +6543,16 @@
         <v>184</v>
       </c>
       <c r="F24">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J24">
         <v>4.9</v>
@@ -6579,7 +6579,7 @@
         <v>1.82</v>
       </c>
       <c r="R24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
         <v>2.88</v>
@@ -6588,10 +6588,10 @@
         <v>2.18</v>
       </c>
       <c r="U24">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V24">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W24">
         <v>3.4</v>
@@ -6603,7 +6603,7 @@
         <v>36</v>
       </c>
       <c r="Z24">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AA24">
         <v>510</v>
@@ -6612,7 +6612,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC24">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
         <v>42</v>
@@ -6630,7 +6630,7 @@
         <v>32</v>
       </c>
       <c r="AI24">
-        <v>190</v>
+        <v>470</v>
       </c>
       <c r="AJ24">
         <v>13.5</v>
@@ -6654,13 +6654,13 @@
         <v>15</v>
       </c>
       <c r="AQ24">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR24">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS24">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT24">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AW24">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX24">
         <v>7</v>
@@ -6684,7 +6684,7 @@
         <v>21</v>
       </c>
       <c r="BA24">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB24">
         <v>10</v>
@@ -6696,13 +6696,13 @@
         <v>34</v>
       </c>
       <c r="BE24">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24">
         <v>6</v>
       </c>
       <c r="BG24">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6785,25 +6785,25 @@
         <v>185</v>
       </c>
       <c r="F25">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G25">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H25">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I25">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J25">
         <v>3.5</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -6821,19 +6821,19 @@
         <v>1.75</v>
       </c>
       <c r="R25">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T25">
         <v>1.63</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W25">
         <v>1.53</v>
@@ -6866,7 +6866,7 @@
         <v>21</v>
       </c>
       <c r="AG25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH25">
         <v>16</v>
@@ -6884,13 +6884,13 @@
         <v>40</v>
       </c>
       <c r="AM25">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP25">
         <v>15</v>
@@ -6929,7 +6929,7 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="BC25">
         <v>24</v>
@@ -7030,13 +7030,13 @@
         <v>1.86</v>
       </c>
       <c r="G26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H26">
         <v>5.1</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J26">
         <v>3.45</v>
@@ -7054,7 +7054,7 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P26">
         <v>1.66</v>
@@ -7066,16 +7066,16 @@
         <v>1.23</v>
       </c>
       <c r="S26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T26">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U26">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W26">
         <v>2.08</v>
@@ -7084,10 +7084,10 @@
         <v>970</v>
       </c>
       <c r="Y26">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA26">
         <v>1000</v>
@@ -7096,10 +7096,10 @@
         <v>970</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE26">
         <v>1000</v>
@@ -7108,85 +7108,85 @@
         <v>970</v>
       </c>
       <c r="AG26">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI26">
         <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.48</v>
+        <v>5.6</v>
       </c>
       <c r="AQ26">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="AR26">
         <v>20</v>
       </c>
       <c r="AS26">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AT26">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU26">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV26">
-        <v>1.61</v>
+        <v>15</v>
       </c>
       <c r="AW26">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AX26">
         <v>7</v>
       </c>
       <c r="AY26">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="AZ26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="BB26">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="BC26">
         <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="BE26">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="BF26">
-        <v>1.61</v>
+        <v>4.6</v>
       </c>
       <c r="BG26">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7269,7 +7269,7 @@
         <v>187</v>
       </c>
       <c r="F27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G27">
         <v>2.6</v>
@@ -7278,7 +7278,7 @@
         <v>2.96</v>
       </c>
       <c r="I27">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J27">
         <v>3.4</v>
@@ -7293,7 +7293,7 @@
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O27">
         <v>1.31</v>
@@ -7302,7 +7302,7 @@
         <v>1.89</v>
       </c>
       <c r="Q27">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R27">
         <v>1.37</v>
@@ -7311,13 +7311,13 @@
         <v>3.15</v>
       </c>
       <c r="T27">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U27">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
         <v>1.62</v>
@@ -7329,46 +7329,46 @@
         <v>970</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB27">
         <v>970</v>
       </c>
       <c r="AC27">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD27">
         <v>970</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG27">
         <v>970</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN27">
         <v>1000</v>
@@ -7377,58 +7377,58 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AQ27">
         <v>8.199999999999999</v>
       </c>
       <c r="AR27">
-        <v>1.31</v>
+        <v>11</v>
       </c>
       <c r="AS27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="AT27">
-        <v>1.23</v>
+        <v>5.8</v>
       </c>
       <c r="AU27">
         <v>5.9</v>
       </c>
       <c r="AV27">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="AW27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="AX27">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AY27">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="AZ27">
-        <v>1.31</v>
+        <v>9</v>
       </c>
       <c r="BA27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="BB27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="BC27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="BD27">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="BE27">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="BF27">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="BG27">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7535,19 +7535,19 @@
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
         <v>1.44</v>
       </c>
       <c r="P28">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S28">
         <v>4.2</v>
@@ -7571,10 +7571,10 @@
         <v>13</v>
       </c>
       <c r="Z28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA28">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -7598,7 +7598,7 @@
         <v>23</v>
       </c>
       <c r="AI28">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AJ28">
         <v>38</v>
@@ -7610,13 +7610,13 @@
         <v>60</v>
       </c>
       <c r="AM28">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN28">
         <v>32</v>
       </c>
       <c r="AO28">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AP28">
         <v>9.6</v>
@@ -7628,10 +7628,10 @@
         <v>19</v>
       </c>
       <c r="AS28">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU28">
         <v>6.6</v>
@@ -7655,10 +7655,10 @@
         <v>6.2</v>
       </c>
       <c r="BB28">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC28">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BD28">
         <v>38</v>
@@ -7670,7 +7670,7 @@
         <v>21</v>
       </c>
       <c r="BG28">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7759,13 +7759,13 @@
         <v>2.84</v>
       </c>
       <c r="H29">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
         <v>3.9</v>
@@ -7777,22 +7777,22 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O29">
         <v>1.29</v>
       </c>
       <c r="P29">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q29">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R29">
         <v>1.36</v>
       </c>
       <c r="S29">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T29">
         <v>1.63</v>
@@ -7801,7 +7801,7 @@
         <v>2.14</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W29">
         <v>1.54</v>
@@ -7810,49 +7810,49 @@
         <v>1000</v>
       </c>
       <c r="Y29">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AC29">
+        <v>14</v>
+      </c>
+      <c r="AD29">
         <v>970</v>
       </c>
-      <c r="AD29">
-        <v>27</v>
-      </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG29">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29">
         <v>1000</v>
@@ -7861,58 +7861,58 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AR29">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AS29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AT29">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AU29">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AV29">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AW29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AX29">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AY29">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AZ29">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="BA29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="BB29">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="BC29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="BD29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="BE29">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="BF29">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="BG29">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7995,16 +7995,16 @@
         <v>190</v>
       </c>
       <c r="F30">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G30">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H30">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="I30">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J30">
         <v>3.9</v>
@@ -8025,16 +8025,16 @@
         <v>1.16</v>
       </c>
       <c r="P30">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q30">
         <v>1.5</v>
       </c>
       <c r="R30">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S30">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="T30">
         <v>1.48</v>
@@ -8043,10 +8043,10 @@
         <v>2.86</v>
       </c>
       <c r="V30">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X30">
         <v>32</v>
@@ -8082,7 +8082,7 @@
         <v>15.5</v>
       </c>
       <c r="AI30">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AJ30">
         <v>44</v>
@@ -8091,16 +8091,16 @@
         <v>28</v>
       </c>
       <c r="AL30">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM30">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN30">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO30">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AP30">
         <v>21</v>
@@ -8109,10 +8109,10 @@
         <v>17</v>
       </c>
       <c r="AR30">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS30">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT30">
         <v>16</v>
@@ -8124,7 +8124,7 @@
         <v>12</v>
       </c>
       <c r="AW30">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX30">
         <v>17.5</v>
@@ -8139,7 +8139,7 @@
         <v>21</v>
       </c>
       <c r="BB30">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC30">
         <v>19.5</v>
@@ -8148,13 +8148,13 @@
         <v>21</v>
       </c>
       <c r="BE30">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF30">
+        <v>11</v>
+      </c>
+      <c r="BG30">
         <v>11.5</v>
-      </c>
-      <c r="BG30">
-        <v>11</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8240,7 +8240,7 @@
         <v>2.58</v>
       </c>
       <c r="G31">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H31">
         <v>2.7</v>
@@ -8249,31 +8249,31 @@
         <v>2.92</v>
       </c>
       <c r="J31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M31">
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P31">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S31">
         <v>3.1</v>
@@ -8282,7 +8282,7 @@
         <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
         <v>1.52</v>
@@ -8336,31 +8336,31 @@
         <v>38</v>
       </c>
       <c r="AM31">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN31">
         <v>22</v>
       </c>
       <c r="AO31">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP31">
         <v>6.6</v>
       </c>
       <c r="AQ31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR31">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS31">
         <v>8.800000000000001</v>
       </c>
       <c r="AT31">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AU31">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV31">
         <v>7.6</v>
@@ -8369,37 +8369,37 @@
         <v>8</v>
       </c>
       <c r="AX31">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY31">
         <v>7.6</v>
       </c>
       <c r="AZ31">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BA31">
         <v>8.6</v>
       </c>
       <c r="BB31">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD31">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF31">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI31">
         <v>2.94</v>
@@ -8426,13 +8426,13 @@
         <v>20</v>
       </c>
       <c r="BQ31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR31">
         <v>32</v>
       </c>
       <c r="BS31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT31">
         <v>6.2</v>
@@ -8444,13 +8444,13 @@
         <v>21</v>
       </c>
       <c r="BW31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX31">
         <v>32</v>
       </c>
       <c r="BY31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8479,16 +8479,16 @@
         <v>192</v>
       </c>
       <c r="F32">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G32">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H32">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I32">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -8509,13 +8509,13 @@
         <v>1.25</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q32">
         <v>1.74</v>
       </c>
       <c r="R32">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S32">
         <v>2.9</v>
@@ -8527,10 +8527,10 @@
         <v>2.14</v>
       </c>
       <c r="V32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X32">
         <v>19.5</v>
@@ -8539,22 +8539,22 @@
         <v>21</v>
       </c>
       <c r="Z32">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AA32">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB32">
         <v>10.5</v>
       </c>
       <c r="AC32">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD32">
         <v>21</v>
       </c>
       <c r="AE32">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AF32">
         <v>11.5</v>
@@ -8566,7 +8566,7 @@
         <v>19.5</v>
       </c>
       <c r="AI32">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AJ32">
         <v>18</v>
@@ -8575,16 +8575,16 @@
         <v>18</v>
       </c>
       <c r="AL32">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AM32">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN32">
         <v>9</v>
       </c>
       <c r="AO32">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="AP32">
         <v>16</v>
@@ -8593,10 +8593,10 @@
         <v>17</v>
       </c>
       <c r="AR32">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT32">
         <v>8.800000000000001</v>
@@ -8608,7 +8608,7 @@
         <v>17</v>
       </c>
       <c r="AW32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX32">
         <v>10</v>
@@ -8620,7 +8620,7 @@
         <v>16.5</v>
       </c>
       <c r="BA32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB32">
         <v>15</v>
@@ -8629,16 +8629,16 @@
         <v>15</v>
       </c>
       <c r="BD32">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BE32">
+        <v>10.5</v>
+      </c>
+      <c r="BF32">
+        <v>8</v>
+      </c>
+      <c r="BG32">
         <v>10</v>
-      </c>
-      <c r="BF32">
-        <v>5</v>
-      </c>
-      <c r="BG32">
-        <v>9.800000000000001</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8721,16 +8721,16 @@
         <v>193</v>
       </c>
       <c r="F33">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H33">
         <v>2.1</v>
       </c>
       <c r="I33">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J33">
         <v>4.2</v>
@@ -8745,7 +8745,7 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>1.11</v>
@@ -8754,7 +8754,7 @@
         <v>3</v>
       </c>
       <c r="Q33">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R33">
         <v>1.82</v>
@@ -8763,13 +8763,13 @@
         <v>2</v>
       </c>
       <c r="T33">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="U33">
         <v>2.84</v>
       </c>
       <c r="V33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W33">
         <v>1.42</v>
@@ -8778,109 +8778,109 @@
         <v>1000</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AC33">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD33">
         <v>970</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH33">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AO33">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP33">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AQ33">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AR33">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AS33">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="AT33">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AU33">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV33">
-        <v>1.15</v>
+        <v>6.4</v>
       </c>
       <c r="AW33">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="AX33">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AY33">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="AZ33">
-        <v>1.27</v>
+        <v>7.6</v>
       </c>
       <c r="BA33">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BB33">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BC33">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BD33">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BE33">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="BF33">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="BG33">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8963,22 +8963,22 @@
         <v>194</v>
       </c>
       <c r="F34">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G34">
         <v>2.66</v>
       </c>
       <c r="H34">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J34">
         <v>3.2</v>
       </c>
       <c r="K34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -8987,16 +8987,16 @@
         <v>1.09</v>
       </c>
       <c r="N34">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O34">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
         <v>1.27</v>
@@ -9005,13 +9005,13 @@
         <v>4.1</v>
       </c>
       <c r="T34">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U34">
         <v>2</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
         <v>1.6</v>
@@ -9062,10 +9062,10 @@
         <v>50</v>
       </c>
       <c r="AM34">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO34">
         <v>46</v>
@@ -9077,22 +9077,22 @@
         <v>10</v>
       </c>
       <c r="AR34">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AS34">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT34">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AU34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV34">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW34">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AX34">
         <v>13.5</v>
@@ -9104,7 +9104,7 @@
         <v>17</v>
       </c>
       <c r="BA34">
-        <v>9.6</v>
+        <v>44</v>
       </c>
       <c r="BB34">
         <v>32</v>
@@ -9116,10 +9116,10 @@
         <v>40</v>
       </c>
       <c r="BE34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF34">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG34">
         <v>30</v>
@@ -9128,7 +9128,7 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
@@ -9205,19 +9205,19 @@
         <v>195</v>
       </c>
       <c r="F35">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H35">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I35">
         <v>2.66</v>
       </c>
       <c r="J35">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>4</v>
@@ -9232,7 +9232,7 @@
         <v>3.2</v>
       </c>
       <c r="O35">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P35">
         <v>1.71</v>
@@ -9244,64 +9244,64 @@
         <v>1.24</v>
       </c>
       <c r="S35">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T35">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U35">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X35">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Y35">
         <v>970</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB35">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AC35">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD35">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF35">
         <v>1000</v>
       </c>
       <c r="AG35">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AH35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ35">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK35">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM35">
         <v>1000</v>
@@ -9313,16 +9313,16 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AQ35">
         <v>6.8</v>
       </c>
       <c r="AR35">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AS35">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AT35">
         <v>7.8</v>
@@ -9334,37 +9334,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW35">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AX35">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AY35">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ35">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="BA35">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BB35">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BC35">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BD35">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BE35">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="BF35">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="BG35">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9447,46 +9447,46 @@
         <v>196</v>
       </c>
       <c r="F36">
-        <v>1.12</v>
+        <v>3.05</v>
       </c>
       <c r="G36">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="H36">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="I36">
-        <v>110</v>
+        <v>2.86</v>
       </c>
       <c r="J36">
-        <v>1.16</v>
+        <v>2.92</v>
       </c>
       <c r="K36">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N36">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="O36">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="Q36">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="R36">
         <v>1.08</v>
       </c>
       <c r="S36">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9495,34 +9495,34 @@
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB36">
         <v>1000</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF36">
         <v>1000</v>
@@ -9534,10 +9534,10 @@
         <v>1000</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK36">
         <v>1000</v>
@@ -9552,67 +9552,67 @@
         <v>1000</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP36">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ36">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR36">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AS36">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AT36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AU36">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV36">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AW36">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AX36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AY36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AZ36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BA36">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BB36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BC36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BD36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BE36">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH36">
         <v>1000</v>
       </c>
       <c r="BI36">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
@@ -9648,7 +9648,7 @@
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV36">
         <v>1000</v>
@@ -9689,64 +9689,64 @@
         <v>197</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N37">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="O37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P37">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="Q37">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="R37">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="S37">
-        <v>1.42</v>
+        <v>4</v>
       </c>
       <c r="T37">
+        <v>2.02</v>
+      </c>
+      <c r="U37">
+        <v>1.71</v>
+      </c>
+      <c r="V37">
+        <v>1.17</v>
+      </c>
+      <c r="W37">
         <v>2.04</v>
-      </c>
-      <c r="U37">
-        <v>1.7</v>
-      </c>
-      <c r="V37">
-        <v>1.01</v>
-      </c>
-      <c r="W37">
-        <v>1.01</v>
       </c>
       <c r="X37">
         <v>970</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z37">
         <v>1000</v>
@@ -9770,7 +9770,7 @@
         <v>970</v>
       </c>
       <c r="AG37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH37">
         <v>1000</v>
@@ -9797,58 +9797,58 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AR37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AS37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AT37">
         <v>5.5</v>
       </c>
       <c r="AU37">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="AV37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AW37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AX37">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AY37">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AZ37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BA37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BB37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BC37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BD37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BE37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BF37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BG37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9934,19 +9934,19 @@
         <v>1.57</v>
       </c>
       <c r="G38">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H38">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I38">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J38">
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L38">
         <v>1.35</v>
@@ -9955,25 +9955,25 @@
         <v>1.06</v>
       </c>
       <c r="N38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
         <v>1.28</v>
       </c>
       <c r="P38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q38">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R38">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S38">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T38">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U38">
         <v>2</v>
@@ -9982,19 +9982,19 @@
         <v>1.16</v>
       </c>
       <c r="W38">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X38">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z38">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA38">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AB38">
         <v>8.800000000000001</v>
@@ -10003,10 +10003,10 @@
         <v>10</v>
       </c>
       <c r="AD38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE38">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF38">
         <v>9.6</v>
@@ -10018,7 +10018,7 @@
         <v>23</v>
       </c>
       <c r="AI38">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AJ38">
         <v>15</v>
@@ -10027,28 +10027,28 @@
         <v>17.5</v>
       </c>
       <c r="AL38">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM38">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AN38">
         <v>8.6</v>
       </c>
       <c r="AO38">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP38">
         <v>14.5</v>
       </c>
       <c r="AQ38">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR38">
         <v>10</v>
       </c>
       <c r="AS38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT38">
         <v>7.8</v>
@@ -10060,7 +10060,7 @@
         <v>20</v>
       </c>
       <c r="AW38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX38">
         <v>8.6</v>
@@ -10069,7 +10069,7 @@
         <v>9</v>
       </c>
       <c r="AZ38">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BA38">
         <v>11</v>
@@ -10078,10 +10078,10 @@
         <v>13</v>
       </c>
       <c r="BC38">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD38">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE38">
         <v>11</v>
@@ -10173,13 +10173,13 @@
         <v>199</v>
       </c>
       <c r="F39">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G39">
         <v>110</v>
       </c>
       <c r="H39">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I39">
         <v>110</v>
@@ -10415,7 +10415,7 @@
         <v>200</v>
       </c>
       <c r="F40">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="G40">
         <v>3.3</v>
@@ -10424,7 +10424,7 @@
         <v>2.3</v>
       </c>
       <c r="I40">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J40">
         <v>3.75</v>
@@ -10439,31 +10439,31 @@
         <v>1.05</v>
       </c>
       <c r="N40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O40">
         <v>1.25</v>
       </c>
       <c r="P40">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q40">
         <v>1.72</v>
       </c>
       <c r="R40">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S40">
         <v>2.82</v>
       </c>
       <c r="T40">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U40">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
         <v>1.44</v>
@@ -10526,10 +10526,10 @@
         <v>16</v>
       </c>
       <c r="AQ40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR40">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS40">
         <v>1.03</v>
@@ -10574,7 +10574,7 @@
         <v>18.5</v>
       </c>
       <c r="BG40">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10684,7 +10684,7 @@
         <v>2.72</v>
       </c>
       <c r="O41">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P41">
         <v>1.58</v>
@@ -10705,7 +10705,7 @@
         <v>1.84</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
         <v>1.53</v>
@@ -10899,22 +10899,22 @@
         <v>202</v>
       </c>
       <c r="F42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G42">
         <v>1.71</v>
       </c>
       <c r="H42">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I42">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J42">
         <v>3.8</v>
       </c>
       <c r="K42">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L42">
         <v>1.42</v>
@@ -10929,7 +10929,7 @@
         <v>1.4</v>
       </c>
       <c r="P42">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q42">
         <v>2.16</v>
@@ -10938,13 +10938,13 @@
         <v>1.28</v>
       </c>
       <c r="S42">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T42">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U42">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V42">
         <v>1.16</v>
@@ -10968,7 +10968,7 @@
         <v>7</v>
       </c>
       <c r="AC42">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD42">
         <v>28</v>
@@ -10977,7 +10977,7 @@
         <v>140</v>
       </c>
       <c r="AF42">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG42">
         <v>10.5</v>
@@ -10986,16 +10986,16 @@
         <v>29</v>
       </c>
       <c r="AI42">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ42">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK42">
         <v>25</v>
       </c>
       <c r="AL42">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM42">
         <v>220</v>
@@ -11004,61 +11004,61 @@
         <v>13</v>
       </c>
       <c r="AO42">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP42">
         <v>10</v>
       </c>
       <c r="AQ42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS42">
+        <v>9</v>
+      </c>
+      <c r="AT42">
+        <v>6.2</v>
+      </c>
+      <c r="AU42">
+        <v>8</v>
+      </c>
+      <c r="AV42">
+        <v>22</v>
+      </c>
+      <c r="AW42">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS42">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT42">
-        <v>6</v>
-      </c>
-      <c r="AU42">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV42">
-        <v>23</v>
-      </c>
-      <c r="AW42">
-        <v>9.4</v>
-      </c>
       <c r="AX42">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY42">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ42">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA42">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB42">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC42">
         <v>17.5</v>
       </c>
       <c r="BD42">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE42">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF42">
         <v>11</v>
       </c>
       <c r="BG42">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH42">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -625,7 +625,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-24 19:53:31</t>
+    <t>2026-09-24 22:09:25</t>
   </si>
 </sst>
 </file>
@@ -1219,226 +1219,226 @@
         <v>162</v>
       </c>
       <c r="F2">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.16</v>
       </c>
       <c r="H2">
+        <v>32</v>
+      </c>
+      <c r="I2">
+        <v>40</v>
+      </c>
+      <c r="J2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>5.1</v>
+      </c>
+      <c r="S2">
+        <v>1.23</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.03</v>
+      </c>
+      <c r="W2">
+        <v>7.2</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
         <v>5.5</v>
       </c>
-      <c r="I2">
-        <v>5.9</v>
-      </c>
-      <c r="J2">
-        <v>4.4</v>
-      </c>
-      <c r="K2">
-        <v>4.7</v>
-      </c>
-      <c r="L2">
-        <v>1.44</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.55</v>
-      </c>
-      <c r="O2">
-        <v>1.37</v>
-      </c>
-      <c r="P2">
-        <v>1.86</v>
-      </c>
-      <c r="Q2">
-        <v>2.12</v>
-      </c>
-      <c r="R2">
-        <v>1.32</v>
-      </c>
-      <c r="S2">
-        <v>3.95</v>
-      </c>
-      <c r="T2">
-        <v>2.12</v>
-      </c>
-      <c r="U2">
-        <v>1.81</v>
-      </c>
-      <c r="V2">
-        <v>1.2</v>
-      </c>
-      <c r="W2">
-        <v>2.48</v>
-      </c>
-      <c r="X2">
-        <v>17.5</v>
-      </c>
-      <c r="Y2">
-        <v>18</v>
-      </c>
-      <c r="Z2">
-        <v>48</v>
-      </c>
-      <c r="AA2">
+      <c r="AH2">
+        <v>25</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>4.6</v>
+      </c>
+      <c r="AL2">
+        <v>10</v>
+      </c>
+      <c r="AM2">
+        <v>65</v>
+      </c>
+      <c r="AN2">
+        <v>3</v>
+      </c>
+      <c r="AO2">
         <v>200</v>
       </c>
-      <c r="AB2">
-        <v>7.4</v>
-      </c>
-      <c r="AC2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>24</v>
-      </c>
-      <c r="AE2">
-        <v>110</v>
-      </c>
-      <c r="AF2">
-        <v>8.6</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>120</v>
-      </c>
-      <c r="AJ2">
-        <v>17</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
-        <v>48</v>
-      </c>
-      <c r="AM2">
-        <v>180</v>
-      </c>
-      <c r="AN2">
-        <v>11.5</v>
-      </c>
-      <c r="AO2">
-        <v>160</v>
-      </c>
       <c r="AP2">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
         <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="BA2">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>2.84</v>
       </c>
       <c r="BG2">
-        <v>13.5</v>
+        <v>110</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>203</v>
@@ -1461,226 +1461,226 @@
         <v>163</v>
       </c>
       <c r="F3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H3">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="I3">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="K3">
+        <v>2.92</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.25</v>
+      </c>
+      <c r="N3">
+        <v>1.86</v>
+      </c>
+      <c r="O3">
+        <v>2.1</v>
+      </c>
+      <c r="P3">
+        <v>1.25</v>
+      </c>
+      <c r="Q3">
+        <v>4.8</v>
+      </c>
+      <c r="R3">
+        <v>1.07</v>
+      </c>
+      <c r="S3">
+        <v>14</v>
+      </c>
+      <c r="T3">
+        <v>3.6</v>
+      </c>
+      <c r="U3">
+        <v>1.32</v>
+      </c>
+      <c r="V3">
+        <v>1.91</v>
+      </c>
+      <c r="W3">
+        <v>1.18</v>
+      </c>
+      <c r="X3">
+        <v>5.1</v>
+      </c>
+      <c r="Y3">
+        <v>4.8</v>
+      </c>
+      <c r="Z3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>11</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>18.5</v>
+      </c>
+      <c r="AE3">
+        <v>70</v>
+      </c>
+      <c r="AF3">
+        <v>60</v>
+      </c>
+      <c r="AG3">
+        <v>50</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>300</v>
+      </c>
+      <c r="AJ3">
+        <v>320</v>
+      </c>
+      <c r="AK3">
+        <v>340</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>65</v>
+      </c>
+      <c r="AP3">
         <v>4.7</v>
       </c>
-      <c r="L3">
-        <v>1.4</v>
-      </c>
-      <c r="M3">
-        <v>1.06</v>
-      </c>
-      <c r="N3">
-        <v>3.8</v>
-      </c>
-      <c r="O3">
-        <v>1.32</v>
-      </c>
-      <c r="P3">
-        <v>1.97</v>
-      </c>
-      <c r="Q3">
-        <v>2</v>
-      </c>
-      <c r="R3">
-        <v>1.36</v>
-      </c>
-      <c r="S3">
-        <v>3.5</v>
-      </c>
-      <c r="T3">
-        <v>2.04</v>
-      </c>
-      <c r="U3">
-        <v>1.83</v>
-      </c>
-      <c r="V3">
-        <v>2.52</v>
-      </c>
-      <c r="W3">
-        <v>1.2</v>
-      </c>
-      <c r="X3">
-        <v>16.5</v>
-      </c>
-      <c r="Y3">
-        <v>8.4</v>
-      </c>
-      <c r="Z3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA3">
-        <v>16</v>
-      </c>
-      <c r="AB3">
-        <v>21</v>
-      </c>
-      <c r="AC3">
-        <v>10</v>
-      </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
-        <v>19</v>
-      </c>
-      <c r="AF3">
-        <v>70</v>
-      </c>
-      <c r="AG3">
-        <v>26</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>44</v>
-      </c>
-      <c r="AJ3">
-        <v>190</v>
-      </c>
-      <c r="AK3">
-        <v>110</v>
-      </c>
-      <c r="AL3">
-        <v>100</v>
-      </c>
-      <c r="AM3">
-        <v>150</v>
-      </c>
-      <c r="AN3">
-        <v>140</v>
-      </c>
-      <c r="AO3">
-        <v>10</v>
-      </c>
-      <c r="AP3">
-        <v>14</v>
-      </c>
       <c r="AQ3">
+        <v>4.2</v>
+      </c>
+      <c r="AR3">
         <v>7.6</v>
       </c>
-      <c r="AR3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AT3">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AY3">
+        <v>30</v>
+      </c>
+      <c r="AZ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA3">
+        <v>130</v>
+      </c>
+      <c r="BB3">
+        <v>200</v>
+      </c>
+      <c r="BC3">
+        <v>170</v>
+      </c>
+      <c r="BD3">
+        <v>9.6</v>
+      </c>
+      <c r="BE3">
         <v>20</v>
       </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
+      <c r="BF3">
+        <v>85</v>
+      </c>
+      <c r="BG3">
         <v>34</v>
       </c>
-      <c r="BB3">
-        <v>10.5</v>
-      </c>
-      <c r="BC3">
-        <v>65</v>
-      </c>
-      <c r="BD3">
-        <v>60</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>42</v>
-      </c>
-      <c r="BG3">
-        <v>8.4</v>
-      </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>203</v>
@@ -1703,226 +1703,226 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I4">
+        <v>7.4</v>
+      </c>
+      <c r="J4">
+        <v>3.4</v>
+      </c>
+      <c r="K4">
+        <v>3.55</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>6.2</v>
+      </c>
+      <c r="Q4">
+        <v>1.18</v>
+      </c>
+      <c r="R4">
+        <v>2.1</v>
+      </c>
+      <c r="S4">
+        <v>1.86</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1.15</v>
+      </c>
+      <c r="W4">
+        <v>2.3</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
         <v>7</v>
       </c>
-      <c r="J4">
-        <v>4.5</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>1.4</v>
-      </c>
-      <c r="M4">
-        <v>1.06</v>
-      </c>
-      <c r="N4">
-        <v>4.1</v>
-      </c>
-      <c r="O4">
-        <v>1.3</v>
-      </c>
-      <c r="P4">
-        <v>2.02</v>
-      </c>
-      <c r="Q4">
-        <v>1.92</v>
-      </c>
-      <c r="R4">
-        <v>1.37</v>
-      </c>
-      <c r="S4">
-        <v>3.45</v>
-      </c>
-      <c r="T4">
-        <v>2.02</v>
-      </c>
-      <c r="U4">
-        <v>1.89</v>
-      </c>
-      <c r="V4">
-        <v>1.16</v>
-      </c>
-      <c r="W4">
-        <v>2.72</v>
-      </c>
-      <c r="X4">
-        <v>18</v>
-      </c>
-      <c r="Y4">
-        <v>21</v>
-      </c>
-      <c r="Z4">
-        <v>60</v>
-      </c>
-      <c r="AA4">
-        <v>230</v>
-      </c>
-      <c r="AB4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC4">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD4">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>4.4</v>
+      </c>
+      <c r="AH4">
+        <v>9</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>7.6</v>
+      </c>
+      <c r="AL4">
+        <v>14.5</v>
+      </c>
+      <c r="AM4">
+        <v>70</v>
+      </c>
+      <c r="AN4">
+        <v>8.6</v>
+      </c>
+      <c r="AO4">
+        <v>120</v>
+      </c>
+      <c r="AP4">
+        <v>14</v>
+      </c>
+      <c r="AQ4">
+        <v>14</v>
+      </c>
+      <c r="AR4">
+        <v>14</v>
+      </c>
+      <c r="AS4">
+        <v>14</v>
+      </c>
+      <c r="AT4">
+        <v>14</v>
+      </c>
+      <c r="AU4">
+        <v>6.2</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>50</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>4</v>
+      </c>
+      <c r="AZ4">
         <v>8.4</v>
       </c>
-      <c r="AG4">
-        <v>9.4</v>
-      </c>
-      <c r="AH4">
-        <v>25</v>
-      </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>14.5</v>
-      </c>
-      <c r="AK4">
-        <v>17.5</v>
-      </c>
-      <c r="AL4">
-        <v>40</v>
-      </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>9.4</v>
-      </c>
-      <c r="AO4">
-        <v>160</v>
-      </c>
-      <c r="AP4">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4">
-        <v>18</v>
-      </c>
-      <c r="AR4">
-        <v>46</v>
-      </c>
-      <c r="AS4">
-        <v>120</v>
-      </c>
-      <c r="AT4">
-        <v>7.6</v>
-      </c>
-      <c r="AU4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>22</v>
-      </c>
-      <c r="AW4">
-        <v>60</v>
-      </c>
-      <c r="AX4">
-        <v>7.6</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4">
-        <v>22</v>
-      </c>
       <c r="BA4">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC4">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BH4">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>1.28</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>1.23</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="BN4">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>203</v>
@@ -1945,226 +1945,226 @@
         <v>165</v>
       </c>
       <c r="F5">
+        <v>2.06</v>
+      </c>
+      <c r="G5">
+        <v>2.1</v>
+      </c>
+      <c r="H5">
+        <v>5.1</v>
+      </c>
+      <c r="I5">
+        <v>5.3</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3.1</v>
+      </c>
+      <c r="L5">
+        <v>2.78</v>
+      </c>
+      <c r="M5">
+        <v>1.18</v>
+      </c>
+      <c r="N5">
+        <v>2.24</v>
+      </c>
+      <c r="O5">
         <v>1.78</v>
       </c>
-      <c r="G5">
-        <v>1.81</v>
-      </c>
-      <c r="H5">
-        <v>4.8</v>
-      </c>
-      <c r="I5">
+      <c r="P5">
+        <v>1.4</v>
+      </c>
+      <c r="Q5">
+        <v>3.4</v>
+      </c>
+      <c r="R5">
+        <v>1.12</v>
+      </c>
+      <c r="S5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T5">
+        <v>2.6</v>
+      </c>
+      <c r="U5">
+        <v>1.53</v>
+      </c>
+      <c r="V5">
+        <v>1.25</v>
+      </c>
+      <c r="W5">
+        <v>1.89</v>
+      </c>
+      <c r="X5">
+        <v>7</v>
+      </c>
+      <c r="Y5">
+        <v>11</v>
+      </c>
+      <c r="Z5">
+        <v>40</v>
+      </c>
+      <c r="AA5">
+        <v>180</v>
+      </c>
+      <c r="AB5">
+        <v>5.5</v>
+      </c>
+      <c r="AC5">
+        <v>7.4</v>
+      </c>
+      <c r="AD5">
+        <v>25</v>
+      </c>
+      <c r="AE5">
+        <v>130</v>
+      </c>
+      <c r="AF5">
+        <v>10.5</v>
+      </c>
+      <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
+        <v>40</v>
+      </c>
+      <c r="AI5">
+        <v>250</v>
+      </c>
+      <c r="AJ5">
+        <v>27</v>
+      </c>
+      <c r="AK5">
+        <v>38</v>
+      </c>
+      <c r="AL5">
+        <v>120</v>
+      </c>
+      <c r="AM5">
+        <v>600</v>
+      </c>
+      <c r="AN5">
+        <v>40</v>
+      </c>
+      <c r="AO5">
+        <v>320</v>
+      </c>
+      <c r="AP5">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5">
+        <v>10</v>
+      </c>
+      <c r="AR5">
+        <v>32</v>
+      </c>
+      <c r="AS5">
+        <v>120</v>
+      </c>
+      <c r="AT5">
+        <v>5.2</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>22</v>
+      </c>
+      <c r="AW5">
+        <v>100</v>
+      </c>
+      <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>12</v>
+      </c>
+      <c r="AZ5">
+        <v>32</v>
+      </c>
+      <c r="BA5">
+        <v>150</v>
+      </c>
+      <c r="BB5">
+        <v>23</v>
+      </c>
+      <c r="BC5">
+        <v>32</v>
+      </c>
+      <c r="BD5">
+        <v>90</v>
+      </c>
+      <c r="BE5">
+        <v>220</v>
+      </c>
+      <c r="BF5">
+        <v>32</v>
+      </c>
+      <c r="BG5">
+        <v>130</v>
+      </c>
+      <c r="BH5">
+        <v>1.56</v>
+      </c>
+      <c r="BI5">
+        <v>1.51</v>
+      </c>
+      <c r="BJ5">
+        <v>44</v>
+      </c>
+      <c r="BK5">
+        <v>36</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>19</v>
+      </c>
+      <c r="BN5">
+        <v>5.5</v>
+      </c>
+      <c r="BO5">
         <v>5.1</v>
       </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4.2</v>
-      </c>
-      <c r="L5">
-        <v>1.34</v>
-      </c>
-      <c r="M5">
-        <v>1.05</v>
-      </c>
-      <c r="N5">
-        <v>4.7</v>
-      </c>
-      <c r="O5">
-        <v>1.25</v>
-      </c>
-      <c r="P5">
-        <v>2.26</v>
-      </c>
-      <c r="Q5">
-        <v>1.76</v>
-      </c>
-      <c r="R5">
-        <v>1.48</v>
-      </c>
-      <c r="S5">
-        <v>2.98</v>
-      </c>
-      <c r="T5">
-        <v>1.74</v>
-      </c>
-      <c r="U5">
-        <v>2.3</v>
-      </c>
-      <c r="V5">
-        <v>1.24</v>
-      </c>
-      <c r="W5">
-        <v>2.22</v>
-      </c>
-      <c r="X5">
-        <v>19.5</v>
-      </c>
-      <c r="Y5">
-        <v>24</v>
-      </c>
-      <c r="Z5">
-        <v>42</v>
-      </c>
-      <c r="AA5">
-        <v>120</v>
-      </c>
-      <c r="AB5">
+      <c r="BP5">
+        <v>60</v>
+      </c>
+      <c r="BQ5">
+        <v>46</v>
+      </c>
+      <c r="BR5">
+        <v>530</v>
+      </c>
+      <c r="BS5">
+        <v>230</v>
+      </c>
+      <c r="BT5">
         <v>10.5</v>
       </c>
-      <c r="AC5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5">
-        <v>18.5</v>
-      </c>
-      <c r="AE5">
-        <v>55</v>
-      </c>
-      <c r="AF5">
-        <v>12</v>
-      </c>
-      <c r="AG5">
-        <v>9.6</v>
-      </c>
-      <c r="AH5">
-        <v>17.5</v>
-      </c>
-      <c r="AI5">
-        <v>55</v>
-      </c>
-      <c r="AJ5">
-        <v>19.5</v>
-      </c>
-      <c r="AK5">
-        <v>17.5</v>
-      </c>
-      <c r="AL5">
-        <v>32</v>
-      </c>
-      <c r="AM5">
-        <v>95</v>
-      </c>
-      <c r="AN5">
-        <v>10</v>
-      </c>
-      <c r="AO5">
-        <v>55</v>
-      </c>
-      <c r="AP5">
-        <v>17</v>
-      </c>
-      <c r="AQ5">
+      <c r="BU5">
+        <v>9.4</v>
+      </c>
+      <c r="BV5">
+        <v>190</v>
+      </c>
+      <c r="BW5">
+        <v>130</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>20</v>
       </c>
-      <c r="AR5">
-        <v>34</v>
-      </c>
-      <c r="AS5">
-        <v>70</v>
-      </c>
-      <c r="AT5">
-        <v>9.6</v>
-      </c>
-      <c r="AU5">
-        <v>8.4</v>
-      </c>
-      <c r="AV5">
-        <v>17</v>
-      </c>
-      <c r="AW5">
-        <v>48</v>
-      </c>
-      <c r="AX5">
-        <v>10.5</v>
-      </c>
-      <c r="AY5">
-        <v>9</v>
-      </c>
-      <c r="AZ5">
-        <v>16</v>
-      </c>
-      <c r="BA5">
-        <v>38</v>
-      </c>
-      <c r="BB5">
-        <v>17</v>
-      </c>
-      <c r="BC5">
-        <v>15.5</v>
-      </c>
-      <c r="BD5">
-        <v>26</v>
-      </c>
-      <c r="BE5">
-        <v>60</v>
-      </c>
-      <c r="BF5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG5">
-        <v>46</v>
-      </c>
-      <c r="BH5">
-        <v>4.4</v>
-      </c>
-      <c r="BI5">
-        <v>3.45</v>
-      </c>
-      <c r="BJ5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK5">
-        <v>8</v>
-      </c>
-      <c r="BL5">
-        <v>120</v>
-      </c>
-      <c r="BM5">
-        <v>75</v>
-      </c>
-      <c r="BN5">
-        <v>4.7</v>
-      </c>
-      <c r="BO5">
-        <v>4.1</v>
-      </c>
-      <c r="BP5">
-        <v>12</v>
-      </c>
-      <c r="BQ5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR5">
-        <v>25</v>
-      </c>
-      <c r="BS5">
-        <v>6.4</v>
-      </c>
-      <c r="BT5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU5">
-        <v>7</v>
-      </c>
-      <c r="BV5">
-        <v>40</v>
-      </c>
-      <c r="BW5">
-        <v>7.2</v>
-      </c>
-      <c r="BX5">
-        <v>46</v>
-      </c>
-      <c r="BY5">
-        <v>7.4</v>
-      </c>
       <c r="BZ5">
-        <v>18.5</v>
+        <v>710</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="CB5" t="s">
         <v>203</v>
@@ -2187,100 +2187,100 @@
         <v>166</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="H6">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA6">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AB6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>25</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
         <v>9</v>
       </c>
-      <c r="AD6">
-        <v>23</v>
-      </c>
-      <c r="AE6">
-        <v>95</v>
-      </c>
-      <c r="AF6">
-        <v>9.6</v>
-      </c>
       <c r="AG6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL6">
         <v>44</v>
@@ -2289,70 +2289,70 @@
         <v>160</v>
       </c>
       <c r="AN6">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO6">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AP6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AS6">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AT6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW6">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA6">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD6">
         <v>36</v>
       </c>
       <c r="BE6">
-        <v>100</v>
+        <v>19.5</v>
       </c>
       <c r="BF6">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG6">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="BH6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2367,13 +2367,13 @@
         <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ6">
         <v>6.4</v>
@@ -2382,19 +2382,19 @@
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2406,7 +2406,7 @@
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
         <v>203</v>
@@ -2432,22 +2432,22 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I7">
         <v>2.52</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
         <v>3.95</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M7">
         <v>1.06</v>
@@ -2465,16 +2465,16 @@
         <v>1.79</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V7">
         <v>1.66</v>
@@ -2483,22 +2483,22 @@
         <v>1.45</v>
       </c>
       <c r="X7">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA7">
         <v>34</v>
       </c>
       <c r="AB7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>12</v>
@@ -2522,13 +2522,13 @@
         <v>55</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN7">
         <v>30</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX7">
         <v>19.5</v>
@@ -2573,82 +2573,82 @@
         <v>18</v>
       </c>
       <c r="BB7">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BC7">
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BF7">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BG7">
         <v>14.5</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>203</v>
@@ -2671,19 +2671,19 @@
         <v>168</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.85</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2740,7 +2740,7 @@
         <v>1000</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2830,7 +2830,7 @@
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3161,7 +3161,7 @@
         <v>2.48</v>
       </c>
       <c r="H10">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I10">
         <v>3.55</v>
@@ -3170,7 +3170,7 @@
         <v>3.65</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3179,25 +3179,25 @@
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
         <v>2.16</v>
       </c>
       <c r="Q10">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="T10">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="U10">
         <v>2.32</v>
@@ -3272,7 +3272,7 @@
         <v>3.7</v>
       </c>
       <c r="AS10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT10">
         <v>3.3</v>
@@ -3281,7 +3281,7 @@
         <v>3.05</v>
       </c>
       <c r="AV10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW10">
         <v>3.85</v>
@@ -3299,13 +3299,13 @@
         <v>3.9</v>
       </c>
       <c r="BB10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE10">
         <v>4</v>
@@ -3397,10 +3397,10 @@
         <v>171</v>
       </c>
       <c r="F11">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G11">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H11">
         <v>4.9</v>
@@ -3409,13 +3409,13 @@
         <v>5</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
         <v>3.85</v>
       </c>
       <c r="L11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M11">
         <v>1.08</v>
@@ -3427,7 +3427,7 @@
         <v>1.37</v>
       </c>
       <c r="P11">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q11">
         <v>2.1</v>
@@ -3448,7 +3448,7 @@
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X11">
         <v>13</v>
@@ -3463,7 +3463,7 @@
         <v>130</v>
       </c>
       <c r="AB11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8.4</v>
@@ -3475,7 +3475,7 @@
         <v>75</v>
       </c>
       <c r="AF11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -3496,10 +3496,10 @@
         <v>42</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO11">
         <v>90</v>
@@ -3514,7 +3514,7 @@
         <v>32</v>
       </c>
       <c r="AS11">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT11">
         <v>7.4</v>
@@ -3532,19 +3532,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11">
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BB11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD11">
         <v>36</v>
@@ -3556,7 +3556,7 @@
         <v>13</v>
       </c>
       <c r="BG11">
-        <v>15.5</v>
+        <v>70</v>
       </c>
       <c r="BH11">
         <v>3.55</v>
@@ -3639,22 +3639,22 @@
         <v>172</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G12">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
         <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3663,7 +3663,7 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.41</v>
@@ -3684,13 +3684,13 @@
         <v>2.04</v>
       </c>
       <c r="U12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X12">
         <v>11.5</v>
@@ -3714,7 +3714,7 @@
         <v>18</v>
       </c>
       <c r="AE12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF12">
         <v>10.5</v>
@@ -3723,7 +3723,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI12">
         <v>80</v>
@@ -3744,7 +3744,7 @@
         <v>16.5</v>
       </c>
       <c r="AO12">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP12">
         <v>10.5</v>
@@ -3762,7 +3762,7 @@
         <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV12">
         <v>17</v>
@@ -3792,16 +3792,16 @@
         <v>40</v>
       </c>
       <c r="BE12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI12">
         <v>2.86</v>
@@ -3816,7 +3816,7 @@
         <v>170</v>
       </c>
       <c r="BM12">
-        <v>15.5</v>
+        <v>70</v>
       </c>
       <c r="BN12">
         <v>4.4</v>
@@ -3828,7 +3828,7 @@
         <v>14</v>
       </c>
       <c r="BQ12">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12">
         <v>32</v>
@@ -3840,7 +3840,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV12">
         <v>48</v>
@@ -3858,7 +3858,7 @@
         <v>30</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
         <v>203</v>
@@ -3941,19 +3941,19 @@
         <v>150</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AC13">
         <v>95</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AE13">
         <v>1000</v>
@@ -3965,7 +3965,7 @@
         <v>36</v>
       </c>
       <c r="AH13">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AI13">
         <v>1000</v>
@@ -3989,28 +3989,28 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AS13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT13">
         <v>2.5</v>
       </c>
       <c r="AU13">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AV13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AW13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AX13">
         <v>2.5</v>
@@ -4019,22 +4019,22 @@
         <v>2.5</v>
       </c>
       <c r="AZ13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BA13">
+        <v>1.33</v>
+      </c>
+      <c r="BB13">
         <v>1.31</v>
       </c>
-      <c r="BB13">
-        <v>1.29</v>
-      </c>
       <c r="BC13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BD13">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BE13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF13">
         <v>2.04</v>
@@ -4153,7 +4153,7 @@
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q14">
         <v>1.23</v>
@@ -4365,55 +4365,55 @@
         <v>175</v>
       </c>
       <c r="F15">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="G15">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="H15">
         <v>1.5</v>
       </c>
       <c r="I15">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J15">
         <v>3.05</v>
       </c>
       <c r="K15">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>3.9</v>
+      </c>
+      <c r="O15">
         <v>1.02</v>
-      </c>
-      <c r="N15">
-        <v>4</v>
-      </c>
-      <c r="O15">
-        <v>1.22</v>
       </c>
       <c r="P15">
         <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R15">
         <v>1.46</v>
       </c>
       <c r="S15">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -4428,7 +4428,7 @@
         <v>1000</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15">
         <v>1000</v>
@@ -4470,7 +4470,7 @@
         <v>1000</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP15">
         <v>1.01</v>
@@ -4521,7 +4521,7 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
@@ -4613,7 +4613,7 @@
         <v>3.35</v>
       </c>
       <c r="H16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I16">
         <v>2.46</v>
@@ -4622,7 +4622,7 @@
         <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4849,25 +4849,25 @@
         <v>177</v>
       </c>
       <c r="F17">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G17">
         <v>1.6</v>
       </c>
       <c r="H17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M17">
         <v>1.04</v>
@@ -4879,7 +4879,7 @@
         <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q17">
         <v>1.66</v>
@@ -4900,7 +4900,7 @@
         <v>1.17</v>
       </c>
       <c r="W17">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X17">
         <v>21</v>
@@ -4966,7 +4966,7 @@
         <v>48</v>
       </c>
       <c r="AS17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -4999,7 +4999,7 @@
         <v>14</v>
       </c>
       <c r="BD17">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BE17">
         <v>28</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
@@ -5026,7 +5026,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="BN17">
         <v>5.7</v>
@@ -5044,10 +5044,10 @@
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU17">
         <v>2.76</v>
@@ -5056,19 +5056,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="CB17" t="s">
         <v>203</v>
@@ -5091,7 +5091,7 @@
         <v>178</v>
       </c>
       <c r="F18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G18">
         <v>1.52</v>
@@ -5118,7 +5118,7 @@
         <v>5.2</v>
       </c>
       <c r="O18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P18">
         <v>2.44</v>
@@ -5127,16 +5127,16 @@
         <v>1.65</v>
       </c>
       <c r="R18">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T18">
         <v>1.83</v>
       </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
         <v>1.16</v>
@@ -5145,7 +5145,7 @@
         <v>2.92</v>
       </c>
       <c r="X18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y18">
         <v>28</v>
@@ -5154,7 +5154,7 @@
         <v>65</v>
       </c>
       <c r="AA18">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -5166,7 +5166,7 @@
         <v>26</v>
       </c>
       <c r="AE18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF18">
         <v>9.6</v>
@@ -5187,7 +5187,7 @@
         <v>14.5</v>
       </c>
       <c r="AL18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM18">
         <v>100</v>
@@ -5202,13 +5202,13 @@
         <v>21</v>
       </c>
       <c r="AQ18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR18">
         <v>55</v>
       </c>
       <c r="AS18">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AT18">
         <v>9.4</v>
@@ -5217,10 +5217,10 @@
         <v>10</v>
       </c>
       <c r="AV18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AX18">
         <v>9.4</v>
@@ -5229,10 +5229,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB18">
         <v>12.5</v>
@@ -5241,7 +5241,7 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE18">
         <v>85</v>
@@ -5268,7 +5268,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BN18">
         <v>4.9</v>
@@ -5333,22 +5333,22 @@
         <v>179</v>
       </c>
       <c r="F19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G19">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H19">
+        <v>1.41</v>
+      </c>
+      <c r="I19">
         <v>1.42</v>
       </c>
-      <c r="I19">
-        <v>1.43</v>
-      </c>
       <c r="J19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L19">
         <v>1.25</v>
@@ -5357,70 +5357,70 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O19">
         <v>1.14</v>
       </c>
       <c r="P19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q19">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R19">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T19">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U19">
         <v>2.4</v>
       </c>
       <c r="V19">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z19">
         <v>11.5</v>
       </c>
       <c r="AA19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB19">
         <v>44</v>
       </c>
       <c r="AC19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD19">
         <v>10.5</v>
       </c>
       <c r="AE19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF19">
         <v>85</v>
       </c>
       <c r="AG19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH19">
         <v>19.5</v>
       </c>
       <c r="AI19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19">
         <v>230</v>
@@ -5438,19 +5438,19 @@
         <v>80</v>
       </c>
       <c r="AO19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AP19">
         <v>30</v>
       </c>
       <c r="AQ19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
         <v>10.5</v>
       </c>
       <c r="AS19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT19">
         <v>38</v>
@@ -5468,25 +5468,25 @@
         <v>80</v>
       </c>
       <c r="AY19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ19">
         <v>17.5</v>
       </c>
       <c r="BA19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BD19">
         <v>60</v>
       </c>
       <c r="BE19">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF19">
         <v>65</v>
@@ -5546,7 +5546,7 @@
         <v>18</v>
       </c>
       <c r="BY19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5581,7 +5581,7 @@
         <v>1.83</v>
       </c>
       <c r="H20">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I20">
         <v>5.3</v>
@@ -5593,7 +5593,7 @@
         <v>3.9</v>
       </c>
       <c r="L20">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M20">
         <v>1.08</v>
@@ -5605,22 +5605,22 @@
         <v>1.37</v>
       </c>
       <c r="P20">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S20">
         <v>3.9</v>
       </c>
       <c r="T20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U20">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
         <v>1.23</v>
@@ -5632,13 +5632,13 @@
         <v>13</v>
       </c>
       <c r="Y20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z20">
         <v>40</v>
       </c>
       <c r="AA20">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB20">
         <v>8.199999999999999</v>
@@ -5656,7 +5656,7 @@
         <v>10</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH20">
         <v>23</v>
@@ -5677,22 +5677,22 @@
         <v>140</v>
       </c>
       <c r="AN20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO20">
         <v>130</v>
       </c>
       <c r="AP20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR20">
         <v>34</v>
       </c>
       <c r="AS20">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT20">
         <v>7.4</v>
@@ -5704,10 +5704,10 @@
         <v>18.5</v>
       </c>
       <c r="AW20">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AX20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
@@ -5734,7 +5734,7 @@
         <v>12</v>
       </c>
       <c r="BG20">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5752,7 +5752,7 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BN20">
         <v>1000</v>
@@ -5820,7 +5820,7 @@
         <v>2.3</v>
       </c>
       <c r="G21">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H21">
         <v>3.35</v>
@@ -5835,7 +5835,7 @@
         <v>3.7</v>
       </c>
       <c r="L21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M21">
         <v>1.06</v>
@@ -5847,7 +5847,7 @@
         <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q21">
         <v>1.83</v>
@@ -5868,7 +5868,7 @@
         <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X21">
         <v>17</v>
@@ -5907,7 +5907,7 @@
         <v>44</v>
       </c>
       <c r="AJ21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK21">
         <v>24</v>
@@ -5949,7 +5949,7 @@
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY21">
         <v>10.5</v>
@@ -5970,73 +5970,73 @@
         <v>30</v>
       </c>
       <c r="BE21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG21">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH21">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BI21">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK21">
+        <v>8</v>
+      </c>
+      <c r="BL21">
+        <v>130</v>
+      </c>
+      <c r="BM21">
+        <v>10.5</v>
+      </c>
+      <c r="BN21">
+        <v>5.3</v>
+      </c>
+      <c r="BO21">
+        <v>4.8</v>
+      </c>
+      <c r="BP21">
+        <v>20</v>
+      </c>
+      <c r="BQ21">
+        <v>14</v>
+      </c>
+      <c r="BR21">
+        <v>34</v>
+      </c>
+      <c r="BS21">
+        <v>8.4</v>
+      </c>
+      <c r="BT21">
         <v>6.6</v>
       </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.01</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>4.3</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>10</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.01</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
       <c r="BU21">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB21" t="s">
         <v>203</v>
@@ -6077,22 +6077,22 @@
         <v>3.45</v>
       </c>
       <c r="L22">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M22">
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O22">
         <v>1.38</v>
       </c>
       <c r="P22">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R22">
         <v>1.3</v>
@@ -6104,7 +6104,7 @@
         <v>1.86</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -6137,7 +6137,7 @@
         <v>55</v>
       </c>
       <c r="AF22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG22">
         <v>12</v>
@@ -6188,7 +6188,7 @@
         <v>13</v>
       </c>
       <c r="AW22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX22">
         <v>13</v>
@@ -6200,13 +6200,13 @@
         <v>17</v>
       </c>
       <c r="BA22">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB22">
         <v>30</v>
       </c>
       <c r="BC22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD22">
         <v>38</v>
@@ -6218,7 +6218,7 @@
         <v>20</v>
       </c>
       <c r="BG22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH22">
         <v>3.5</v>
@@ -6236,7 +6236,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BN22">
         <v>1000</v>
@@ -6301,22 +6301,22 @@
         <v>183</v>
       </c>
       <c r="F23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G23">
         <v>1.76</v>
       </c>
       <c r="H23">
+        <v>5.5</v>
+      </c>
+      <c r="I23">
         <v>5.6</v>
       </c>
-      <c r="I23">
-        <v>5.7</v>
-      </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.42</v>
@@ -6325,7 +6325,7 @@
         <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O23">
         <v>1.32</v>
@@ -6343,7 +6343,7 @@
         <v>3.5</v>
       </c>
       <c r="T23">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U23">
         <v>2.02</v>
@@ -6430,7 +6430,7 @@
         <v>19</v>
       </c>
       <c r="AW23">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX23">
         <v>9</v>
@@ -6442,19 +6442,19 @@
         <v>19.5</v>
       </c>
       <c r="BA23">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BB23">
         <v>16</v>
       </c>
       <c r="BC23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD23">
         <v>34</v>
       </c>
       <c r="BE23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BF23">
         <v>10</v>
@@ -6543,64 +6543,64 @@
         <v>184</v>
       </c>
       <c r="F24">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P24">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S24">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T24">
         <v>2.18</v>
       </c>
       <c r="U24">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V24">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W24">
         <v>3.4</v>
       </c>
       <c r="X24">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z24">
         <v>540</v>
@@ -6609,7 +6609,7 @@
         <v>510</v>
       </c>
       <c r="AB24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>12.5</v>
@@ -6642,16 +6642,16 @@
         <v>55</v>
       </c>
       <c r="AM24">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN24">
         <v>6.8</v>
       </c>
       <c r="AO24">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24">
         <v>14.5</v>
@@ -6663,7 +6663,7 @@
         <v>7.6</v>
       </c>
       <c r="AT24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU24">
         <v>10</v>
@@ -6681,22 +6681,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BA24">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD24">
         <v>34</v>
       </c>
       <c r="BE24">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF24">
         <v>6</v>
@@ -6785,22 +6785,22 @@
         <v>185</v>
       </c>
       <c r="F25">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G25">
         <v>2.88</v>
       </c>
       <c r="H25">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I25">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L25">
         <v>1.3</v>
@@ -6824,13 +6824,13 @@
         <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T25">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
         <v>1.56</v>
@@ -6938,7 +6938,7 @@
         <v>30</v>
       </c>
       <c r="BE25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF25">
         <v>17</v>
@@ -7027,22 +7027,22 @@
         <v>186</v>
       </c>
       <c r="F26">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H26">
         <v>5.1</v>
       </c>
       <c r="I26">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7051,7 +7051,7 @@
         <v>1.1</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O26">
         <v>1.45</v>
@@ -7060,13 +7060,13 @@
         <v>1.66</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S26">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T26">
         <v>2.14</v>
@@ -7075,7 +7075,7 @@
         <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
         <v>2.08</v>
@@ -7093,10 +7093,10 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC26">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26">
         <v>110</v>
@@ -7105,10 +7105,10 @@
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG26">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
         <v>130</v>
@@ -7132,7 +7132,7 @@
         <v>55</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP26">
         <v>5.6</v>
@@ -7141,52 +7141,52 @@
         <v>6.4</v>
       </c>
       <c r="AR26">
-        <v>20</v>
+        <v>2.56</v>
       </c>
       <c r="AS26">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="AT26">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU26">
         <v>4.9</v>
       </c>
       <c r="AV26">
-        <v>15</v>
+        <v>2.56</v>
       </c>
       <c r="AW26">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="AX26">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AY26">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ26">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA26">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="BB26">
-        <v>1.93</v>
+        <v>17.5</v>
       </c>
       <c r="BC26">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD26">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="BE26">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="BF26">
         <v>4.6</v>
       </c>
       <c r="BG26">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7287,19 +7287,19 @@
         <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27">
         <v>3.9</v>
       </c>
       <c r="O27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P27">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q27">
         <v>1.94</v>
@@ -7308,13 +7308,13 @@
         <v>1.37</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
         <v>1.47</v>
@@ -7323,112 +7323,112 @@
         <v>1.62</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z27">
+        <v>22</v>
+      </c>
+      <c r="AA27">
+        <v>60</v>
+      </c>
+      <c r="AB27">
+        <v>13</v>
+      </c>
+      <c r="AC27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>16</v>
+      </c>
+      <c r="AE27">
+        <v>50</v>
+      </c>
+      <c r="AF27">
+        <v>21</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>18</v>
+      </c>
+      <c r="AI27">
+        <v>55</v>
+      </c>
+      <c r="AJ27">
         <v>85</v>
       </c>
-      <c r="AA27">
-        <v>210</v>
-      </c>
-      <c r="AB27">
-        <v>970</v>
-      </c>
-      <c r="AC27">
-        <v>14</v>
-      </c>
-      <c r="AD27">
-        <v>970</v>
-      </c>
-      <c r="AE27">
-        <v>210</v>
-      </c>
-      <c r="AF27">
-        <v>75</v>
-      </c>
-      <c r="AG27">
-        <v>970</v>
-      </c>
-      <c r="AH27">
-        <v>60</v>
-      </c>
-      <c r="AI27">
-        <v>270</v>
-      </c>
-      <c r="AJ27">
-        <v>170</v>
-      </c>
       <c r="AK27">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="AL27">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="AM27">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP27">
-        <v>1.71</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AS27">
-        <v>1.69</v>
+        <v>6</v>
       </c>
       <c r="AT27">
+        <v>9.6</v>
+      </c>
+      <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>11.5</v>
+      </c>
+      <c r="AW27">
+        <v>5.7</v>
+      </c>
+      <c r="AX27">
+        <v>14.5</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>14.5</v>
+      </c>
+      <c r="BA27">
+        <v>6</v>
+      </c>
+      <c r="BB27">
         <v>5.8</v>
       </c>
-      <c r="AU27">
-        <v>5.9</v>
-      </c>
-      <c r="AV27">
-        <v>8</v>
-      </c>
-      <c r="AW27">
-        <v>1.69</v>
-      </c>
-      <c r="AX27">
-        <v>1.67</v>
-      </c>
-      <c r="AY27">
-        <v>7</v>
-      </c>
-      <c r="AZ27">
-        <v>9</v>
-      </c>
-      <c r="BA27">
-        <v>1.69</v>
-      </c>
-      <c r="BB27">
-        <v>1.69</v>
-      </c>
       <c r="BC27">
-        <v>1.69</v>
+        <v>20</v>
       </c>
       <c r="BD27">
-        <v>1.69</v>
+        <v>6</v>
       </c>
       <c r="BE27">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF27">
-        <v>1.71</v>
+        <v>19</v>
       </c>
       <c r="BG27">
-        <v>1.71</v>
+        <v>5.6</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7511,16 +7511,16 @@
         <v>188</v>
       </c>
       <c r="F28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H28">
         <v>3.3</v>
       </c>
       <c r="I28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J28">
         <v>3.3</v>
@@ -7535,34 +7535,34 @@
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q28">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
         <v>1.27</v>
       </c>
       <c r="S28">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T28">
         <v>1.9</v>
       </c>
       <c r="U28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V28">
         <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X28">
         <v>13</v>
@@ -7607,7 +7607,7 @@
         <v>32</v>
       </c>
       <c r="AL28">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM28">
         <v>580</v>
@@ -7628,7 +7628,7 @@
         <v>19</v>
       </c>
       <c r="AS28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT28">
         <v>7.8</v>
@@ -7652,7 +7652,7 @@
         <v>17</v>
       </c>
       <c r="BA28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB28">
         <v>14.5</v>
@@ -7664,7 +7664,7 @@
         <v>38</v>
       </c>
       <c r="BE28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF28">
         <v>21</v>
@@ -7753,22 +7753,22 @@
         <v>189</v>
       </c>
       <c r="F29">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="G29">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H29">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I29">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>3.45</v>
       </c>
       <c r="K29">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
         <v>1.33</v>
@@ -7777,142 +7777,142 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>1.29</v>
       </c>
       <c r="P29">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S29">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T29">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U29">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="V29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
         <v>1.54</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y29">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z29">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="AA29">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AB29">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC29">
+        <v>8.6</v>
+      </c>
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
+        <v>36</v>
+      </c>
+      <c r="AF29">
+        <v>23</v>
+      </c>
+      <c r="AG29">
+        <v>15</v>
+      </c>
+      <c r="AH29">
+        <v>19.5</v>
+      </c>
+      <c r="AI29">
+        <v>46</v>
+      </c>
+      <c r="AJ29">
+        <v>48</v>
+      </c>
+      <c r="AK29">
+        <v>34</v>
+      </c>
+      <c r="AL29">
+        <v>46</v>
+      </c>
+      <c r="AM29">
+        <v>95</v>
+      </c>
+      <c r="AN29">
+        <v>26</v>
+      </c>
+      <c r="AO29">
+        <v>27</v>
+      </c>
+      <c r="AP29">
         <v>14</v>
       </c>
-      <c r="AD29">
-        <v>970</v>
-      </c>
-      <c r="AE29">
-        <v>200</v>
-      </c>
-      <c r="AF29">
-        <v>80</v>
-      </c>
-      <c r="AG29">
-        <v>970</v>
-      </c>
-      <c r="AH29">
-        <v>60</v>
-      </c>
-      <c r="AI29">
-        <v>260</v>
-      </c>
-      <c r="AJ29">
-        <v>900</v>
-      </c>
-      <c r="AK29">
-        <v>180</v>
-      </c>
-      <c r="AL29">
-        <v>260</v>
-      </c>
-      <c r="AM29">
-        <v>580</v>
-      </c>
-      <c r="AN29">
-        <v>1000</v>
-      </c>
-      <c r="AO29">
-        <v>1000</v>
-      </c>
-      <c r="AP29">
-        <v>1.66</v>
-      </c>
       <c r="AQ29">
-        <v>1.53</v>
+        <v>11</v>
       </c>
       <c r="AR29">
-        <v>1.63</v>
+        <v>17</v>
       </c>
       <c r="AS29">
-        <v>1.65</v>
+        <v>4.6</v>
       </c>
       <c r="AT29">
-        <v>1.53</v>
+        <v>10.5</v>
       </c>
       <c r="AU29">
-        <v>1.45</v>
+        <v>7.2</v>
       </c>
       <c r="AV29">
-        <v>1.52</v>
+        <v>11</v>
       </c>
       <c r="AW29">
-        <v>1.65</v>
+        <v>21</v>
       </c>
       <c r="AX29">
-        <v>1.63</v>
+        <v>16</v>
       </c>
       <c r="AY29">
-        <v>1.52</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>1.56</v>
+        <v>14</v>
       </c>
       <c r="BA29">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="BB29">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="BC29">
-        <v>1.65</v>
+        <v>20</v>
       </c>
       <c r="BD29">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="BE29">
-        <v>1.65</v>
+        <v>4.8</v>
       </c>
       <c r="BF29">
-        <v>1.66</v>
+        <v>18.5</v>
       </c>
       <c r="BG29">
-        <v>1.66</v>
+        <v>19</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7998,7 +7998,7 @@
         <v>2.54</v>
       </c>
       <c r="G30">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H30">
         <v>2.6</v>
@@ -8007,7 +8007,7 @@
         <v>2.72</v>
       </c>
       <c r="J30">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
         <v>4.2</v>
@@ -8031,10 +8031,10 @@
         <v>1.5</v>
       </c>
       <c r="R30">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S30">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="T30">
         <v>1.48</v>
@@ -8076,7 +8076,7 @@
         <v>26</v>
       </c>
       <c r="AG30">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
         <v>15.5</v>
@@ -8097,7 +8097,7 @@
         <v>50</v>
       </c>
       <c r="AN30">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO30">
         <v>13</v>
@@ -8249,7 +8249,7 @@
         <v>2.92</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K31">
         <v>3.85</v>
@@ -8273,16 +8273,16 @@
         <v>1.86</v>
       </c>
       <c r="R31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
         <v>3.1</v>
       </c>
       <c r="T31">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U31">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
         <v>1.52</v>
@@ -8345,37 +8345,37 @@
         <v>25</v>
       </c>
       <c r="AP31">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AR31">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AS31">
         <v>8.800000000000001</v>
       </c>
       <c r="AT31">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV31">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AW31">
         <v>8</v>
       </c>
       <c r="AX31">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AY31">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ31">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BA31">
         <v>8.6</v>
@@ -8384,7 +8384,7 @@
         <v>8.6</v>
       </c>
       <c r="BC31">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BD31">
         <v>8.4</v>
@@ -8482,16 +8482,16 @@
         <v>1.69</v>
       </c>
       <c r="G32">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I32">
         <v>5.5</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K32">
         <v>4.4</v>
@@ -8506,19 +8506,19 @@
         <v>4.4</v>
       </c>
       <c r="O32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P32">
         <v>2.18</v>
       </c>
       <c r="Q32">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R32">
         <v>1.46</v>
       </c>
       <c r="S32">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T32">
         <v>1.76</v>
@@ -8584,7 +8584,7 @@
         <v>9</v>
       </c>
       <c r="AO32">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AP32">
         <v>16</v>
@@ -8596,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="AS32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT32">
         <v>8.800000000000001</v>
@@ -8608,7 +8608,7 @@
         <v>17</v>
       </c>
       <c r="AW32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX32">
         <v>10</v>
@@ -8724,7 +8724,7 @@
         <v>3.15</v>
       </c>
       <c r="G33">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H33">
         <v>2.1</v>
@@ -8745,31 +8745,31 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="O33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P33">
         <v>3</v>
       </c>
       <c r="Q33">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R33">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S33">
         <v>2</v>
       </c>
       <c r="T33">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="U33">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="V33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W33">
         <v>1.42</v>
@@ -8778,16 +8778,16 @@
         <v>1000</v>
       </c>
       <c r="Y33">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Z33">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA33">
         <v>140</v>
       </c>
       <c r="AB33">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC33">
         <v>19</v>
@@ -8796,7 +8796,7 @@
         <v>970</v>
       </c>
       <c r="AE33">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF33">
         <v>95</v>
@@ -8829,19 +8829,19 @@
         <v>55</v>
       </c>
       <c r="AP33">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ33">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AR33">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AS33">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AT33">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AU33">
         <v>5.8</v>
@@ -8850,34 +8850,34 @@
         <v>6.4</v>
       </c>
       <c r="AW33">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AX33">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AY33">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="AZ33">
         <v>7.6</v>
       </c>
       <c r="BA33">
-        <v>1.67</v>
+        <v>18.5</v>
       </c>
       <c r="BB33">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="BC33">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="BD33">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="BE33">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="BF33">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="BG33">
         <v>2.26</v>
@@ -8978,7 +8978,7 @@
         <v>3.2</v>
       </c>
       <c r="K34">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -8990,13 +8990,13 @@
         <v>3.15</v>
       </c>
       <c r="O34">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P34">
         <v>1.75</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
         <v>1.27</v>
@@ -9065,7 +9065,7 @@
         <v>580</v>
       </c>
       <c r="AN34">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO34">
         <v>46</v>
@@ -9217,7 +9217,7 @@
         <v>2.66</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K35">
         <v>4</v>
@@ -9232,7 +9232,7 @@
         <v>3.2</v>
       </c>
       <c r="O35">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P35">
         <v>1.71</v>
@@ -9265,7 +9265,7 @@
         <v>970</v>
       </c>
       <c r="Z35">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA35">
         <v>900</v>
@@ -9283,7 +9283,7 @@
         <v>160</v>
       </c>
       <c r="AF35">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG35">
         <v>27</v>
@@ -9304,7 +9304,7 @@
         <v>270</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN35">
         <v>1000</v>
@@ -9313,16 +9313,16 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AQ35">
         <v>6.8</v>
       </c>
       <c r="AR35">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AS35">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AT35">
         <v>7.8</v>
@@ -9334,37 +9334,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW35">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AX35">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AY35">
         <v>8.4</v>
       </c>
       <c r="AZ35">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BA35">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BB35">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BC35">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BD35">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BE35">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BF35">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BG35">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
         <v>2.92</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9480,7 +9480,7 @@
         <v>1.37</v>
       </c>
       <c r="Q36">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
         <v>1.08</v>
@@ -9495,64 +9495,64 @@
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W36">
         <v>1.35</v>
       </c>
       <c r="X36">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="Y36">
-        <v>14.5</v>
+        <v>500</v>
       </c>
       <c r="Z36">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA36">
         <v>900</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC36">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD36">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE36">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI36">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ36">
         <v>900</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO36">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP36">
         <v>4.9</v>
@@ -9561,46 +9561,46 @@
         <v>4.4</v>
       </c>
       <c r="AR36">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AS36">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AT36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AU36">
         <v>4.2</v>
       </c>
       <c r="AV36">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AW36">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AX36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AY36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AZ36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="BA36">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="BB36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="BC36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="BD36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="BE36">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="BF36">
         <v>1.55</v>
@@ -9689,7 +9689,7 @@
         <v>197</v>
       </c>
       <c r="F37">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G37">
         <v>1.97</v>
@@ -9698,7 +9698,7 @@
         <v>4.7</v>
       </c>
       <c r="I37">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J37">
         <v>3.25</v>
@@ -9737,7 +9737,7 @@
         <v>1.71</v>
       </c>
       <c r="V37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W37">
         <v>2.04</v>
@@ -9931,16 +9931,16 @@
         <v>198</v>
       </c>
       <c r="F38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G38">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H38">
         <v>6.6</v>
       </c>
       <c r="I38">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J38">
         <v>4.2</v>
@@ -9958,22 +9958,22 @@
         <v>4.2</v>
       </c>
       <c r="O38">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P38">
         <v>2.08</v>
       </c>
       <c r="Q38">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S38">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U38">
         <v>2</v>
@@ -9982,7 +9982,7 @@
         <v>1.16</v>
       </c>
       <c r="W38">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X38">
         <v>17</v>
@@ -10000,7 +10000,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD38">
         <v>27</v>
@@ -10018,22 +10018,22 @@
         <v>23</v>
       </c>
       <c r="AI38">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="AJ38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK38">
         <v>17.5</v>
       </c>
       <c r="AL38">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM38">
         <v>700</v>
       </c>
       <c r="AN38">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AO38">
         <v>700</v>
@@ -10045,13 +10045,13 @@
         <v>19.5</v>
       </c>
       <c r="AR38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS38">
         <v>11</v>
       </c>
       <c r="AT38">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU38">
         <v>8.6</v>
@@ -10063,16 +10063,16 @@
         <v>10.5</v>
       </c>
       <c r="AX38">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY38">
         <v>9</v>
       </c>
       <c r="AZ38">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB38">
         <v>13</v>
@@ -10081,34 +10081,34 @@
         <v>14.5</v>
       </c>
       <c r="BD38">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF38">
         <v>7.6</v>
       </c>
       <c r="BG38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH38">
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BJ38">
         <v>1000</v>
       </c>
       <c r="BK38">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BN38">
         <v>1000</v>
@@ -10120,37 +10120,37 @@
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BT38">
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="CB38" t="s">
         <v>203</v>
@@ -10173,46 +10173,46 @@
         <v>199</v>
       </c>
       <c r="F39">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>110</v>
+        <v>2.4</v>
       </c>
       <c r="H39">
-        <v>1.12</v>
+        <v>3.75</v>
       </c>
       <c r="I39">
-        <v>110</v>
+        <v>5.3</v>
       </c>
       <c r="J39">
-        <v>1.15</v>
+        <v>2.72</v>
       </c>
       <c r="K39">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N39">
-        <v>1.07</v>
+        <v>2.48</v>
       </c>
       <c r="O39">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P39">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="Q39">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="R39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S39">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10221,10 +10221,10 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10338,7 +10338,7 @@
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ39">
         <v>1000</v>
@@ -10356,7 +10356,7 @@
         <v>1000</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP39">
         <v>1000</v>
@@ -10415,25 +10415,25 @@
         <v>200</v>
       </c>
       <c r="F40">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="G40">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="I40">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K40">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M40">
         <v>1.05</v>
@@ -10445,28 +10445,28 @@
         <v>1.25</v>
       </c>
       <c r="P40">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q40">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R40">
         <v>1.48</v>
       </c>
       <c r="S40">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T40">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U40">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W40">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="X40">
         <v>23</v>
@@ -10487,13 +10487,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE40">
         <v>29</v>
       </c>
       <c r="AF40">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG40">
         <v>16.5</v>
@@ -10505,52 +10505,52 @@
         <v>40</v>
       </c>
       <c r="AJ40">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK40">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM40">
         <v>85</v>
       </c>
       <c r="AN40">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO40">
         <v>18.5</v>
       </c>
       <c r="AP40">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ40">
         <v>11</v>
       </c>
       <c r="AR40">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS40">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT40">
         <v>12.5</v>
       </c>
       <c r="AU40">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV40">
         <v>10</v>
       </c>
       <c r="AW40">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX40">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY40">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ40">
         <v>13.5</v>
@@ -10562,7 +10562,7 @@
         <v>1.03</v>
       </c>
       <c r="BC40">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD40">
         <v>1.03</v>
@@ -10574,7 +10574,7 @@
         <v>18.5</v>
       </c>
       <c r="BG40">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10669,13 +10669,13 @@
         <v>3.2</v>
       </c>
       <c r="J41">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K41">
         <v>3.15</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M41">
         <v>1.12</v>
@@ -10684,25 +10684,25 @@
         <v>2.72</v>
       </c>
       <c r="O41">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P41">
         <v>1.58</v>
       </c>
       <c r="Q41">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
         <v>1.21</v>
       </c>
       <c r="S41">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T41">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U41">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V41">
         <v>1.45</v>
@@ -10711,25 +10711,25 @@
         <v>1.53</v>
       </c>
       <c r="X41">
+        <v>9</v>
+      </c>
+      <c r="Y41">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y41">
-        <v>9.4</v>
-      </c>
       <c r="Z41">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA41">
         <v>70</v>
       </c>
       <c r="AB41">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD41">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE41">
         <v>55</v>
@@ -10741,10 +10741,10 @@
         <v>13.5</v>
       </c>
       <c r="AH41">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI41">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ41">
         <v>60</v>
@@ -10762,7 +10762,7 @@
         <v>55</v>
       </c>
       <c r="AO41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP41">
         <v>8</v>
@@ -10774,7 +10774,7 @@
         <v>17</v>
       </c>
       <c r="AS41">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT41">
         <v>7.6</v>
@@ -10786,7 +10786,7 @@
         <v>12.5</v>
       </c>
       <c r="AW41">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX41">
         <v>14.5</v>
@@ -10795,28 +10795,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ41">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BA41">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BB41">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BC41">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD41">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BE41">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BF41">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BG41">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10899,10 +10899,10 @@
         <v>202</v>
       </c>
       <c r="F42">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G42">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H42">
         <v>6.4</v>
@@ -10911,10 +10911,10 @@
         <v>7</v>
       </c>
       <c r="J42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L42">
         <v>1.42</v>
@@ -10932,7 +10932,7 @@
         <v>1.76</v>
       </c>
       <c r="Q42">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R42">
         <v>1.28</v>
@@ -10941,55 +10941,55 @@
         <v>4.1</v>
       </c>
       <c r="T42">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U42">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W42">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X42">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y42">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z42">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA42">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC42">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE42">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF42">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG42">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH42">
         <v>29</v>
       </c>
       <c r="AI42">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ42">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AK42">
         <v>25</v>
@@ -10998,67 +10998,67 @@
         <v>55</v>
       </c>
       <c r="AM42">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN42">
         <v>13</v>
       </c>
       <c r="AO42">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AP42">
         <v>10</v>
       </c>
       <c r="AQ42">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR42">
+        <v>7.6</v>
+      </c>
+      <c r="AS42">
+        <v>8.4</v>
+      </c>
+      <c r="AT42">
+        <v>6.4</v>
+      </c>
+      <c r="AU42">
+        <v>7.4</v>
+      </c>
+      <c r="AV42">
+        <v>20</v>
+      </c>
+      <c r="AW42">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS42">
-        <v>9</v>
-      </c>
-      <c r="AT42">
-        <v>6.2</v>
-      </c>
-      <c r="AU42">
-        <v>8</v>
-      </c>
-      <c r="AV42">
-        <v>22</v>
-      </c>
-      <c r="AW42">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AX42">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY42">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ42">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BA42">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB42">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC42">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD42">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE42">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF42">
         <v>11</v>
       </c>
       <c r="BG42">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11070,7 +11070,7 @@
         <v>1000</v>
       </c>
       <c r="BK42">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11088,7 +11088,7 @@
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BR42">
         <v>1000</v>
@@ -11100,7 +11100,7 @@
         <v>1000</v>
       </c>
       <c r="BU42">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BV42">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -577,7 +577,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-25 02:45:47</t>
+    <t>2026-09-25 03:59:38</t>
   </si>
 </sst>
 </file>
@@ -1174,10 +1174,10 @@
         <v>3.15</v>
       </c>
       <c r="G2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
         <v>2.38</v>
@@ -1186,43 +1186,43 @@
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V2">
         <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X2">
         <v>18</v>
@@ -1276,10 +1276,10 @@
         <v>28</v>
       </c>
       <c r="AO2">
+        <v>970</v>
+      </c>
+      <c r="AP2">
         <v>16</v>
-      </c>
-      <c r="AP2">
-        <v>15</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1288,16 +1288,16 @@
         <v>14</v>
       </c>
       <c r="AS2">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW2">
         <v>20</v>
@@ -1315,7 +1315,7 @@
         <v>18</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
         <v>16</v>
@@ -1324,16 +1324,16 @@
         <v>18.5</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG2">
         <v>13</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
         <v>3.4</v>
@@ -1342,55 +1342,55 @@
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
         <v>5.5</v>
       </c>
       <c r="BU2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>22</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1416,7 +1416,7 @@
         <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H3">
         <v>3.35</v>
@@ -1425,7 +1425,7 @@
         <v>3.7</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1443,16 +1443,16 @@
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T3">
         <v>1.83</v>
@@ -1464,16 +1464,16 @@
         <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X3">
         <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA3">
         <v>90</v>
@@ -1521,7 +1521,7 @@
         <v>65</v>
       </c>
       <c r="AP3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3">
         <v>3.5</v>
@@ -1530,28 +1530,28 @@
         <v>4</v>
       </c>
       <c r="AS3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AU3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AV3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AW3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AY3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BA3">
         <v>4.3</v>
@@ -1560,19 +1560,19 @@
         <v>4.1</v>
       </c>
       <c r="BC3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH3">
         <v>3.6</v>
@@ -1673,19 +1673,19 @@
         <v>3.8</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>1.96</v>
@@ -1694,7 +1694,7 @@
         <v>1.31</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
         <v>1.74</v>
@@ -1766,7 +1766,7 @@
         <v>4.6</v>
       </c>
       <c r="AQ4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR4">
         <v>5.4</v>
@@ -1775,13 +1775,13 @@
         <v>6</v>
       </c>
       <c r="AT4">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW4">
         <v>5.8</v>
@@ -1793,13 +1793,13 @@
         <v>4.5</v>
       </c>
       <c r="AZ4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA4">
         <v>6</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC4">
         <v>5.5</v>
@@ -1811,16 +1811,16 @@
         <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BG4">
         <v>5.8</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>10</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4">
         <v>5.6</v>
@@ -1841,7 +1841,7 @@
         <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4">
         <v>6.6</v>
@@ -1850,31 +1850,31 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
+        <v>7.2</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>8</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>7.4</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>2.42</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>7.6</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,19 +1897,19 @@
         <v>154</v>
       </c>
       <c r="F5">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -1939,28 +1939,28 @@
         <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U5">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
         <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
         <v>23</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB5">
         <v>15.5</v>
@@ -1969,16 +1969,16 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>34</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>16</v>
@@ -1987,19 +1987,19 @@
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL5">
         <v>38</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO5">
         <v>23</v>
@@ -2008,13 +2008,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT5">
         <v>12</v>
@@ -2026,10 +2026,10 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -2038,16 +2038,16 @@
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE5">
         <v>46</v>
@@ -2139,25 +2139,25 @@
         <v>155</v>
       </c>
       <c r="F6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I6">
         <v>4.8</v>
       </c>
       <c r="J6">
+        <v>3.65</v>
+      </c>
+      <c r="K6">
         <v>3.7</v>
       </c>
-      <c r="K6">
-        <v>3.75</v>
-      </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -2169,13 +2169,13 @@
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
         <v>2.16</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
         <v>4</v>
@@ -2187,10 +2187,10 @@
         <v>1.99</v>
       </c>
       <c r="V6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X6">
         <v>12.5</v>
@@ -2223,7 +2223,7 @@
         <v>9.6</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>75</v>
@@ -2232,7 +2232,7 @@
         <v>22</v>
       </c>
       <c r="AK6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6">
         <v>40</v>
@@ -2271,13 +2271,13 @@
         <v>55</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY6">
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
         <v>65</v>
@@ -2286,7 +2286,7 @@
         <v>21</v>
       </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD6">
         <v>38</v>
@@ -2298,67 +2298,67 @@
         <v>14.5</v>
       </c>
       <c r="BG6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
         <v>7.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN6">
         <v>4.4</v>
       </c>
       <c r="BO6">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>32</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU6">
         <v>7</v>
       </c>
       <c r="BV6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6">
         <v>29</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,10 +2381,10 @@
         <v>156</v>
       </c>
       <c r="F7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G7">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H7">
         <v>4.8</v>
@@ -2405,7 +2405,7 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>1.41</v>
@@ -2420,7 +2420,7 @@
         <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
         <v>2.04</v>
@@ -2429,10 +2429,10 @@
         <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X7">
         <v>11.5</v>
@@ -2441,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2468,10 +2468,10 @@
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
         <v>23</v>
@@ -2480,10 +2480,10 @@
         <v>44</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO7">
         <v>100</v>
@@ -2519,22 +2519,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB7">
         <v>20</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF7">
         <v>15</v>
@@ -2543,16 +2543,16 @@
         <v>80</v>
       </c>
       <c r="BH7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
         <v>2.84</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL7">
         <v>170</v>
@@ -2564,43 +2564,43 @@
         <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP7">
         <v>14</v>
       </c>
       <c r="BQ7">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>8</v>
       </c>
       <c r="BU7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV7">
         <v>46</v>
       </c>
       <c r="BW7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX7">
         <v>60</v>
       </c>
       <c r="BY7">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2623,64 +2623,64 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="G8">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="H8">
+        <v>6.2</v>
+      </c>
+      <c r="I8">
+        <v>7.8</v>
+      </c>
+      <c r="J8">
+        <v>4.7</v>
+      </c>
+      <c r="K8">
+        <v>5.2</v>
+      </c>
+      <c r="L8">
+        <v>1.28</v>
+      </c>
+      <c r="M8">
+        <v>1.04</v>
+      </c>
+      <c r="N8">
         <v>5.4</v>
-      </c>
-      <c r="I8">
-        <v>6.6</v>
-      </c>
-      <c r="J8">
-        <v>4.3</v>
-      </c>
-      <c r="K8">
-        <v>5.1</v>
-      </c>
-      <c r="L8">
-        <v>1.29</v>
-      </c>
-      <c r="M8">
-        <v>1.03</v>
-      </c>
-      <c r="N8">
-        <v>5.2</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
+        <v>2.52</v>
+      </c>
+      <c r="Q8">
+        <v>1.58</v>
+      </c>
+      <c r="R8">
+        <v>1.62</v>
+      </c>
+      <c r="S8">
         <v>2.48</v>
       </c>
-      <c r="Q8">
-        <v>1.6</v>
-      </c>
-      <c r="R8">
-        <v>1.58</v>
-      </c>
-      <c r="S8">
-        <v>2.5</v>
-      </c>
       <c r="T8">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U8">
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y8">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="Z8">
         <v>500</v>
@@ -2692,109 +2692,109 @@
         <v>12</v>
       </c>
       <c r="AC8">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE8">
         <v>500</v>
       </c>
       <c r="AF8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO8">
         <v>500</v>
       </c>
       <c r="AP8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ8">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AR8">
+        <v>7</v>
+      </c>
+      <c r="AS8">
+        <v>7.6</v>
+      </c>
+      <c r="AT8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>10</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8">
         <v>7.2</v>
       </c>
-      <c r="AS8">
-        <v>7.8</v>
-      </c>
-      <c r="AT8">
-        <v>9.6</v>
-      </c>
-      <c r="AU8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8">
-        <v>19</v>
-      </c>
-      <c r="AW8">
-        <v>7.4</v>
-      </c>
       <c r="AX8">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BE8">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF8">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2803,28 +2803,28 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2833,13 +2833,13 @@
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -2865,64 +2865,64 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="G9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H9">
         <v>10.5</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="L9">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M9">
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P9">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S9">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="T9">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.08</v>
       </c>
       <c r="W9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Y9">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Z9">
         <v>140</v>
@@ -2931,10 +2931,10 @@
         <v>380</v>
       </c>
       <c r="AB9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AC9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AD9">
         <v>48</v>
@@ -2943,19 +2943,19 @@
         <v>150</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>27</v>
       </c>
       <c r="AI9">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK9">
         <v>14</v>
@@ -2964,19 +2964,19 @@
         <v>28</v>
       </c>
       <c r="AM9">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN9">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="AO9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR9">
         <v>9.4</v>
@@ -2991,10 +2991,10 @@
         <v>15.5</v>
       </c>
       <c r="AV9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -3021,52 +3021,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="BG9">
         <v>10.5</v>
       </c>
       <c r="BH9">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BI9">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BL9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
         <v>7.2</v>
       </c>
       <c r="BQ9">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BR9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BV9">
         <v>80</v>
@@ -3075,7 +3075,7 @@
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
@@ -3110,13 +3110,13 @@
         <v>5.6</v>
       </c>
       <c r="G10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J10">
         <v>4.4</v>
@@ -3149,16 +3149,16 @@
         <v>2.62</v>
       </c>
       <c r="T10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
         <v>2.16</v>
       </c>
       <c r="V10">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="W10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
         <v>26</v>
@@ -3167,19 +3167,19 @@
         <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB10">
         <v>26</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE10">
         <v>16.5</v>
@@ -3197,7 +3197,7 @@
         <v>32</v>
       </c>
       <c r="AJ10">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AK10">
         <v>190</v>
@@ -3218,64 +3218,64 @@
         <v>17</v>
       </c>
       <c r="AQ10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10">
         <v>20</v>
       </c>
       <c r="AU10">
+        <v>9.4</v>
+      </c>
+      <c r="AV10">
+        <v>9</v>
+      </c>
+      <c r="AW10">
+        <v>13.5</v>
+      </c>
+      <c r="AX10">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV10">
-        <v>7.8</v>
-      </c>
-      <c r="AW10">
-        <v>12</v>
-      </c>
-      <c r="AX10">
+      <c r="AY10">
+        <v>6.8</v>
+      </c>
+      <c r="AZ10">
+        <v>16.5</v>
+      </c>
+      <c r="BA10">
         <v>7.4</v>
       </c>
-      <c r="AY10">
-        <v>6.2</v>
-      </c>
-      <c r="AZ10">
-        <v>14.5</v>
-      </c>
-      <c r="BA10">
-        <v>6.8</v>
-      </c>
       <c r="BB10">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD10">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG10">
         <v>6</v>
       </c>
       <c r="BH10">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
@@ -3287,43 +3287,43 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
         <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3349,10 +3349,10 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H11">
         <v>2.36</v>
@@ -3382,7 +3382,7 @@
         <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R11">
         <v>1.48</v>
@@ -3391,16 +3391,16 @@
         <v>2.96</v>
       </c>
       <c r="T11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
         <v>1.69</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X11">
         <v>18.5</v>
@@ -3409,7 +3409,7 @@
         <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA11">
         <v>32</v>
@@ -3418,7 +3418,7 @@
         <v>15</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
         <v>12</v>
@@ -3433,13 +3433,13 @@
         <v>14</v>
       </c>
       <c r="AH11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI11">
         <v>34</v>
       </c>
       <c r="AJ11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK11">
         <v>34</v>
@@ -3490,7 +3490,7 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB11">
         <v>34</v>
@@ -3499,7 +3499,7 @@
         <v>25</v>
       </c>
       <c r="BD11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE11">
         <v>55</v>
@@ -3514,61 +3514,61 @@
         <v>3.85</v>
       </c>
       <c r="BI11">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11">
         <v>9</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN11">
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP11">
         <v>23</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR11">
         <v>32</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11">
         <v>5.6</v>
       </c>
       <c r="BU11">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV11">
         <v>17</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
         <v>27</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11">
         <v>21</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="s">
         <v>187</v>
@@ -3591,10 +3591,10 @@
         <v>161</v>
       </c>
       <c r="F12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
         <v>6.4</v>
@@ -3603,7 +3603,7 @@
         <v>6.6</v>
       </c>
       <c r="J12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
         <v>4.7</v>
@@ -3615,34 +3615,34 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O12">
         <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R12">
         <v>1.57</v>
       </c>
       <c r="S12">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T12">
         <v>1.77</v>
       </c>
       <c r="U12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V12">
         <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X12">
         <v>22</v>
@@ -3663,16 +3663,16 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE12">
         <v>80</v>
       </c>
       <c r="AF12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH12">
         <v>19</v>
@@ -3696,10 +3696,10 @@
         <v>6.8</v>
       </c>
       <c r="AO12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
         <v>24</v>
@@ -3708,7 +3708,7 @@
         <v>48</v>
       </c>
       <c r="AS12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT12">
         <v>9.800000000000001</v>
@@ -3720,7 +3720,7 @@
         <v>21</v>
       </c>
       <c r="AW12">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AX12">
         <v>9.800000000000001</v>
@@ -3741,28 +3741,28 @@
         <v>14</v>
       </c>
       <c r="BD12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF12">
         <v>6.2</v>
       </c>
       <c r="BG12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ12">
         <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12">
         <v>110</v>
@@ -3780,7 +3780,7 @@
         <v>9.6</v>
       </c>
       <c r="BQ12">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
         <v>23</v>
@@ -3792,7 +3792,7 @@
         <v>10</v>
       </c>
       <c r="BU12">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV12">
         <v>50</v>
@@ -3833,16 +3833,16 @@
         <v>162</v>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G13">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I13">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -3851,67 +3851,67 @@
         <v>5.1</v>
       </c>
       <c r="L13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
         <v>2.44</v>
       </c>
       <c r="Q13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R13">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T13">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X13">
         <v>22</v>
       </c>
       <c r="Y13">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA13">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AB13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>11</v>
       </c>
       <c r="AD13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE13">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG13">
         <v>9.6</v>
@@ -3920,10 +3920,10 @@
         <v>22</v>
       </c>
       <c r="AI13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK13">
         <v>14.5</v>
@@ -3935,37 +3935,37 @@
         <v>110</v>
       </c>
       <c r="AN13">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO13">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AP13">
         <v>20</v>
       </c>
       <c r="AQ13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR13">
         <v>55</v>
       </c>
       <c r="AS13">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU13">
         <v>10</v>
       </c>
       <c r="AV13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW13">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AX13">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY13">
         <v>9.199999999999999</v>
@@ -3974,85 +3974,85 @@
         <v>20</v>
       </c>
       <c r="BA13">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
       </c>
       <c r="BC13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE13">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF13">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BG13">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BH13">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BI13">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK13">
-        <v>2.18</v>
+        <v>9.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM13">
-        <v>2.46</v>
+        <v>50</v>
       </c>
       <c r="BN13">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BO13">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ13">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS13">
-        <v>2.42</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW13">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY13">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA13">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="s">
         <v>187</v>
@@ -4075,55 +4075,55 @@
         <v>163</v>
       </c>
       <c r="F14">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="I14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="J14">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M14">
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -4132,73 +4132,73 @@
         <v>36</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
         <v>11.5</v>
       </c>
       <c r="AA14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB14">
         <v>46</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE14">
         <v>13</v>
       </c>
       <c r="AF14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG14">
         <v>30</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI14">
         <v>26</v>
       </c>
       <c r="AJ14">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AK14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL14">
         <v>80</v>
       </c>
       <c r="AM14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO14">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AP14">
         <v>32</v>
       </c>
       <c r="AQ14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR14">
         <v>10.5</v>
       </c>
       <c r="AS14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV14">
         <v>10</v>
@@ -4207,88 +4207,88 @@
         <v>12</v>
       </c>
       <c r="AX14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AY14">
         <v>29</v>
       </c>
       <c r="AZ14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="BC14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BD14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BE14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BG14">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BH14">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM14">
         <v>13</v>
       </c>
       <c r="BN14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BO14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BP14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BQ14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR14">
         <v>55</v>
       </c>
       <c r="BS14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BY14">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4320,13 +4320,13 @@
         <v>1.85</v>
       </c>
       <c r="G15">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15">
         <v>3.75</v>
@@ -4335,7 +4335,7 @@
         <v>3.8</v>
       </c>
       <c r="L15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M15">
         <v>1.08</v>
@@ -4347,28 +4347,28 @@
         <v>1.37</v>
       </c>
       <c r="P15">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q15">
         <v>2.1</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
         <v>3.9</v>
       </c>
       <c r="T15">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X15">
         <v>13</v>
@@ -4380,19 +4380,19 @@
         <v>38</v>
       </c>
       <c r="AA15">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB15">
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF15">
         <v>10.5</v>
@@ -4401,22 +4401,22 @@
         <v>9.6</v>
       </c>
       <c r="AH15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15">
         <v>40</v>
       </c>
       <c r="AM15">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN15">
         <v>14</v>
@@ -4431,112 +4431,112 @@
         <v>14.5</v>
       </c>
       <c r="AR15">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AS15">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="AT15">
         <v>7.4</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15">
         <v>60</v>
       </c>
       <c r="AX15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB15">
         <v>18.5</v>
       </c>
       <c r="BC15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD15">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE15">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH15">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI15">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>2.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM15">
-        <v>2.82</v>
+        <v>17.5</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO15">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ15">
-        <v>2.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU15">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW15">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY15">
-        <v>2.8</v>
+        <v>14</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA15">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
         <v>187</v>
@@ -4559,25 +4559,25 @@
         <v>165</v>
       </c>
       <c r="F16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G16">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H16">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I16">
         <v>3.4</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M16">
         <v>1.05</v>
@@ -4595,10 +4595,10 @@
         <v>1.75</v>
       </c>
       <c r="R16">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T16">
         <v>1.62</v>
@@ -4610,7 +4610,7 @@
         <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X16">
         <v>18</v>
@@ -4619,7 +4619,7 @@
         <v>16.5</v>
       </c>
       <c r="Z16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA16">
         <v>55</v>
@@ -4628,10 +4628,10 @@
         <v>13</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
         <v>34</v>
@@ -4655,25 +4655,25 @@
         <v>22</v>
       </c>
       <c r="AL16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM16">
         <v>65</v>
       </c>
       <c r="AN16">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16">
         <v>15.5</v>
       </c>
       <c r="AR16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS16">
         <v>50</v>
@@ -4682,7 +4682,7 @@
         <v>12</v>
       </c>
       <c r="AU16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16">
         <v>13</v>
@@ -4700,61 +4700,61 @@
         <v>14</v>
       </c>
       <c r="BA16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE16">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ16">
         <v>8.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL16">
         <v>110</v>
       </c>
       <c r="BM16">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP16">
         <v>16</v>
       </c>
       <c r="BQ16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR16">
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BT16">
         <v>6.6</v>
@@ -4766,19 +4766,19 @@
         <v>24</v>
       </c>
       <c r="BW16">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BY16">
         <v>11</v>
       </c>
       <c r="BZ16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA16">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB16" t="s">
         <v>187</v>
@@ -4801,7 +4801,7 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G17">
         <v>2.42</v>
@@ -4819,7 +4819,7 @@
         <v>3.4</v>
       </c>
       <c r="L17">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M17">
         <v>1.08</v>
@@ -4828,7 +4828,7 @@
         <v>3.5</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
         <v>1.83</v>
@@ -4843,10 +4843,10 @@
         <v>4</v>
       </c>
       <c r="T17">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V17">
         <v>1.4</v>
@@ -4855,7 +4855,7 @@
         <v>1.7</v>
       </c>
       <c r="X17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y17">
         <v>12</v>
@@ -4870,13 +4870,13 @@
         <v>9.4</v>
       </c>
       <c r="AC17">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE17">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF17">
         <v>14.5</v>
@@ -4885,7 +4885,7 @@
         <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17">
         <v>55</v>
@@ -4906,7 +4906,7 @@
         <v>23</v>
       </c>
       <c r="AO17">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP17">
         <v>11</v>
@@ -4924,7 +4924,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17">
         <v>13</v>
@@ -4933,7 +4933,7 @@
         <v>38</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
         <v>10.5</v>
@@ -4945,16 +4945,16 @@
         <v>48</v>
       </c>
       <c r="BB17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD17">
         <v>38</v>
       </c>
       <c r="BE17">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="BF17">
         <v>20</v>
@@ -4972,7 +4972,7 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4981,46 +4981,46 @@
         <v>2.66</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO17">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>2.64</v>
+        <v>11</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5043,82 +5043,82 @@
         <v>167</v>
       </c>
       <c r="F18">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="G18">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="H18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W18">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="X18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z18">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA18">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB18">
         <v>8.4</v>
       </c>
       <c r="AC18">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD18">
         <v>23</v>
       </c>
       <c r="AE18">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AF18">
         <v>9.6</v>
@@ -5133,10 +5133,10 @@
         <v>85</v>
       </c>
       <c r="AJ18">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL18">
         <v>38</v>
@@ -5145,37 +5145,37 @@
         <v>130</v>
       </c>
       <c r="AN18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO18">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="AP18">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR18">
         <v>38</v>
       </c>
       <c r="AS18">
-        <v>19.5</v>
+        <v>110</v>
       </c>
       <c r="AT18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
         <v>19</v>
       </c>
       <c r="AW18">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AX18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY18">
         <v>9.4</v>
@@ -5184,85 +5184,85 @@
         <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="BB18">
+        <v>14.5</v>
+      </c>
+      <c r="BC18">
         <v>15.5</v>
-      </c>
-      <c r="BC18">
-        <v>16.5</v>
       </c>
       <c r="BD18">
         <v>32</v>
       </c>
       <c r="BE18">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="BF18">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG18">
-        <v>18.5</v>
+        <v>95</v>
       </c>
       <c r="BH18">
         <v>3.45</v>
       </c>
       <c r="BI18">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18">
         <v>11</v>
       </c>
       <c r="BK18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN18">
         <v>4.2</v>
       </c>
       <c r="BO18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP18">
         <v>11.5</v>
       </c>
       <c r="BQ18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR18">
         <v>28</v>
       </c>
       <c r="BS18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BU18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BV18">
         <v>55</v>
       </c>
       <c r="BW18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX18">
         <v>60</v>
       </c>
       <c r="BY18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA18">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5288,7 +5288,7 @@
         <v>1.38</v>
       </c>
       <c r="G19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H19">
         <v>11</v>
@@ -5297,10 +5297,10 @@
         <v>12</v>
       </c>
       <c r="J19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
         <v>1.37</v>
@@ -5336,7 +5336,7 @@
         <v>1.09</v>
       </c>
       <c r="W19">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X19">
         <v>21</v>
@@ -5399,10 +5399,10 @@
         <v>26</v>
       </c>
       <c r="AR19">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS19">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>16</v>
       </c>
       <c r="AW19">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX19">
         <v>7</v>
@@ -5426,7 +5426,7 @@
         <v>16</v>
       </c>
       <c r="BA19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB19">
         <v>9.800000000000001</v>
@@ -5527,10 +5527,10 @@
         <v>169</v>
       </c>
       <c r="F20">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H20">
         <v>5.1</v>
@@ -5542,7 +5542,7 @@
         <v>3.45</v>
       </c>
       <c r="K20">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
         <v>1.5</v>
@@ -5551,13 +5551,13 @@
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P20">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q20">
         <v>2.38</v>
@@ -5566,10 +5566,10 @@
         <v>1.25</v>
       </c>
       <c r="S20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T20">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U20">
         <v>1.81</v>
@@ -5587,7 +5587,7 @@
         <v>15.5</v>
       </c>
       <c r="Z20">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AA20">
         <v>700</v>
@@ -5623,13 +5623,13 @@
         <v>25</v>
       </c>
       <c r="AL20">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM20">
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO20">
         <v>700</v>
@@ -5641,10 +5641,10 @@
         <v>12.5</v>
       </c>
       <c r="AR20">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AS20">
-        <v>9.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="AT20">
         <v>6</v>
@@ -5656,7 +5656,7 @@
         <v>18.5</v>
       </c>
       <c r="AW20">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AX20">
         <v>8.800000000000001</v>
@@ -5668,7 +5668,7 @@
         <v>19.5</v>
       </c>
       <c r="BA20">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BB20">
         <v>18.5</v>
@@ -5677,16 +5677,16 @@
         <v>19.5</v>
       </c>
       <c r="BD20">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BE20">
-        <v>9.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BF20">
         <v>14.5</v>
       </c>
       <c r="BG20">
-        <v>9.6</v>
+        <v>80</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5769,25 +5769,25 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G21">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H21">
+        <v>2.92</v>
+      </c>
+      <c r="I21">
         <v>3.05</v>
       </c>
-      <c r="I21">
-        <v>3.2</v>
-      </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
         <v>3.6</v>
       </c>
       <c r="L21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M21">
         <v>1.07</v>
@@ -5796,10 +5796,10 @@
         <v>3.85</v>
       </c>
       <c r="O21">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q21">
         <v>1.98</v>
@@ -5817,19 +5817,19 @@
         <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X21">
         <v>17</v>
       </c>
       <c r="Y21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z21">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA21">
         <v>60</v>
@@ -5838,16 +5838,16 @@
         <v>11.5</v>
       </c>
       <c r="AC21">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE21">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF21">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG21">
         <v>12.5</v>
@@ -5856,139 +5856,139 @@
         <v>17.5</v>
       </c>
       <c r="AI21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ21">
         <v>40</v>
       </c>
       <c r="AK21">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL21">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM21">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO21">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP21">
         <v>12.5</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR21">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS21">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AT21">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU21">
         <v>7</v>
       </c>
       <c r="AV21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW21">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AX21">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY21">
         <v>10.5</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BB21">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BC21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BE21">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="BF21">
         <v>19</v>
       </c>
       <c r="BG21">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6011,52 +6011,52 @@
         <v>171</v>
       </c>
       <c r="F22">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G22">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H22">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I22">
         <v>2.74</v>
       </c>
       <c r="J22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L22">
         <v>1.35</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T22">
         <v>1.65</v>
       </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V22">
         <v>1.57</v>
@@ -6068,7 +6068,7 @@
         <v>22</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
         <v>21</v>
@@ -6104,22 +6104,22 @@
         <v>42</v>
       </c>
       <c r="AK22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL22">
         <v>36</v>
       </c>
       <c r="AM22">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AN22">
         <v>21</v>
       </c>
       <c r="AO22">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AP22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
         <v>12</v>
@@ -6155,7 +6155,7 @@
         <v>30</v>
       </c>
       <c r="BB22">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BC22">
         <v>24</v>
@@ -6173,64 +6173,64 @@
         <v>17</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI22">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK22">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO22">
-        <v>1.57</v>
+        <v>5.3</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU22">
-        <v>1.56</v>
+        <v>5.3</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6253,19 +6253,19 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G23">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H23">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I23">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
         <v>3.85</v>
@@ -6280,13 +6280,13 @@
         <v>4.2</v>
       </c>
       <c r="O23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P23">
         <v>2.08</v>
       </c>
       <c r="Q23">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R23">
         <v>1.42</v>
@@ -6298,13 +6298,13 @@
         <v>1.68</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X23">
         <v>20</v>
@@ -6319,7 +6319,7 @@
         <v>46</v>
       </c>
       <c r="AB23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC23">
         <v>8.6</v>
@@ -6334,7 +6334,7 @@
         <v>24</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH23">
         <v>16.5</v>
@@ -6343,19 +6343,19 @@
         <v>46</v>
       </c>
       <c r="AJ23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK23">
         <v>36</v>
       </c>
       <c r="AL23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM23">
         <v>95</v>
       </c>
       <c r="AN23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO23">
         <v>25</v>
@@ -6364,13 +6364,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR23">
         <v>16</v>
       </c>
       <c r="AS23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT23">
         <v>11</v>
@@ -6382,7 +6382,7 @@
         <v>10.5</v>
       </c>
       <c r="AW23">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AX23">
         <v>16.5</v>
@@ -6394,19 +6394,19 @@
         <v>14</v>
       </c>
       <c r="BA23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB23">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BC23">
         <v>21</v>
       </c>
       <c r="BD23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE23">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF23">
         <v>20</v>
@@ -6495,19 +6495,19 @@
         <v>173</v>
       </c>
       <c r="F24">
+        <v>2.56</v>
+      </c>
+      <c r="G24">
         <v>2.62</v>
       </c>
-      <c r="G24">
-        <v>2.7</v>
-      </c>
       <c r="H24">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>4.2</v>
@@ -6519,115 +6519,115 @@
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P24">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q24">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R24">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S24">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T24">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U24">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X24">
         <v>32</v>
       </c>
       <c r="Y24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z24">
         <v>26</v>
       </c>
       <c r="AA24">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC24">
         <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE24">
         <v>27</v>
       </c>
       <c r="AF24">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH24">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI24">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK24">
         <v>27</v>
       </c>
       <c r="AL24">
+        <v>38</v>
+      </c>
+      <c r="AM24">
         <v>48</v>
       </c>
-      <c r="AM24">
-        <v>50</v>
-      </c>
       <c r="AN24">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO24">
         <v>12.5</v>
       </c>
       <c r="AP24">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
         <v>17</v>
       </c>
       <c r="AR24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS24">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AT24">
         <v>16</v>
       </c>
       <c r="AU24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV24">
         <v>12</v>
       </c>
       <c r="AW24">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AX24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY24">
         <v>11.5</v>
@@ -6636,34 +6636,34 @@
         <v>11.5</v>
       </c>
       <c r="BA24">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BB24">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC24">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE24">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BF24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG24">
         <v>11</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK24">
         <v>1.01</v>
@@ -6675,31 +6675,31 @@
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ24">
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
@@ -6711,7 +6711,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
@@ -6737,16 +6737,16 @@
         <v>174</v>
       </c>
       <c r="F25">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="G25">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="H25">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="I25">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <v>3.55</v>
@@ -6782,13 +6782,13 @@
         <v>1.72</v>
       </c>
       <c r="U25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X25">
         <v>17</v>
@@ -6797,25 +6797,25 @@
         <v>13</v>
       </c>
       <c r="Z25">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA25">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB25">
         <v>12.5</v>
       </c>
       <c r="AC25">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE25">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF25">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG25">
         <v>13</v>
@@ -6824,133 +6824,133 @@
         <v>17</v>
       </c>
       <c r="AI25">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK25">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL25">
         <v>38</v>
       </c>
       <c r="AM25">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO25">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP25">
         <v>13.5</v>
       </c>
       <c r="AQ25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR25">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS25">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AT25">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25">
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AX25">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AY25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25">
+        <v>15</v>
+      </c>
+      <c r="BA25">
+        <v>28</v>
+      </c>
+      <c r="BB25">
+        <v>26</v>
+      </c>
+      <c r="BC25">
+        <v>21</v>
+      </c>
+      <c r="BD25">
+        <v>24</v>
+      </c>
+      <c r="BE25">
+        <v>42</v>
+      </c>
+      <c r="BF25">
         <v>14</v>
       </c>
-      <c r="BA25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC25">
-        <v>20</v>
-      </c>
-      <c r="BD25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE25">
-        <v>10</v>
-      </c>
-      <c r="BF25">
-        <v>7.4</v>
-      </c>
       <c r="BG25">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BH25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI25">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ25">
         <v>9.4</v>
       </c>
       <c r="BK25">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN25">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP25">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ25">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR25">
         <v>32</v>
       </c>
       <c r="BS25">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT25">
         <v>6.2</v>
       </c>
       <c r="BU25">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW25">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX25">
         <v>32</v>
       </c>
       <c r="BY25">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
         <v>1.25</v>
@@ -7012,7 +7012,7 @@
         <v>2.22</v>
       </c>
       <c r="Q26">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R26">
         <v>1.48</v>
@@ -7021,7 +7021,7 @@
         <v>2.94</v>
       </c>
       <c r="T26">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U26">
         <v>2.14</v>
@@ -7036,7 +7036,7 @@
         <v>19.5</v>
       </c>
       <c r="Y26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z26">
         <v>100</v>
@@ -7048,7 +7048,7 @@
         <v>10.5</v>
       </c>
       <c r="AC26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26">
         <v>21</v>
@@ -7063,7 +7063,7 @@
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI26">
         <v>250</v>
@@ -7075,16 +7075,16 @@
         <v>17.5</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AM26">
         <v>580</v>
       </c>
       <c r="AN26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO26">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP26">
         <v>16</v>
@@ -7093,22 +7093,22 @@
         <v>18</v>
       </c>
       <c r="AR26">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AS26">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="AT26">
         <v>9</v>
       </c>
       <c r="AU26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26">
         <v>18</v>
       </c>
       <c r="AW26">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AX26">
         <v>10</v>
@@ -7120,7 +7120,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BB26">
         <v>15</v>
@@ -7129,16 +7129,16 @@
         <v>15</v>
       </c>
       <c r="BD26">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BE26">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BF26">
         <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7251,10 +7251,10 @@
         <v>1.43</v>
       </c>
       <c r="P27">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R27">
         <v>1.27</v>
@@ -7281,10 +7281,10 @@
         <v>11.5</v>
       </c>
       <c r="Z27">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA27">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB27">
         <v>9</v>
@@ -7302,13 +7302,13 @@
         <v>15.5</v>
       </c>
       <c r="AG27">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH27">
         <v>21</v>
       </c>
       <c r="AI27">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AJ27">
         <v>38</v>
@@ -7317,28 +7317,28 @@
         <v>32</v>
       </c>
       <c r="AL27">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM27">
         <v>580</v>
       </c>
       <c r="AN27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO27">
         <v>90</v>
       </c>
       <c r="AP27">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27">
         <v>19</v>
       </c>
       <c r="AS27">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AT27">
         <v>7.8</v>
@@ -7347,7 +7347,7 @@
         <v>6.6</v>
       </c>
       <c r="AV27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW27">
         <v>36</v>
@@ -7362,43 +7362,43 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BB27">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BC27">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BD27">
         <v>38</v>
       </c>
       <c r="BE27">
-        <v>8.4</v>
+        <v>90</v>
       </c>
       <c r="BF27">
         <v>21</v>
       </c>
       <c r="BG27">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BN27">
         <v>1000</v>
@@ -7410,37 +7410,37 @@
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="CB27" t="s">
         <v>187</v>
@@ -7466,49 +7466,49 @@
         <v>3.2</v>
       </c>
       <c r="G28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H28">
         <v>2.08</v>
       </c>
       <c r="I28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J28">
         <v>4.3</v>
       </c>
       <c r="K28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L28">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M28">
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O28">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P28">
+        <v>3.35</v>
+      </c>
+      <c r="Q28">
+        <v>1.4</v>
+      </c>
+      <c r="R28">
+        <v>1.96</v>
+      </c>
+      <c r="S28">
+        <v>1.99</v>
+      </c>
+      <c r="T28">
+        <v>1.41</v>
+      </c>
+      <c r="U28">
         <v>3.25</v>
-      </c>
-      <c r="Q28">
-        <v>1.41</v>
-      </c>
-      <c r="R28">
-        <v>1.91</v>
-      </c>
-      <c r="S28">
-        <v>2.02</v>
-      </c>
-      <c r="T28">
-        <v>1.43</v>
-      </c>
-      <c r="U28">
-        <v>3.1</v>
       </c>
       <c r="V28">
         <v>1.87</v>
@@ -7529,7 +7529,7 @@
         <v>30</v>
       </c>
       <c r="AB28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC28">
         <v>12</v>
@@ -7559,22 +7559,22 @@
         <v>30</v>
       </c>
       <c r="AL28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM28">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN28">
         <v>15.5</v>
       </c>
       <c r="AO28">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ28">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR28">
         <v>17</v>
@@ -7595,7 +7595,7 @@
         <v>15.5</v>
       </c>
       <c r="AX28">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AY28">
         <v>13</v>
@@ -7607,7 +7607,7 @@
         <v>19.5</v>
       </c>
       <c r="BB28">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28">
         <v>21</v>
@@ -7616,13 +7616,13 @@
         <v>21</v>
       </c>
       <c r="BE28">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BF28">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG28">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7708,10 +7708,10 @@
         <v>2.62</v>
       </c>
       <c r="G29">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H29">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I29">
         <v>3.2</v>
@@ -7723,7 +7723,7 @@
         <v>3.35</v>
       </c>
       <c r="L29">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M29">
         <v>1.09</v>
@@ -7735,10 +7735,10 @@
         <v>1.4</v>
       </c>
       <c r="P29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
         <v>1.28</v>
@@ -7747,7 +7747,7 @@
         <v>4.2</v>
       </c>
       <c r="T29">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U29">
         <v>2</v>
@@ -7756,7 +7756,7 @@
         <v>1.45</v>
       </c>
       <c r="W29">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X29">
         <v>11.5</v>
@@ -7783,7 +7783,7 @@
         <v>40</v>
       </c>
       <c r="AF29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG29">
         <v>13</v>
@@ -7813,7 +7813,7 @@
         <v>42</v>
       </c>
       <c r="AP29">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ29">
         <v>10</v>
@@ -7822,16 +7822,16 @@
         <v>17</v>
       </c>
       <c r="AS29">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AT29">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU29">
         <v>6.8</v>
       </c>
       <c r="AV29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW29">
         <v>32</v>
@@ -7840,13 +7840,13 @@
         <v>13.5</v>
       </c>
       <c r="AY29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ29">
         <v>17</v>
       </c>
       <c r="BA29">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB29">
         <v>32</v>
@@ -7858,7 +7858,7 @@
         <v>40</v>
       </c>
       <c r="BE29">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BF29">
         <v>25</v>
@@ -7870,7 +7870,7 @@
         <v>3.15</v>
       </c>
       <c r="BI29">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ29">
         <v>10.5</v>
@@ -7915,7 +7915,7 @@
         <v>8.4</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY29">
         <v>9.6</v>
@@ -7950,19 +7950,19 @@
         <v>3.15</v>
       </c>
       <c r="G30">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I30">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
         <v>1.46</v>
@@ -7977,7 +7977,7 @@
         <v>1.39</v>
       </c>
       <c r="P30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -7989,184 +7989,184 @@
         <v>4.1</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X30">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y30">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z30">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="AA30">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB30">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AC30">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="AE30">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="AF30">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AG30">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AH30">
+        <v>19</v>
+      </c>
+      <c r="AI30">
+        <v>110</v>
+      </c>
+      <c r="AJ30">
+        <v>150</v>
+      </c>
+      <c r="AK30">
+        <v>100</v>
+      </c>
+      <c r="AL30">
         <v>60</v>
-      </c>
-      <c r="AI30">
-        <v>220</v>
-      </c>
-      <c r="AJ30">
-        <v>900</v>
-      </c>
-      <c r="AK30">
-        <v>210</v>
-      </c>
-      <c r="AL30">
-        <v>270</v>
       </c>
       <c r="AM30">
         <v>580</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP30">
-        <v>1.59</v>
+        <v>10</v>
       </c>
       <c r="AQ30">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR30">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="AS30">
-        <v>1.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT30">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU30">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV30">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW30">
-        <v>1.72</v>
+        <v>8.4</v>
       </c>
       <c r="AX30">
-        <v>1.72</v>
+        <v>19</v>
       </c>
       <c r="AY30">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
-        <v>1.67</v>
+        <v>16</v>
       </c>
       <c r="BA30">
-        <v>1.72</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30">
-        <v>1.72</v>
+        <v>9.6</v>
       </c>
       <c r="BC30">
-        <v>1.72</v>
+        <v>9</v>
       </c>
       <c r="BD30">
-        <v>1.73</v>
+        <v>9.6</v>
       </c>
       <c r="BE30">
-        <v>1.73</v>
+        <v>9.4</v>
       </c>
       <c r="BF30">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG30">
-        <v>1.74</v>
+        <v>8</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB30" t="s">
         <v>187</v>
@@ -8189,112 +8189,112 @@
         <v>180</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="G31">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H31">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="I31">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="J31">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="K31">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L31">
         <v>1.54</v>
       </c>
       <c r="M31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N31">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="P31">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S31">
-        <v>2.72</v>
+        <v>5.5</v>
       </c>
       <c r="T31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
         <v>1.35</v>
       </c>
       <c r="X31">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y31">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z31">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AA31">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AB31">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
+        <v>7.4</v>
+      </c>
+      <c r="AD31">
+        <v>14.5</v>
+      </c>
+      <c r="AE31">
+        <v>44</v>
+      </c>
+      <c r="AF31">
+        <v>26</v>
+      </c>
+      <c r="AG31">
+        <v>18</v>
+      </c>
+      <c r="AH31">
+        <v>27</v>
+      </c>
+      <c r="AI31">
+        <v>75</v>
+      </c>
+      <c r="AJ31">
+        <v>85</v>
+      </c>
+      <c r="AK31">
+        <v>65</v>
+      </c>
+      <c r="AL31">
         <v>95</v>
-      </c>
-      <c r="AD31">
-        <v>500</v>
-      </c>
-      <c r="AE31">
-        <v>500</v>
-      </c>
-      <c r="AF31">
-        <v>500</v>
-      </c>
-      <c r="AG31">
-        <v>500</v>
-      </c>
-      <c r="AH31">
-        <v>500</v>
-      </c>
-      <c r="AI31">
-        <v>500</v>
-      </c>
-      <c r="AJ31">
-        <v>900</v>
-      </c>
-      <c r="AK31">
-        <v>500</v>
-      </c>
-      <c r="AL31">
-        <v>500</v>
       </c>
       <c r="AM31">
         <v>500</v>
       </c>
       <c r="AN31">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AO31">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP31">
         <v>4.9</v>
@@ -8303,52 +8303,52 @@
         <v>4.4</v>
       </c>
       <c r="AR31">
-        <v>1.12</v>
+        <v>4.5</v>
       </c>
       <c r="AS31">
-        <v>1.12</v>
+        <v>5.4</v>
       </c>
       <c r="AT31">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="AU31">
         <v>4.2</v>
       </c>
       <c r="AV31">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="AW31">
-        <v>1.12</v>
+        <v>5.4</v>
       </c>
       <c r="AX31">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="AY31">
-        <v>1.12</v>
+        <v>4.5</v>
       </c>
       <c r="AZ31">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="BA31">
-        <v>1.12</v>
+        <v>5.6</v>
       </c>
       <c r="BB31">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="BC31">
-        <v>1.12</v>
+        <v>5.6</v>
       </c>
       <c r="BD31">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="BE31">
-        <v>1.12</v>
+        <v>5.9</v>
       </c>
       <c r="BF31">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="BG31">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8390,7 +8390,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8509,10 +8509,10 @@
         <v>120</v>
       </c>
       <c r="AF32">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH32">
         <v>25</v>
@@ -8548,7 +8548,7 @@
         <v>28</v>
       </c>
       <c r="AS32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT32">
         <v>6</v>
@@ -8560,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="AW32">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX32">
         <v>8.800000000000001</v>
@@ -8572,7 +8572,7 @@
         <v>17</v>
       </c>
       <c r="BA32">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB32">
         <v>18</v>
@@ -8584,13 +8584,13 @@
         <v>34</v>
       </c>
       <c r="BE32">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32">
         <v>15</v>
       </c>
       <c r="BG32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH32">
         <v>3.4</v>
@@ -8614,7 +8614,7 @@
         <v>4.4</v>
       </c>
       <c r="BO32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP32">
         <v>14.5</v>
@@ -8673,19 +8673,19 @@
         <v>182</v>
       </c>
       <c r="F33">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G33">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="H33">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I33">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K33">
         <v>4.4</v>
@@ -8697,61 +8697,61 @@
         <v>1.06</v>
       </c>
       <c r="N33">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O33">
         <v>1.3</v>
       </c>
       <c r="P33">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q33">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T33">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W33">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="X33">
         <v>17</v>
       </c>
       <c r="Y33">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z33">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AA33">
         <v>700</v>
       </c>
       <c r="AB33">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE33">
         <v>700</v>
       </c>
       <c r="AF33">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -8760,79 +8760,79 @@
         <v>23</v>
       </c>
       <c r="AI33">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AJ33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK33">
         <v>17.5</v>
       </c>
       <c r="AL33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM33">
         <v>700</v>
       </c>
       <c r="AN33">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AO33">
         <v>700</v>
       </c>
       <c r="AP33">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ33">
+        <v>18.5</v>
+      </c>
+      <c r="AR33">
+        <v>10.5</v>
+      </c>
+      <c r="AS33">
         <v>11.5</v>
-      </c>
-      <c r="AR33">
-        <v>11</v>
-      </c>
-      <c r="AS33">
-        <v>12.5</v>
       </c>
       <c r="AT33">
         <v>7.6</v>
       </c>
       <c r="AU33">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV33">
         <v>20</v>
       </c>
       <c r="AW33">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ33">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA33">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC33">
         <v>14.5</v>
       </c>
       <c r="BD33">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE33">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BF33">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8915,22 +8915,22 @@
         <v>183</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H34">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I34">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K34">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L34">
         <v>1.53</v>
@@ -8939,88 +8939,88 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O34">
         <v>1.5</v>
       </c>
       <c r="P34">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q34">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S34">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W34">
         <v>1.78</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP34">
         <v>1.03</v>
@@ -9071,64 +9071,64 @@
         <v>1.03</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG34">
         <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI34">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO34">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9157,16 +9157,16 @@
         <v>184</v>
       </c>
       <c r="F35">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G35">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H35">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I35">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J35">
         <v>3.8</v>
@@ -9190,10 +9190,10 @@
         <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R35">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S35">
         <v>2.88</v>
@@ -9205,10 +9205,10 @@
         <v>2.38</v>
       </c>
       <c r="V35">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X35">
         <v>23</v>
@@ -9247,19 +9247,19 @@
         <v>42</v>
       </c>
       <c r="AJ35">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM35">
         <v>85</v>
       </c>
       <c r="AN35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO35">
         <v>18.5</v>
@@ -9289,13 +9289,13 @@
         <v>16</v>
       </c>
       <c r="AX35">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY35">
         <v>11</v>
       </c>
       <c r="AZ35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA35">
         <v>1.03</v>
@@ -9399,7 +9399,7 @@
         <v>185</v>
       </c>
       <c r="F36">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G36">
         <v>2.82</v>
@@ -9429,7 +9429,7 @@
         <v>1.53</v>
       </c>
       <c r="P36">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q36">
         <v>2.64</v>
@@ -9441,7 +9441,7 @@
         <v>5.4</v>
       </c>
       <c r="T36">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U36">
         <v>1.83</v>
@@ -9546,7 +9546,7 @@
         <v>10.5</v>
       </c>
       <c r="BC36">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD36">
         <v>10.5</v>
@@ -9561,13 +9561,13 @@
         <v>10.5</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI36">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK36">
         <v>1.01</v>
@@ -9579,10 +9579,10 @@
         <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP36">
         <v>1000</v>
@@ -9597,10 +9597,10 @@
         <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV36">
         <v>1000</v>
@@ -9653,10 +9653,10 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K37">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L37">
         <v>1.48</v>
@@ -9665,22 +9665,22 @@
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O37">
         <v>1.4</v>
       </c>
       <c r="P37">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q37">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R37">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S37">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T37">
         <v>2.06</v>
@@ -9695,7 +9695,7 @@
         <v>2.44</v>
       </c>
       <c r="X37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y37">
         <v>19.5</v>
@@ -9743,13 +9743,13 @@
         <v>210</v>
       </c>
       <c r="AN37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO37">
         <v>180</v>
       </c>
       <c r="AP37">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ37">
         <v>15</v>
@@ -9770,7 +9770,7 @@
         <v>20</v>
       </c>
       <c r="AW37">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX37">
         <v>8.199999999999999</v>
@@ -9788,7 +9788,7 @@
         <v>15</v>
       </c>
       <c r="BC37">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD37">
         <v>7.8</v>
@@ -9797,70 +9797,70 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI37">
-        <v>1.29</v>
+        <v>2.88</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK37">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO37">
-        <v>1.43</v>
+        <v>3.6</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ37">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU37">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB37" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -577,7 +577,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-25 03:59:38</t>
+    <t>2026-09-25 06:19:10</t>
   </si>
 </sst>
 </file>
@@ -1171,22 +1171,22 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H2">
         <v>2.28</v>
       </c>
       <c r="I2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1195,142 +1195,142 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W2">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X2">
+        <v>22</v>
+      </c>
+      <c r="Y2">
+        <v>16.5</v>
+      </c>
+      <c r="Z2">
+        <v>17.5</v>
+      </c>
+      <c r="AA2">
+        <v>34</v>
+      </c>
+      <c r="AB2">
+        <v>22</v>
+      </c>
+      <c r="AC2">
+        <v>8.4</v>
+      </c>
+      <c r="AD2">
+        <v>11</v>
+      </c>
+      <c r="AE2">
+        <v>22</v>
+      </c>
+      <c r="AF2">
+        <v>29</v>
+      </c>
+      <c r="AG2">
+        <v>15.5</v>
+      </c>
+      <c r="AH2">
+        <v>15</v>
+      </c>
+      <c r="AI2">
+        <v>32</v>
+      </c>
+      <c r="AJ2">
+        <v>120</v>
+      </c>
+      <c r="AK2">
+        <v>34</v>
+      </c>
+      <c r="AL2">
+        <v>40</v>
+      </c>
+      <c r="AM2">
+        <v>70</v>
+      </c>
+      <c r="AN2">
+        <v>29</v>
+      </c>
+      <c r="AO2">
+        <v>14.5</v>
+      </c>
+      <c r="AP2">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2">
+        <v>11.5</v>
+      </c>
+      <c r="AR2">
+        <v>15</v>
+      </c>
+      <c r="AS2">
+        <v>14.5</v>
+      </c>
+      <c r="AT2">
+        <v>15</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW2">
         <v>18</v>
       </c>
-      <c r="Y2">
+      <c r="AX2">
+        <v>15.5</v>
+      </c>
+      <c r="AY2">
+        <v>13</v>
+      </c>
+      <c r="AZ2">
         <v>12.5</v>
       </c>
-      <c r="Z2">
-        <v>17</v>
-      </c>
-      <c r="AA2">
+      <c r="BA2">
+        <v>23</v>
+      </c>
+      <c r="BB2">
+        <v>20</v>
+      </c>
+      <c r="BC2">
+        <v>20</v>
+      </c>
+      <c r="BD2">
         <v>32</v>
       </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>12</v>
-      </c>
-      <c r="AE2">
-        <v>24</v>
-      </c>
-      <c r="AF2">
-        <v>24</v>
-      </c>
-      <c r="AG2">
-        <v>14</v>
-      </c>
-      <c r="AH2">
-        <v>16.5</v>
-      </c>
-      <c r="AI2">
-        <v>85</v>
-      </c>
-      <c r="AJ2">
-        <v>55</v>
-      </c>
-      <c r="AK2">
-        <v>36</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>320</v>
-      </c>
-      <c r="AN2">
-        <v>28</v>
-      </c>
-      <c r="AO2">
-        <v>970</v>
-      </c>
-      <c r="AP2">
-        <v>16</v>
-      </c>
-      <c r="AQ2">
-        <v>10</v>
-      </c>
-      <c r="AR2">
-        <v>14</v>
-      </c>
-      <c r="AS2">
-        <v>25</v>
-      </c>
-      <c r="AT2">
+      <c r="BE2">
+        <v>30</v>
+      </c>
+      <c r="BF2">
+        <v>7</v>
+      </c>
+      <c r="BG2">
         <v>12.5</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>20</v>
-      </c>
-      <c r="AX2">
-        <v>20</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>13.5</v>
-      </c>
-      <c r="BA2">
-        <v>18</v>
-      </c>
-      <c r="BB2">
-        <v>6.8</v>
-      </c>
-      <c r="BC2">
-        <v>16</v>
-      </c>
-      <c r="BD2">
-        <v>18.5</v>
-      </c>
-      <c r="BE2">
-        <v>7.2</v>
-      </c>
-      <c r="BF2">
-        <v>6.2</v>
-      </c>
-      <c r="BG2">
-        <v>13</v>
       </c>
       <c r="BH2">
         <v>3.85</v>
@@ -1339,25 +1339,25 @@
         <v>3.4</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
         <v>8.4</v>
@@ -1366,7 +1366,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
         <v>5.5</v>
@@ -1381,16 +1381,16 @@
         <v>7.2</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,19 +1413,19 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H3">
         <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1440,19 +1440,19 @@
         <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
         <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
         <v>1.83</v>
@@ -1461,7 +1461,7 @@
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.69</v>
@@ -1473,10 +1473,10 @@
         <v>15</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>11</v>
@@ -1515,67 +1515,67 @@
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO3">
         <v>65</v>
       </c>
       <c r="AP3">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AR3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS3">
+        <v>4.5</v>
+      </c>
+      <c r="AT3">
+        <v>4.2</v>
+      </c>
+      <c r="AU3">
+        <v>3.7</v>
+      </c>
+      <c r="AV3">
+        <v>6.2</v>
+      </c>
+      <c r="AW3">
+        <v>4.4</v>
+      </c>
+      <c r="AX3">
+        <v>4.1</v>
+      </c>
+      <c r="AY3">
+        <v>5.2</v>
+      </c>
+      <c r="AZ3">
         <v>4.3</v>
       </c>
-      <c r="AT3">
+      <c r="BA3">
+        <v>4.4</v>
+      </c>
+      <c r="BB3">
+        <v>4.3</v>
+      </c>
+      <c r="BC3">
+        <v>4.2</v>
+      </c>
+      <c r="BD3">
+        <v>4.3</v>
+      </c>
+      <c r="BE3">
+        <v>4.6</v>
+      </c>
+      <c r="BF3">
+        <v>3.95</v>
+      </c>
+      <c r="BG3">
+        <v>4.4</v>
+      </c>
+      <c r="BH3">
         <v>3.2</v>
-      </c>
-      <c r="AU3">
-        <v>2.9</v>
-      </c>
-      <c r="AV3">
-        <v>3.65</v>
-      </c>
-      <c r="AW3">
-        <v>4.2</v>
-      </c>
-      <c r="AX3">
-        <v>3.6</v>
-      </c>
-      <c r="AY3">
-        <v>3.45</v>
-      </c>
-      <c r="AZ3">
-        <v>3.8</v>
-      </c>
-      <c r="BA3">
-        <v>4.3</v>
-      </c>
-      <c r="BB3">
-        <v>4.1</v>
-      </c>
-      <c r="BC3">
-        <v>4</v>
-      </c>
-      <c r="BD3">
-        <v>4.2</v>
-      </c>
-      <c r="BE3">
-        <v>4.4</v>
-      </c>
-      <c r="BF3">
-        <v>3.9</v>
-      </c>
-      <c r="BG3">
-        <v>4.2</v>
-      </c>
-      <c r="BH3">
-        <v>3.6</v>
       </c>
       <c r="BI3">
         <v>2.52</v>
@@ -1584,55 +1584,55 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BN3">
         <v>6</v>
       </c>
       <c r="BO3">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
         <v>22</v>
       </c>
       <c r="BQ3">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT3">
         <v>8</v>
       </c>
       <c r="BU3">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="BV3">
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ3">
         <v>40</v>
       </c>
       <c r="CA3">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1655,7 +1655,7 @@
         <v>153</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
         <v>2.68</v>
@@ -1676,28 +1676,28 @@
         <v>1.4</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
+        <v>1.82</v>
+      </c>
+      <c r="Q4">
+        <v>1.97</v>
+      </c>
+      <c r="R4">
+        <v>1.32</v>
+      </c>
+      <c r="S4">
+        <v>3.5</v>
+      </c>
+      <c r="T4">
         <v>1.83</v>
-      </c>
-      <c r="Q4">
-        <v>1.96</v>
-      </c>
-      <c r="R4">
-        <v>1.31</v>
-      </c>
-      <c r="S4">
-        <v>3.45</v>
-      </c>
-      <c r="T4">
-        <v>1.74</v>
       </c>
       <c r="U4">
         <v>2.06</v>
@@ -1706,19 +1706,19 @@
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB4">
         <v>11</v>
@@ -1727,7 +1727,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1736,7 +1736,7 @@
         <v>17</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
         <v>18.5</v>
@@ -1745,10 +1745,10 @@
         <v>130</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL4">
         <v>110</v>
@@ -1757,67 +1757,67 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO4">
         <v>42</v>
       </c>
       <c r="AP4">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS4">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="AX4">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AY4">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BB4">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>65</v>
       </c>
       <c r="BF4">
         <v>19</v>
       </c>
       <c r="BG4">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
         <v>2.76</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
         <v>5.6</v>
@@ -1841,7 +1841,7 @@
         <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ4">
         <v>6.6</v>
@@ -1850,19 +1850,19 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1874,7 +1874,7 @@
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,61 +1897,61 @@
         <v>154</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G5">
         <v>2.62</v>
       </c>
       <c r="H5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
         <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y5">
         <v>16.5</v>
@@ -1966,16 +1966,16 @@
         <v>15.5</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
         <v>34</v>
       </c>
       <c r="AF5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -1987,7 +1987,7 @@
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK5">
         <v>30</v>
@@ -1996,16 +1996,16 @@
         <v>38</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
         <v>13</v>
@@ -2014,7 +2014,7 @@
         <v>18</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT5">
         <v>12</v>
@@ -2026,7 +2026,7 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -2038,16 +2038,16 @@
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>46</v>
@@ -2056,13 +2056,13 @@
         <v>13</v>
       </c>
       <c r="BG5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
@@ -2074,19 +2074,19 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN5">
         <v>7</v>
       </c>
       <c r="BO5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
         <v>21</v>
       </c>
       <c r="BQ5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BR5">
         <v>32</v>
@@ -2104,19 +2104,19 @@
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BX5">
         <v>34</v>
       </c>
       <c r="BY5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ5">
         <v>22</v>
       </c>
       <c r="CA5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,16 +2139,16 @@
         <v>155</v>
       </c>
       <c r="F6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G6">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H6">
         <v>4.6</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6">
         <v>3.65</v>
@@ -2157,7 +2157,7 @@
         <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -2166,25 +2166,25 @@
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
         <v>4</v>
       </c>
       <c r="T6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V6">
         <v>1.27</v>
@@ -2205,22 +2205,22 @@
         <v>110</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF6">
         <v>11</v>
       </c>
       <c r="AG6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH6">
         <v>21</v>
@@ -2229,10 +2229,10 @@
         <v>75</v>
       </c>
       <c r="AJ6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL6">
         <v>40</v>
@@ -2241,82 +2241,82 @@
         <v>130</v>
       </c>
       <c r="AN6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR6">
         <v>30</v>
       </c>
       <c r="AS6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA6">
         <v>65</v>
       </c>
       <c r="BB6">
+        <v>22</v>
+      </c>
+      <c r="BC6">
         <v>21</v>
-      </c>
-      <c r="BC6">
-        <v>20</v>
       </c>
       <c r="BD6">
         <v>38</v>
       </c>
       <c r="BE6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL6">
         <v>160</v>
       </c>
       <c r="BM6">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
         <v>4.4</v>
@@ -2325,40 +2325,40 @@
         <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BR6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
         <v>7</v>
       </c>
       <c r="BV6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2387,55 +2387,55 @@
         <v>1.93</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W7">
         <v>2.06</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y7">
         <v>14</v>
@@ -2444,28 +2444,28 @@
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
         <v>10</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI7">
         <v>85</v>
@@ -2477,22 +2477,22 @@
         <v>23</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO7">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR7">
         <v>32</v>
@@ -2501,25 +2501,25 @@
         <v>95</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX7">
         <v>10</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
         <v>70</v>
@@ -2531,31 +2531,31 @@
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE7">
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL7">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM7">
         <v>70</v>
@@ -2564,10 +2564,10 @@
         <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
         <v>12.5</v>
@@ -2579,19 +2579,19 @@
         <v>12</v>
       </c>
       <c r="BT7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7">
         <v>7.2</v>
       </c>
       <c r="BV7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW7">
         <v>13.5</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY7">
         <v>14.5</v>
@@ -2600,7 +2600,7 @@
         <v>32</v>
       </c>
       <c r="CA7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2623,64 +2623,64 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="S8">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="T8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="X8">
+        <v>27</v>
+      </c>
+      <c r="Y8">
         <v>32</v>
-      </c>
-      <c r="Y8">
-        <v>34</v>
       </c>
       <c r="Z8">
         <v>500</v>
@@ -2689,10 +2689,10 @@
         <v>500</v>
       </c>
       <c r="AB8">
+        <v>11.5</v>
+      </c>
+      <c r="AC8">
         <v>12</v>
-      </c>
-      <c r="AC8">
-        <v>13</v>
       </c>
       <c r="AD8">
         <v>40</v>
@@ -2701,7 +2701,7 @@
         <v>500</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG8">
         <v>11</v>
@@ -2713,136 +2713,136 @@
         <v>500</v>
       </c>
       <c r="AJ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL8">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ8">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AR8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AV8">
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC8">
+        <v>12.5</v>
+      </c>
+      <c r="BD8">
         <v>12</v>
-      </c>
-      <c r="BD8">
-        <v>6.2</v>
       </c>
       <c r="BE8">
         <v>7.2</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG8">
         <v>7.2</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB8" t="s">
         <v>187</v>
@@ -2868,7 +2868,7 @@
         <v>1.24</v>
       </c>
       <c r="G9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H9">
         <v>10.5</v>
@@ -2898,16 +2898,16 @@
         <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T9">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -2916,7 +2916,7 @@
         <v>1.08</v>
       </c>
       <c r="W9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X9">
         <v>75</v>
@@ -2925,43 +2925,43 @@
         <v>80</v>
       </c>
       <c r="Z9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA9">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AB9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AD9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE9">
         <v>150</v>
       </c>
       <c r="AF9">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI9">
         <v>95</v>
       </c>
       <c r="AJ9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK9">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM9">
         <v>90</v>
@@ -2973,52 +2973,52 @@
         <v>100</v>
       </c>
       <c r="AP9">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AR9">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AT9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU9">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AV9">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AW9">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA9">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BB9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC9">
         <v>11.5</v>
       </c>
       <c r="BD9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE9">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BF9">
         <v>2.52</v>
@@ -3033,52 +3033,52 @@
         <v>5.3</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BL9">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN9">
         <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BQ9">
         <v>5.4</v>
       </c>
       <c r="BR9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT9">
         <v>17.5</v>
       </c>
       <c r="BU9">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
         <v>80</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3107,94 +3107,94 @@
         <v>159</v>
       </c>
       <c r="F10">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="H10">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="I10">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="J10">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M10">
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="Q10">
+        <v>1.57</v>
+      </c>
+      <c r="R10">
         <v>1.64</v>
       </c>
-      <c r="R10">
-        <v>1.55</v>
-      </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X10">
+        <v>30</v>
+      </c>
+      <c r="Y10">
+        <v>12</v>
+      </c>
+      <c r="Z10">
+        <v>12</v>
+      </c>
+      <c r="AA10">
+        <v>15.5</v>
+      </c>
+      <c r="AB10">
+        <v>29</v>
+      </c>
+      <c r="AC10">
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <v>11</v>
+      </c>
+      <c r="AE10">
+        <v>15.5</v>
+      </c>
+      <c r="AF10">
+        <v>120</v>
+      </c>
+      <c r="AG10">
         <v>26</v>
-      </c>
-      <c r="Y10">
-        <v>11.5</v>
-      </c>
-      <c r="Z10">
-        <v>11</v>
-      </c>
-      <c r="AA10">
-        <v>16</v>
-      </c>
-      <c r="AB10">
-        <v>26</v>
-      </c>
-      <c r="AC10">
-        <v>11</v>
-      </c>
-      <c r="AD10">
-        <v>10.5</v>
-      </c>
-      <c r="AE10">
-        <v>16.5</v>
-      </c>
-      <c r="AF10">
-        <v>55</v>
-      </c>
-      <c r="AG10">
-        <v>24</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ10">
         <v>700</v>
@@ -3209,124 +3209,124 @@
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO10">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AP10">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT10">
+        <v>6.8</v>
+      </c>
+      <c r="AU10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW10">
+        <v>12.5</v>
+      </c>
+      <c r="AX10">
+        <v>7.8</v>
+      </c>
+      <c r="AY10">
         <v>20</v>
-      </c>
-      <c r="AU10">
-        <v>9.4</v>
-      </c>
-      <c r="AV10">
-        <v>9</v>
-      </c>
-      <c r="AW10">
-        <v>13.5</v>
-      </c>
-      <c r="AX10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>6.8</v>
       </c>
       <c r="AZ10">
         <v>16.5</v>
       </c>
       <c r="BA10">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BB10">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD10">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE10">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3349,55 +3349,55 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G11">
         <v>3.25</v>
       </c>
       <c r="H11">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J11">
         <v>3.65</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W11">
         <v>1.44</v>
@@ -3412,7 +3412,7 @@
         <v>17.5</v>
       </c>
       <c r="AA11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB11">
         <v>15</v>
@@ -3445,10 +3445,10 @@
         <v>34</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM11">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN11">
         <v>26</v>
@@ -3457,7 +3457,7 @@
         <v>16</v>
       </c>
       <c r="AP11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ11">
         <v>10.5</v>
@@ -3487,19 +3487,19 @@
         <v>12</v>
       </c>
       <c r="AZ11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB11">
         <v>34</v>
       </c>
       <c r="BC11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE11">
         <v>55</v>
@@ -3514,7 +3514,7 @@
         <v>3.85</v>
       </c>
       <c r="BI11">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BJ11">
         <v>9</v>
@@ -3532,7 +3532,7 @@
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
         <v>23</v>
@@ -3550,7 +3550,7 @@
         <v>5.6</v>
       </c>
       <c r="BU11">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV11">
         <v>17</v>
@@ -3591,226 +3591,226 @@
         <v>161</v>
       </c>
       <c r="F12">
+        <v>1.57</v>
+      </c>
+      <c r="G12">
         <v>1.59</v>
       </c>
-      <c r="G12">
-        <v>1.61</v>
-      </c>
       <c r="H12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
         <v>4.5</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S12">
+        <v>2.9</v>
+      </c>
+      <c r="T12">
+        <v>1.87</v>
+      </c>
+      <c r="U12">
+        <v>2.12</v>
+      </c>
+      <c r="V12">
+        <v>1.16</v>
+      </c>
+      <c r="W12">
         <v>2.68</v>
       </c>
-      <c r="T12">
-        <v>1.77</v>
-      </c>
-      <c r="U12">
-        <v>2.26</v>
-      </c>
-      <c r="V12">
-        <v>1.17</v>
-      </c>
-      <c r="W12">
-        <v>2.64</v>
-      </c>
       <c r="X12">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB12">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12">
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE12">
+        <v>90</v>
+      </c>
+      <c r="AF12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG12">
+        <v>9.6</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
         <v>80</v>
       </c>
-      <c r="AF12">
-        <v>10.5</v>
-      </c>
-      <c r="AG12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH12">
-        <v>19</v>
-      </c>
-      <c r="AI12">
-        <v>160</v>
-      </c>
       <c r="AJ12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK12">
         <v>15.5</v>
       </c>
       <c r="AL12">
+        <v>32</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>7.2</v>
+      </c>
+      <c r="AO12">
+        <v>110</v>
+      </c>
+      <c r="AP12">
+        <v>18</v>
+      </c>
+      <c r="AQ12">
+        <v>22</v>
+      </c>
+      <c r="AR12">
+        <v>50</v>
+      </c>
+      <c r="AS12">
         <v>29</v>
       </c>
-      <c r="AM12">
-        <v>90</v>
-      </c>
-      <c r="AN12">
-        <v>6.8</v>
-      </c>
-      <c r="AO12">
-        <v>80</v>
-      </c>
-      <c r="AP12">
-        <v>21</v>
-      </c>
-      <c r="AQ12">
-        <v>24</v>
-      </c>
-      <c r="AR12">
-        <v>48</v>
-      </c>
-      <c r="AS12">
-        <v>19</v>
-      </c>
       <c r="AT12">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW12">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AX12">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB12">
         <v>13.5</v>
       </c>
       <c r="BC12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE12">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="BF12">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BH12">
+        <v>3.85</v>
+      </c>
+      <c r="BI12">
+        <v>3.6</v>
+      </c>
+      <c r="BJ12">
+        <v>11</v>
+      </c>
+      <c r="BK12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL12">
+        <v>130</v>
+      </c>
+      <c r="BM12">
+        <v>14.5</v>
+      </c>
+      <c r="BN12">
         <v>4.1</v>
       </c>
-      <c r="BI12">
-        <v>3.8</v>
-      </c>
-      <c r="BJ12">
-        <v>10.5</v>
-      </c>
-      <c r="BK12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL12">
-        <v>110</v>
-      </c>
-      <c r="BM12">
-        <v>13.5</v>
-      </c>
-      <c r="BN12">
-        <v>4.3</v>
-      </c>
       <c r="BO12">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BP12">
         <v>9.6</v>
       </c>
       <c r="BQ12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT12">
         <v>10</v>
       </c>
       <c r="BU12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BW12">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY12">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="s">
         <v>187</v>
@@ -3845,13 +3845,13 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M13">
         <v>1.04</v>
@@ -3863,7 +3863,7 @@
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q13">
         <v>1.65</v>
@@ -3875,10 +3875,10 @@
         <v>2.68</v>
       </c>
       <c r="T13">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V13">
         <v>1.14</v>
@@ -3887,7 +3887,7 @@
         <v>3.05</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y13">
         <v>29</v>
@@ -3896,19 +3896,19 @@
         <v>70</v>
       </c>
       <c r="AA13">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
         <v>28</v>
       </c>
       <c r="AE13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF13">
         <v>9.4</v>
@@ -3938,76 +3938,76 @@
         <v>5.8</v>
       </c>
       <c r="AO13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP13">
         <v>20</v>
       </c>
       <c r="AQ13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR13">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AS13">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AT13">
         <v>9.6</v>
       </c>
       <c r="AU13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV13">
         <v>26</v>
       </c>
       <c r="AW13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AX13">
         <v>9</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
         <v>20</v>
       </c>
       <c r="BA13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
       </c>
       <c r="BC13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD13">
         <v>29</v>
       </c>
       <c r="BE13">
+        <v>90</v>
+      </c>
+      <c r="BF13">
+        <v>5.5</v>
+      </c>
+      <c r="BG13">
         <v>95</v>
-      </c>
-      <c r="BF13">
-        <v>5.6</v>
-      </c>
-      <c r="BG13">
-        <v>90</v>
       </c>
       <c r="BH13">
         <v>4.2</v>
       </c>
       <c r="BI13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL13">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM13">
         <v>50</v>
@@ -4016,7 +4016,7 @@
         <v>4</v>
       </c>
       <c r="BO13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP13">
         <v>8.6</v>
@@ -4025,10 +4025,10 @@
         <v>7.6</v>
       </c>
       <c r="BR13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BS13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT13">
         <v>11.5</v>
@@ -4037,22 +4037,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BV13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW13">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BX13">
         <v>70</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13">
         <v>15</v>
       </c>
       <c r="CA13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
         <v>187</v>
@@ -4081,70 +4081,70 @@
         <v>10</v>
       </c>
       <c r="H14">
+        <v>1.36</v>
+      </c>
+      <c r="I14">
         <v>1.37</v>
       </c>
-      <c r="I14">
-        <v>1.38</v>
-      </c>
       <c r="J14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O14">
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R14">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="W14">
         <v>1.11</v>
       </c>
       <c r="X14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y14">
         <v>14.5</v>
       </c>
       <c r="Z14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA14">
         <v>12.5</v>
       </c>
       <c r="AB14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AC14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD14">
         <v>11</v>
@@ -4153,19 +4153,19 @@
         <v>13</v>
       </c>
       <c r="AF14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AG14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI14">
         <v>26</v>
       </c>
       <c r="AJ14">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AK14">
         <v>110</v>
@@ -4174,7 +4174,7 @@
         <v>80</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN14">
         <v>110</v>
@@ -4183,22 +4183,22 @@
         <v>3.8</v>
       </c>
       <c r="AP14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS14">
         <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AU14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV14">
         <v>10</v>
@@ -4207,88 +4207,88 @@
         <v>12</v>
       </c>
       <c r="AX14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AY14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA14">
         <v>24</v>
       </c>
       <c r="BB14">
+        <v>150</v>
+      </c>
+      <c r="BC14">
         <v>95</v>
       </c>
-      <c r="BC14">
-        <v>90</v>
-      </c>
       <c r="BD14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE14">
         <v>70</v>
       </c>
       <c r="BF14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BG14">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BH14">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BI14">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14">
+        <v>12.5</v>
+      </c>
+      <c r="BK14">
+        <v>8</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>4.2</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>4.2</v>
+      </c>
+      <c r="BR14">
+        <v>70</v>
+      </c>
+      <c r="BS14">
+        <v>3.7</v>
+      </c>
+      <c r="BT14">
+        <v>5</v>
+      </c>
+      <c r="BU14">
+        <v>3.55</v>
+      </c>
+      <c r="BV14">
+        <v>8</v>
+      </c>
+      <c r="BW14">
+        <v>6</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
         <v>10.5</v>
-      </c>
-      <c r="BK14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL14">
-        <v>95</v>
-      </c>
-      <c r="BM14">
-        <v>13</v>
-      </c>
-      <c r="BN14">
-        <v>13</v>
-      </c>
-      <c r="BO14">
-        <v>11.5</v>
-      </c>
-      <c r="BP14">
-        <v>65</v>
-      </c>
-      <c r="BQ14">
-        <v>12.5</v>
-      </c>
-      <c r="BR14">
-        <v>55</v>
-      </c>
-      <c r="BS14">
-        <v>12</v>
-      </c>
-      <c r="BT14">
-        <v>4.4</v>
-      </c>
-      <c r="BU14">
-        <v>3.95</v>
-      </c>
-      <c r="BV14">
-        <v>7.4</v>
-      </c>
-      <c r="BW14">
-        <v>6.6</v>
-      </c>
-      <c r="BX14">
-        <v>18.5</v>
-      </c>
-      <c r="BY14">
-        <v>15.5</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4317,16 +4317,16 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G15">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
         <v>5.1</v>
-      </c>
-      <c r="I15">
-        <v>5.2</v>
       </c>
       <c r="J15">
         <v>3.75</v>
@@ -4335,49 +4335,49 @@
         <v>3.8</v>
       </c>
       <c r="L15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P15">
         <v>1.86</v>
       </c>
       <c r="Q15">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R15">
         <v>1.32</v>
       </c>
       <c r="S15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V15">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA15">
         <v>130</v>
@@ -4386,13 +4386,13 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF15">
         <v>10.5</v>
@@ -4401,16 +4401,16 @@
         <v>9.6</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15">
         <v>80</v>
       </c>
       <c r="AJ15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL15">
         <v>40</v>
@@ -4419,31 +4419,31 @@
         <v>130</v>
       </c>
       <c r="AN15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO15">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15">
         <v>14.5</v>
       </c>
       <c r="AR15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT15">
         <v>7.4</v>
       </c>
       <c r="AU15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW15">
         <v>60</v>
@@ -4452,13 +4452,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
         <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB15">
         <v>18.5</v>
@@ -4467,34 +4467,34 @@
         <v>19</v>
       </c>
       <c r="BD15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG15">
         <v>75</v>
       </c>
       <c r="BH15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ15">
         <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL15">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM15">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN15">
         <v>4.3</v>
@@ -4503,16 +4503,16 @@
         <v>4</v>
       </c>
       <c r="BP15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BQ15">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT15">
         <v>8.199999999999999</v>
@@ -4521,22 +4521,22 @@
         <v>7.4</v>
       </c>
       <c r="BV15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW15">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BX15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BZ15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA15">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="s">
         <v>187</v>
@@ -4559,16 +4559,16 @@
         <v>165</v>
       </c>
       <c r="F16">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G16">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H16">
+        <v>3.25</v>
+      </c>
+      <c r="I16">
         <v>3.3</v>
-      </c>
-      <c r="I16">
-        <v>3.4</v>
       </c>
       <c r="J16">
         <v>3.7</v>
@@ -4583,40 +4583,40 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U16">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z16">
         <v>24</v>
@@ -4634,28 +4634,28 @@
         <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK16">
         <v>22</v>
       </c>
       <c r="AL16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM16">
         <v>65</v>
@@ -4664,7 +4664,7 @@
         <v>14.5</v>
       </c>
       <c r="AO16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP16">
         <v>17.5</v>
@@ -4679,10 +4679,10 @@
         <v>50</v>
       </c>
       <c r="AT16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV16">
         <v>13</v>
@@ -4691,22 +4691,22 @@
         <v>30</v>
       </c>
       <c r="AX16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16">
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA16">
         <v>34</v>
       </c>
       <c r="BB16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD16">
         <v>27</v>
@@ -4715,19 +4715,19 @@
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG16">
         <v>23</v>
       </c>
       <c r="BH16">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
         <v>7.8</v>
@@ -4736,16 +4736,16 @@
         <v>110</v>
       </c>
       <c r="BM16">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BN16">
         <v>5.4</v>
       </c>
       <c r="BO16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP16">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BQ16">
         <v>14</v>
@@ -4754,28 +4754,28 @@
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="BT16">
         <v>6.6</v>
       </c>
       <c r="BU16">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX16">
         <v>38</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BZ16">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="CA16">
         <v>9</v>
@@ -4801,10 +4801,10 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G17">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H17">
         <v>3.45</v>
@@ -4819,208 +4819,208 @@
         <v>3.4</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q17">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T17">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="U17">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V17">
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB17">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD17">
         <v>14.5</v>
       </c>
       <c r="AE17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ17">
         <v>34</v>
       </c>
       <c r="AK17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL17">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM17">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17">
         <v>10.5</v>
       </c>
       <c r="AR17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS17">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT17">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV17">
+        <v>13.5</v>
+      </c>
+      <c r="AW17">
+        <v>42</v>
+      </c>
+      <c r="AX17">
         <v>13</v>
-      </c>
-      <c r="AW17">
-        <v>38</v>
-      </c>
-      <c r="AX17">
-        <v>13.5</v>
       </c>
       <c r="AY17">
         <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA17">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB17">
         <v>29</v>
       </c>
       <c r="BC17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE17">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BG17">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BH17">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BI17">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM17">
-        <v>2.66</v>
+        <v>12</v>
       </c>
       <c r="BN17">
+        <v>5.1</v>
+      </c>
+      <c r="BO17">
+        <v>4.7</v>
+      </c>
+      <c r="BP17">
+        <v>24</v>
+      </c>
+      <c r="BQ17">
+        <v>16</v>
+      </c>
+      <c r="BR17">
+        <v>46</v>
+      </c>
+      <c r="BS17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT17">
         <v>6.4</v>
       </c>
-      <c r="BO17">
-        <v>4.2</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>11</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>2.66</v>
-      </c>
-      <c r="BT17">
-        <v>8.6</v>
-      </c>
       <c r="BU17">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW17">
-        <v>2.66</v>
+        <v>9.4</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY17">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA17">
-        <v>2.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5046,10 +5046,10 @@
         <v>1.65</v>
       </c>
       <c r="G18">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I18">
         <v>6.4</v>
@@ -5061,55 +5061,55 @@
         <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U18">
         <v>2.04</v>
       </c>
       <c r="V18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W18">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X18">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA18">
         <v>180</v>
       </c>
       <c r="AB18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18">
         <v>9.4</v>
@@ -5118,16 +5118,16 @@
         <v>23</v>
       </c>
       <c r="AE18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF18">
         <v>9.6</v>
       </c>
       <c r="AG18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI18">
         <v>85</v>
@@ -5136,49 +5136,49 @@
         <v>15.5</v>
       </c>
       <c r="AK18">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM18">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN18">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO18">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP18">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR18">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AS18">
         <v>110</v>
       </c>
       <c r="AT18">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
         <v>19.5</v>
@@ -5187,7 +5187,7 @@
         <v>70</v>
       </c>
       <c r="BB18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC18">
         <v>15.5</v>
@@ -5196,49 +5196,49 @@
         <v>32</v>
       </c>
       <c r="BE18">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BF18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG18">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BH18">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI18">
         <v>3.25</v>
       </c>
       <c r="BJ18">
+        <v>10.5</v>
+      </c>
+      <c r="BK18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL18">
+        <v>140</v>
+      </c>
+      <c r="BM18">
+        <v>16</v>
+      </c>
+      <c r="BN18">
+        <v>4.1</v>
+      </c>
+      <c r="BO18">
+        <v>3.85</v>
+      </c>
+      <c r="BP18">
         <v>11</v>
-      </c>
-      <c r="BK18">
-        <v>9.4</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>13.5</v>
-      </c>
-      <c r="BN18">
-        <v>4.2</v>
-      </c>
-      <c r="BO18">
-        <v>3.8</v>
-      </c>
-      <c r="BP18">
-        <v>11.5</v>
       </c>
       <c r="BQ18">
         <v>9.4</v>
       </c>
       <c r="BR18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS18">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
         <v>9.6</v>
@@ -5247,22 +5247,22 @@
         <v>8.4</v>
       </c>
       <c r="BV18">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW18">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX18">
         <v>60</v>
       </c>
       <c r="BY18">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ18">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA18">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5285,97 +5285,97 @@
         <v>168</v>
       </c>
       <c r="F19">
+        <v>1.35</v>
+      </c>
+      <c r="G19">
         <v>1.38</v>
-      </c>
-      <c r="G19">
-        <v>1.4</v>
       </c>
       <c r="H19">
         <v>11</v>
       </c>
       <c r="I19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="R19">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S19">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
         <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z19">
         <v>540</v>
       </c>
       <c r="AA19">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD19">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AE19">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AF19">
         <v>8.199999999999999</v>
       </c>
       <c r="AG19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AI19">
         <v>470</v>
       </c>
       <c r="AJ19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK19">
         <v>19.5</v>
@@ -5384,67 +5384,67 @@
         <v>55</v>
       </c>
       <c r="AM19">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN19">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO19">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AP19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
         <v>26</v>
       </c>
       <c r="AR19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS19">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT19">
         <v>7</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV19">
         <v>16</v>
       </c>
       <c r="AW19">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AX19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY19">
         <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC19">
         <v>14</v>
       </c>
       <c r="BD19">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="BE19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="BF19">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BG19">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5527,16 +5527,16 @@
         <v>169</v>
       </c>
       <c r="F20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G20">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J20">
         <v>3.45</v>
@@ -5545,55 +5545,55 @@
         <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M20">
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S20">
         <v>4.7</v>
       </c>
       <c r="T20">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
         <v>2.1</v>
       </c>
       <c r="X20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y20">
         <v>15.5</v>
       </c>
       <c r="Z20">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AA20">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AB20">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>8.199999999999999</v>
@@ -5602,28 +5602,28 @@
         <v>23</v>
       </c>
       <c r="AE20">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AF20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>11</v>
       </c>
       <c r="AH20">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI20">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AJ20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL20">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM20">
         <v>580</v>
@@ -5632,121 +5632,121 @@
         <v>18</v>
       </c>
       <c r="AO20">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AP20">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS20">
         <v>100</v>
       </c>
       <c r="AT20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY20">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB20">
         <v>18.5</v>
       </c>
       <c r="BC20">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD20">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BE20">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="BF20">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB20" t="s">
         <v>187</v>
@@ -5769,28 +5769,28 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="G21">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H21">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="I21">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L21">
         <v>1.41</v>
       </c>
       <c r="M21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
         <v>3.85</v>
@@ -5799,31 +5799,31 @@
         <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q21">
         <v>1.98</v>
       </c>
       <c r="R21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21">
         <v>3.5</v>
       </c>
       <c r="T21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y21">
         <v>12</v>
@@ -5835,7 +5835,7 @@
         <v>60</v>
       </c>
       <c r="AB21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
         <v>7.6</v>
@@ -5844,7 +5844,7 @@
         <v>13</v>
       </c>
       <c r="AE21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF21">
         <v>19</v>
@@ -5859,46 +5859,46 @@
         <v>50</v>
       </c>
       <c r="AJ21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL21">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM21">
         <v>200</v>
       </c>
       <c r="AN21">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ21">
         <v>10</v>
       </c>
       <c r="AR21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT21">
         <v>10</v>
       </c>
       <c r="AU21">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
         <v>11</v>
       </c>
       <c r="AW21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX21">
         <v>15.5</v>
@@ -5910,13 +5910,13 @@
         <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB21">
         <v>28</v>
       </c>
       <c r="BC21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21">
         <v>30</v>
@@ -5925,13 +5925,13 @@
         <v>60</v>
       </c>
       <c r="BF21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH21">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BI21">
         <v>2.74</v>
@@ -5940,55 +5940,55 @@
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BN21">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP21">
         <v>24</v>
       </c>
       <c r="BQ21">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="BR21">
         <v>40</v>
       </c>
       <c r="BS21">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT21">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BU21">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BX21">
         <v>42</v>
       </c>
       <c r="BY21">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ21">
         <v>32</v>
       </c>
       <c r="CA21">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6011,19 +6011,19 @@
         <v>171</v>
       </c>
       <c r="F22">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G22">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H22">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I22">
         <v>2.74</v>
       </c>
       <c r="J22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K22">
         <v>3.65</v>
@@ -6035,7 +6035,7 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
         <v>1.26</v>
@@ -6047,7 +6047,7 @@
         <v>1.79</v>
       </c>
       <c r="R22">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
         <v>2.98</v>
@@ -6056,7 +6056,7 @@
         <v>1.65</v>
       </c>
       <c r="U22">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V22">
         <v>1.57</v>
@@ -6065,13 +6065,13 @@
         <v>1.53</v>
       </c>
       <c r="X22">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y22">
         <v>13.5</v>
       </c>
       <c r="Z22">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA22">
         <v>40</v>
@@ -6080,10 +6080,10 @@
         <v>13.5</v>
       </c>
       <c r="AC22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE22">
         <v>27</v>
@@ -6095,7 +6095,7 @@
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI22">
         <v>36</v>
@@ -6110,16 +6110,16 @@
         <v>36</v>
       </c>
       <c r="AM22">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN22">
         <v>21</v>
       </c>
       <c r="AO22">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AP22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22">
         <v>12</v>
@@ -6140,10 +6140,10 @@
         <v>11</v>
       </c>
       <c r="AW22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY22">
         <v>11</v>
@@ -6155,25 +6155,25 @@
         <v>30</v>
       </c>
       <c r="BB22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE22">
         <v>60</v>
       </c>
       <c r="BF22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH22">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI22">
         <v>3.45</v>
@@ -6182,13 +6182,13 @@
         <v>9</v>
       </c>
       <c r="BK22">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN22">
         <v>6</v>
@@ -6200,13 +6200,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ22">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR22">
         <v>29</v>
       </c>
       <c r="BS22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT22">
         <v>5.9</v>
@@ -6218,19 +6218,19 @@
         <v>19</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX22">
         <v>29</v>
       </c>
       <c r="BY22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22">
         <v>21</v>
       </c>
       <c r="CA22">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6256,19 +6256,19 @@
         <v>2.7</v>
       </c>
       <c r="G23">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H23">
         <v>2.62</v>
       </c>
       <c r="I23">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L23">
         <v>1.38</v>
@@ -6277,16 +6277,16 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P23">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R23">
         <v>1.42</v>
@@ -6298,16 +6298,16 @@
         <v>1.68</v>
       </c>
       <c r="U23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W23">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y23">
         <v>15</v>
@@ -6319,7 +6319,7 @@
         <v>46</v>
       </c>
       <c r="AB23">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC23">
         <v>8.6</v>
@@ -6331,10 +6331,10 @@
         <v>34</v>
       </c>
       <c r="AF23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH23">
         <v>16.5</v>
@@ -6343,19 +6343,19 @@
         <v>46</v>
       </c>
       <c r="AJ23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL23">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM23">
         <v>95</v>
       </c>
       <c r="AN23">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO23">
         <v>25</v>
@@ -6364,13 +6364,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR23">
         <v>16</v>
       </c>
       <c r="AS23">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT23">
         <v>11</v>
@@ -6382,10 +6382,10 @@
         <v>10.5</v>
       </c>
       <c r="AW23">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="AX23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY23">
         <v>11</v>
@@ -6394,85 +6394,85 @@
         <v>14</v>
       </c>
       <c r="BA23">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB23">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC23">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BD23">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE23">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF23">
         <v>20</v>
       </c>
       <c r="BG23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB23" t="s">
         <v>187</v>
@@ -6495,22 +6495,22 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G24">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H24">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="I24">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="J24">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>1.27</v>
@@ -6525,7 +6525,7 @@
         <v>1.15</v>
       </c>
       <c r="P24">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q24">
         <v>1.48</v>
@@ -6540,67 +6540,67 @@
         <v>1.46</v>
       </c>
       <c r="U24">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="X24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z24">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC24">
         <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE24">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24">
         <v>13.5</v>
       </c>
       <c r="AI24">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK24">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AL24">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AM24">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AN24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP24">
         <v>23</v>
@@ -6609,40 +6609,40 @@
         <v>17</v>
       </c>
       <c r="AR24">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS24">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AT24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU24">
         <v>9.199999999999999</v>
       </c>
       <c r="AV24">
+        <v>11</v>
+      </c>
+      <c r="AW24">
+        <v>20</v>
+      </c>
+      <c r="AX24">
+        <v>19.5</v>
+      </c>
+      <c r="AY24">
         <v>12</v>
-      </c>
-      <c r="AW24">
-        <v>18</v>
-      </c>
-      <c r="AX24">
-        <v>19</v>
-      </c>
-      <c r="AY24">
-        <v>11.5</v>
       </c>
       <c r="AZ24">
         <v>11.5</v>
       </c>
       <c r="BA24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24">
         <v>27</v>
       </c>
       <c r="BC24">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD24">
         <v>22</v>
@@ -6651,13 +6651,13 @@
         <v>36</v>
       </c>
       <c r="BF24">
+        <v>11</v>
+      </c>
+      <c r="BG24">
         <v>10</v>
       </c>
-      <c r="BG24">
-        <v>11</v>
-      </c>
       <c r="BH24">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI24">
         <v>3.95</v>
@@ -6666,31 +6666,31 @@
         <v>9.4</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL24">
+        <v>70</v>
+      </c>
+      <c r="BM24">
+        <v>7.6</v>
+      </c>
+      <c r="BN24">
+        <v>6.4</v>
+      </c>
+      <c r="BO24">
+        <v>5.7</v>
+      </c>
+      <c r="BP24">
+        <v>20</v>
+      </c>
+      <c r="BQ24">
+        <v>6</v>
+      </c>
+      <c r="BR24">
         <v>1000</v>
       </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>7.4</v>
-      </c>
-      <c r="BO24">
-        <v>5</v>
-      </c>
-      <c r="BP24">
-        <v>19.5</v>
-      </c>
-      <c r="BQ24">
-        <v>1.01</v>
-      </c>
-      <c r="BR24">
-        <v>26</v>
-      </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT24">
         <v>6.4</v>
@@ -6699,22 +6699,22 @@
         <v>5</v>
       </c>
       <c r="BV24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ24">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB24" t="s">
         <v>187</v>
@@ -6737,28 +6737,28 @@
         <v>174</v>
       </c>
       <c r="F25">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G25">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H25">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L25">
         <v>1.38</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25">
         <v>4.1</v>
@@ -6767,49 +6767,49 @@
         <v>1.29</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q25">
         <v>1.89</v>
       </c>
       <c r="R25">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25">
         <v>3.25</v>
       </c>
       <c r="T25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U25">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y25">
         <v>13</v>
       </c>
       <c r="Z25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA25">
         <v>50</v>
       </c>
       <c r="AB25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE25">
         <v>34</v>
@@ -6818,139 +6818,139 @@
         <v>17.5</v>
       </c>
       <c r="AG25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ25">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL25">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM25">
         <v>200</v>
       </c>
       <c r="AN25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO25">
         <v>27</v>
       </c>
       <c r="AP25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR25">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AS25">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT25">
         <v>9.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV25">
         <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX25">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY25">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD25">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE25">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BF25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG25">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH25">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BI25">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BJ25">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK25">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BN25">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO25">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP25">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ25">
+        <v>12.5</v>
+      </c>
+      <c r="BR25">
+        <v>30</v>
+      </c>
+      <c r="BS25">
+        <v>7.8</v>
+      </c>
+      <c r="BT25">
+        <v>6.6</v>
+      </c>
+      <c r="BU25">
+        <v>5.4</v>
+      </c>
+      <c r="BV25">
+        <v>24</v>
+      </c>
+      <c r="BW25">
+        <v>7.4</v>
+      </c>
+      <c r="BX25">
+        <v>34</v>
+      </c>
+      <c r="BY25">
         <v>8</v>
-      </c>
-      <c r="BR25">
-        <v>32</v>
-      </c>
-      <c r="BS25">
-        <v>9.4</v>
-      </c>
-      <c r="BT25">
-        <v>6.2</v>
-      </c>
-      <c r="BU25">
-        <v>5.2</v>
-      </c>
-      <c r="BV25">
-        <v>23</v>
-      </c>
-      <c r="BW25">
-        <v>8.4</v>
-      </c>
-      <c r="BX25">
-        <v>32</v>
-      </c>
-      <c r="BY25">
-        <v>9.4</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -6979,28 +6979,28 @@
         <v>175</v>
       </c>
       <c r="F26">
+        <v>1.66</v>
+      </c>
+      <c r="G26">
         <v>1.71</v>
       </c>
-      <c r="G26">
-        <v>1.74</v>
-      </c>
       <c r="H26">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K26">
         <v>4.4</v>
       </c>
       <c r="L26">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N26">
         <v>4.7</v>
@@ -7009,34 +7009,34 @@
         <v>1.25</v>
       </c>
       <c r="P26">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q26">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
         <v>1.48</v>
       </c>
       <c r="S26">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T26">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U26">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W26">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z26">
         <v>100</v>
@@ -7048,55 +7048,55 @@
         <v>10.5</v>
       </c>
       <c r="AC26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE26">
         <v>320</v>
       </c>
       <c r="AF26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI26">
         <v>250</v>
       </c>
       <c r="AJ26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK26">
         <v>17.5</v>
       </c>
       <c r="AL26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM26">
         <v>580</v>
       </c>
       <c r="AN26">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO26">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP26">
         <v>16</v>
       </c>
       <c r="AQ26">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR26">
         <v>34</v>
       </c>
       <c r="AS26">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AT26">
         <v>9</v>
@@ -7105,13 +7105,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV26">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW26">
         <v>44</v>
       </c>
       <c r="AX26">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY26">
         <v>9</v>
@@ -7123,10 +7123,10 @@
         <v>40</v>
       </c>
       <c r="BB26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD26">
         <v>24</v>
@@ -7135,70 +7135,70 @@
         <v>60</v>
       </c>
       <c r="BF26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB26" t="s">
         <v>187</v>
@@ -7221,10 +7221,10 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H27">
         <v>3.3</v>
@@ -7239,7 +7239,7 @@
         <v>3.45</v>
       </c>
       <c r="L27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7251,28 +7251,28 @@
         <v>1.43</v>
       </c>
       <c r="P27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T27">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X27">
         <v>11.5</v>
@@ -7287,7 +7287,7 @@
         <v>160</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27">
         <v>7.8</v>
@@ -7308,13 +7308,13 @@
         <v>21</v>
       </c>
       <c r="AI27">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK27">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7326,13 +7326,13 @@
         <v>30</v>
       </c>
       <c r="AO27">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AP27">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ27">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR27">
         <v>19</v>
@@ -7347,31 +7347,31 @@
         <v>6.6</v>
       </c>
       <c r="AV27">
+        <v>12.5</v>
+      </c>
+      <c r="AW27">
+        <v>30</v>
+      </c>
+      <c r="AX27">
         <v>13</v>
-      </c>
-      <c r="AW27">
-        <v>36</v>
-      </c>
-      <c r="AX27">
-        <v>12.5</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB27">
+        <v>25</v>
+      </c>
+      <c r="BC27">
         <v>24</v>
       </c>
-      <c r="BC27">
-        <v>22</v>
-      </c>
       <c r="BD27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE27">
         <v>90</v>
@@ -7380,67 +7380,67 @@
         <v>21</v>
       </c>
       <c r="BG27">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI27">
-        <v>1.16</v>
+        <v>2.52</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK27">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.16</v>
+        <v>7.4</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ27">
-        <v>1.16</v>
+        <v>5.8</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.16</v>
+        <v>6.4</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU27">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW27">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY27">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.16</v>
+        <v>6.4</v>
       </c>
       <c r="CB27" t="s">
         <v>187</v>
@@ -7463,16 +7463,16 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G28">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H28">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I28">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J28">
         <v>4.3</v>
@@ -7481,16 +7481,16 @@
         <v>4.6</v>
       </c>
       <c r="L28">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M28">
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P28">
         <v>3.35</v>
@@ -7502,22 +7502,22 @@
         <v>1.96</v>
       </c>
       <c r="S28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T28">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V28">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="W28">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y28">
         <v>21</v>
@@ -7529,7 +7529,7 @@
         <v>30</v>
       </c>
       <c r="AB28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC28">
         <v>12</v>
@@ -7538,40 +7538,40 @@
         <v>12.5</v>
       </c>
       <c r="AE28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG28">
         <v>15.5</v>
       </c>
       <c r="AH28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ28">
         <v>60</v>
       </c>
       <c r="AK28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL28">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM28">
         <v>42</v>
       </c>
       <c r="AN28">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="AO28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP28">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AQ28">
         <v>17.5</v>
@@ -7580,22 +7580,22 @@
         <v>17</v>
       </c>
       <c r="AS28">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AT28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU28">
         <v>10</v>
       </c>
       <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>16</v>
+      </c>
+      <c r="AX28">
         <v>10.5</v>
-      </c>
-      <c r="AW28">
-        <v>15.5</v>
-      </c>
-      <c r="AX28">
-        <v>13</v>
       </c>
       <c r="AY28">
         <v>13</v>
@@ -7607,79 +7607,79 @@
         <v>19.5</v>
       </c>
       <c r="BB28">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BC28">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD28">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE28">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BF28">
         <v>12.5</v>
       </c>
       <c r="BG28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM28">
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ28">
         <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS28">
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW28">
         <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA28">
         <v>1.01</v>
@@ -7705,22 +7705,22 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="G29">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="H29">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="I29">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="J29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L29">
         <v>1.47</v>
@@ -7729,19 +7729,19 @@
         <v>1.09</v>
       </c>
       <c r="N29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O29">
         <v>1.4</v>
       </c>
       <c r="P29">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S29">
         <v>4.2</v>
@@ -7753,91 +7753,91 @@
         <v>2</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X29">
         <v>11.5</v>
       </c>
       <c r="Y29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA29">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB29">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC29">
         <v>7.8</v>
       </c>
       <c r="AD29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF29">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH29">
         <v>19</v>
       </c>
       <c r="AI29">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ29">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK29">
+        <v>38</v>
+      </c>
+      <c r="AL29">
+        <v>55</v>
+      </c>
+      <c r="AM29">
+        <v>120</v>
+      </c>
+      <c r="AN29">
+        <v>38</v>
+      </c>
+      <c r="AO29">
+        <v>36</v>
+      </c>
+      <c r="AP29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ29">
+        <v>9.4</v>
+      </c>
+      <c r="AR29">
+        <v>15.5</v>
+      </c>
+      <c r="AS29">
         <v>34</v>
       </c>
-      <c r="AL29">
-        <v>50</v>
-      </c>
-      <c r="AM29">
-        <v>580</v>
-      </c>
-      <c r="AN29">
-        <v>32</v>
-      </c>
-      <c r="AO29">
-        <v>42</v>
-      </c>
-      <c r="AP29">
-        <v>10</v>
-      </c>
-      <c r="AQ29">
-        <v>10</v>
-      </c>
-      <c r="AR29">
-        <v>17</v>
-      </c>
-      <c r="AS29">
-        <v>44</v>
-      </c>
       <c r="AT29">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU29">
         <v>6.8</v>
       </c>
       <c r="AV29">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX29">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY29">
         <v>11</v>
@@ -7846,28 +7846,28 @@
         <v>17</v>
       </c>
       <c r="BA29">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BB29">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC29">
+        <v>30</v>
+      </c>
+      <c r="BD29">
+        <v>42</v>
+      </c>
+      <c r="BE29">
+        <v>80</v>
+      </c>
+      <c r="BF29">
         <v>27</v>
       </c>
-      <c r="BD29">
-        <v>40</v>
-      </c>
-      <c r="BE29">
-        <v>29</v>
-      </c>
-      <c r="BF29">
-        <v>25</v>
-      </c>
       <c r="BG29">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BH29">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI29">
         <v>2.76</v>
@@ -7876,55 +7876,55 @@
         <v>10.5</v>
       </c>
       <c r="BK29">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN29">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO29">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP29">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ29">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR29">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU29">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV29">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW29">
         <v>8.4</v>
       </c>
       <c r="BX29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
         <v>9.6</v>
-      </c>
-      <c r="BZ29">
-        <v>36</v>
-      </c>
-      <c r="CA29">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7947,7 +7947,7 @@
         <v>179</v>
       </c>
       <c r="F30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G30">
         <v>3.45</v>
@@ -7956,16 +7956,16 @@
         <v>2.42</v>
       </c>
       <c r="I30">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J30">
         <v>3.25</v>
       </c>
       <c r="K30">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L30">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M30">
         <v>1.09</v>
@@ -7974,37 +7974,37 @@
         <v>3.3</v>
       </c>
       <c r="O30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P30">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T30">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U30">
         <v>2</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X30">
         <v>12</v>
       </c>
       <c r="Y30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z30">
         <v>16</v>
@@ -8013,13 +8013,13 @@
         <v>38</v>
       </c>
       <c r="AB30">
+        <v>11.5</v>
+      </c>
+      <c r="AC30">
+        <v>7.6</v>
+      </c>
+      <c r="AD30">
         <v>12</v>
-      </c>
-      <c r="AC30">
-        <v>7.8</v>
-      </c>
-      <c r="AD30">
-        <v>12.5</v>
       </c>
       <c r="AE30">
         <v>32</v>
@@ -8028,7 +8028,7 @@
         <v>23</v>
       </c>
       <c r="AG30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH30">
         <v>19</v>
@@ -8049,10 +8049,10 @@
         <v>580</v>
       </c>
       <c r="AN30">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO30">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP30">
         <v>10</v>
@@ -8064,7 +8064,7 @@
         <v>13.5</v>
       </c>
       <c r="AS30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT30">
         <v>9.800000000000001</v>
@@ -8076,49 +8076,49 @@
         <v>10</v>
       </c>
       <c r="AW30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30">
         <v>16</v>
       </c>
       <c r="BA30">
+        <v>9.4</v>
+      </c>
+      <c r="BB30">
+        <v>10</v>
+      </c>
+      <c r="BC30">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB30">
+      <c r="BD30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE30">
+        <v>10</v>
+      </c>
+      <c r="BF30">
         <v>9.6</v>
       </c>
-      <c r="BC30">
-        <v>9</v>
-      </c>
-      <c r="BD30">
-        <v>9.6</v>
-      </c>
-      <c r="BE30">
-        <v>9.4</v>
-      </c>
-      <c r="BF30">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG30">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH30">
         <v>3.15</v>
       </c>
       <c r="BI30">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ30">
         <v>10.5</v>
       </c>
       <c r="BK30">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8130,7 +8130,7 @@
         <v>6.4</v>
       </c>
       <c r="BO30">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP30">
         <v>28</v>
@@ -8148,7 +8148,7 @@
         <v>5.4</v>
       </c>
       <c r="BU30">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV30">
         <v>20</v>
@@ -8189,7 +8189,7 @@
         <v>180</v>
       </c>
       <c r="F31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G31">
         <v>4.1</v>
@@ -8198,52 +8198,52 @@
         <v>2.42</v>
       </c>
       <c r="I31">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="J31">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L31">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M31">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O31">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="P31">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q31">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
         <v>1.17</v>
       </c>
       <c r="S31">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="T31">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U31">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
         <v>1.35</v>
       </c>
       <c r="X31">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y31">
         <v>8.800000000000001</v>
@@ -8270,7 +8270,7 @@
         <v>26</v>
       </c>
       <c r="AG31">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH31">
         <v>27</v>
@@ -8279,10 +8279,10 @@
         <v>75</v>
       </c>
       <c r="AJ31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL31">
         <v>95</v>
@@ -8303,106 +8303,106 @@
         <v>4.4</v>
       </c>
       <c r="AR31">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS31">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT31">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AU31">
         <v>4.2</v>
       </c>
       <c r="AV31">
+        <v>4</v>
+      </c>
+      <c r="AW31">
+        <v>5</v>
+      </c>
+      <c r="AX31">
+        <v>4.6</v>
+      </c>
+      <c r="AY31">
         <v>4.3</v>
       </c>
-      <c r="AW31">
-        <v>5.4</v>
-      </c>
-      <c r="AX31">
-        <v>4.9</v>
-      </c>
-      <c r="AY31">
-        <v>4.5</v>
-      </c>
       <c r="AZ31">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BA31">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB31">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC31">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD31">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE31">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF31">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG31">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI31">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU31">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8431,10 +8431,10 @@
         <v>181</v>
       </c>
       <c r="F32">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G32">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H32">
         <v>5.1</v>
@@ -8443,10 +8443,10 @@
         <v>5.6</v>
       </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L32">
         <v>1.51</v>
@@ -8455,7 +8455,7 @@
         <v>1.1</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
         <v>1.45</v>
@@ -8476,25 +8476,25 @@
         <v>2.06</v>
       </c>
       <c r="U32">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
         <v>2.06</v>
       </c>
       <c r="X32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y32">
         <v>15.5</v>
       </c>
       <c r="Z32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA32">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB32">
         <v>7.2</v>
@@ -8503,7 +8503,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE32">
         <v>120</v>
@@ -8515,22 +8515,22 @@
         <v>11</v>
       </c>
       <c r="AH32">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI32">
         <v>130</v>
       </c>
       <c r="AJ32">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK32">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL32">
         <v>60</v>
       </c>
       <c r="AM32">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN32">
         <v>19</v>
@@ -8545,10 +8545,10 @@
         <v>12.5</v>
       </c>
       <c r="AR32">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="AS32">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AT32">
         <v>6</v>
@@ -8557,40 +8557,40 @@
         <v>7</v>
       </c>
       <c r="AV32">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW32">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX32">
         <v>8.800000000000001</v>
       </c>
       <c r="AY32">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ32">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA32">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BB32">
         <v>18</v>
       </c>
       <c r="BC32">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD32">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE32">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BF32">
         <v>15</v>
       </c>
       <c r="BG32">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BH32">
         <v>3.4</v>
@@ -8602,52 +8602,52 @@
         <v>12</v>
       </c>
       <c r="BK32">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN32">
         <v>4.4</v>
       </c>
       <c r="BO32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP32">
         <v>14.5</v>
       </c>
       <c r="BQ32">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR32">
         <v>36</v>
       </c>
       <c r="BS32">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT32">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU32">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV32">
         <v>65</v>
       </c>
       <c r="BW32">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX32">
         <v>85</v>
       </c>
       <c r="BY32">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ32">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="CA32">
         <v>6.4</v>
@@ -8673,64 +8673,64 @@
         <v>182</v>
       </c>
       <c r="F33">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H33">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
         <v>4.4</v>
       </c>
       <c r="L33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M33">
         <v>1.06</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
         <v>1.3</v>
       </c>
       <c r="P33">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q33">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R33">
         <v>1.4</v>
       </c>
       <c r="S33">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W33">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X33">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z33">
         <v>55</v>
@@ -8745,16 +8745,16 @@
         <v>9.4</v>
       </c>
       <c r="AD33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE33">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF33">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH33">
         <v>23</v>
@@ -8766,22 +8766,22 @@
         <v>16</v>
       </c>
       <c r="AK33">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL33">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM33">
         <v>700</v>
       </c>
       <c r="AN33">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO33">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AP33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ33">
         <v>18.5</v>
@@ -8790,109 +8790,109 @@
         <v>10.5</v>
       </c>
       <c r="AS33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT33">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV33">
         <v>20</v>
       </c>
       <c r="AW33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX33">
         <v>8.6</v>
       </c>
       <c r="AY33">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC33">
         <v>14.5</v>
       </c>
       <c r="BD33">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE33">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BF33">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG33">
+        <v>11.5</v>
+      </c>
+      <c r="BH33">
+        <v>3.65</v>
+      </c>
+      <c r="BI33">
+        <v>3.3</v>
+      </c>
+      <c r="BJ33">
         <v>11</v>
       </c>
-      <c r="BH33">
-        <v>1000</v>
-      </c>
-      <c r="BI33">
-        <v>1.28</v>
-      </c>
-      <c r="BJ33">
-        <v>1000</v>
-      </c>
       <c r="BK33">
-        <v>1.86</v>
+        <v>7.8</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO33">
-        <v>1.33</v>
+        <v>3.7</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ33">
-        <v>1.86</v>
+        <v>5.7</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS33">
-        <v>1.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU33">
-        <v>1.86</v>
+        <v>5.7</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA33">
-        <v>1.28</v>
+        <v>7.4</v>
       </c>
       <c r="CB33" t="s">
         <v>187</v>
@@ -8915,58 +8915,58 @@
         <v>183</v>
       </c>
       <c r="F34">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G34">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H34">
         <v>3.95</v>
       </c>
       <c r="I34">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J34">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L34">
         <v>1.53</v>
       </c>
       <c r="M34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P34">
         <v>1.51</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R34">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S34">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="T34">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="V34">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W34">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="X34">
         <v>10.5</v>
@@ -8975,7 +8975,7 @@
         <v>13.5</v>
       </c>
       <c r="Z34">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA34">
         <v>140</v>
@@ -8984,13 +8984,13 @@
         <v>7.8</v>
       </c>
       <c r="AC34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD34">
         <v>23</v>
       </c>
       <c r="AE34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF34">
         <v>14</v>
@@ -9008,7 +9008,7 @@
         <v>34</v>
       </c>
       <c r="AK34">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL34">
         <v>70</v>
@@ -9017,10 +9017,10 @@
         <v>230</v>
       </c>
       <c r="AN34">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO34">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP34">
         <v>1.03</v>
@@ -9071,7 +9071,7 @@
         <v>1.03</v>
       </c>
       <c r="BF34">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG34">
         <v>1.01</v>
@@ -9092,43 +9092,43 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN34">
         <v>5.2</v>
       </c>
       <c r="BO34">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP34">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BQ34">
         <v>13.5</v>
       </c>
       <c r="BR34">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS34">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT34">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU34">
         <v>5.9</v>
       </c>
       <c r="BV34">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BW34">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX34">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY34">
-        <v>48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9157,7 +9157,7 @@
         <v>184</v>
       </c>
       <c r="F35">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G35">
         <v>2.94</v>
@@ -9166,10 +9166,10 @@
         <v>2.46</v>
       </c>
       <c r="I35">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J35">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K35">
         <v>4.1</v>
@@ -9190,10 +9190,10 @@
         <v>2.26</v>
       </c>
       <c r="Q35">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R35">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S35">
         <v>2.88</v>
@@ -9205,40 +9205,40 @@
         <v>2.38</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W35">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X35">
+        <v>24</v>
+      </c>
+      <c r="Y35">
+        <v>16.5</v>
+      </c>
+      <c r="Z35">
         <v>23</v>
       </c>
-      <c r="Y35">
-        <v>15</v>
-      </c>
-      <c r="Z35">
-        <v>21</v>
-      </c>
       <c r="AA35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB35">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35">
         <v>12.5</v>
       </c>
       <c r="AE35">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF35">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG35">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH35">
         <v>19.5</v>
@@ -9247,22 +9247,22 @@
         <v>42</v>
       </c>
       <c r="AJ35">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK35">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL35">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM35">
         <v>85</v>
       </c>
       <c r="AN35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO35">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP35">
         <v>16.5</v>
@@ -9271,25 +9271,25 @@
         <v>11.5</v>
       </c>
       <c r="AR35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS35">
         <v>21</v>
       </c>
       <c r="AT35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV35">
         <v>10.5</v>
       </c>
       <c r="AW35">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AX35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY35">
         <v>11</v>
@@ -9304,7 +9304,7 @@
         <v>1.03</v>
       </c>
       <c r="BC35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD35">
         <v>1.03</v>
@@ -9316,7 +9316,7 @@
         <v>17.5</v>
       </c>
       <c r="BG35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH35">
         <v>4</v>
@@ -9399,10 +9399,10 @@
         <v>185</v>
       </c>
       <c r="F36">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G36">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H36">
         <v>3</v>
@@ -9417,34 +9417,34 @@
         <v>3.2</v>
       </c>
       <c r="L36">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M36">
         <v>1.12</v>
       </c>
       <c r="N36">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
         <v>1.53</v>
       </c>
       <c r="P36">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q36">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R36">
         <v>1.21</v>
       </c>
       <c r="S36">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T36">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U36">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V36">
         <v>1.46</v>
@@ -9453,19 +9453,19 @@
         <v>1.54</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Y36">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z36">
         <v>20</v>
       </c>
       <c r="AA36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB36">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC36">
         <v>7.2</v>
@@ -9474,7 +9474,7 @@
         <v>14.5</v>
       </c>
       <c r="AE36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF36">
         <v>17</v>
@@ -9486,16 +9486,16 @@
         <v>23</v>
       </c>
       <c r="AI36">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ36">
         <v>60</v>
       </c>
       <c r="AK36">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL36">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM36">
         <v>200</v>
@@ -9504,7 +9504,7 @@
         <v>55</v>
       </c>
       <c r="AO36">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP36">
         <v>8</v>
@@ -9516,7 +9516,7 @@
         <v>17</v>
       </c>
       <c r="AS36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT36">
         <v>7.6</v>
@@ -9528,7 +9528,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX36">
         <v>14.5</v>
@@ -9537,88 +9537,88 @@
         <v>11.5</v>
       </c>
       <c r="AZ36">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA36">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB36">
         <v>10.5</v>
       </c>
       <c r="BC36">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD36">
         <v>10.5</v>
       </c>
       <c r="BE36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF36">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BG36">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BH36">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BI36">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BJ36">
         <v>11</v>
       </c>
       <c r="BK36">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN36">
         <v>5.6</v>
       </c>
       <c r="BO36">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT36">
         <v>6</v>
       </c>
       <c r="BU36">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB36" t="s">
         <v>187</v>
@@ -9641,13 +9641,13 @@
         <v>186</v>
       </c>
       <c r="F37">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -9665,7 +9665,7 @@
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O37">
         <v>1.4</v>
@@ -9677,28 +9677,28 @@
         <v>2.2</v>
       </c>
       <c r="R37">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S37">
         <v>4.1</v>
       </c>
       <c r="T37">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V37">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W37">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y37">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z37">
         <v>55</v>
@@ -9707,100 +9707,100 @@
         <v>220</v>
       </c>
       <c r="AB37">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC37">
         <v>8.800000000000001</v>
       </c>
       <c r="AD37">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE37">
         <v>120</v>
       </c>
       <c r="AF37">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH37">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI37">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ37">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AK37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL37">
         <v>55</v>
       </c>
       <c r="AM37">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN37">
         <v>12.5</v>
       </c>
       <c r="AO37">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AP37">
         <v>10.5</v>
       </c>
       <c r="AQ37">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR37">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AS37">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AT37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU37">
         <v>8</v>
       </c>
       <c r="AV37">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW37">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AX37">
         <v>8.199999999999999</v>
       </c>
       <c r="AY37">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37">
         <v>22</v>
       </c>
       <c r="BA37">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BB37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC37">
         <v>17.5</v>
       </c>
       <c r="BD37">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BE37">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BF37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG37">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH37">
         <v>3.2</v>
@@ -9809,58 +9809,58 @@
         <v>2.88</v>
       </c>
       <c r="BJ37">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BK37">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BN37">
         <v>4.1</v>
       </c>
       <c r="BO37">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP37">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BQ37">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS37">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT37">
         <v>12</v>
       </c>
       <c r="BU37">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV37">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BW37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BX37">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BY37">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="CA37">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB37" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-25.xlsx
@@ -577,7 +577,7 @@
     <t>Londrina</t>
   </si>
   <si>
-    <t>2026-09-25 06:19:10</t>
+    <t>2026-09-25 08:39:13</t>
   </si>
 </sst>
 </file>
@@ -1171,226 +1171,226 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="G2">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
         <v>2.36</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>2.56</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA2">
         <v>34</v>
       </c>
       <c r="AB2">
+        <v>9.6</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>13.5</v>
+      </c>
+      <c r="AE2">
+        <v>40</v>
+      </c>
+      <c r="AF2">
+        <v>26</v>
+      </c>
+      <c r="AG2">
+        <v>20</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>90</v>
+      </c>
+      <c r="AJ2">
+        <v>110</v>
+      </c>
+      <c r="AK2">
+        <v>85</v>
+      </c>
+      <c r="AL2">
+        <v>140</v>
+      </c>
+      <c r="AM2">
+        <v>420</v>
+      </c>
+      <c r="AN2">
+        <v>140</v>
+      </c>
+      <c r="AO2">
+        <v>44</v>
+      </c>
+      <c r="AP2">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2">
+        <v>6</v>
+      </c>
+      <c r="AR2">
+        <v>10.5</v>
+      </c>
+      <c r="AS2">
+        <v>29</v>
+      </c>
+      <c r="AT2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
         <v>22</v>
       </c>
-      <c r="AC2">
-        <v>8.4</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
-      </c>
-      <c r="AE2">
-        <v>22</v>
-      </c>
-      <c r="AF2">
-        <v>29</v>
-      </c>
-      <c r="AG2">
-        <v>15.5</v>
-      </c>
-      <c r="AH2">
-        <v>15</v>
-      </c>
-      <c r="AI2">
-        <v>32</v>
-      </c>
-      <c r="AJ2">
-        <v>120</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>70</v>
-      </c>
-      <c r="AN2">
-        <v>29</v>
-      </c>
-      <c r="AO2">
-        <v>14.5</v>
-      </c>
-      <c r="AP2">
-        <v>18.5</v>
-      </c>
-      <c r="AQ2">
-        <v>11.5</v>
-      </c>
-      <c r="AR2">
-        <v>15</v>
-      </c>
-      <c r="AS2">
-        <v>14.5</v>
-      </c>
-      <c r="AT2">
-        <v>15</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>18</v>
-      </c>
-      <c r="AX2">
-        <v>15.5</v>
-      </c>
       <c r="AY2">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BA2">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="BC2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="BE2">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="BG2">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>1.63</v>
       </c>
       <c r="BI2">
-        <v>3.4</v>
+        <v>1.58</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>80</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>910</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BX2">
-        <v>27</v>
+        <v>320</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>160</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>180</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,22 +1413,22 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
         <v>1.46</v>
@@ -1437,202 +1437,202 @@
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AB3">
         <v>11</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
+        <v>32</v>
+      </c>
+      <c r="AF3">
+        <v>21</v>
+      </c>
+      <c r="AG3">
+        <v>13.5</v>
+      </c>
+      <c r="AH3">
+        <v>22</v>
+      </c>
+      <c r="AI3">
+        <v>55</v>
+      </c>
+      <c r="AJ3">
+        <v>65</v>
+      </c>
+      <c r="AK3">
+        <v>46</v>
+      </c>
+      <c r="AL3">
         <v>60</v>
       </c>
-      <c r="AF3">
-        <v>17.5</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <v>70</v>
-      </c>
-      <c r="AJ3">
+      <c r="AM3">
+        <v>130</v>
+      </c>
+      <c r="AN3">
+        <v>46</v>
+      </c>
+      <c r="AO3">
+        <v>26</v>
+      </c>
+      <c r="AP3">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3">
+        <v>8.4</v>
+      </c>
+      <c r="AR3">
+        <v>13.5</v>
+      </c>
+      <c r="AS3">
+        <v>27</v>
+      </c>
+      <c r="AT3">
+        <v>9.4</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
+      <c r="AX3">
+        <v>17</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>34</v>
+      </c>
+      <c r="BB3">
+        <v>38</v>
+      </c>
+      <c r="BC3">
+        <v>27</v>
+      </c>
+      <c r="BD3">
         <v>40</v>
       </c>
-      <c r="AK3">
-        <v>34</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>580</v>
-      </c>
-      <c r="AN3">
-        <v>24</v>
-      </c>
-      <c r="AO3">
-        <v>65</v>
-      </c>
-      <c r="AP3">
-        <v>5.7</v>
-      </c>
-      <c r="AQ3">
-        <v>5</v>
-      </c>
-      <c r="AR3">
-        <v>4.1</v>
-      </c>
-      <c r="AS3">
-        <v>4.5</v>
-      </c>
-      <c r="AT3">
-        <v>4.2</v>
-      </c>
-      <c r="AU3">
-        <v>3.7</v>
-      </c>
-      <c r="AV3">
-        <v>6.2</v>
-      </c>
-      <c r="AW3">
-        <v>4.4</v>
-      </c>
-      <c r="AX3">
-        <v>4.1</v>
-      </c>
-      <c r="AY3">
-        <v>5.2</v>
-      </c>
-      <c r="AZ3">
-        <v>4.3</v>
-      </c>
-      <c r="BA3">
-        <v>4.4</v>
-      </c>
-      <c r="BB3">
-        <v>4.3</v>
-      </c>
-      <c r="BC3">
-        <v>4.2</v>
-      </c>
-      <c r="BD3">
-        <v>4.3</v>
-      </c>
       <c r="BE3">
-        <v>4.6</v>
+        <v>80</v>
       </c>
       <c r="BF3">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BG3">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BH3">
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BT3">
+        <v>5.5</v>
+      </c>
+      <c r="BU3">
+        <v>4.8</v>
+      </c>
+      <c r="BV3">
+        <v>24</v>
+      </c>
+      <c r="BW3">
+        <v>16.5</v>
+      </c>
+      <c r="BX3">
+        <v>44</v>
+      </c>
+      <c r="BY3">
         <v>8</v>
       </c>
-      <c r="BU3">
-        <v>3.65</v>
-      </c>
-      <c r="BV3">
+      <c r="BZ3">
         <v>38</v>
       </c>
-      <c r="BW3">
-        <v>5.1</v>
-      </c>
-      <c r="BX3">
-        <v>55</v>
-      </c>
-      <c r="BY3">
-        <v>5.3</v>
-      </c>
-      <c r="BZ3">
-        <v>40</v>
-      </c>
       <c r="CA3">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1658,10 +1658,10 @@
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
         <v>3.5</v>
@@ -1679,16 +1679,16 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R4">
         <v>1.32</v>
@@ -1697,7 +1697,7 @@
         <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U4">
         <v>2.06</v>
@@ -1712,7 +1712,7 @@
         <v>14</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
         <v>29</v>
@@ -1721,7 +1721,7 @@
         <v>130</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>8.199999999999999</v>
@@ -1742,13 +1742,13 @@
         <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ4">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL4">
         <v>110</v>
@@ -1757,7 +1757,7 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO4">
         <v>42</v>
@@ -1766,25 +1766,25 @@
         <v>11</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AR4">
         <v>18.5</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX4">
         <v>13.5</v>
@@ -1793,19 +1793,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB4">
         <v>24</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BE4">
         <v>65</v>
@@ -1817,10 +1817,10 @@
         <v>19</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
         <v>10</v>
@@ -1832,16 +1832,16 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4">
         <v>5.6</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4">
         <v>6.6</v>
@@ -1850,19 +1850,19 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1874,7 +1874,7 @@
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,22 +1897,22 @@
         <v>154</v>
       </c>
       <c r="F5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H5">
         <v>2.76</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1921,43 +1921,43 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA5">
         <v>50</v>
@@ -1969,10 +1969,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF5">
         <v>21</v>
@@ -1981,16 +1981,16 @@
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL5">
         <v>38</v>
@@ -1999,28 +1999,28 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
         <v>18</v>
       </c>
       <c r="AS5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
         <v>11</v>
@@ -2029,22 +2029,22 @@
         <v>22</v>
       </c>
       <c r="AX5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB5">
         <v>25</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD5">
         <v>24</v>
@@ -2053,22 +2053,22 @@
         <v>46</v>
       </c>
       <c r="BF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2077,7 +2077,7 @@
         <v>4.3</v>
       </c>
       <c r="BN5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO5">
         <v>4.5</v>
@@ -2092,7 +2092,7 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BT5">
         <v>7.4</v>
@@ -2101,22 +2101,22 @@
         <v>4.7</v>
       </c>
       <c r="BV5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BX5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,31 +2139,31 @@
         <v>155</v>
       </c>
       <c r="F6">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="G6">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H6">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
         <v>1.39</v>
@@ -2172,25 +2172,25 @@
         <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X6">
         <v>12.5</v>
@@ -2199,19 +2199,19 @@
         <v>14.5</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA6">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB6">
         <v>7.8</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE6">
         <v>70</v>
@@ -2226,13 +2226,13 @@
         <v>21</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>23</v>
       </c>
       <c r="AK6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6">
         <v>40</v>
@@ -2241,13 +2241,13 @@
         <v>130</v>
       </c>
       <c r="AN6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2262,10 +2262,10 @@
         <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
         <v>60</v>
@@ -2280,10 +2280,10 @@
         <v>20</v>
       </c>
       <c r="BA6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC6">
         <v>21</v>
@@ -2292,7 +2292,7 @@
         <v>38</v>
       </c>
       <c r="BE6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF6">
         <v>15</v>
@@ -2301,22 +2301,22 @@
         <v>75</v>
       </c>
       <c r="BH6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL6">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>4.4</v>
@@ -2334,31 +2334,31 @@
         <v>34</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
         <v>32</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,10 +2381,10 @@
         <v>156</v>
       </c>
       <c r="F7">
+        <v>1.91</v>
+      </c>
+      <c r="G7">
         <v>1.92</v>
-      </c>
-      <c r="G7">
-        <v>1.93</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -2393,46 +2393,46 @@
         <v>5.1</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M7">
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
         <v>4.5</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V7">
         <v>1.24</v>
       </c>
       <c r="W7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X7">
         <v>11</v>
@@ -2444,31 +2444,31 @@
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE7">
         <v>80</v>
       </c>
       <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
         <v>10.5</v>
-      </c>
-      <c r="AG7">
-        <v>10</v>
       </c>
       <c r="AH7">
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2483,13 +2483,13 @@
         <v>160</v>
       </c>
       <c r="AN7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
         <v>13</v>
@@ -2498,31 +2498,31 @@
         <v>32</v>
       </c>
       <c r="AS7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY7">
         <v>10</v>
-      </c>
-      <c r="AY7">
-        <v>9.6</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2534,22 +2534,22 @@
         <v>42</v>
       </c>
       <c r="BE7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF7">
         <v>16</v>
       </c>
       <c r="BG7">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
         <v>9.800000000000001</v>
@@ -2561,46 +2561,46 @@
         <v>70</v>
       </c>
       <c r="BN7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO7">
         <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR7">
         <v>34</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT7">
         <v>8.199999999999999</v>
       </c>
       <c r="BU7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BW7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX7">
         <v>65</v>
       </c>
       <c r="BY7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ7">
         <v>32</v>
       </c>
       <c r="CA7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2623,16 +2623,16 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
         <v>4.4</v>
@@ -2641,31 +2641,31 @@
         <v>4.9</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
         <v>2.08</v>
@@ -2674,13 +2674,13 @@
         <v>1.17</v>
       </c>
       <c r="W8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z8">
         <v>500</v>
@@ -2689,10 +2689,10 @@
         <v>500</v>
       </c>
       <c r="AB8">
+        <v>11</v>
+      </c>
+      <c r="AC8">
         <v>11.5</v>
-      </c>
-      <c r="AC8">
-        <v>12</v>
       </c>
       <c r="AD8">
         <v>40</v>
@@ -2737,10 +2737,10 @@
         <v>21</v>
       </c>
       <c r="AR8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS8">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8">
         <v>9</v>
@@ -2752,7 +2752,7 @@
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX8">
         <v>8.800000000000001</v>
@@ -2764,7 +2764,7 @@
         <v>17</v>
       </c>
       <c r="BA8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB8">
         <v>12</v>
@@ -2776,19 +2776,19 @@
         <v>12</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2800,49 +2800,49 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BP8">
         <v>10</v>
       </c>
       <c r="BQ8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
         <v>10.5</v>
       </c>
       <c r="BU8">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>187</v>
@@ -2865,7 +2865,7 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G9">
         <v>1.27</v>
@@ -2874,10 +2874,10 @@
         <v>10.5</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K9">
         <v>8.6</v>
@@ -2901,13 +2901,13 @@
         <v>1.27</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -2928,7 +2928,7 @@
         <v>150</v>
       </c>
       <c r="AA9">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB9">
         <v>23</v>
@@ -2943,10 +2943,10 @@
         <v>150</v>
       </c>
       <c r="AF9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG9">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
         <v>30</v>
@@ -2958,7 +2958,7 @@
         <v>15</v>
       </c>
       <c r="AK9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL9">
         <v>30</v>
@@ -2967,22 +2967,22 @@
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AO9">
         <v>100</v>
       </c>
       <c r="AP9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT9">
         <v>17</v>
@@ -2991,10 +2991,10 @@
         <v>17.5</v>
       </c>
       <c r="AV9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX9">
         <v>12</v>
@@ -3003,10 +3003,10 @@
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB9">
         <v>11</v>
@@ -3018,10 +3018,10 @@
         <v>22</v>
       </c>
       <c r="BE9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BG9">
         <v>10.5</v>
@@ -3033,52 +3033,52 @@
         <v>5.3</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM9">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BQ9">
         <v>5.4</v>
       </c>
       <c r="BR9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS9">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BT9">
         <v>17.5</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV9">
         <v>80</v>
       </c>
       <c r="BW9">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX9">
         <v>70</v>
       </c>
       <c r="BY9">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>159</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G10">
         <v>7.4</v>
@@ -3116,13 +3116,13 @@
         <v>1.51</v>
       </c>
       <c r="I10">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -3131,31 +3131,31 @@
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O10">
         <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R10">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S10">
         <v>2.4</v>
       </c>
       <c r="T10">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W10">
         <v>1.16</v>
@@ -3167,13 +3167,13 @@
         <v>12</v>
       </c>
       <c r="Z10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA10">
         <v>15.5</v>
       </c>
       <c r="AB10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC10">
         <v>12</v>
@@ -3212,7 +3212,7 @@
         <v>85</v>
       </c>
       <c r="AO10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP10">
         <v>19.5</v>
@@ -3227,7 +3227,7 @@
         <v>12.5</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AU10">
         <v>9.800000000000001</v>
@@ -3239,7 +3239,7 @@
         <v>12.5</v>
       </c>
       <c r="AX10">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY10">
         <v>20</v>
@@ -3251,58 +3251,58 @@
         <v>21</v>
       </c>
       <c r="BB10">
+        <v>9.4</v>
+      </c>
+      <c r="BC10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD10">
         <v>8.6</v>
       </c>
-      <c r="BC10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD10">
-        <v>8</v>
-      </c>
       <c r="BE10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10">
         <v>5.3</v>
       </c>
       <c r="BH10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10">
         <v>11</v>
       </c>
       <c r="BO10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP10">
         <v>50</v>
       </c>
       <c r="BQ10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT10">
         <v>4.6</v>
@@ -3311,10 +3311,10 @@
         <v>3.55</v>
       </c>
       <c r="BV10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
         <v>21</v>
@@ -3326,7 +3326,7 @@
         <v>13</v>
       </c>
       <c r="CA10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3349,28 +3349,28 @@
         <v>160</v>
       </c>
       <c r="F11">
+        <v>2.92</v>
+      </c>
+      <c r="G11">
         <v>3.05</v>
       </c>
-      <c r="G11">
-        <v>3.25</v>
-      </c>
       <c r="H11">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="I11">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
         <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
         <v>4.7</v>
@@ -3388,49 +3388,49 @@
         <v>1.49</v>
       </c>
       <c r="S11">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T11">
+        <v>1.62</v>
+      </c>
+      <c r="U11">
+        <v>2.4</v>
+      </c>
+      <c r="V11">
         <v>1.64</v>
       </c>
-      <c r="U11">
-        <v>2.36</v>
-      </c>
-      <c r="V11">
-        <v>1.7</v>
-      </c>
       <c r="W11">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X11">
+        <v>19</v>
+      </c>
+      <c r="Y11">
+        <v>13.5</v>
+      </c>
+      <c r="Z11">
         <v>18.5</v>
       </c>
-      <c r="Y11">
-        <v>12.5</v>
-      </c>
-      <c r="Z11">
-        <v>17.5</v>
-      </c>
       <c r="AA11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB11">
         <v>15</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11">
         <v>12</v>
       </c>
       <c r="AE11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
         <v>16</v>
@@ -3439,10 +3439,10 @@
         <v>34</v>
       </c>
       <c r="AJ11">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL11">
         <v>50</v>
@@ -3451,25 +3451,25 @@
         <v>80</v>
       </c>
       <c r="AN11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AP11">
         <v>16</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU11">
         <v>7.6</v>
@@ -3481,10 +3481,10 @@
         <v>20</v>
       </c>
       <c r="AX11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
         <v>13.5</v>
@@ -3493,10 +3493,10 @@
         <v>26</v>
       </c>
       <c r="BB11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD11">
         <v>27</v>
@@ -3505,70 +3505,70 @@
         <v>55</v>
       </c>
       <c r="BF11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI11">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ11">
         <v>9</v>
       </c>
       <c r="BK11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BR11">
         <v>32</v>
       </c>
       <c r="BS11">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BV11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BW11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY11">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
         <v>21</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="s">
         <v>187</v>
@@ -3597,16 +3597,16 @@
         <v>1.59</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
         <v>1.35</v>
@@ -3621,7 +3621,7 @@
         <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
         <v>1.75</v>
@@ -3630,19 +3630,19 @@
         <v>1.5</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U12">
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X12">
         <v>20</v>
@@ -3669,7 +3669,7 @@
         <v>90</v>
       </c>
       <c r="AF12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG12">
         <v>9.6</v>
@@ -3693,7 +3693,7 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO12">
         <v>110</v>
@@ -3702,7 +3702,7 @@
         <v>18</v>
       </c>
       <c r="AQ12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR12">
         <v>50</v>
@@ -3711,7 +3711,7 @@
         <v>29</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
         <v>9.4</v>
@@ -3732,7 +3732,7 @@
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB12">
         <v>13.5</v>
@@ -3744,16 +3744,16 @@
         <v>29</v>
       </c>
       <c r="BE12">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="BF12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG12">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI12">
         <v>3.6</v>
@@ -3762,40 +3762,40 @@
         <v>11</v>
       </c>
       <c r="BK12">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BL12">
         <v>130</v>
       </c>
       <c r="BM12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN12">
         <v>4.1</v>
       </c>
       <c r="BO12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP12">
         <v>9.6</v>
       </c>
       <c r="BQ12">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS12">
         <v>10</v>
       </c>
       <c r="BT12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BV12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW12">
         <v>13</v>
@@ -3810,7 +3810,7 @@
         <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="s">
         <v>187</v>
@@ -3833,25 +3833,25 @@
         <v>162</v>
       </c>
       <c r="F13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H13">
+        <v>7.6</v>
+      </c>
+      <c r="I13">
         <v>7.8</v>
       </c>
-      <c r="I13">
-        <v>8</v>
-      </c>
       <c r="J13">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
         <v>1.04</v>
@@ -3863,10 +3863,10 @@
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R13">
         <v>1.57</v>
@@ -3875,82 +3875,82 @@
         <v>2.68</v>
       </c>
       <c r="T13">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U13">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V13">
         <v>1.14</v>
       </c>
       <c r="W13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X13">
         <v>23</v>
       </c>
       <c r="Y13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z13">
         <v>70</v>
       </c>
       <c r="AA13">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE13">
         <v>100</v>
       </c>
       <c r="AF13">
+        <v>9.6</v>
+      </c>
+      <c r="AG13">
         <v>9.4</v>
       </c>
-      <c r="AG13">
-        <v>9.6</v>
-      </c>
       <c r="AH13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ13">
         <v>13</v>
       </c>
       <c r="AK13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM13">
         <v>110</v>
       </c>
       <c r="AN13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO13">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP13">
         <v>20</v>
       </c>
       <c r="AQ13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS13">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AT13">
         <v>9.6</v>
@@ -3959,22 +3959,22 @@
         <v>10.5</v>
       </c>
       <c r="AV13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AX13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
         <v>20</v>
       </c>
       <c r="BA13">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
@@ -3983,13 +3983,13 @@
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE13">
         <v>90</v>
       </c>
       <c r="BF13">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG13">
         <v>95</v>
@@ -3998,7 +3998,7 @@
         <v>4.2</v>
       </c>
       <c r="BI13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ13">
         <v>10.5</v>
@@ -4013,46 +4013,46 @@
         <v>50</v>
       </c>
       <c r="BN13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR13">
         <v>22</v>
       </c>
       <c r="BS13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
+        <v>11</v>
+      </c>
+      <c r="BU13">
+        <v>9.6</v>
+      </c>
+      <c r="BV13">
+        <v>65</v>
+      </c>
+      <c r="BW13">
         <v>11.5</v>
       </c>
-      <c r="BU13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BV13">
-        <v>70</v>
-      </c>
-      <c r="BW13">
-        <v>12.5</v>
-      </c>
       <c r="BX13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="s">
         <v>187</v>
@@ -4075,76 +4075,76 @@
         <v>163</v>
       </c>
       <c r="F14">
+        <v>9.6</v>
+      </c>
+      <c r="G14">
         <v>9.800000000000001</v>
       </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
       <c r="H14">
+        <v>1.35</v>
+      </c>
+      <c r="I14">
         <v>1.36</v>
       </c>
-      <c r="I14">
-        <v>1.37</v>
-      </c>
       <c r="J14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L14">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M14">
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P14">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R14">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S14">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="T14">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W14">
         <v>1.11</v>
       </c>
       <c r="X14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Y14">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA14">
         <v>12.5</v>
       </c>
       <c r="AB14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD14">
         <v>11</v>
@@ -4159,49 +4159,49 @@
         <v>34</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
         <v>26</v>
       </c>
       <c r="AJ14">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AK14">
         <v>110</v>
       </c>
       <c r="AL14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN14">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AO14">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AP14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AQ14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AU14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
         <v>12</v>
@@ -4213,82 +4213,82 @@
         <v>30</v>
       </c>
       <c r="AZ14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA14">
         <v>24</v>
       </c>
       <c r="BB14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="BC14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BD14">
+        <v>60</v>
+      </c>
+      <c r="BE14">
         <v>65</v>
       </c>
-      <c r="BE14">
-        <v>70</v>
-      </c>
       <c r="BF14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BG14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BH14">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI14">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BJ14">
+        <v>10</v>
+      </c>
+      <c r="BK14">
+        <v>9</v>
+      </c>
+      <c r="BL14">
+        <v>80</v>
+      </c>
+      <c r="BM14">
+        <v>14</v>
+      </c>
+      <c r="BN14">
+        <v>13</v>
+      </c>
+      <c r="BO14">
+        <v>11.5</v>
+      </c>
+      <c r="BP14">
+        <v>60</v>
+      </c>
+      <c r="BQ14">
+        <v>13</v>
+      </c>
+      <c r="BR14">
+        <v>48</v>
+      </c>
+      <c r="BS14">
         <v>12.5</v>
       </c>
-      <c r="BK14">
-        <v>8</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>4.2</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>4.2</v>
-      </c>
-      <c r="BR14">
-        <v>70</v>
-      </c>
-      <c r="BS14">
-        <v>3.7</v>
-      </c>
       <c r="BT14">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BU14">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY14">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4317,10 +4317,10 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G15">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -4329,13 +4329,13 @@
         <v>5.1</v>
       </c>
       <c r="J15">
+        <v>3.7</v>
+      </c>
+      <c r="K15">
         <v>3.75</v>
       </c>
-      <c r="K15">
-        <v>3.8</v>
-      </c>
       <c r="L15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M15">
         <v>1.08</v>
@@ -4344,10 +4344,10 @@
         <v>3.55</v>
       </c>
       <c r="O15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
         <v>2.12</v>
@@ -4356,25 +4356,25 @@
         <v>1.32</v>
       </c>
       <c r="S15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T15">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U15">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
         <v>1.24</v>
       </c>
       <c r="W15">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X15">
         <v>12.5</v>
       </c>
       <c r="Y15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z15">
         <v>36</v>
@@ -4383,7 +4383,7 @@
         <v>130</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC15">
         <v>8.199999999999999</v>
@@ -4392,13 +4392,13 @@
         <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF15">
         <v>10.5</v>
       </c>
       <c r="AG15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH15">
         <v>20</v>
@@ -4407,7 +4407,7 @@
         <v>80</v>
       </c>
       <c r="AJ15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK15">
         <v>21</v>
@@ -4419,7 +4419,7 @@
         <v>130</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO15">
         <v>100</v>
@@ -4437,13 +4437,13 @@
         <v>95</v>
       </c>
       <c r="AT15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
         <v>7.8</v>
       </c>
       <c r="AV15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW15">
         <v>60</v>
@@ -4458,7 +4458,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB15">
         <v>18.5</v>
@@ -4467,10 +4467,10 @@
         <v>19</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE15">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF15">
         <v>13</v>
@@ -4482,61 +4482,61 @@
         <v>3.2</v>
       </c>
       <c r="BI15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK15">
         <v>9.4</v>
       </c>
       <c r="BL15">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM15">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>4.3</v>
       </c>
       <c r="BO15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS15">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU15">
         <v>7.4</v>
       </c>
       <c r="BV15">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BW15">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BX15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY15">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="CA15">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB15" t="s">
         <v>187</v>
@@ -4565,10 +4565,10 @@
         <v>2.36</v>
       </c>
       <c r="H16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J16">
         <v>3.7</v>
@@ -4577,34 +4577,34 @@
         <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S16">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T16">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U16">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V16">
         <v>1.43</v>
@@ -4613,19 +4613,19 @@
         <v>1.73</v>
       </c>
       <c r="X16">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA16">
         <v>55</v>
       </c>
       <c r="AB16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC16">
         <v>8.4</v>
@@ -4637,10 +4637,10 @@
         <v>32</v>
       </c>
       <c r="AF16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH16">
         <v>14</v>
@@ -4655,34 +4655,34 @@
         <v>22</v>
       </c>
       <c r="AL16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO16">
         <v>24</v>
       </c>
       <c r="AP16">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16">
         <v>15.5</v>
       </c>
       <c r="AR16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS16">
         <v>50</v>
       </c>
       <c r="AT16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16">
         <v>13</v>
@@ -4706,25 +4706,25 @@
         <v>29</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG16">
         <v>23</v>
       </c>
       <c r="BH16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16">
         <v>8.6</v>
@@ -4733,52 +4733,52 @@
         <v>7.8</v>
       </c>
       <c r="BL16">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM16">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BN16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO16">
         <v>5</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ16">
         <v>14</v>
       </c>
       <c r="BR16">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BS16">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
         <v>6.6</v>
       </c>
       <c r="BU16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW16">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BX16">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BY16">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CA16">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="CB16" t="s">
         <v>187</v>
@@ -4801,100 +4801,100 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H17">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I17">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J17">
+        <v>3.3</v>
+      </c>
+      <c r="K17">
         <v>3.35</v>
       </c>
-      <c r="K17">
-        <v>3.4</v>
-      </c>
       <c r="L17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M17">
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P17">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q17">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
         <v>1.27</v>
       </c>
       <c r="S17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T17">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U17">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W17">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD17">
         <v>14.5</v>
       </c>
       <c r="AE17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17">
         <v>60</v>
       </c>
       <c r="AJ17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL17">
         <v>48</v>
@@ -4903,25 +4903,25 @@
         <v>130</v>
       </c>
       <c r="AN17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO17">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS17">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4930,13 +4930,13 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17">
         <v>17.5</v>
@@ -4945,10 +4945,10 @@
         <v>50</v>
       </c>
       <c r="BB17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BC17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD17">
         <v>44</v>
@@ -4957,16 +4957,16 @@
         <v>95</v>
       </c>
       <c r="BF17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BG17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BH17">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI17">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
@@ -4978,49 +4978,49 @@
         <v>190</v>
       </c>
       <c r="BM17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BR17">
         <v>46</v>
       </c>
       <c r="BS17">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU17">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX17">
         <v>55</v>
       </c>
       <c r="BY17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA17">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5049,10 +5049,10 @@
         <v>1.66</v>
       </c>
       <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
         <v>6.2</v>
-      </c>
-      <c r="I18">
-        <v>6.4</v>
       </c>
       <c r="J18">
         <v>4.2</v>
@@ -5061,55 +5061,55 @@
         <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P18">
+        <v>2.18</v>
+      </c>
+      <c r="Q18">
+        <v>1.82</v>
+      </c>
+      <c r="R18">
+        <v>1.45</v>
+      </c>
+      <c r="S18">
+        <v>3.05</v>
+      </c>
+      <c r="T18">
+        <v>1.86</v>
+      </c>
+      <c r="U18">
         <v>2.1</v>
       </c>
-      <c r="Q18">
-        <v>1.88</v>
-      </c>
-      <c r="R18">
-        <v>1.42</v>
-      </c>
-      <c r="S18">
-        <v>3.3</v>
-      </c>
-      <c r="T18">
-        <v>1.92</v>
-      </c>
-      <c r="U18">
-        <v>2.04</v>
-      </c>
       <c r="V18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W18">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X18">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA18">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18">
         <v>9.4</v>
@@ -5118,52 +5118,52 @@
         <v>23</v>
       </c>
       <c r="AE18">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF18">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG18">
         <v>9.6</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI18">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK18">
         <v>16.5</v>
       </c>
       <c r="AL18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM18">
         <v>120</v>
       </c>
       <c r="AN18">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO18">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR18">
         <v>46</v>
       </c>
       <c r="AS18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU18">
         <v>9</v>
@@ -5172,16 +5172,16 @@
         <v>21</v>
       </c>
       <c r="AW18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX18">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA18">
         <v>70</v>
@@ -5193,76 +5193,76 @@
         <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE18">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BF18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BH18">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BI18">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL18">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP18">
         <v>11</v>
       </c>
       <c r="BQ18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR18">
+        <v>25</v>
+      </c>
+      <c r="BS18">
+        <v>9.6</v>
+      </c>
+      <c r="BT18">
         <v>9.4</v>
-      </c>
-      <c r="BR18">
-        <v>27</v>
-      </c>
-      <c r="BS18">
-        <v>10.5</v>
-      </c>
-      <c r="BT18">
-        <v>9.6</v>
       </c>
       <c r="BU18">
         <v>8.4</v>
       </c>
       <c r="BV18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW18">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BX18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ18">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="CA18">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5285,22 +5285,22 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G19">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J19">
         <v>5.2</v>
       </c>
       <c r="K19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L19">
         <v>1.36</v>
@@ -5318,37 +5318,37 @@
         <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S19">
         <v>3.05</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W19">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z19">
         <v>540</v>
       </c>
       <c r="AA19">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="AB19">
         <v>8.199999999999999</v>
@@ -5357,19 +5357,19 @@
         <v>12.5</v>
       </c>
       <c r="AD19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE19">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF19">
         <v>8.199999999999999</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI19">
         <v>470</v>
@@ -5378,19 +5378,19 @@
         <v>11</v>
       </c>
       <c r="AK19">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM19">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN19">
         <v>6.4</v>
       </c>
       <c r="AO19">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AP19">
         <v>15.5</v>
@@ -5399,52 +5399,52 @@
         <v>26</v>
       </c>
       <c r="AR19">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU19">
         <v>10.5</v>
       </c>
       <c r="AV19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW19">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AX19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY19">
         <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="BA19">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB19">
         <v>9.6</v>
       </c>
       <c r="BC19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD19">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF19">
         <v>5.6</v>
       </c>
       <c r="BG19">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5530,10 +5530,10 @@
         <v>1.85</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I20">
         <v>5.6</v>
@@ -5545,40 +5545,40 @@
         <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M20">
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P20">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q20">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
         <v>4.7</v>
       </c>
       <c r="T20">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20">
         <v>10.5</v>
@@ -5587,7 +5587,7 @@
         <v>15.5</v>
       </c>
       <c r="Z20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA20">
         <v>160</v>
@@ -5602,7 +5602,7 @@
         <v>23</v>
       </c>
       <c r="AE20">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AF20">
         <v>10</v>
@@ -5632,7 +5632,7 @@
         <v>18</v>
       </c>
       <c r="AO20">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AP20">
         <v>9.199999999999999</v>
@@ -5641,7 +5641,7 @@
         <v>13</v>
       </c>
       <c r="AR20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS20">
         <v>100</v>
@@ -5668,7 +5668,7 @@
         <v>22</v>
       </c>
       <c r="BA20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB20">
         <v>18.5</v>
@@ -5686,13 +5686,13 @@
         <v>15.5</v>
       </c>
       <c r="BG20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BH20">
         <v>3</v>
       </c>
       <c r="BI20">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ20">
         <v>11.5</v>
@@ -5710,7 +5710,7 @@
         <v>4.5</v>
       </c>
       <c r="BO20">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BP20">
         <v>15</v>
@@ -5769,22 +5769,22 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G21">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H21">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I21">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
         <v>1.41</v>
@@ -5793,10 +5793,10 @@
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P21">
         <v>1.96</v>
@@ -5817,10 +5817,10 @@
         <v>2.22</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X21">
         <v>15</v>
@@ -5829,13 +5829,13 @@
         <v>12</v>
       </c>
       <c r="Z21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC21">
         <v>7.6</v>
@@ -5844,10 +5844,10 @@
         <v>13</v>
       </c>
       <c r="AE21">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF21">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG21">
         <v>12.5</v>
@@ -5856,28 +5856,28 @@
         <v>17.5</v>
       </c>
       <c r="AI21">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ21">
+        <v>42</v>
+      </c>
+      <c r="AK21">
+        <v>30</v>
+      </c>
+      <c r="AL21">
         <v>44</v>
       </c>
-      <c r="AK21">
-        <v>32</v>
-      </c>
-      <c r="AL21">
-        <v>50</v>
-      </c>
       <c r="AM21">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO21">
         <v>32</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21">
         <v>10</v>
@@ -5886,7 +5886,7 @@
         <v>18</v>
       </c>
       <c r="AS21">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5898,7 +5898,7 @@
         <v>11</v>
       </c>
       <c r="AW21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX21">
         <v>15.5</v>
@@ -5910,25 +5910,25 @@
         <v>14.5</v>
       </c>
       <c r="BA21">
+        <v>34</v>
+      </c>
+      <c r="BB21">
+        <v>29</v>
+      </c>
+      <c r="BC21">
+        <v>23</v>
+      </c>
+      <c r="BD21">
         <v>32</v>
       </c>
-      <c r="BB21">
-        <v>28</v>
-      </c>
-      <c r="BC21">
-        <v>22</v>
-      </c>
-      <c r="BD21">
-        <v>30</v>
-      </c>
       <c r="BE21">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF21">
         <v>20</v>
       </c>
       <c r="BG21">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BH21">
         <v>3.45</v>
@@ -5940,34 +5940,34 @@
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN21">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO21">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ21">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BR21">
         <v>40</v>
       </c>
       <c r="BS21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BT21">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BU21">
         <v>5.4</v>
@@ -5976,19 +5976,19 @@
         <v>27</v>
       </c>
       <c r="BW21">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BX21">
         <v>42</v>
       </c>
       <c r="BY21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BZ21">
         <v>32</v>
       </c>
       <c r="CA21">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6011,82 +6011,82 @@
         <v>171</v>
       </c>
       <c r="F22">
+        <v>2.82</v>
+      </c>
+      <c r="G22">
+        <v>2.86</v>
+      </c>
+      <c r="H22">
+        <v>2.64</v>
+      </c>
+      <c r="I22">
+        <v>2.7</v>
+      </c>
+      <c r="J22">
+        <v>3.6</v>
+      </c>
+      <c r="K22">
+        <v>3.7</v>
+      </c>
+      <c r="L22">
+        <v>1.34</v>
+      </c>
+      <c r="M22">
+        <v>1.05</v>
+      </c>
+      <c r="N22">
+        <v>4.9</v>
+      </c>
+      <c r="O22">
+        <v>1.24</v>
+      </c>
+      <c r="P22">
+        <v>2.32</v>
+      </c>
+      <c r="Q22">
+        <v>1.74</v>
+      </c>
+      <c r="R22">
+        <v>1.53</v>
+      </c>
+      <c r="S22">
         <v>2.84</v>
       </c>
-      <c r="G22">
-        <v>2.88</v>
-      </c>
-      <c r="H22">
-        <v>2.66</v>
-      </c>
-      <c r="I22">
-        <v>2.74</v>
-      </c>
-      <c r="J22">
-        <v>3.55</v>
-      </c>
-      <c r="K22">
-        <v>3.65</v>
-      </c>
-      <c r="L22">
-        <v>1.35</v>
-      </c>
-      <c r="M22">
-        <v>1.06</v>
-      </c>
-      <c r="N22">
-        <v>4.6</v>
-      </c>
-      <c r="O22">
-        <v>1.26</v>
-      </c>
-      <c r="P22">
-        <v>2.2</v>
-      </c>
-      <c r="Q22">
-        <v>1.79</v>
-      </c>
-      <c r="R22">
-        <v>1.48</v>
-      </c>
-      <c r="S22">
-        <v>2.98</v>
-      </c>
       <c r="T22">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W22">
         <v>1.53</v>
       </c>
       <c r="X22">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y22">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z22">
         <v>19.5</v>
       </c>
       <c r="AA22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB22">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD22">
         <v>12</v>
       </c>
       <c r="AE22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF22">
         <v>21</v>
@@ -6095,55 +6095,55 @@
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK22">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN22">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO22">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AP22">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS22">
         <v>34</v>
       </c>
       <c r="AT22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU22">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV22">
         <v>11</v>
       </c>
       <c r="AW22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY22">
         <v>11</v>
@@ -6161,52 +6161,52 @@
         <v>25</v>
       </c>
       <c r="BD22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE22">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF22">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG22">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH22">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI22">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BJ22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK22">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL22">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN22">
         <v>6</v>
       </c>
       <c r="BO22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP22">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR22">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT22">
         <v>5.9</v>
@@ -6215,19 +6215,19 @@
         <v>5.3</v>
       </c>
       <c r="BV22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX22">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY22">
         <v>10.5</v>
       </c>
       <c r="BZ22">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA22">
         <v>9.4</v>
@@ -6253,22 +6253,22 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G23">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H23">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I23">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J23">
         <v>3.75</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
         <v>1.38</v>
@@ -6286,55 +6286,55 @@
         <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
         <v>3.2</v>
       </c>
       <c r="T23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U23">
         <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X23">
         <v>21</v>
       </c>
       <c r="Y23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC23">
         <v>8.6</v>
       </c>
       <c r="AD23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF23">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
         <v>16.5</v>
@@ -6343,76 +6343,76 @@
         <v>46</v>
       </c>
       <c r="AJ23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK23">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL23">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM23">
         <v>95</v>
       </c>
       <c r="AN23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS23">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AT23">
         <v>11</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
+        <v>11</v>
+      </c>
+      <c r="AW23">
+        <v>11.5</v>
+      </c>
+      <c r="AX23">
+        <v>16</v>
+      </c>
+      <c r="AY23">
         <v>10.5</v>
       </c>
-      <c r="AW23">
-        <v>23</v>
-      </c>
-      <c r="AX23">
-        <v>17.5</v>
-      </c>
-      <c r="AY23">
-        <v>11</v>
-      </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB23">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="BC23">
         <v>11</v>
       </c>
       <c r="BD23">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BE23">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG23">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH23">
         <v>4.3</v>
@@ -6424,7 +6424,7 @@
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BL23">
         <v>120</v>
@@ -6433,37 +6433,37 @@
         <v>4.5</v>
       </c>
       <c r="BN23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO23">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP23">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR23">
         <v>38</v>
       </c>
       <c r="BS23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BW23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BX23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY23">
         <v>4.1</v>
@@ -6495,22 +6495,22 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G24">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I24">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J24">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24">
         <v>1.27</v>
@@ -6540,64 +6540,64 @@
         <v>1.46</v>
       </c>
       <c r="U24">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V24">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y24">
+        <v>21</v>
+      </c>
+      <c r="Z24">
+        <v>29</v>
+      </c>
+      <c r="AA24">
+        <v>40</v>
+      </c>
+      <c r="AB24">
         <v>24</v>
-      </c>
-      <c r="Z24">
-        <v>30</v>
-      </c>
-      <c r="AA24">
-        <v>44</v>
-      </c>
-      <c r="AB24">
-        <v>21</v>
       </c>
       <c r="AC24">
         <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF24">
         <v>32</v>
       </c>
       <c r="AG24">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH24">
         <v>13.5</v>
       </c>
       <c r="AI24">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ24">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK24">
+        <v>30</v>
+      </c>
+      <c r="AL24">
         <v>34</v>
       </c>
-      <c r="AL24">
-        <v>48</v>
-      </c>
       <c r="AM24">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AN24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO24">
         <v>11.5</v>
@@ -6606,10 +6606,10 @@
         <v>23</v>
       </c>
       <c r="AQ24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS24">
         <v>26</v>
@@ -6618,16 +6618,16 @@
         <v>18</v>
       </c>
       <c r="AU24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW24">
         <v>20</v>
       </c>
       <c r="AX24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY24">
         <v>12</v>
@@ -6636,16 +6636,16 @@
         <v>11.5</v>
       </c>
       <c r="BA24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC24">
         <v>21</v>
       </c>
       <c r="BD24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE24">
         <v>36</v>
@@ -6663,58 +6663,58 @@
         <v>3.95</v>
       </c>
       <c r="BJ24">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BK24">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL24">
         <v>70</v>
       </c>
       <c r="BM24">
-        <v>7.6</v>
+        <v>3.65</v>
       </c>
       <c r="BN24">
         <v>6.4</v>
       </c>
       <c r="BO24">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP24">
         <v>20</v>
       </c>
       <c r="BQ24">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT24">
         <v>6.4</v>
       </c>
       <c r="BU24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW24">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB24" t="s">
         <v>187</v>
@@ -6737,19 +6737,19 @@
         <v>174</v>
       </c>
       <c r="F25">
+        <v>2.44</v>
+      </c>
+      <c r="G25">
         <v>2.48</v>
       </c>
-      <c r="G25">
-        <v>2.56</v>
-      </c>
       <c r="H25">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I25">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
         <v>3.85</v>
@@ -6758,22 +6758,22 @@
         <v>1.38</v>
       </c>
       <c r="M25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
         <v>1.29</v>
       </c>
       <c r="P25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q25">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S25">
         <v>3.25</v>
@@ -6785,10 +6785,10 @@
         <v>2.26</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X25">
         <v>16.5</v>
@@ -6806,7 +6806,7 @@
         <v>12</v>
       </c>
       <c r="AC25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25">
         <v>13.5</v>
@@ -6815,7 +6815,7 @@
         <v>34</v>
       </c>
       <c r="AF25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG25">
         <v>12.5</v>
@@ -6836,73 +6836,73 @@
         <v>40</v>
       </c>
       <c r="AM25">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN25">
         <v>19</v>
       </c>
       <c r="AO25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP25">
+        <v>14</v>
+      </c>
+      <c r="AQ25">
+        <v>11</v>
+      </c>
+      <c r="AR25">
+        <v>17.5</v>
+      </c>
+      <c r="AS25">
+        <v>36</v>
+      </c>
+      <c r="AT25">
+        <v>10</v>
+      </c>
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
         <v>11.5</v>
       </c>
-      <c r="AQ25">
+      <c r="AW25">
+        <v>25</v>
+      </c>
+      <c r="AX25">
+        <v>14.5</v>
+      </c>
+      <c r="AY25">
         <v>10.5</v>
       </c>
-      <c r="AR25">
-        <v>16.5</v>
-      </c>
-      <c r="AS25">
-        <v>34</v>
-      </c>
-      <c r="AT25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU25">
-        <v>6.6</v>
-      </c>
-      <c r="AV25">
-        <v>10.5</v>
-      </c>
-      <c r="AW25">
-        <v>23</v>
-      </c>
-      <c r="AX25">
-        <v>13</v>
-      </c>
-      <c r="AY25">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ25">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB25">
         <v>25</v>
       </c>
       <c r="BC25">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE25">
         <v>60</v>
       </c>
       <c r="BF25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH25">
         <v>3.75</v>
       </c>
       <c r="BI25">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ25">
         <v>9.6</v>
@@ -6914,13 +6914,13 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN25">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP25">
         <v>18</v>
@@ -6932,25 +6932,25 @@
         <v>30</v>
       </c>
       <c r="BS25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT25">
         <v>6.6</v>
       </c>
       <c r="BU25">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX25">
         <v>34</v>
       </c>
       <c r="BY25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -6979,25 +6979,25 @@
         <v>175</v>
       </c>
       <c r="F26">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G26">
         <v>1.71</v>
       </c>
       <c r="H26">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I26">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M26">
         <v>1.06</v>
@@ -7018,28 +7018,28 @@
         <v>1.48</v>
       </c>
       <c r="S26">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T26">
         <v>1.8</v>
       </c>
       <c r="U26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
         <v>2.4</v>
       </c>
       <c r="X26">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y26">
         <v>23</v>
       </c>
       <c r="Z26">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AA26">
         <v>900</v>
@@ -7054,7 +7054,7 @@
         <v>23</v>
       </c>
       <c r="AE26">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AF26">
         <v>11</v>
@@ -7066,25 +7066,25 @@
         <v>21</v>
       </c>
       <c r="AI26">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AJ26">
         <v>17</v>
       </c>
       <c r="AK26">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM26">
         <v>580</v>
       </c>
       <c r="AN26">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO26">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP26">
         <v>16</v>
@@ -7105,13 +7105,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV26">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW26">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY26">
         <v>9</v>
@@ -7120,10 +7120,10 @@
         <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC26">
         <v>14.5</v>
@@ -7132,7 +7132,7 @@
         <v>24</v>
       </c>
       <c r="BE26">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF26">
         <v>7.6</v>
@@ -7162,7 +7162,7 @@
         <v>4.6</v>
       </c>
       <c r="BO26">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP26">
         <v>11.5</v>
@@ -7221,10 +7221,10 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G27">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H27">
         <v>3.3</v>
@@ -7233,13 +7233,13 @@
         <v>3.45</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L27">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7251,40 +7251,40 @@
         <v>1.43</v>
       </c>
       <c r="P27">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S27">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T27">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U27">
         <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X27">
         <v>11.5</v>
       </c>
       <c r="Y27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA27">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB27">
         <v>9.199999999999999</v>
@@ -7293,10 +7293,10 @@
         <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE27">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF27">
         <v>15.5</v>
@@ -7305,25 +7305,25 @@
         <v>12.5</v>
       </c>
       <c r="AH27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI27">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM27">
         <v>580</v>
       </c>
       <c r="AN27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO27">
         <v>60</v>
@@ -7332,13 +7332,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27">
         <v>19</v>
       </c>
       <c r="AS27">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT27">
         <v>7.8</v>
@@ -7350,22 +7350,22 @@
         <v>12.5</v>
       </c>
       <c r="AW27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX27">
         <v>13</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC27">
         <v>24</v>
@@ -7380,7 +7380,7 @@
         <v>21</v>
       </c>
       <c r="BG27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH27">
         <v>3.1</v>
@@ -7392,13 +7392,13 @@
         <v>12</v>
       </c>
       <c r="BK27">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN27">
         <v>5.9</v>
@@ -7410,37 +7410,37 @@
         <v>23</v>
       </c>
       <c r="BQ27">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS27">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BT27">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU27">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV27">
         <v>34</v>
       </c>
       <c r="BW27">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX27">
         <v>55</v>
       </c>
       <c r="BY27">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA27">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="CB27" t="s">
         <v>187</v>
@@ -7463,22 +7463,22 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G28">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H28">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I28">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="J28">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L28">
         <v>1.23</v>
@@ -7493,7 +7493,7 @@
         <v>1.13</v>
       </c>
       <c r="P28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
         <v>1.4</v>
@@ -7511,13 +7511,13 @@
         <v>3.15</v>
       </c>
       <c r="V28">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="W28">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X28">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y28">
         <v>21</v>
@@ -7529,7 +7529,7 @@
         <v>30</v>
       </c>
       <c r="AB28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC28">
         <v>12</v>
@@ -7541,7 +7541,7 @@
         <v>18.5</v>
       </c>
       <c r="AF28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG28">
         <v>15.5</v>
@@ -7565,10 +7565,10 @@
         <v>42</v>
       </c>
       <c r="AN28">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AO28">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP28">
         <v>29</v>
@@ -7577,7 +7577,7 @@
         <v>17.5</v>
       </c>
       <c r="AR28">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS28">
         <v>26</v>
@@ -7586,7 +7586,7 @@
         <v>22</v>
       </c>
       <c r="AU28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV28">
         <v>11</v>
@@ -7595,10 +7595,10 @@
         <v>16</v>
       </c>
       <c r="AX28">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="AY28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ28">
         <v>12.5</v>
@@ -7619,13 +7619,13 @@
         <v>34</v>
       </c>
       <c r="BF28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG28">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH28">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI28">
         <v>4.2</v>
@@ -7646,7 +7646,7 @@
         <v>7.8</v>
       </c>
       <c r="BO28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP28">
         <v>21</v>
@@ -7673,7 +7673,7 @@
         <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
@@ -7705,25 +7705,25 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="G29">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="H29">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="I29">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="J29">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K29">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M29">
         <v>1.09</v>
@@ -7735,7 +7735,7 @@
         <v>1.4</v>
       </c>
       <c r="P29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7744,130 +7744,130 @@
         <v>1.29</v>
       </c>
       <c r="S29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T29">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="X29">
         <v>11.5</v>
       </c>
       <c r="Y29">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z29">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA29">
+        <v>75</v>
+      </c>
+      <c r="AB29">
+        <v>9</v>
+      </c>
+      <c r="AC29">
+        <v>7.6</v>
+      </c>
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
         <v>48</v>
       </c>
-      <c r="AB29">
-        <v>10.5</v>
-      </c>
-      <c r="AC29">
-        <v>7.8</v>
-      </c>
-      <c r="AD29">
-        <v>13.5</v>
-      </c>
-      <c r="AE29">
-        <v>38</v>
-      </c>
       <c r="AF29">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG29">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH29">
         <v>19</v>
       </c>
       <c r="AI29">
+        <v>65</v>
+      </c>
+      <c r="AJ29">
+        <v>36</v>
+      </c>
+      <c r="AK29">
+        <v>27</v>
+      </c>
+      <c r="AL29">
+        <v>46</v>
+      </c>
+      <c r="AM29">
+        <v>130</v>
+      </c>
+      <c r="AN29">
+        <v>24</v>
+      </c>
+      <c r="AO29">
         <v>55</v>
       </c>
-      <c r="AJ29">
-        <v>48</v>
-      </c>
-      <c r="AK29">
-        <v>38</v>
-      </c>
-      <c r="AL29">
-        <v>55</v>
-      </c>
-      <c r="AM29">
-        <v>120</v>
-      </c>
-      <c r="AN29">
-        <v>38</v>
-      </c>
-      <c r="AO29">
-        <v>36</v>
-      </c>
       <c r="AP29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ29">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR29">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS29">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT29">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV29">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW29">
         <v>30</v>
       </c>
       <c r="AX29">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ29">
         <v>17</v>
       </c>
       <c r="BA29">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB29">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BC29">
+        <v>24</v>
+      </c>
+      <c r="BD29">
+        <v>40</v>
+      </c>
+      <c r="BE29">
+        <v>85</v>
+      </c>
+      <c r="BF29">
+        <v>20</v>
+      </c>
+      <c r="BG29">
         <v>30</v>
       </c>
-      <c r="BD29">
-        <v>42</v>
-      </c>
-      <c r="BE29">
-        <v>80</v>
-      </c>
-      <c r="BF29">
-        <v>27</v>
-      </c>
-      <c r="BG29">
-        <v>28</v>
-      </c>
       <c r="BH29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI29">
         <v>2.76</v>
@@ -7882,49 +7882,49 @@
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN29">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO29">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP29">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BQ29">
         <v>8.4</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS29">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT29">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BU29">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV29">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BW29">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY29">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA29">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7953,16 +7953,16 @@
         <v>3.45</v>
       </c>
       <c r="H30">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I30">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L30">
         <v>1.47</v>
@@ -7980,7 +7980,7 @@
         <v>1.79</v>
       </c>
       <c r="Q30">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
         <v>1.28</v>
@@ -7989,13 +7989,13 @@
         <v>4.2</v>
       </c>
       <c r="T30">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U30">
         <v>2</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
         <v>1.41</v>
@@ -8022,7 +8022,7 @@
         <v>12</v>
       </c>
       <c r="AE30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF30">
         <v>23</v>
@@ -8052,7 +8052,7 @@
         <v>55</v>
       </c>
       <c r="AO30">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP30">
         <v>10</v>
@@ -8064,10 +8064,10 @@
         <v>13.5</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU30">
         <v>6.6</v>
@@ -8076,10 +8076,10 @@
         <v>10</v>
       </c>
       <c r="AW30">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AX30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY30">
         <v>12.5</v>
@@ -8088,25 +8088,25 @@
         <v>16</v>
       </c>
       <c r="BA30">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB30">
+        <v>10.5</v>
+      </c>
+      <c r="BC30">
         <v>10</v>
       </c>
-      <c r="BC30">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BD30">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF30">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH30">
         <v>3.15</v>
@@ -8192,88 +8192,88 @@
         <v>3.3</v>
       </c>
       <c r="G31">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H31">
         <v>2.42</v>
       </c>
       <c r="I31">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="J31">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K31">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L31">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M31">
         <v>1.12</v>
       </c>
       <c r="N31">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O31">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="P31">
         <v>1.5</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
         <v>1.17</v>
       </c>
       <c r="S31">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T31">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U31">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W31">
         <v>1.35</v>
       </c>
       <c r="X31">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y31">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA31">
         <v>48</v>
       </c>
       <c r="AB31">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC31">
         <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE31">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF31">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG31">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH31">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI31">
         <v>75</v>
@@ -8297,58 +8297,58 @@
         <v>48</v>
       </c>
       <c r="AP31">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR31">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS31">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AT31">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="AU31">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV31">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AX31">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="AY31">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AZ31">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA31">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="BB31">
-        <v>5.3</v>
+        <v>46</v>
       </c>
       <c r="BC31">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="BD31">
-        <v>5.3</v>
+        <v>46</v>
       </c>
       <c r="BE31">
-        <v>5.5</v>
+        <v>100</v>
       </c>
       <c r="BF31">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="BG31">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH31">
         <v>2.98</v>
@@ -8366,7 +8366,7 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BN31">
         <v>7.4</v>
@@ -8378,13 +8378,13 @@
         <v>40</v>
       </c>
       <c r="BQ31">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BR31">
         <v>65</v>
       </c>
       <c r="BS31">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BT31">
         <v>5.9</v>
@@ -8402,7 +8402,7 @@
         <v>55</v>
       </c>
       <c r="BY31">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8431,13 +8431,13 @@
         <v>181</v>
       </c>
       <c r="F32">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G32">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H32">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I32">
         <v>5.6</v>
@@ -8455,13 +8455,13 @@
         <v>1.1</v>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P32">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q32">
         <v>2.36</v>
@@ -8473,7 +8473,7 @@
         <v>4.6</v>
       </c>
       <c r="T32">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U32">
         <v>1.8</v>
@@ -8482,16 +8482,16 @@
         <v>1.22</v>
       </c>
       <c r="W32">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X32">
         <v>13</v>
       </c>
       <c r="Y32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z32">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA32">
         <v>900</v>
@@ -8509,7 +8509,7 @@
         <v>120</v>
       </c>
       <c r="AF32">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8521,10 +8521,10 @@
         <v>130</v>
       </c>
       <c r="AJ32">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AK32">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL32">
         <v>60</v>
@@ -8533,10 +8533,10 @@
         <v>580</v>
       </c>
       <c r="AN32">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO32">
-        <v>170</v>
+        <v>600</v>
       </c>
       <c r="AP32">
         <v>9.199999999999999</v>
@@ -8545,10 +8545,10 @@
         <v>12.5</v>
       </c>
       <c r="AR32">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS32">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT32">
         <v>6</v>
@@ -8560,55 +8560,55 @@
         <v>18.5</v>
       </c>
       <c r="AW32">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX32">
         <v>8.800000000000001</v>
       </c>
       <c r="AY32">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32">
         <v>20</v>
       </c>
       <c r="BA32">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB32">
         <v>18</v>
       </c>
       <c r="BC32">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD32">
         <v>40</v>
       </c>
       <c r="BE32">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF32">
         <v>15</v>
       </c>
       <c r="BG32">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH32">
         <v>3.4</v>
       </c>
       <c r="BI32">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ32">
         <v>12</v>
       </c>
       <c r="BK32">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BN32">
         <v>4.4</v>
@@ -8620,34 +8620,34 @@
         <v>14.5</v>
       </c>
       <c r="BQ32">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR32">
         <v>36</v>
       </c>
       <c r="BS32">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT32">
         <v>9</v>
       </c>
       <c r="BU32">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV32">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX32">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BY32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ32">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA32">
         <v>6.4</v>
@@ -8685,13 +8685,13 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K33">
         <v>4.4</v>
       </c>
       <c r="L33">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M33">
         <v>1.06</v>
@@ -8706,28 +8706,28 @@
         <v>2.06</v>
       </c>
       <c r="Q33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R33">
         <v>1.4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T33">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W33">
         <v>2.56</v>
       </c>
       <c r="X33">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y33">
         <v>23</v>
@@ -8745,7 +8745,7 @@
         <v>9.4</v>
       </c>
       <c r="AD33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE33">
         <v>400</v>
@@ -8766,7 +8766,7 @@
         <v>16</v>
       </c>
       <c r="AK33">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL33">
         <v>38</v>
@@ -8775,7 +8775,7 @@
         <v>700</v>
       </c>
       <c r="AN33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO33">
         <v>140</v>
@@ -8784,10 +8784,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR33">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AS33">
         <v>12</v>
@@ -8796,13 +8796,13 @@
         <v>7.8</v>
       </c>
       <c r="AU33">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX33">
         <v>8.6</v>
@@ -8811,10 +8811,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB33">
         <v>13</v>
@@ -8823,19 +8823,19 @@
         <v>14.5</v>
       </c>
       <c r="BD33">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BE33">
         <v>11.5</v>
       </c>
       <c r="BF33">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI33">
         <v>3.3</v>
@@ -8844,55 +8844,55 @@
         <v>11</v>
       </c>
       <c r="BK33">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP33">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR33">
         <v>27</v>
       </c>
       <c r="BS33">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT33">
         <v>10.5</v>
       </c>
       <c r="BU33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ33">
         <v>19.5</v>
       </c>
       <c r="CA33">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB33" t="s">
         <v>187</v>
@@ -8915,25 +8915,25 @@
         <v>183</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H34">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I34">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J34">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K34">
         <v>3.45</v>
       </c>
       <c r="L34">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="M34">
         <v>1.12</v>
@@ -8942,31 +8942,31 @@
         <v>2.5</v>
       </c>
       <c r="O34">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P34">
         <v>1.51</v>
       </c>
       <c r="Q34">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="R34">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S34">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U34">
         <v>1.73</v>
       </c>
       <c r="V34">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W34">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X34">
         <v>10.5</v>
@@ -8975,16 +8975,16 @@
         <v>13.5</v>
       </c>
       <c r="Z34">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA34">
         <v>140</v>
       </c>
       <c r="AB34">
+        <v>7.2</v>
+      </c>
+      <c r="AC34">
         <v>7.8</v>
-      </c>
-      <c r="AC34">
-        <v>7.6</v>
       </c>
       <c r="AD34">
         <v>23</v>
@@ -9071,7 +9071,7 @@
         <v>1.03</v>
       </c>
       <c r="BF34">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG34">
         <v>1.01</v>
@@ -9107,7 +9107,7 @@
         <v>13.5</v>
       </c>
       <c r="BR34">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS34">
         <v>8.800000000000001</v>
@@ -9125,7 +9125,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX34">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY34">
         <v>8.800000000000001</v>
@@ -9160,13 +9160,13 @@
         <v>2.78</v>
       </c>
       <c r="G35">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H35">
         <v>2.46</v>
       </c>
       <c r="I35">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J35">
         <v>3.85</v>
@@ -9187,34 +9187,34 @@
         <v>1.25</v>
       </c>
       <c r="P35">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S35">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T35">
         <v>1.64</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X35">
         <v>24</v>
       </c>
       <c r="Y35">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z35">
         <v>23</v>
@@ -9235,7 +9235,7 @@
         <v>32</v>
       </c>
       <c r="AF35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG35">
         <v>15.5</v>
@@ -9262,7 +9262,7 @@
         <v>25</v>
       </c>
       <c r="AO35">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP35">
         <v>16.5</v>
@@ -9280,13 +9280,13 @@
         <v>12</v>
       </c>
       <c r="AU35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV35">
         <v>10.5</v>
       </c>
       <c r="AW35">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AX35">
         <v>18</v>
@@ -9295,31 +9295,31 @@
         <v>11</v>
       </c>
       <c r="AZ35">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB35">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC35">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="BD35">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH35">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI35">
         <v>3.05</v>
@@ -9337,7 +9337,7 @@
         <v>60</v>
       </c>
       <c r="BN35">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO35">
         <v>4.7</v>
@@ -9346,7 +9346,7 @@
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BR35">
         <v>1000</v>
@@ -9355,7 +9355,7 @@
         <v>21</v>
       </c>
       <c r="BT35">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU35">
         <v>4.4</v>
@@ -9364,7 +9364,7 @@
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX35">
         <v>1000</v>
@@ -9399,7 +9399,7 @@
         <v>185</v>
       </c>
       <c r="F36">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G36">
         <v>2.84</v>
@@ -9417,7 +9417,7 @@
         <v>3.2</v>
       </c>
       <c r="L36">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M36">
         <v>1.12</v>
@@ -9426,7 +9426,7 @@
         <v>2.8</v>
       </c>
       <c r="O36">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P36">
         <v>1.59</v>
@@ -9459,7 +9459,7 @@
         <v>9.4</v>
       </c>
       <c r="Z36">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA36">
         <v>75</v>
@@ -9507,16 +9507,16 @@
         <v>80</v>
       </c>
       <c r="AP36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ36">
         <v>8</v>
-      </c>
-      <c r="AQ36">
-        <v>8.199999999999999</v>
       </c>
       <c r="AR36">
         <v>17</v>
       </c>
       <c r="AS36">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AT36">
         <v>7.6</v>
@@ -9528,7 +9528,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AX36">
         <v>14.5</v>
@@ -9540,28 +9540,28 @@
         <v>19</v>
       </c>
       <c r="BA36">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BB36">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BC36">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BD36">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BE36">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="BF36">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BG36">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BH36">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI36">
         <v>2.36</v>
@@ -9570,25 +9570,25 @@
         <v>11</v>
       </c>
       <c r="BK36">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN36">
         <v>5.6</v>
       </c>
       <c r="BO36">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR36">
         <v>1000</v>
@@ -9603,7 +9603,7 @@
         <v>5.3</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW36">
         <v>10</v>
@@ -9612,13 +9612,13 @@
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB36" t="s">
         <v>187</v>
@@ -9641,31 +9641,31 @@
         <v>186</v>
       </c>
       <c r="F37">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G37">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H37">
         <v>6.6</v>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K37">
         <v>3.95</v>
       </c>
       <c r="L37">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M37">
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O37">
         <v>1.4</v>
@@ -9710,7 +9710,7 @@
         <v>7.2</v>
       </c>
       <c r="AC37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD37">
         <v>26</v>
@@ -9734,7 +9734,7 @@
         <v>16</v>
       </c>
       <c r="AK37">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL37">
         <v>55</v>
@@ -9746,7 +9746,7 @@
         <v>12.5</v>
       </c>
       <c r="AO37">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AP37">
         <v>10.5</v>
@@ -9755,25 +9755,25 @@
         <v>17</v>
       </c>
       <c r="AR37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT37">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU37">
         <v>8</v>
       </c>
       <c r="AV37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX37">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY37">
         <v>9.4</v>
@@ -9782,7 +9782,7 @@
         <v>22</v>
       </c>
       <c r="BA37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB37">
         <v>14</v>
@@ -9794,10 +9794,10 @@
         <v>40</v>
       </c>
       <c r="BE37">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG37">
         <v>14.5</v>
@@ -9809,16 +9809,16 @@
         <v>2.88</v>
       </c>
       <c r="BJ37">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK37">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN37">
         <v>4.1</v>
@@ -9827,40 +9827,40 @@
         <v>3.55</v>
       </c>
       <c r="BP37">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ37">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR37">
         <v>38</v>
       </c>
       <c r="BS37">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT37">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BU37">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV37">
         <v>85</v>
       </c>
       <c r="BW37">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX37">
         <v>95</v>
       </c>
       <c r="BY37">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ37">
         <v>32</v>
       </c>
       <c r="CA37">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB37" t="s">
         <v>187</v>
